--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>54768</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>108734</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>11672</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>6838</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -62796,10 +62796,10 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>39294</v>
+        <v>75573</v>
       </c>
       <c r="C2715" t="n">
         <v>3.0699999332428</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>21584</v>
+        <v>39294</v>
       </c>
       <c r="C2716" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="D2716" t="n">
         <v>3.05999994277954</v>
-      </c>
-      <c r="D2716" t="n">
-        <v>3.04999995231628</v>
       </c>
       <c r="E2716" t="n">
         <v>3.05999994277954</v>
       </c>
       <c r="F2716" t="n">
-        <v>3.04999995231628</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,10 +62842,10 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>193497</v>
+        <v>21584</v>
       </c>
       <c r="C2717" t="n">
         <v>3.05999994277954</v>
@@ -62857,7 +62857,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="F2717" t="n">
-        <v>3.05999994277954</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,10 +62865,10 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>46328</v>
+        <v>193497</v>
       </c>
       <c r="C2718" t="n">
         <v>3.05999994277954</v>
@@ -62880,7 +62880,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="F2718" t="n">
-        <v>3.04999995231628</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,10 +62888,10 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>54768</v>
+        <v>46328</v>
       </c>
       <c r="C2719" t="n">
         <v>3.05999994277954</v>
@@ -62900,7 +62900,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="E2719" t="n">
-        <v>3.04999995231628</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="F2719" t="n">
         <v>3.04999995231628</v>
@@ -62911,10 +62911,10 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>108734</v>
+        <v>54768</v>
       </c>
       <c r="C2720" t="n">
         <v>3.05999994277954</v>
@@ -62923,10 +62923,10 @@
         <v>3.04999995231628</v>
       </c>
       <c r="E2720" t="n">
-        <v>3.05999994277954</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="F2720" t="n">
-        <v>3.05999994277954</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>11672</v>
+        <v>108734</v>
       </c>
       <c r="C2721" t="n">
-        <v>3.0699999332428</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="D2721" t="n">
-        <v>3.05999994277954</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="E2721" t="n">
         <v>3.05999994277954</v>
       </c>
       <c r="F2721" t="n">
-        <v>3.0699999332428</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,10 +62957,10 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>6838</v>
+        <v>11672</v>
       </c>
       <c r="C2722" t="n">
         <v>3.0699999332428</v>
@@ -62972,9 +62972,32 @@
         <v>3.05999994277954</v>
       </c>
       <c r="F2722" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>67004</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="D2723" t="n">
         <v>3.05999994277954</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="E2723" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -525,7 +525,7 @@
         <v>5.07366609573364</v>
       </c>
       <c r="G6" t="n">
-        <v>4.19709157943726</v>
+        <v>4.1970911026001</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.84223508834839</v>
       </c>
       <c r="G7" t="n">
-        <v>4.00564479827881</v>
+        <v>4.00564527511597</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.80663108825684</v>
       </c>
       <c r="G8" t="n">
-        <v>3.97619152069092</v>
+        <v>3.97619223594666</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.81019115447998</v>
       </c>
       <c r="G9" t="n">
-        <v>3.97913646697998</v>
+        <v>3.97913718223572</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G12" t="n">
-        <v>3.53439211845398</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.77409505844116</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12204647064209</v>
+        <v>3.12204670906067</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G16" t="n">
-        <v>3.38712596893311</v>
+        <v>3.38712573051453</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G17" t="n">
-        <v>3.38712596893311</v>
+        <v>3.38712573051453</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.77102613449097</v>
       </c>
       <c r="G22" t="n">
-        <v>3.94673824310303</v>
+        <v>3.94673871994019</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.52891397476196</v>
       </c>
       <c r="G27" t="n">
-        <v>3.74645566940308</v>
+        <v>3.7464554309845</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G30" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G31" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G32" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G33" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G34" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G35" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G36" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G37" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.99840402603149</v>
       </c>
       <c r="G38" t="n">
-        <v>3.30760192871094</v>
+        <v>3.30760169029236</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.03044891357422</v>
       </c>
       <c r="G39" t="n">
-        <v>3.33411026000977</v>
+        <v>3.33411002159119</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.03222894668579</v>
       </c>
       <c r="G40" t="n">
-        <v>3.33558297157288</v>
+        <v>3.33558249473572</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.08563613891602</v>
       </c>
       <c r="G41" t="n">
-        <v>3.37976264953613</v>
+        <v>3.37976288795471</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.30816507339478</v>
       </c>
       <c r="G42" t="n">
-        <v>3.56384563446045</v>
+        <v>3.56384539604187</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G43" t="n">
-        <v>3.53439211845398</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.03400897979736</v>
       </c>
       <c r="G44" t="n">
-        <v>3.33705520629883</v>
+        <v>3.33705544471741</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G47" t="n">
-        <v>3.49315738677979</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G48" t="n">
-        <v>3.49315738677979</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G49" t="n">
-        <v>3.49315738677979</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G50" t="n">
-        <v>3.49315738677979</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.26722002029419</v>
       </c>
       <c r="G51" t="n">
-        <v>3.52997446060181</v>
+        <v>3.52997469902039</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.59300184249878</v>
       </c>
       <c r="G52" t="n">
-        <v>3.79947113990784</v>
+        <v>3.799471616745</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G53" t="n">
-        <v>3.82892489433289</v>
+        <v>3.82892441749573</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G54" t="n">
-        <v>3.82892489433289</v>
+        <v>3.82892441749573</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G55" t="n">
-        <v>3.82892489433289</v>
+        <v>3.82892441749573</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G56" t="n">
-        <v>3.82892489433289</v>
+        <v>3.82892441749573</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.21915292739868</v>
       </c>
       <c r="G59" t="n">
-        <v>3.49021196365356</v>
+        <v>3.49021220207214</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.21915292739868</v>
       </c>
       <c r="G60" t="n">
-        <v>3.49021196365356</v>
+        <v>3.49021220207214</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.01620721817017</v>
       </c>
       <c r="G61" t="n">
-        <v>3.32232904434204</v>
+        <v>3.32232928276062</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.08563613891602</v>
       </c>
       <c r="G62" t="n">
-        <v>3.37976264953613</v>
+        <v>3.37976288795471</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G63" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G64" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G65" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G66" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G67" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G68" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.82750201225281</v>
       </c>
       <c r="G69" t="n">
-        <v>3.16622638702393</v>
+        <v>3.16622614860535</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.18176794052124</v>
       </c>
       <c r="G75" t="n">
-        <v>3.45928573608398</v>
+        <v>3.45928597450256</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G76" t="n">
-        <v>3.53439211845398</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G77" t="n">
-        <v>3.53439211845398</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.94321703910828</v>
       </c>
       <c r="G78" t="n">
-        <v>3.26194953918457</v>
+        <v>3.26194930076599</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.9343159198761</v>
       </c>
       <c r="G80" t="n">
-        <v>3.2545862197876</v>
+        <v>3.25458598136902</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.9343159198761</v>
       </c>
       <c r="G81" t="n">
-        <v>3.2545862197876</v>
+        <v>3.25458598136902</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.29036283493042</v>
       </c>
       <c r="G82" t="n">
-        <v>3.5491189956665</v>
+        <v>3.54911875724792</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.16574621200562</v>
       </c>
       <c r="G83" t="n">
-        <v>3.44603228569031</v>
+        <v>3.44603204727173</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G84" t="n">
-        <v>3.53439211845398</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G85" t="n">
-        <v>3.53439211845398</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G86" t="n">
-        <v>3.53439211845398</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.2102518081665</v>
       </c>
       <c r="G90" t="n">
-        <v>3.48284840583801</v>
+        <v>3.48284864425659</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.96101999282837</v>
       </c>
       <c r="G91" t="n">
-        <v>3.27667641639709</v>
+        <v>3.27667665481567</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.89871096611023</v>
       </c>
       <c r="G92" t="n">
-        <v>3.22513270378113</v>
+        <v>3.22513246536255</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G93" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G94" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G97" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.38422393798828</v>
       </c>
       <c r="G98" t="n">
-        <v>2.79953336715698</v>
+        <v>2.7995331287384</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G101" t="n">
-        <v>2.85696721076965</v>
+        <v>2.85696744918823</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.90583205223083</v>
       </c>
       <c r="G102" t="n">
-        <v>3.23102355003357</v>
+        <v>3.23102331161499</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G103" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G104" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G105" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G106" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G107" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G108" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G109" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G110" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G111" t="n">
-        <v>2.90409207344055</v>
+        <v>2.90409231185913</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G114" t="n">
-        <v>2.90114712715149</v>
+        <v>2.90114688873291</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.29521203041077</v>
       </c>
       <c r="G122" t="n">
-        <v>2.72589993476868</v>
+        <v>2.72590017318726</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.3005530834198</v>
       </c>
       <c r="G123" t="n">
-        <v>2.73031806945801</v>
+        <v>2.73031830787659</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G124" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G125" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G126" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.95518708229065</v>
       </c>
       <c r="G127" t="n">
-        <v>2.44462084770203</v>
+        <v>2.44462060928345</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G128" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G129" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G130" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G133" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.40331506729126</v>
       </c>
       <c r="G134" t="n">
-        <v>1.9880952835083</v>
+        <v>1.98809564113617</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G135" t="n">
-        <v>1.76719605922699</v>
+        <v>1.76719617843628</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G136" t="n">
-        <v>1.76719605922699</v>
+        <v>1.76719617843628</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.17010402679443</v>
       </c>
       <c r="G142" t="n">
-        <v>1.79517638683319</v>
+        <v>1.79517614841461</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.23241305351257</v>
       </c>
       <c r="G143" t="n">
-        <v>1.84672021865845</v>
+        <v>1.84672009944916</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.26267695426941</v>
       </c>
       <c r="G144" t="n">
-        <v>1.87175536155701</v>
+        <v>1.87175559997559</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.15408205986023</v>
       </c>
       <c r="G145" t="n">
-        <v>1.78192234039307</v>
+        <v>1.78192245960236</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.21817088127136</v>
       </c>
       <c r="G148" t="n">
-        <v>1.83493852615356</v>
+        <v>1.83493876457214</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.09711503982544</v>
       </c>
       <c r="G156" t="n">
-        <v>1.73479747772217</v>
+        <v>1.73479735851288</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.02590489387512</v>
       </c>
       <c r="G157" t="n">
-        <v>1.67589044570923</v>
+        <v>1.67589032649994</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.04370808601379</v>
       </c>
       <c r="G158" t="n">
-        <v>1.69061768054962</v>
+        <v>1.69061756134033</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G159" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.02946591377258</v>
       </c>
       <c r="G161" t="n">
-        <v>1.67883622646332</v>
+        <v>1.67883610725403</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G163" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.94935500621796</v>
       </c>
       <c r="G164" t="n">
-        <v>1.6125659942627</v>
+        <v>1.61256587505341</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G165" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G166" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.92265200614929</v>
       </c>
       <c r="G167" t="n">
-        <v>1.59047639369965</v>
+        <v>1.59047627449036</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.92265200614929</v>
       </c>
       <c r="G168" t="n">
-        <v>1.59047639369965</v>
+        <v>1.59047627449036</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.92265200614929</v>
       </c>
       <c r="G169" t="n">
-        <v>1.59047639369965</v>
+        <v>1.59047627449036</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.83542001247406</v>
       </c>
       <c r="G172" t="n">
-        <v>1.51831531524658</v>
+        <v>1.51831543445587</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.83542001247406</v>
       </c>
       <c r="G173" t="n">
-        <v>1.51831531524658</v>
+        <v>1.51831543445587</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.83542001247406</v>
       </c>
       <c r="G174" t="n">
-        <v>1.51831531524658</v>
+        <v>1.51831543445587</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.11313700675964</v>
       </c>
       <c r="G178" t="n">
-        <v>1.748051404953</v>
+        <v>1.74805128574371</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.08287310600281</v>
       </c>
       <c r="G180" t="n">
-        <v>1.72301614284515</v>
+        <v>1.72301602363586</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.09177398681641</v>
       </c>
       <c r="G181" t="n">
-        <v>1.73037910461426</v>
+        <v>1.73037922382355</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.97605895996094</v>
       </c>
       <c r="G182" t="n">
-        <v>1.63465631008148</v>
+        <v>1.63465619087219</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.11847805976868</v>
       </c>
       <c r="G183" t="n">
-        <v>1.75246977806091</v>
+        <v>1.7524698972702</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.05082893371582</v>
       </c>
       <c r="G184" t="n">
-        <v>1.69650828838348</v>
+        <v>1.69650840759277</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.93155300617218</v>
       </c>
       <c r="G185" t="n">
-        <v>1.59783947467804</v>
+        <v>1.59783959388733</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.93155300617218</v>
       </c>
       <c r="G188" t="n">
-        <v>1.59783947467804</v>
+        <v>1.59783959388733</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.29650092124939</v>
       </c>
       <c r="G192" t="n">
-        <v>1.89973556995392</v>
+        <v>1.8997358083725</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.24309396743774</v>
       </c>
       <c r="G193" t="n">
-        <v>1.85555577278137</v>
+        <v>1.85555589199066</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G194" t="n">
-        <v>1.76719605922699</v>
+        <v>1.76719617843628</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.30362200737</v>
       </c>
       <c r="G195" t="n">
-        <v>1.90562629699707</v>
+        <v>1.90562641620636</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.40331506729126</v>
       </c>
       <c r="G196" t="n">
-        <v>1.9880952835083</v>
+        <v>1.98809564113617</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.31608390808105</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91593527793884</v>
+        <v>1.91593551635742</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.41577696800232</v>
       </c>
       <c r="G198" t="n">
-        <v>1.99840450286865</v>
+        <v>1.99840438365936</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.44248008728027</v>
       </c>
       <c r="G200" t="n">
-        <v>2.02049398422241</v>
+        <v>2.02049422264099</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.35880899429321</v>
       </c>
       <c r="G201" t="n">
-        <v>1.95127868652344</v>
+        <v>1.95127856731415</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G205" t="n">
-        <v>1.76719605922699</v>
+        <v>1.76719617843628</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.14340090751648</v>
       </c>
       <c r="G207" t="n">
-        <v>1.77308666706085</v>
+        <v>1.77308654785156</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.10245609283447</v>
       </c>
       <c r="G209" t="n">
-        <v>1.73921597003937</v>
+        <v>1.7392156124115</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.12025809288025</v>
       </c>
       <c r="G210" t="n">
-        <v>1.75394213199615</v>
+        <v>1.75394225120544</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.09177398681641</v>
       </c>
       <c r="G211" t="n">
-        <v>1.73037910461426</v>
+        <v>1.73037922382355</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.059730052948</v>
       </c>
       <c r="G212" t="n">
-        <v>1.70387148857117</v>
+        <v>1.70387172698975</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.059730052948</v>
       </c>
       <c r="G213" t="n">
-        <v>1.70387148857117</v>
+        <v>1.70387172698975</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.11313700675964</v>
       </c>
       <c r="G214" t="n">
-        <v>1.748051404953</v>
+        <v>1.74805128574371</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.11669707298279</v>
       </c>
       <c r="G215" t="n">
-        <v>1.75099623203278</v>
+        <v>1.75099647045135</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.99920201301575</v>
       </c>
       <c r="G217" t="n">
-        <v>1.65380096435547</v>
+        <v>1.65380084514618</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.02946591377258</v>
       </c>
       <c r="G220" t="n">
-        <v>1.67883622646332</v>
+        <v>1.67883610725403</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.09711503982544</v>
       </c>
       <c r="G221" t="n">
-        <v>1.73479747772217</v>
+        <v>1.73479735851288</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.15408205986023</v>
       </c>
       <c r="G223" t="n">
-        <v>1.78192234039307</v>
+        <v>1.78192245960236</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.15052199363708</v>
       </c>
       <c r="G224" t="n">
-        <v>1.77897727489471</v>
+        <v>1.778977394104</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.13806009292603</v>
       </c>
       <c r="G228" t="n">
-        <v>1.76866841316223</v>
+        <v>1.76866865158081</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G229" t="n">
-        <v>1.7642502784729</v>
+        <v>1.76425015926361</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G230" t="n">
-        <v>1.7642502784729</v>
+        <v>1.76425015926361</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.059730052948</v>
       </c>
       <c r="G231" t="n">
-        <v>1.70387148857117</v>
+        <v>1.70387172698975</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G238" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G239" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.07041096687317</v>
       </c>
       <c r="G240" t="n">
-        <v>1.7127069234848</v>
+        <v>1.71270716190338</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.07041096687317</v>
       </c>
       <c r="G241" t="n">
-        <v>1.7127069234848</v>
+        <v>1.71270716190338</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.11847805976868</v>
       </c>
       <c r="G242" t="n">
-        <v>1.75246977806091</v>
+        <v>1.7524698972702</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G243" t="n">
-        <v>1.7642502784729</v>
+        <v>1.76425015926361</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.15408205986023</v>
       </c>
       <c r="G244" t="n">
-        <v>1.78192234039307</v>
+        <v>1.78192245960236</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G245" t="n">
-        <v>1.7642502784729</v>
+        <v>1.76425015926361</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.0846529006958</v>
       </c>
       <c r="G248" t="n">
-        <v>1.72448861598969</v>
+        <v>1.7244884967804</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G250" t="n">
-        <v>1.76719605922699</v>
+        <v>1.76719617843628</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.03124594688416</v>
       </c>
       <c r="G251" t="n">
-        <v>1.68030858039856</v>
+        <v>1.68030869960785</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.04904794692993</v>
       </c>
       <c r="G252" t="n">
-        <v>1.69503498077393</v>
+        <v>1.69503486156464</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.45672202110291</v>
       </c>
       <c r="G254" t="n">
-        <v>2.03227543830872</v>
+        <v>2.03227519989014</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.36415004730225</v>
       </c>
       <c r="G255" t="n">
-        <v>1.95569694042206</v>
+        <v>1.95569717884064</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.41221594810486</v>
       </c>
       <c r="G256" t="n">
-        <v>1.99545872211456</v>
+        <v>1.99545860290527</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.34456706047058</v>
       </c>
       <c r="G257" t="n">
-        <v>1.93949711322784</v>
+        <v>1.93949770927429</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.74155902862549</v>
       </c>
       <c r="G258" t="n">
-        <v>2.26790142059326</v>
+        <v>2.26790118217468</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.93738508224487</v>
       </c>
       <c r="G259" t="n">
-        <v>2.42989468574524</v>
+        <v>2.42989444732666</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.79318594932556</v>
       </c>
       <c r="G260" t="n">
-        <v>2.31060838699341</v>
+        <v>2.31060886383057</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.85905504226685</v>
       </c>
       <c r="G261" t="n">
-        <v>2.3650975227356</v>
+        <v>2.36509728431702</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.23824501037598</v>
       </c>
       <c r="G262" t="n">
-        <v>2.6787748336792</v>
+        <v>2.67877531051636</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G263" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>4.67133283615112</v>
       </c>
       <c r="G265" t="n">
-        <v>3.86426877975464</v>
+        <v>3.86426901817322</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>4.40073680877686</v>
       </c>
       <c r="G267" t="n">
-        <v>3.64042353630066</v>
+        <v>3.64042377471924</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.16574621200562</v>
       </c>
       <c r="G270" t="n">
-        <v>3.44603228569031</v>
+        <v>3.44603204727173</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.05893182754517</v>
       </c>
       <c r="G271" t="n">
-        <v>3.35767245292664</v>
+        <v>3.35767221450806</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.59300184249878</v>
       </c>
       <c r="G272" t="n">
-        <v>3.79947113990784</v>
+        <v>3.799471616745</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.3953971862793</v>
       </c>
       <c r="G273" t="n">
-        <v>3.63600635528564</v>
+        <v>3.63600659370422</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.42210006713867</v>
       </c>
       <c r="G274" t="n">
-        <v>3.65809631347656</v>
+        <v>3.65809607505798</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.3241868019104</v>
       </c>
       <c r="G275" t="n">
-        <v>3.57709932327271</v>
+        <v>3.57709884643555</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.43278121948242</v>
       </c>
       <c r="G276" t="n">
-        <v>3.66693210601807</v>
+        <v>3.66693186759949</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.35979223251343</v>
       </c>
       <c r="G280" t="n">
-        <v>3.60655331611633</v>
+        <v>3.60655307769775</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G281" t="n">
-        <v>3.49315738677979</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.3241868019104</v>
       </c>
       <c r="G282" t="n">
-        <v>3.57709932327271</v>
+        <v>3.57709884643555</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.32774782180786</v>
       </c>
       <c r="G284" t="n">
-        <v>3.58004522323608</v>
+        <v>3.58004474639893</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.07495403289795</v>
       </c>
       <c r="G286" t="n">
-        <v>3.37092614173889</v>
+        <v>3.37092638015747</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.94677805900574</v>
       </c>
       <c r="G287" t="n">
-        <v>3.26489543914795</v>
+        <v>3.26489520072937</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.92007398605347</v>
       </c>
       <c r="G288" t="n">
-        <v>3.24280476570129</v>
+        <v>3.24280500411987</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.92007398605347</v>
       </c>
       <c r="G289" t="n">
-        <v>3.24280476570129</v>
+        <v>3.24280500411987</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G290" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G293" t="n">
-        <v>3.38712596893311</v>
+        <v>3.38712573051453</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.85954594612122</v>
       </c>
       <c r="G294" t="n">
-        <v>3.19273400306702</v>
+        <v>3.1927342414856</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G295" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G296" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G297" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.54266500473022</v>
       </c>
       <c r="G298" t="n">
-        <v>2.93060064315796</v>
+        <v>2.93060088157654</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G300" t="n">
-        <v>3.38712596893311</v>
+        <v>3.38712573051453</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G302" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G303" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G307" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G309" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.9093930721283</v>
       </c>
       <c r="G310" t="n">
-        <v>3.23396897315979</v>
+        <v>3.23396944999695</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.69576501846313</v>
       </c>
       <c r="G314" t="n">
-        <v>3.05724930763245</v>
+        <v>3.0572497844696</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.65481901168823</v>
       </c>
       <c r="G315" t="n">
-        <v>3.02337765693665</v>
+        <v>3.02337789535522</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.65303897857666</v>
       </c>
       <c r="G318" t="n">
-        <v>3.02190494537354</v>
+        <v>3.02190518379211</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G319" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.53910398483276</v>
       </c>
       <c r="G320" t="n">
-        <v>2.92765474319458</v>
+        <v>2.92765498161316</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.48213696479797</v>
       </c>
       <c r="G324" t="n">
-        <v>2.88053011894226</v>
+        <v>2.88052988052368</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G326" t="n">
-        <v>3.82892489433289</v>
+        <v>3.82892441749573</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G327" t="n">
-        <v>3.53439211845398</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.41319894790649</v>
       </c>
       <c r="G328" t="n">
-        <v>3.65073323249817</v>
+        <v>3.65073275566101</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.21381282806396</v>
       </c>
       <c r="G329" t="n">
-        <v>3.48579478263855</v>
+        <v>3.48579430580139</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.77409505844116</v>
       </c>
       <c r="G332" t="n">
-        <v>3.12204647064209</v>
+        <v>3.12204670906067</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.00730609893799</v>
       </c>
       <c r="G333" t="n">
-        <v>3.31496548652649</v>
+        <v>3.31496596336365</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.99662399291992</v>
       </c>
       <c r="G336" t="n">
-        <v>3.30612945556641</v>
+        <v>3.30612921714783</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.0055251121521</v>
       </c>
       <c r="G337" t="n">
-        <v>3.3134925365448</v>
+        <v>3.31349277496338</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>3.85598611831665</v>
       </c>
       <c r="G340" t="n">
-        <v>3.18978905677795</v>
+        <v>3.18978929519653</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.8915901184082</v>
       </c>
       <c r="G341" t="n">
-        <v>3.21924209594727</v>
+        <v>3.21924233436584</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.92185401916504</v>
       </c>
       <c r="G343" t="n">
-        <v>3.24427700042725</v>
+        <v>3.24427723884583</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.84530401229858</v>
       </c>
       <c r="G345" t="n">
-        <v>3.18095278739929</v>
+        <v>3.18095254898071</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.85954594612122</v>
       </c>
       <c r="G346" t="n">
-        <v>3.19273400306702</v>
+        <v>3.1927342414856</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.79189705848694</v>
       </c>
       <c r="G347" t="n">
-        <v>3.13677310943604</v>
+        <v>3.13677287101746</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.82750201225281</v>
       </c>
       <c r="G356" t="n">
-        <v>3.16622638702393</v>
+        <v>3.16622614860535</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.89693093299866</v>
       </c>
       <c r="G358" t="n">
-        <v>3.2236602306366</v>
+        <v>3.22365999221802</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.95211791992188</v>
       </c>
       <c r="G359" t="n">
-        <v>3.26931262016296</v>
+        <v>3.26931238174438</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.79189705848694</v>
       </c>
       <c r="G360" t="n">
-        <v>3.13677310943604</v>
+        <v>3.13677287101746</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.79189705848694</v>
       </c>
       <c r="G361" t="n">
-        <v>3.13677310943604</v>
+        <v>3.13677287101746</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.82750201225281</v>
       </c>
       <c r="G364" t="n">
-        <v>3.16622638702393</v>
+        <v>3.16622614860535</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.78299593925476</v>
       </c>
       <c r="G365" t="n">
-        <v>3.12940979003906</v>
+        <v>3.1294093132019</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.69220399856567</v>
       </c>
       <c r="G367" t="n">
-        <v>3.0543041229248</v>
+        <v>3.05430364608765</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.58004903793335</v>
       </c>
       <c r="G368" t="n">
-        <v>2.96152591705322</v>
+        <v>2.96152567863464</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.54800510406494</v>
       </c>
       <c r="G370" t="n">
-        <v>2.93501782417297</v>
+        <v>2.93501806259155</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.53910398483276</v>
       </c>
       <c r="G371" t="n">
-        <v>2.92765474319458</v>
+        <v>2.92765498161316</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G377" t="n">
-        <v>2.94827222824097</v>
+        <v>2.94827175140381</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.53554391860962</v>
       </c>
       <c r="G380" t="n">
-        <v>2.92470979690552</v>
+        <v>2.92470955848694</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.53554391860962</v>
       </c>
       <c r="G381" t="n">
-        <v>2.92470979690552</v>
+        <v>2.92470955848694</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.62989592552185</v>
       </c>
       <c r="G382" t="n">
-        <v>3.00276064872742</v>
+        <v>3.00276041030884</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.61565399169922</v>
       </c>
       <c r="G383" t="n">
-        <v>2.99097919464111</v>
+        <v>2.99097943305969</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G384" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.49459791183472</v>
       </c>
       <c r="G386" t="n">
-        <v>2.89083814620972</v>
+        <v>2.89083790779114</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.48925805091858</v>
       </c>
       <c r="G391" t="n">
-        <v>2.88642048835754</v>
+        <v>2.88642072677612</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.52486205101013</v>
       </c>
       <c r="G392" t="n">
-        <v>2.91587352752686</v>
+        <v>2.91587328910828</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.50349903106689</v>
       </c>
       <c r="G394" t="n">
-        <v>2.89820098876953</v>
+        <v>2.89820122718811</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G395" t="n">
-        <v>2.84224057197571</v>
+        <v>2.84224104881287</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G396" t="n">
-        <v>2.84224057197571</v>
+        <v>2.84224104881287</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G397" t="n">
-        <v>2.85696721076965</v>
+        <v>2.85696744918823</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G398" t="n">
-        <v>2.85696721076965</v>
+        <v>2.85696744918823</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G399" t="n">
-        <v>2.85696721076965</v>
+        <v>2.85696744918823</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G400" t="n">
-        <v>2.85696721076965</v>
+        <v>2.85696744918823</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G401" t="n">
-        <v>2.85696721076965</v>
+        <v>2.85696744918823</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G402" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G408" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.59785199165344</v>
       </c>
       <c r="G410" t="n">
-        <v>2.97625279426575</v>
+        <v>2.97625303268433</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.59963202476501</v>
       </c>
       <c r="G411" t="n">
-        <v>2.97772550582886</v>
+        <v>2.97772574424744</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.59963202476501</v>
       </c>
       <c r="G412" t="n">
-        <v>2.97772550582886</v>
+        <v>2.97772574424744</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G414" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G415" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G417" t="n">
-        <v>2.94827222824097</v>
+        <v>2.94827175140381</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G418" t="n">
-        <v>2.94827222824097</v>
+        <v>2.94827175140381</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.62989592552185</v>
       </c>
       <c r="G419" t="n">
-        <v>3.00276064872742</v>
+        <v>3.00276041030884</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G421" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.61209392547607</v>
       </c>
       <c r="G422" t="n">
-        <v>2.98803424835205</v>
+        <v>2.98803400993347</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.57292890548706</v>
       </c>
       <c r="G424" t="n">
-        <v>2.95563578605652</v>
+        <v>2.95563554763794</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G428" t="n">
-        <v>2.90114712715149</v>
+        <v>2.90114688873291</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G429" t="n">
-        <v>2.90114712715149</v>
+        <v>2.90114688873291</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G431" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.47323489189148</v>
       </c>
       <c r="G432" t="n">
-        <v>2.87316608428955</v>
+        <v>2.87316584587097</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.49281811714172</v>
       </c>
       <c r="G433" t="n">
-        <v>2.88936543464661</v>
+        <v>2.88936567306519</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G434" t="n">
-        <v>2.84224057197571</v>
+        <v>2.84224104881287</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.4394109249115</v>
       </c>
       <c r="G435" t="n">
-        <v>2.84518575668335</v>
+        <v>2.84518527984619</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.52486205101013</v>
       </c>
       <c r="G438" t="n">
-        <v>2.91587352752686</v>
+        <v>2.91587328910828</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.41092705726624</v>
       </c>
       <c r="G441" t="n">
-        <v>2.82162308692932</v>
+        <v>2.82162284851074</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G446" t="n">
-        <v>2.79658770561218</v>
+        <v>2.7965874671936</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G447" t="n">
-        <v>2.79658770561218</v>
+        <v>2.7965874671936</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.33971810340881</v>
       </c>
       <c r="G448" t="n">
-        <v>2.76271653175354</v>
+        <v>2.7627170085907</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3.33615708351135</v>
       </c>
       <c r="G449" t="n">
-        <v>2.75977063179016</v>
+        <v>2.75977110862732</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.24714589118958</v>
       </c>
       <c r="G450" t="n">
-        <v>2.68613839149475</v>
+        <v>2.68613791465759</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.25426697731018</v>
       </c>
       <c r="G451" t="n">
-        <v>2.69202876091003</v>
+        <v>2.69202899932861</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G454" t="n">
-        <v>2.79658770561218</v>
+        <v>2.7965874671936</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.32903695106506</v>
       </c>
       <c r="G455" t="n">
-        <v>2.75388073921204</v>
+        <v>2.75388121604919</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.27919006347656</v>
       </c>
       <c r="G456" t="n">
-        <v>2.71264600753784</v>
+        <v>2.71264624595642</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G459" t="n">
-        <v>2.73915362358093</v>
+        <v>2.73915410041809</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G460" t="n">
-        <v>2.73915362358093</v>
+        <v>2.73915410041809</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73915362358093</v>
+        <v>2.73915410041809</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.24714589118958</v>
       </c>
       <c r="G462" t="n">
-        <v>2.68613839149475</v>
+        <v>2.68613791465759</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.08158397674561</v>
       </c>
       <c r="G464" t="n">
-        <v>2.54918003082275</v>
+        <v>2.54918026924133</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G465" t="n">
-        <v>2.73915362358093</v>
+        <v>2.73915410041809</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.21332097053528</v>
       </c>
       <c r="G467" t="n">
-        <v>2.65815711021423</v>
+        <v>2.65815734863281</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.18483805656433</v>
       </c>
       <c r="G470" t="n">
-        <v>2.63459515571594</v>
+        <v>2.63459539413452</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.22222304344177</v>
       </c>
       <c r="G471" t="n">
-        <v>2.66552114486694</v>
+        <v>2.66552138328552</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.19373893737793</v>
       </c>
       <c r="G472" t="n">
-        <v>2.64195823669434</v>
+        <v>2.64195871353149</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.29343199729919</v>
       </c>
       <c r="G473" t="n">
-        <v>2.72442722320557</v>
+        <v>2.72442746162415</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.15457391738892</v>
       </c>
       <c r="G475" t="n">
-        <v>2.60956001281738</v>
+        <v>2.6095597743988</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.18483805656433</v>
       </c>
       <c r="G477" t="n">
-        <v>2.63459515571594</v>
+        <v>2.63459539413452</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>3.13321089744568</v>
       </c>
       <c r="G479" t="n">
-        <v>2.59188771247864</v>
+        <v>2.59188747406006</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.074462890625</v>
       </c>
       <c r="G480" t="n">
-        <v>2.54328918457031</v>
+        <v>2.54328942298889</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G489" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.10828804969788</v>
       </c>
       <c r="G490" t="n">
-        <v>2.57127094268799</v>
+        <v>2.57127070426941</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.02639698982239</v>
       </c>
       <c r="G491" t="n">
-        <v>2.50352764129639</v>
+        <v>2.50352787971497</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.02639698982239</v>
       </c>
       <c r="G492" t="n">
-        <v>2.50352764129639</v>
+        <v>2.50352787971497</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.93738508224487</v>
       </c>
       <c r="G493" t="n">
-        <v>2.42989468574524</v>
+        <v>2.42989444732666</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G495" t="n">
-        <v>2.35920667648315</v>
+        <v>2.35920691490173</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G496" t="n">
-        <v>2.35920667648315</v>
+        <v>2.35920691490173</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G497" t="n">
-        <v>2.35920667648315</v>
+        <v>2.35920691490173</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G498" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G500" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.95518708229065</v>
       </c>
       <c r="G501" t="n">
-        <v>2.44462084770203</v>
+        <v>2.44462060928345</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.98189091682434</v>
       </c>
       <c r="G502" t="n">
-        <v>2.4667112827301</v>
+        <v>2.46671104431152</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.98011088371277</v>
       </c>
       <c r="G503" t="n">
-        <v>2.46523857116699</v>
+        <v>2.46523880958557</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.98011088371277</v>
       </c>
       <c r="G504" t="n">
-        <v>2.46523857116699</v>
+        <v>2.46523880958557</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.86617588996887</v>
       </c>
       <c r="G507" t="n">
-        <v>2.37098789215088</v>
+        <v>2.37098813056946</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.85905504226685</v>
       </c>
       <c r="G508" t="n">
-        <v>2.3650975227356</v>
+        <v>2.36509728431702</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G509" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.25</v>
       </c>
       <c r="G511" t="n">
-        <v>2.68849921226501</v>
+        <v>2.68849897384644</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G512" t="n">
-        <v>3.06075286865234</v>
+        <v>3.06075310707092</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.25</v>
       </c>
       <c r="G516" t="n">
-        <v>2.68849921226501</v>
+        <v>2.68849897384644</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G517" t="n">
-        <v>2.70918011665344</v>
+        <v>2.70917987823486</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G518" t="n">
-        <v>2.64713764190674</v>
+        <v>2.64713740348816</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G519" t="n">
-        <v>2.50237226486206</v>
+        <v>2.50237250328064</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G520" t="n">
-        <v>2.46101069450378</v>
+        <v>2.46101093292236</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G522" t="n">
-        <v>2.31624507904053</v>
+        <v>2.31624531745911</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.29556488990784</v>
+        <v>2.29556465148926</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.19216084480286</v>
+        <v>2.19216060638428</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G525" t="n">
-        <v>2.13011837005615</v>
+        <v>2.13011860847473</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G526" t="n">
-        <v>2.0473952293396</v>
+        <v>2.04739546775818</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G528" t="n">
-        <v>2.0432596206665</v>
+        <v>2.04325938224792</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.9605358839035</v>
+        <v>1.96053624153137</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G531" t="n">
-        <v>1.86540484428406</v>
+        <v>1.86540496349335</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>1.82817935943604</v>
+        <v>1.82817959785461</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G533" t="n">
-        <v>1.84886002540588</v>
+        <v>1.84886014461517</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84058773517609</v>
+        <v>1.84058785438538</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G535" t="n">
-        <v>1.8157707452774</v>
+        <v>1.81577086448669</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G536" t="n">
-        <v>1.81990718841553</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G537" t="n">
-        <v>1.74545621871948</v>
+        <v>1.74545609951019</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>1.77854549884796</v>
+        <v>1.77854573726654</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G542" t="n">
-        <v>1.67514193058014</v>
+        <v>1.67514181137085</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G544" t="n">
-        <v>1.67514193058014</v>
+        <v>1.67514181137085</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G545" t="n">
-        <v>1.8157707452774</v>
+        <v>1.81577086448669</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G546" t="n">
-        <v>1.81990718841553</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G548" t="n">
-        <v>1.74545621871948</v>
+        <v>1.74545609951019</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G549" t="n">
-        <v>1.73718416690826</v>
+        <v>1.73718404769897</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>1.80336236953735</v>
+        <v>1.80336248874664</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G553" t="n">
-        <v>1.76613712310791</v>
+        <v>1.76613700389862</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G555" t="n">
-        <v>1.71650314331055</v>
+        <v>1.71650326251984</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>1.77854549884796</v>
+        <v>1.77854573726654</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>1.77854549884796</v>
+        <v>1.77854573726654</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G559" t="n">
-        <v>1.80336236953735</v>
+        <v>1.80336248874664</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G561" t="n">
-        <v>1.81990718841553</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G562" t="n">
-        <v>1.83645164966583</v>
+        <v>1.83645153045654</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G564" t="n">
-        <v>1.76613712310791</v>
+        <v>1.76613700389862</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G566" t="n">
-        <v>1.73718416690826</v>
+        <v>1.73718404769897</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G568" t="n">
-        <v>1.74545621871948</v>
+        <v>1.74545609951019</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G572" t="n">
-        <v>1.74545621871948</v>
+        <v>1.74545609951019</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G576" t="n">
-        <v>1.77854549884796</v>
+        <v>1.77854573726654</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G578" t="n">
-        <v>1.84886002540588</v>
+        <v>1.84886014461517</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G579" t="n">
-        <v>1.91917479038239</v>
+        <v>1.9191746711731</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G580" t="n">
-        <v>1.89022195339203</v>
+        <v>1.89022159576416</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G584" t="n">
-        <v>1.9894894361496</v>
+        <v>1.98948907852173</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>1.99362564086914</v>
+        <v>1.99362576007843</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.31624507904053</v>
+        <v>2.31624531745911</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>2.31624507904053</v>
+        <v>2.31624531745911</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.78749990463257</v>
       </c>
       <c r="G593" t="n">
-        <v>2.30590486526489</v>
+        <v>2.30590510368347</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.6875</v>
       </c>
       <c r="G594" t="n">
-        <v>2.2231822013855</v>
+        <v>2.22318196296692</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.6875</v>
       </c>
       <c r="G595" t="n">
-        <v>2.2231822013855</v>
+        <v>2.22318196296692</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.63750004768372</v>
       </c>
       <c r="G596" t="n">
-        <v>2.18182015419006</v>
+        <v>2.18182039260864</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.61249995231628</v>
       </c>
       <c r="G597" t="n">
-        <v>2.16113972663879</v>
+        <v>2.16113948822021</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>2.19216084480286</v>
+        <v>2.19216060638428</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.63750004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>2.18182015419006</v>
+        <v>2.18182039260864</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.71250009536743</v>
       </c>
       <c r="G600" t="n">
-        <v>2.24386310577393</v>
+        <v>2.24386286735535</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.6875</v>
       </c>
       <c r="G601" t="n">
-        <v>2.2231822013855</v>
+        <v>2.22318196296692</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>2.19216084480286</v>
+        <v>2.19216060638428</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.61249995231628</v>
       </c>
       <c r="G603" t="n">
-        <v>2.16113972663879</v>
+        <v>2.16113948822021</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G604" t="n">
-        <v>2.15079927444458</v>
+        <v>2.15079879760742</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G614" t="n">
-        <v>1.86540484428406</v>
+        <v>1.86540496349335</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G616" t="n">
-        <v>1.91917479038239</v>
+        <v>1.9191746711731</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G618" t="n">
-        <v>1.96880853176117</v>
+        <v>1.96880865097046</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G619" t="n">
-        <v>1.89022195339203</v>
+        <v>1.89022159576416</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G621" t="n">
-        <v>1.94812786579132</v>
+        <v>1.94812774658203</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G622" t="n">
-        <v>1.86540484428406</v>
+        <v>1.86540496349335</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G624" t="n">
-        <v>1.91917479038239</v>
+        <v>1.9191746711731</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G625" t="n">
-        <v>1.93985569477081</v>
+        <v>1.93985545635223</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G626" t="n">
-        <v>1.92331099510193</v>
+        <v>1.92331111431122</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G634" t="n">
-        <v>1.83645164966583</v>
+        <v>1.83645153045654</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G635" t="n">
-        <v>1.90676617622375</v>
+        <v>1.90676641464233</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>1.91090261936188</v>
+        <v>1.9109023809433</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G637" t="n">
-        <v>1.87781345844269</v>
+        <v>1.87781310081482</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G638" t="n">
-        <v>1.84886002540588</v>
+        <v>1.84886014461517</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G641" t="n">
-        <v>1.78681802749634</v>
+        <v>1.78681778907776</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G642" t="n">
-        <v>1.81163501739502</v>
+        <v>1.81163489818573</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G644" t="n">
-        <v>1.81163501739502</v>
+        <v>1.81163489818573</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G645" t="n">
-        <v>1.78681802749634</v>
+        <v>1.78681778907776</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G647" t="n">
-        <v>1.8074985742569</v>
+        <v>1.80749869346619</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G648" t="n">
-        <v>1.73718416690826</v>
+        <v>1.73718404769897</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G651" t="n">
-        <v>1.78268158435822</v>
+        <v>1.7826817035675</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>1.81990718841553</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G657" t="n">
-        <v>1.85134172439575</v>
+        <v>1.85134184360504</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G659" t="n">
-        <v>1.81990718841553</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G660" t="n">
-        <v>1.79839897155762</v>
+        <v>1.79839909076691</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.17549991607666</v>
       </c>
       <c r="G661" t="n">
-        <v>1.79963994026184</v>
+        <v>1.79963982105255</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.17650008201599</v>
       </c>
       <c r="G664" t="n">
-        <v>1.80046725273132</v>
+        <v>1.80046713352203</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G666" t="n">
-        <v>1.83976066112518</v>
+        <v>1.83976054191589</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G667" t="n">
-        <v>1.83727896213531</v>
+        <v>1.83727872371674</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G668" t="n">
-        <v>1.83645164966583</v>
+        <v>1.83645153045654</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.18700003623962</v>
       </c>
       <c r="G670" t="n">
-        <v>1.80915307998657</v>
+        <v>1.80915331840515</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G673" t="n">
-        <v>1.76200115680695</v>
+        <v>1.76200103759766</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G674" t="n">
-        <v>1.75207424163818</v>
+        <v>1.75207412242889</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>1.69168639183044</v>
+        <v>1.69168651103973</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G677" t="n">
-        <v>1.57008349895477</v>
+        <v>1.57008337974548</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>1.82879996299744</v>
       </c>
       <c r="G678" t="n">
-        <v>1.51283919811249</v>
+        <v>1.51283895969391</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>1.79139995574951</v>
       </c>
       <c r="G680" t="n">
-        <v>1.48190081119537</v>
+        <v>1.48190057277679</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>1.47247004508972</v>
+        <v>1.4724702835083</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.76979994773865</v>
       </c>
       <c r="G690" t="n">
-        <v>1.46403241157532</v>
+        <v>1.46403253078461</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>1.71580004692078</v>
       </c>
       <c r="G692" t="n">
-        <v>1.41936218738556</v>
+        <v>1.41936206817627</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G698" t="n">
-        <v>1.41952753067017</v>
+        <v>1.41952764987946</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>1.72440004348755</v>
       </c>
       <c r="G699" t="n">
-        <v>1.42647624015808</v>
+        <v>1.42647635936737</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1.74479997158051</v>
       </c>
       <c r="G700" t="n">
-        <v>1.44335186481476</v>
+        <v>1.44335174560547</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.6793999671936</v>
       </c>
       <c r="G703" t="n">
-        <v>1.38925099372864</v>
+        <v>1.38925087451935</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>1.41456413269043</v>
+        <v>1.41456425189972</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G706" t="n">
-        <v>1.41952753067017</v>
+        <v>1.41952764987946</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.71539998054504</v>
       </c>
       <c r="G707" t="n">
-        <v>1.41903126239777</v>
+        <v>1.41903114318848</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.6793999671936</v>
       </c>
       <c r="G708" t="n">
-        <v>1.38925099372864</v>
+        <v>1.38925087451935</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G710" t="n">
-        <v>1.35665786266327</v>
+        <v>1.35665810108185</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.66460001468658</v>
       </c>
       <c r="G711" t="n">
-        <v>1.37700796127319</v>
+        <v>1.37700772285461</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.72019994258881</v>
       </c>
       <c r="G712" t="n">
-        <v>1.42300176620483</v>
+        <v>1.42300200462341</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.78779995441437</v>
       </c>
       <c r="G716" t="n">
-        <v>1.47892272472382</v>
+        <v>1.47892260551453</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.72979998588562</v>
       </c>
       <c r="G718" t="n">
-        <v>1.43094336986542</v>
+        <v>1.43094325065613</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.81140005588531</v>
       </c>
       <c r="G721" t="n">
-        <v>1.49844539165497</v>
+        <v>1.49844527244568</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.81140005588531</v>
       </c>
       <c r="G722" t="n">
-        <v>1.49844539165497</v>
+        <v>1.49844527244568</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.81140005588531</v>
       </c>
       <c r="G723" t="n">
-        <v>1.49844539165497</v>
+        <v>1.49844527244568</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.81120002269745</v>
       </c>
       <c r="G724" t="n">
-        <v>1.49827992916107</v>
+        <v>1.49827980995178</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G729" t="n">
-        <v>1.51796805858612</v>
+        <v>1.51796793937683</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G730" t="n">
-        <v>1.48653328418732</v>
+        <v>1.48653340339661</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G731" t="n">
-        <v>1.48653328418732</v>
+        <v>1.48653340339661</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.7985999584198</v>
       </c>
       <c r="G734" t="n">
-        <v>1.48785662651062</v>
+        <v>1.48785674571991</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.84179997444153</v>
       </c>
       <c r="G738" t="n">
-        <v>1.52359318733215</v>
+        <v>1.52359306812286</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G739" t="n">
-        <v>1.48884952068329</v>
+        <v>1.48884928226471</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G743" t="n">
-        <v>1.48156988620758</v>
+        <v>1.48156976699829</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G747" t="n">
-        <v>1.46916139125824</v>
+        <v>1.46916151046753</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.78120005130768</v>
       </c>
       <c r="G748" t="n">
-        <v>1.47346305847168</v>
+        <v>1.47346293926239</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G749" t="n">
-        <v>1.48156988620758</v>
+        <v>1.48156976699829</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G752" t="n">
-        <v>1.48884952068329</v>
+        <v>1.48884928226471</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.88940000534058</v>
       </c>
       <c r="G756" t="n">
-        <v>1.56296932697296</v>
+        <v>1.56296920776367</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.90240001678467</v>
       </c>
       <c r="G757" t="n">
-        <v>1.64630568027496</v>
+        <v>1.64630579948425</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.93239998817444</v>
       </c>
       <c r="G759" t="n">
-        <v>1.67226719856262</v>
+        <v>1.67226731777191</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>1.69615197181702</v>
+        <v>1.69615185260773</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.94760000705719</v>
       </c>
       <c r="G770" t="n">
-        <v>1.68542110919952</v>
+        <v>1.68542098999023</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.91380000114441</v>
       </c>
       <c r="G771" t="n">
-        <v>1.65617108345032</v>
+        <v>1.65617120265961</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.89979994297028</v>
       </c>
       <c r="G773" t="n">
-        <v>1.64405572414398</v>
+        <v>1.64405560493469</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>1.69615197181702</v>
+        <v>1.69615185260773</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G782" t="n">
-        <v>1.68126726150513</v>
+        <v>1.68126714229584</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G783" t="n">
-        <v>1.68126726150513</v>
+        <v>1.68126714229584</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G786" t="n">
-        <v>1.68749797344208</v>
+        <v>1.68749809265137</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G788" t="n">
-        <v>1.68126726150513</v>
+        <v>1.68126714229584</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G789" t="n">
-        <v>1.66759419441223</v>
+        <v>1.66759431362152</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.89859998226166</v>
       </c>
       <c r="G790" t="n">
-        <v>1.64301717281342</v>
+        <v>1.64301729202271</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.89979994297028</v>
       </c>
       <c r="G791" t="n">
-        <v>1.64405572414398</v>
+        <v>1.64405560493469</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G794" t="n">
-        <v>1.66240179538727</v>
+        <v>1.66240191459656</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G795" t="n">
-        <v>1.65980565547943</v>
+        <v>1.65980577468872</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G798" t="n">
-        <v>1.61913275718689</v>
+        <v>1.61913287639618</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.85739994049072</v>
       </c>
       <c r="G800" t="n">
-        <v>1.60736346244812</v>
+        <v>1.60736334323883</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.89979994297028</v>
       </c>
       <c r="G801" t="n">
-        <v>1.64405572414398</v>
+        <v>1.64405560493469</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.8775999546051</v>
       </c>
       <c r="G805" t="n">
-        <v>1.62484419345856</v>
+        <v>1.62484431266785</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G810" t="n">
-        <v>1.60355591773987</v>
+        <v>1.60355579853058</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>1.75220000743866</v>
       </c>
       <c r="G814" t="n">
-        <v>1.51632523536682</v>
+        <v>1.51632511615753</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G816" t="n">
-        <v>1.50144040584564</v>
+        <v>1.50144064426422</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G817" t="n">
-        <v>1.50144040584564</v>
+        <v>1.50144064426422</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.76960003376007</v>
       </c>
       <c r="G819" t="n">
-        <v>1.53138279914856</v>
+        <v>1.53138291835785</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.76279997825623</v>
       </c>
       <c r="G820" t="n">
-        <v>1.52549815177917</v>
+        <v>1.52549803256989</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.76279997825623</v>
       </c>
       <c r="G821" t="n">
-        <v>1.52549815177917</v>
+        <v>1.52549803256989</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G830" t="n">
-        <v>1.50144040584564</v>
+        <v>1.50144064426422</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G831" t="n">
-        <v>1.48845982551575</v>
+        <v>1.48845970630646</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G832" t="n">
-        <v>1.4971137046814</v>
+        <v>1.49711358547211</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G833" t="n">
-        <v>1.44951748847961</v>
+        <v>1.44951736927032</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G836" t="n">
-        <v>1.47547912597656</v>
+        <v>1.47547900676727</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G838" t="n">
-        <v>1.55336344242096</v>
+        <v>1.55336356163025</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G842" t="n">
-        <v>1.44519066810608</v>
+        <v>1.44519054889679</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G843" t="n">
-        <v>1.44519066810608</v>
+        <v>1.44519054889679</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G851" t="n">
-        <v>1.44951748847961</v>
+        <v>1.44951736927032</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G852" t="n">
-        <v>1.44951748847961</v>
+        <v>1.44951736927032</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G853" t="n">
-        <v>1.44519066810608</v>
+        <v>1.44519054889679</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G855" t="n">
-        <v>1.4322098493576</v>
+        <v>1.43220996856689</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G856" t="n">
-        <v>1.34134459495544</v>
+        <v>1.34134447574615</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G857" t="n">
-        <v>1.36730599403381</v>
+        <v>1.3673061132431</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G858" t="n">
-        <v>1.44951748847961</v>
+        <v>1.44951736927032</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G861" t="n">
-        <v>1.4322098493576</v>
+        <v>1.43220996856689</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G863" t="n">
-        <v>1.4322098493576</v>
+        <v>1.43220996856689</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G865" t="n">
-        <v>1.41922891139984</v>
+        <v>1.41922914981842</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G866" t="n">
-        <v>1.41922891139984</v>
+        <v>1.41922914981842</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G873" t="n">
-        <v>1.41922891139984</v>
+        <v>1.41922914981842</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G878" t="n">
-        <v>1.38028681278229</v>
+        <v>1.38028693199158</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G879" t="n">
-        <v>1.38028681278229</v>
+        <v>1.38028693199158</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G880" t="n">
-        <v>1.37595999240875</v>
+        <v>1.37595987319946</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G881" t="n">
-        <v>1.37595999240875</v>
+        <v>1.37595987319946</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G885" t="n">
-        <v>1.37595999240875</v>
+        <v>1.37595987319946</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G887" t="n">
-        <v>1.37163317203522</v>
+        <v>1.37163305282593</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G888" t="n">
-        <v>1.33701765537262</v>
+        <v>1.33701753616333</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G890" t="n">
-        <v>1.31971001625061</v>
+        <v>1.31970989704132</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G893" t="n">
-        <v>1.31971001625061</v>
+        <v>1.31970989704132</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G895" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950406551361</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G896" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950406551361</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>1.38617515563965</v>
+        <v>1.38617527484894</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>1.38617515563965</v>
+        <v>1.38617527484894</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G903" t="n">
-        <v>1.38617515563965</v>
+        <v>1.38617527484894</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G908" t="n">
-        <v>1.41283249855042</v>
+        <v>1.4128326177597</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G914" t="n">
-        <v>1.38617515563965</v>
+        <v>1.38617527484894</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G915" t="n">
-        <v>1.38617515563965</v>
+        <v>1.38617527484894</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G916" t="n">
-        <v>1.38617515563965</v>
+        <v>1.38617527484894</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>1.38617515563965</v>
+        <v>1.38617527484894</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.38617515563965</v>
+        <v>1.38617527484894</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G942" t="n">
-        <v>1.41283249855042</v>
+        <v>1.4128326177597</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G943" t="n">
-        <v>1.41283249855042</v>
+        <v>1.4128326177597</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G944" t="n">
-        <v>1.41283249855042</v>
+        <v>1.4128326177597</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G948" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950406551361</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G949" t="n">
-        <v>1.41283249855042</v>
+        <v>1.4128326177597</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G953" t="n">
-        <v>1.38617515563965</v>
+        <v>1.38617527484894</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G956" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950406551361</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G958" t="n">
-        <v>1.37728953361511</v>
+        <v>1.37728941440582</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G962" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G963" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.5</v>
       </c>
       <c r="G983" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.5</v>
       </c>
       <c r="G984" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G991" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G994" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G996" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G997" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.5</v>
       </c>
       <c r="G998" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G999" t="n">
-        <v>1.28398931026459</v>
+        <v>1.28398942947388</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.5</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>1.5</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.31064653396606</v>
+        <v>1.31064665317535</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.5</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.5</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.5</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.5</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.5</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.5</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.50613284111023</v>
+        <v>1.50613296031952</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.47503268718719</v>
+        <v>1.47503256797791</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.38617515563965</v>
+        <v>1.38617527484894</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950406551361</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950406551361</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.37728953361511</v>
+        <v>1.37728941440582</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.2928751707077</v>
+        <v>1.29287505149841</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.5</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>1.5</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.5</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.986317038536072</v>
+        <v>0.986316978931427</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.986317038536072</v>
+        <v>0.986316978931427</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.12848877906799</v>
+        <v>1.12848889827728</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.14181745052338</v>
+        <v>1.14181756973267</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.12848877906799</v>
+        <v>1.12848889827728</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.1151602268219</v>
+        <v>1.11516034603119</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.1151602268219</v>
+        <v>1.11516034603119</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.12848877906799</v>
+        <v>1.12848889827728</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.12848877906799</v>
+        <v>1.12848889827728</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.19513201713562</v>
+        <v>1.19513189792633</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.19068896770477</v>
+        <v>1.19068908691406</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.19068896770477</v>
+        <v>1.19068908691406</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.17736041545868</v>
+        <v>1.17736053466797</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.17736041545868</v>
+        <v>1.17736053466797</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.16847479343414</v>
+        <v>1.16847467422485</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.17736041545868</v>
+        <v>1.17736053466797</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.17736041545868</v>
+        <v>1.17736053466797</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.17736041545868</v>
+        <v>1.17736053466797</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.19513201713562</v>
+        <v>1.19513189792633</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.29731786251068</v>
+        <v>1.29731798171997</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.29731786251068</v>
+        <v>1.29731798171997</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.2928751707077</v>
+        <v>1.29287505149841</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.2928751707077</v>
+        <v>1.29287505149841</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.17736041545868</v>
+        <v>1.17736053466797</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.21734619140625</v>
+        <v>1.21734631061554</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.21734619140625</v>
+        <v>1.21734631061554</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.21734619140625</v>
+        <v>1.21734631061554</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.19513201713562</v>
+        <v>1.19513189792633</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.19068896770477</v>
+        <v>1.19068908691406</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.18180334568024</v>
+        <v>1.18180322647095</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.12848877906799</v>
+        <v>1.12848889827728</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.12848877906799</v>
+        <v>1.12848889827728</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.13293182849884</v>
+        <v>1.13293170928955</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.12848877906799</v>
+        <v>1.12848889827728</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.02630293369293</v>
+        <v>1.02630281448364</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.00853133201599</v>
+        <v>1.00853145122528</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.986317038536072</v>
+        <v>0.986316978931427</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.964102804660797</v>
+        <v>0.964102745056152</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.955217063426971</v>
+        <v>0.955217003822327</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.937445402145386</v>
+        <v>0.937445461750031</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.946331322193146</v>
+        <v>0.946331262588501</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>1.125</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.999645709991455</v>
+        <v>0.99964565038681</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.995202720165253</v>
+        <v>0.995202779769897</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.12848877906799</v>
+        <v>1.12848889827728</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.13293182849884</v>
+        <v>1.13293170928955</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1247" t="n">
-        <v>1.13293182849884</v>
+        <v>1.13293170928955</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.13293182849884</v>
+        <v>1.13293170928955</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.1151602268219</v>
+        <v>1.11516034603119</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.12848877906799</v>
+        <v>1.12848889827728</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.13293182849884</v>
+        <v>1.13293170928955</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.1151602268219</v>
+        <v>1.11516034603119</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.1151602268219</v>
+        <v>1.11516034603119</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.1151602268219</v>
+        <v>1.11516034603119</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.14181745052338</v>
+        <v>1.14181756973267</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.14181745052338</v>
+        <v>1.14181756973267</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.1151602268219</v>
+        <v>1.11516034603119</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.14181745052338</v>
+        <v>1.14181756973267</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.13293182849884</v>
+        <v>1.13293170928955</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.27954649925232</v>
+        <v>1.27954638004303</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.5</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>1.5</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.31064653396606</v>
+        <v>1.31064665317535</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.28398931026459</v>
+        <v>1.28398942947388</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.27954649925232</v>
+        <v>1.27954638004303</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.38617515563965</v>
+        <v>1.38617527484894</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.38617515563965</v>
+        <v>1.38617527484894</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.69273328781128</v>
+        <v>1.69273340702057</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.67051899433136</v>
+        <v>1.67051887512207</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.68829035758972</v>
+        <v>1.68829047679901</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.71050488948822</v>
+        <v>1.71050477027893</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.70606184005737</v>
+        <v>1.70606195926666</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.63497614860535</v>
+        <v>1.63497602939606</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.68384766578674</v>
+        <v>1.68384754657745</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.66163313388824</v>
+        <v>1.66163325309753</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.62164759635925</v>
+        <v>1.62164747714996</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.57277584075928</v>
+        <v>1.57277572154999</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.7016190290451</v>
+        <v>1.70161914825439</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.68829035758972</v>
+        <v>1.68829047679901</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.69717621803284</v>
+        <v>1.69717609882355</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.7016190290451</v>
+        <v>1.70161914825439</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.67051899433136</v>
+        <v>1.67051887512207</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.7016190290451</v>
+        <v>1.70161914825439</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.70606184005737</v>
+        <v>1.70606195926666</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.68384766578674</v>
+        <v>1.68384754657745</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.7016190290451</v>
+        <v>1.70161914825439</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.71050488948822</v>
+        <v>1.71050477027893</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.68829035758972</v>
+        <v>1.68829047679901</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.69717621803284</v>
+        <v>1.69717609882355</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.7016190290451</v>
+        <v>1.70161914825439</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.68384766578674</v>
+        <v>1.68384754657745</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.67051899433136</v>
+        <v>1.67051887512207</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.67051899433136</v>
+        <v>1.67051887512207</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1415" t="n">
-        <v>2.01706266403198</v>
+        <v>2.01706290245056</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.97263407707214</v>
+        <v>1.97263395786285</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.94597697257996</v>
+        <v>1.94597685337067</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.95486271381378</v>
+        <v>1.95486259460449</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.87489080429077</v>
+        <v>1.87489092350006</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.87489080429077</v>
+        <v>1.87489092350006</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.87489080429077</v>
+        <v>1.87489092350006</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.87489080429077</v>
+        <v>1.87489092350006</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.87489080429077</v>
+        <v>1.87489092350006</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.90154814720154</v>
+        <v>1.90154826641083</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.90154814720154</v>
+        <v>1.90154826641083</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.89266264438629</v>
+        <v>1.892662525177</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.90154814720154</v>
+        <v>1.90154826641083</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.98151993751526</v>
+        <v>1.98151981830597</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.98151993751526</v>
+        <v>1.98151981830597</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>2.25</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.99929141998291</v>
+        <v>1.99929130077362</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.0259485244751</v>
+        <v>2.02594828605652</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>2.25</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.99929141998291</v>
+        <v>1.99929130077362</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.97263407707214</v>
+        <v>1.97263395786285</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.98151993751526</v>
+        <v>1.98151981830597</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.94597697257996</v>
+        <v>1.94597685337067</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.99040544033051</v>
+        <v>1.99040555953979</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.96374833583832</v>
+        <v>1.96374845504761</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.96374833583832</v>
+        <v>1.96374845504761</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.05260586738586</v>
+        <v>2.05260562896729</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.05260586738586</v>
+        <v>2.05260562896729</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>2.25</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.99929141998291</v>
+        <v>1.99929130077362</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1486" t="n">
-        <v>2.01706266403198</v>
+        <v>2.01706290245056</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>2.25</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.99929141998291</v>
+        <v>1.99929130077362</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.0259485244751</v>
+        <v>2.02594828605652</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1489" t="n">
-        <v>2.0259485244751</v>
+        <v>2.02594828605652</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.99040544033051</v>
+        <v>1.99040555953979</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.99040544033051</v>
+        <v>1.99040555953979</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.01706266403198</v>
+        <v>2.01706290245056</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>2.25</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.99929141998291</v>
+        <v>1.99929130077362</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>2.25</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.99929141998291</v>
+        <v>1.99929130077362</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.89266264438629</v>
+        <v>1.892662525177</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1501" t="n">
-        <v>1.87489080429077</v>
+        <v>1.87489092350006</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.89266264438629</v>
+        <v>1.892662525177</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.92820560932159</v>
+        <v>1.9282054901123</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.92820560932159</v>
+        <v>1.9282054901123</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.97263407707214</v>
+        <v>1.97263395786285</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.97263407707214</v>
+        <v>1.97263395786285</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.96374833583832</v>
+        <v>1.96374845504761</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.98151993751526</v>
+        <v>1.98151981830597</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.94597697257996</v>
+        <v>1.94597685337067</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1516" t="n">
-        <v>1.95486271381378</v>
+        <v>1.95486259460449</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.87489080429077</v>
+        <v>1.87489092350006</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.90154814720154</v>
+        <v>1.90154826641083</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.92820560932159</v>
+        <v>1.9282054901123</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.90154814720154</v>
+        <v>1.90154826641083</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.89266264438629</v>
+        <v>1.892662525177</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.90154814720154</v>
+        <v>1.90154826641083</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.87489080429077</v>
+        <v>1.87489092350006</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.96374833583832</v>
+        <v>1.96374845504761</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.05260586738586</v>
+        <v>2.05260562896729</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.99040544033051</v>
+        <v>1.99040555953979</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.97263407707214</v>
+        <v>1.97263395786285</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.97263407707214</v>
+        <v>1.97263395786285</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.94597697257996</v>
+        <v>1.94597685337067</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.89266264438629</v>
+        <v>1.892662525177</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.67496180534363</v>
+        <v>1.67496192455292</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.7016190290451</v>
+        <v>1.70161914825439</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.63497614860535</v>
+        <v>1.63497602939606</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1577" t="n">
-        <v>1.68829035758972</v>
+        <v>1.68829047679901</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1579" t="n">
-        <v>1.67051899433136</v>
+        <v>1.67051887512207</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.67051899433136</v>
+        <v>1.67051887512207</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.64830458164215</v>
+        <v>1.64830470085144</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.57277584075928</v>
+        <v>1.57277572154999</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.69717621803284</v>
+        <v>1.69717609882355</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.71050488948822</v>
+        <v>1.71050477027893</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1610" t="n">
-        <v>1.64830458164215</v>
+        <v>1.64830470085144</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.98151993751526</v>
+        <v>1.98151981830597</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1619" t="n">
-        <v>1.75493347644806</v>
+        <v>1.75493359565735</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1628" t="n">
-        <v>1.98151993751526</v>
+        <v>1.98151981830597</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>1.92820560932159</v>
+        <v>1.9282054901123</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1631" t="n">
-        <v>1.98151993751526</v>
+        <v>1.98151981830597</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.90154814720154</v>
+        <v>1.90154826641083</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1635" t="n">
-        <v>1.89266264438629</v>
+        <v>1.892662525177</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1636" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1637" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1640" t="n">
-        <v>1.69717621803284</v>
+        <v>1.69717609882355</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1641" t="n">
-        <v>1.63497614860535</v>
+        <v>1.63497602939606</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.66163313388824</v>
+        <v>1.66163325309753</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.71050488948822</v>
+        <v>1.71050477027893</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.97263407707214</v>
+        <v>1.97263395786285</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1651" t="n">
-        <v>1.95486271381378</v>
+        <v>1.95486259460449</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1656" t="n">
-        <v>1.67051899433136</v>
+        <v>1.67051887512207</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1658" t="n">
-        <v>1.75493347644806</v>
+        <v>1.75493359565735</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.69273328781128</v>
+        <v>1.69273340702057</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1667" t="n">
-        <v>1.70606184005737</v>
+        <v>1.70606195926666</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.7016190290451</v>
+        <v>1.70161914825439</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1672" t="n">
-        <v>1.68829035758972</v>
+        <v>1.68829047679901</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1688" t="n">
-        <v>1.75493347644806</v>
+        <v>1.75493359565735</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1693" t="n">
-        <v>1.70606184005737</v>
+        <v>1.70606195926666</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.68829035758972</v>
+        <v>1.68829047679901</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.67496180534363</v>
+        <v>1.67496192455292</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1699" t="n">
-        <v>1.63497614860535</v>
+        <v>1.63497602939606</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1701" t="n">
-        <v>1.66163313388824</v>
+        <v>1.66163325309753</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.62164759635925</v>
+        <v>1.62164747714996</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1703" t="n">
-        <v>1.70606184005737</v>
+        <v>1.70606195926666</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1704" t="n">
-        <v>1.70606184005737</v>
+        <v>1.70606195926666</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1705" t="n">
-        <v>1.68384766578674</v>
+        <v>1.68384754657745</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1706" t="n">
-        <v>1.68384766578674</v>
+        <v>1.68384754657745</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1708" t="n">
-        <v>1.67496180534363</v>
+        <v>1.67496192455292</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1709" t="n">
-        <v>1.66163313388824</v>
+        <v>1.66163325309753</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.63497614860535</v>
+        <v>1.63497602939606</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1711" t="n">
-        <v>1.64830458164215</v>
+        <v>1.64830470085144</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.5105756521225</v>
+        <v>1.51057577133179</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>1.5</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1723" t="n">
-        <v>1.27954649925232</v>
+        <v>1.27954638004303</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1724" t="n">
-        <v>1.27954649925232</v>
+        <v>1.27954638004303</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.29731786251068</v>
+        <v>1.29731798171997</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.27954649925232</v>
+        <v>1.27954638004303</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.27954649925232</v>
+        <v>1.27954638004303</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1731" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.2928751707077</v>
+        <v>1.29287505149841</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1733" t="n">
-        <v>1.2928751707077</v>
+        <v>1.29287505149841</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1734" t="n">
-        <v>1.27954649925232</v>
+        <v>1.27954638004303</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.27954649925232</v>
+        <v>1.27954638004303</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1749" t="n">
-        <v>1.27954649925232</v>
+        <v>1.27954638004303</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1753" t="n">
-        <v>1.21734619140625</v>
+        <v>1.21734631061554</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>1.5</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1764" t="n">
-        <v>1.29731786251068</v>
+        <v>1.29731798171997</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>1.5</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1768" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1769" t="n">
-        <v>1.31064653396606</v>
+        <v>1.31064665317535</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1776" t="n">
-        <v>1.2928751707077</v>
+        <v>1.29287505149841</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1779" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.38617515563965</v>
+        <v>1.38617527484894</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1791" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950406551361</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950406551361</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1794" t="n">
-        <v>1.37728953361511</v>
+        <v>1.37728941440582</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1802" t="n">
-        <v>1.2928751707077</v>
+        <v>1.29287505149841</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.38617515563965</v>
+        <v>1.38617527484894</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.2928751707077</v>
+        <v>1.29287505149841</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>1.5</v>
       </c>
       <c r="G1811" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>1.5</v>
       </c>
       <c r="G1812" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1814" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1815" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1816" t="n">
-        <v>1.29731786251068</v>
+        <v>1.29731798171997</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.28398931026459</v>
+        <v>1.28398942947388</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.2928751707077</v>
+        <v>1.29287505149841</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.29731786251068</v>
+        <v>1.29731798171997</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1826" t="n">
-        <v>1.2928751707077</v>
+        <v>1.29287505149841</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>1.5</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>1.5</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>1.5</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.27954649925232</v>
+        <v>1.27954638004303</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.31064653396606</v>
+        <v>1.31064665317535</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1844" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1845" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.21734619140625</v>
+        <v>1.21734631061554</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.19068896770477</v>
+        <v>1.19068908691406</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.19513201713562</v>
+        <v>1.19513189792633</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.19513201713562</v>
+        <v>1.19513189792633</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.21734619140625</v>
+        <v>1.21734631061554</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.20846056938171</v>
+        <v>1.20846045017242</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.20846056938171</v>
+        <v>1.20846045017242</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.18180334568024</v>
+        <v>1.18180322647095</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.20846056938171</v>
+        <v>1.20846045017242</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.19068896770477</v>
+        <v>1.19068908691406</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.21734619140625</v>
+        <v>1.21734631061554</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.21734619140625</v>
+        <v>1.21734631061554</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.18180334568024</v>
+        <v>1.18180322647095</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.20846056938171</v>
+        <v>1.20846045017242</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.21734619140625</v>
+        <v>1.21734631061554</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1927" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>1.5</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1930" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1937" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1938" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1939" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1940" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.31064653396606</v>
+        <v>1.31064665317535</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1943" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1944" t="n">
-        <v>1.29731786251068</v>
+        <v>1.29731798171997</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1946" t="n">
-        <v>1.28398931026459</v>
+        <v>1.28398942947388</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.31064653396606</v>
+        <v>1.31064665317535</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1953" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>1.5</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>1.5</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>1.5</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>1.5</v>
       </c>
       <c r="G1960" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>1.5</v>
       </c>
       <c r="G1962" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.29731786251068</v>
+        <v>1.29731798171997</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51719,7 +51719,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1975" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H1975" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1979" t="n">
-        <v>1.21734619140625</v>
+        <v>1.21734631061554</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.21734619140625</v>
+        <v>1.21734631061554</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.19068896770477</v>
+        <v>1.19068908691406</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.20401763916016</v>
+        <v>1.20401775836945</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G1997" t="n">
-        <v>1.16847479343414</v>
+        <v>1.16847467422485</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.19068896770477</v>
+        <v>1.19068908691406</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.13293182849884</v>
+        <v>1.13293170928955</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G2005" t="n">
-        <v>1.13293182849884</v>
+        <v>1.13293170928955</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G2006" t="n">
-        <v>1.14181745052338</v>
+        <v>1.14181756973267</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.18180334568024</v>
+        <v>1.18180322647095</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G2008" t="n">
-        <v>1.17736041545868</v>
+        <v>1.17736053466797</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G2015" t="n">
-        <v>1.29731786251068</v>
+        <v>1.29731798171997</v>
       </c>
       <c r="H2015" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2019" t="n">
-        <v>1.37728953361511</v>
+        <v>1.37728941440582</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G2020" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.37728953361511</v>
+        <v>1.37728941440582</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.37728953361511</v>
+        <v>1.37728941440582</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2024" t="n">
-        <v>1.37728953361511</v>
+        <v>1.37728941440582</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.47503268718719</v>
+        <v>1.47503256797791</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.51501870155334</v>
+        <v>1.51501858234406</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2039" t="n">
-        <v>1.69273328781128</v>
+        <v>1.69273340702057</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.68829035758972</v>
+        <v>1.68829047679901</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2043" t="n">
-        <v>1.57277584075928</v>
+        <v>1.57277572154999</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G2046" t="n">
-        <v>1.50613284111023</v>
+        <v>1.50613296031952</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2051" t="n">
-        <v>1.50169003009796</v>
+        <v>1.50168991088867</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.5105756521225</v>
+        <v>1.51057577133179</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2053" t="n">
-        <v>1.49280405044556</v>
+        <v>1.49280416965485</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2054" t="n">
-        <v>1.52834725379944</v>
+        <v>1.52834713459015</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53851,7 +53851,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2057" t="n">
-        <v>1.50169003009796</v>
+        <v>1.50168991088867</v>
       </c>
       <c r="H2057" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2060" t="n">
-        <v>1.49280405044556</v>
+        <v>1.49280416965485</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2061" t="n">
-        <v>1.49280405044556</v>
+        <v>1.49280416965485</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G2064" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950406551361</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2068" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54163,7 +54163,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2069" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H2069" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>1.5</v>
       </c>
       <c r="G2070" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>1.5</v>
       </c>
       <c r="G2071" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>1.5</v>
       </c>
       <c r="G2074" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2076" t="n">
-        <v>1.3062037229538</v>
+        <v>1.30620360374451</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.31953239440918</v>
+        <v>1.31953227519989</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54501,7 +54501,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2082" t="n">
-        <v>1.32397508621216</v>
+        <v>1.32397520542145</v>
       </c>
       <c r="H2082" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.37728953361511</v>
+        <v>1.37728941440582</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.57277584075928</v>
+        <v>1.57277572154999</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -54943,7 +54943,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2099" t="n">
-        <v>1.63497614860535</v>
+        <v>1.63497602939606</v>
       </c>
       <c r="H2099" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G2104" t="n">
-        <v>1.48836135864258</v>
+        <v>1.48836123943329</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2105" t="n">
-        <v>1.50169003009796</v>
+        <v>1.50168991088867</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2108" t="n">
-        <v>1.51501870155334</v>
+        <v>1.51501858234406</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G2109" t="n">
-        <v>1.48836135864258</v>
+        <v>1.48836123943329</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.47947549819946</v>
+        <v>1.47947561740875</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55255,7 +55255,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G2111" t="n">
-        <v>1.47503268718719</v>
+        <v>1.47503256797791</v>
       </c>
       <c r="H2111" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.41283249855042</v>
+        <v>1.4128326177597</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>3.07999992370605</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>20379</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -499,7 +499,7 @@
         <v>5.16267681121826</v>
       </c>
       <c r="G5" t="n">
-        <v>4.27072381973267</v>
+        <v>4.27072334289551</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5343918800354</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G16" t="n">
-        <v>3.38712549209595</v>
+        <v>3.38712573051453</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G17" t="n">
-        <v>3.38712549209595</v>
+        <v>3.38712573051453</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.11233901977539</v>
       </c>
       <c r="G18" t="n">
-        <v>3.40185189247131</v>
+        <v>3.40185236930847</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.11233901977539</v>
       </c>
       <c r="G19" t="n">
-        <v>3.40185189247131</v>
+        <v>3.40185236930847</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.11233901977539</v>
       </c>
       <c r="G20" t="n">
-        <v>3.40185189247131</v>
+        <v>3.40185236930847</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.19957113265991</v>
       </c>
       <c r="G25" t="n">
-        <v>3.47401356697083</v>
+        <v>3.47401332855225</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.03044891357422</v>
       </c>
       <c r="G39" t="n">
-        <v>3.33411049842834</v>
+        <v>3.33411026000977</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.30816507339478</v>
       </c>
       <c r="G42" t="n">
-        <v>3.56384515762329</v>
+        <v>3.56384563446045</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G43" t="n">
-        <v>3.5343918800354</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.03400897979736</v>
       </c>
       <c r="G44" t="n">
-        <v>3.33705520629883</v>
+        <v>3.33705544471741</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.40785789489746</v>
       </c>
       <c r="G45" t="n">
-        <v>3.64631485939026</v>
+        <v>3.64631462097168</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.40785789489746</v>
       </c>
       <c r="G46" t="n">
-        <v>3.64631485939026</v>
+        <v>3.64631462097168</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G47" t="n">
-        <v>3.49315762519836</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G48" t="n">
-        <v>3.49315762519836</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G49" t="n">
-        <v>3.49315762519836</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G50" t="n">
-        <v>3.49315762519836</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.82750201225281</v>
       </c>
       <c r="G69" t="n">
-        <v>3.16622638702393</v>
+        <v>3.1662266254425</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.04113006591797</v>
       </c>
       <c r="G71" t="n">
-        <v>3.34294605255127</v>
+        <v>3.34294581413269</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.04113006591797</v>
       </c>
       <c r="G72" t="n">
-        <v>3.34294605255127</v>
+        <v>3.34294581413269</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.18176794052124</v>
       </c>
       <c r="G75" t="n">
-        <v>3.45928597450256</v>
+        <v>3.45928621292114</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G76" t="n">
-        <v>3.5343918800354</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G77" t="n">
-        <v>3.5343918800354</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.94321703910828</v>
       </c>
       <c r="G78" t="n">
-        <v>3.26194930076599</v>
+        <v>3.26194953918457</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.9343159198761</v>
       </c>
       <c r="G80" t="n">
-        <v>3.25458598136902</v>
+        <v>3.2545862197876</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.9343159198761</v>
       </c>
       <c r="G81" t="n">
-        <v>3.25458598136902</v>
+        <v>3.2545862197876</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.29036283493042</v>
       </c>
       <c r="G82" t="n">
-        <v>3.54911875724792</v>
+        <v>3.5491189956665</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.16574621200562</v>
       </c>
       <c r="G83" t="n">
-        <v>3.44603204727173</v>
+        <v>3.44603228569031</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G84" t="n">
-        <v>3.5343918800354</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G85" t="n">
-        <v>3.5343918800354</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G86" t="n">
-        <v>3.5343918800354</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.20313119888306</v>
       </c>
       <c r="G87" t="n">
-        <v>3.47695827484131</v>
+        <v>3.47695851325989</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.20313119888306</v>
       </c>
       <c r="G88" t="n">
-        <v>3.47695827484131</v>
+        <v>3.47695851325989</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.9254150390625</v>
       </c>
       <c r="G89" t="n">
-        <v>3.24722266197205</v>
+        <v>3.24722290039062</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.96101999282837</v>
       </c>
       <c r="G91" t="n">
-        <v>3.27667641639709</v>
+        <v>3.27667665481567</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.89871096611023</v>
       </c>
       <c r="G92" t="n">
-        <v>3.22513270378113</v>
+        <v>3.22513246536255</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G95" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G96" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G103" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G104" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G105" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G106" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G107" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G108" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G109" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G110" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G111" t="n">
-        <v>2.90409207344055</v>
+        <v>2.90409231185913</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G114" t="n">
-        <v>2.90114712715149</v>
+        <v>2.90114736557007</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.29521203041077</v>
       </c>
       <c r="G122" t="n">
-        <v>2.7258996963501</v>
+        <v>2.72589993476868</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.95518708229065</v>
       </c>
       <c r="G127" t="n">
-        <v>2.44462084770203</v>
+        <v>2.44462060928345</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.88041806221008</v>
       </c>
       <c r="G131" t="n">
-        <v>2.38276958465576</v>
+        <v>2.38276982307434</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.79852700233459</v>
       </c>
       <c r="G132" t="n">
-        <v>2.3150269985199</v>
+        <v>2.31502676010132</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G135" t="n">
-        <v>1.7671959400177</v>
+        <v>1.76719617843628</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G136" t="n">
-        <v>1.7671959400177</v>
+        <v>1.76719617843628</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.86924505233765</v>
       </c>
       <c r="G138" t="n">
-        <v>1.5462965965271</v>
+        <v>1.54629647731781</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.13450002670288</v>
       </c>
       <c r="G139" t="n">
-        <v>1.76572334766388</v>
+        <v>1.76572346687317</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.17010402679443</v>
       </c>
       <c r="G142" t="n">
-        <v>1.79517650604248</v>
+        <v>1.7951762676239</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.15408205986023</v>
       </c>
       <c r="G145" t="n">
-        <v>1.78192222118378</v>
+        <v>1.78192234039307</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.21461009979248</v>
       </c>
       <c r="G147" t="n">
-        <v>1.83199322223663</v>
+        <v>1.83199298381805</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G149" t="n">
-        <v>1.73774266242981</v>
+        <v>1.73774254322052</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.09711503982544</v>
       </c>
       <c r="G156" t="n">
-        <v>1.73479747772217</v>
+        <v>1.73479759693146</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.94935500621796</v>
       </c>
       <c r="G164" t="n">
-        <v>1.61256587505341</v>
+        <v>1.61256575584412</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.86924505233765</v>
       </c>
       <c r="G170" t="n">
-        <v>1.5462965965271</v>
+        <v>1.54629647731781</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.86924505233765</v>
       </c>
       <c r="G171" t="n">
-        <v>1.5462965965271</v>
+        <v>1.54629647731781</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.17188501358032</v>
       </c>
       <c r="G177" t="n">
-        <v>1.79664957523346</v>
+        <v>1.79664969444275</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.11313700675964</v>
       </c>
       <c r="G178" t="n">
-        <v>1.74805152416229</v>
+        <v>1.748051404953</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.08287310600281</v>
       </c>
       <c r="G180" t="n">
-        <v>1.72301602363586</v>
+        <v>1.72301614284515</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.97605895996094</v>
       </c>
       <c r="G182" t="n">
-        <v>1.63465619087219</v>
+        <v>1.63465631008148</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.90485000610352</v>
       </c>
       <c r="G186" t="n">
-        <v>1.57574999332428</v>
+        <v>1.57575011253357</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.87992596626282</v>
       </c>
       <c r="G187" t="n">
-        <v>1.55513215065002</v>
+        <v>1.55513203144073</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.90485000610352</v>
       </c>
       <c r="G189" t="n">
-        <v>1.57574999332428</v>
+        <v>1.57575011253357</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G191" t="n">
-        <v>1.73774266242981</v>
+        <v>1.73774254322052</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G194" t="n">
-        <v>1.7671959400177</v>
+        <v>1.76719617843628</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.31608390808105</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91593515872955</v>
+        <v>1.91593539714813</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.41577696800232</v>
       </c>
       <c r="G198" t="n">
-        <v>1.99840450286865</v>
+        <v>1.99840474128723</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.35880899429321</v>
       </c>
       <c r="G201" t="n">
-        <v>1.95127868652344</v>
+        <v>1.95127892494202</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.13450002670288</v>
       </c>
       <c r="G202" t="n">
-        <v>1.76572334766388</v>
+        <v>1.76572346687317</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.27869892120361</v>
       </c>
       <c r="G203" t="n">
-        <v>1.88500905036926</v>
+        <v>1.88500928878784</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.15764307975769</v>
       </c>
       <c r="G204" t="n">
-        <v>1.78486824035645</v>
+        <v>1.78486812114716</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G205" t="n">
-        <v>1.7671959400177</v>
+        <v>1.76719617843628</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.16298294067383</v>
       </c>
       <c r="G208" t="n">
-        <v>1.78928530216217</v>
+        <v>1.78928542137146</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.10245609283447</v>
       </c>
       <c r="G209" t="n">
-        <v>1.73921597003937</v>
+        <v>1.73921585083008</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.12025809288025</v>
       </c>
       <c r="G210" t="n">
-        <v>1.75394213199615</v>
+        <v>1.75394225120544</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.059730052948</v>
       </c>
       <c r="G212" t="n">
-        <v>1.70387160778046</v>
+        <v>1.70387148857117</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.059730052948</v>
       </c>
       <c r="G213" t="n">
-        <v>1.70387160778046</v>
+        <v>1.70387148857117</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.11313700675964</v>
       </c>
       <c r="G214" t="n">
-        <v>1.74805152416229</v>
+        <v>1.748051404953</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.09711503982544</v>
       </c>
       <c r="G221" t="n">
-        <v>1.73479747772217</v>
+        <v>1.73479759693146</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.15408205986023</v>
       </c>
       <c r="G223" t="n">
-        <v>1.78192222118378</v>
+        <v>1.78192234039307</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.00454306602478</v>
       </c>
       <c r="G226" t="n">
-        <v>1.6582190990448</v>
+        <v>1.65821921825409</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.99030101299286</v>
       </c>
       <c r="G227" t="n">
-        <v>1.6464376449585</v>
+        <v>1.64643776416779</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.13806009292603</v>
       </c>
       <c r="G228" t="n">
-        <v>1.76866841316223</v>
+        <v>1.76866853237152</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G229" t="n">
-        <v>1.7642502784729</v>
+        <v>1.76425015926361</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G230" t="n">
-        <v>1.7642502784729</v>
+        <v>1.76425015926361</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.059730052948</v>
       </c>
       <c r="G231" t="n">
-        <v>1.70387160778046</v>
+        <v>1.70387148857117</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G243" t="n">
-        <v>1.7642502784729</v>
+        <v>1.76425015926361</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.15408205986023</v>
       </c>
       <c r="G244" t="n">
-        <v>1.78192222118378</v>
+        <v>1.78192234039307</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G245" t="n">
-        <v>1.7642502784729</v>
+        <v>1.76425015926361</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G246" t="n">
-        <v>1.73774266242981</v>
+        <v>1.73774254322052</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.0846529006958</v>
       </c>
       <c r="G248" t="n">
-        <v>1.72448861598969</v>
+        <v>1.7244884967804</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G250" t="n">
-        <v>1.7671959400177</v>
+        <v>1.76719617843628</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.45672202110291</v>
       </c>
       <c r="G254" t="n">
-        <v>2.03227519989014</v>
+        <v>2.03227543830872</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.34456706047058</v>
       </c>
       <c r="G257" t="n">
-        <v>1.93949711322784</v>
+        <v>1.93949735164642</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.74155902862549</v>
       </c>
       <c r="G258" t="n">
-        <v>2.26790142059326</v>
+        <v>2.26790118217468</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.93738508224487</v>
       </c>
       <c r="G259" t="n">
-        <v>2.42989468574524</v>
+        <v>2.42989444732666</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.79318594932556</v>
       </c>
       <c r="G260" t="n">
-        <v>2.31060862541199</v>
+        <v>2.31060886383057</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.23824501037598</v>
       </c>
       <c r="G262" t="n">
-        <v>2.6787748336792</v>
+        <v>2.67877507209778</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.35445117950439</v>
       </c>
       <c r="G266" t="n">
-        <v>3.60213494300842</v>
+        <v>3.60213470458984</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>4.3793740272522</v>
       </c>
       <c r="G269" t="n">
-        <v>3.62275171279907</v>
+        <v>3.62275195121765</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.16574621200562</v>
       </c>
       <c r="G270" t="n">
-        <v>3.44603204727173</v>
+        <v>3.44603228569031</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.42210006713867</v>
       </c>
       <c r="G274" t="n">
-        <v>3.65809631347656</v>
+        <v>3.65809607505798</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.3241868019104</v>
       </c>
       <c r="G275" t="n">
-        <v>3.57709932327271</v>
+        <v>3.57709908485413</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25475788116455</v>
       </c>
       <c r="G278" t="n">
-        <v>3.51966547966003</v>
+        <v>3.51966571807861</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.35979223251343</v>
       </c>
       <c r="G280" t="n">
-        <v>3.60655307769775</v>
+        <v>3.60655283927917</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G281" t="n">
-        <v>3.49315762519836</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.3241868019104</v>
       </c>
       <c r="G282" t="n">
-        <v>3.57709932327271</v>
+        <v>3.57709908485413</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.32596683502197</v>
       </c>
       <c r="G283" t="n">
-        <v>3.57857155799866</v>
+        <v>3.57857179641724</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.32774782180786</v>
       </c>
       <c r="G284" t="n">
-        <v>3.58004522323608</v>
+        <v>3.5800449848175</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>4.11233901977539</v>
       </c>
       <c r="G285" t="n">
-        <v>3.40185189247131</v>
+        <v>3.40185236930847</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.07495403289795</v>
       </c>
       <c r="G286" t="n">
-        <v>3.37092614173889</v>
+        <v>3.37092638015747</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.94677805900574</v>
       </c>
       <c r="G287" t="n">
-        <v>3.26489520072937</v>
+        <v>3.26489496231079</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G293" t="n">
-        <v>3.38712549209595</v>
+        <v>3.38712573051453</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.04113006591797</v>
       </c>
       <c r="G299" t="n">
-        <v>3.34294605255127</v>
+        <v>3.34294581413269</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G300" t="n">
-        <v>3.38712549209595</v>
+        <v>3.38712573051453</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.65303897857666</v>
       </c>
       <c r="G318" t="n">
-        <v>3.02190518379211</v>
+        <v>3.02190542221069</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.94904899597168</v>
       </c>
       <c r="G325" t="n">
-        <v>4.09400367736816</v>
+        <v>4.09400415420532</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G327" t="n">
-        <v>3.5343918800354</v>
+        <v>3.53439235687256</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.21381282806396</v>
       </c>
       <c r="G329" t="n">
-        <v>3.48579478263855</v>
+        <v>3.48579430580139</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.32596683502197</v>
       </c>
       <c r="G330" t="n">
-        <v>3.57857155799866</v>
+        <v>3.57857179641724</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G331" t="n">
-        <v>3.24575042724609</v>
+        <v>3.24575066566467</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.92185401916504</v>
       </c>
       <c r="G343" t="n">
-        <v>3.24427723884583</v>
+        <v>3.2442774772644</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.79189705848694</v>
       </c>
       <c r="G347" t="n">
-        <v>3.13677287101746</v>
+        <v>3.13677310943604</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G348" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G349" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.70822596549988</v>
       </c>
       <c r="G351" t="n">
-        <v>3.06755757331848</v>
+        <v>3.0675573348999</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G352" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G353" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G354" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.83462309837341</v>
       </c>
       <c r="G355" t="n">
-        <v>3.17211699485779</v>
+        <v>3.17211675643921</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.82750201225281</v>
       </c>
       <c r="G356" t="n">
-        <v>3.16622638702393</v>
+        <v>3.1662266254425</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.80970001220703</v>
       </c>
       <c r="G357" t="n">
-        <v>3.15149998664856</v>
+        <v>3.15150022506714</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.95211791992188</v>
       </c>
       <c r="G359" t="n">
-        <v>3.26931238174438</v>
+        <v>3.26931262016296</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.79189705848694</v>
       </c>
       <c r="G360" t="n">
-        <v>3.13677287101746</v>
+        <v>3.13677310943604</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.79189705848694</v>
       </c>
       <c r="G361" t="n">
-        <v>3.13677287101746</v>
+        <v>3.13677310943604</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.87200808525085</v>
       </c>
       <c r="G362" t="n">
-        <v>3.20304346084595</v>
+        <v>3.20304322242737</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G363" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.82750201225281</v>
       </c>
       <c r="G364" t="n">
-        <v>3.16622638702393</v>
+        <v>3.1662266254425</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.78299593925476</v>
       </c>
       <c r="G365" t="n">
-        <v>3.12940955162048</v>
+        <v>3.12940979003906</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.81682109832764</v>
       </c>
       <c r="G366" t="n">
-        <v>3.15739107131958</v>
+        <v>3.157390832901</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.8114800453186</v>
       </c>
       <c r="G372" t="n">
-        <v>3.15297245979309</v>
+        <v>3.15297269821167</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G373" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.72068810462952</v>
       </c>
       <c r="G374" t="n">
-        <v>3.07786679267883</v>
+        <v>3.07786655426025</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.60675311088562</v>
       </c>
       <c r="G376" t="n">
-        <v>2.9836163520813</v>
+        <v>2.98361611366272</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.60675311088562</v>
       </c>
       <c r="G378" t="n">
-        <v>2.9836163520813</v>
+        <v>2.98361611366272</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.58183002471924</v>
       </c>
       <c r="G379" t="n">
-        <v>2.96299910545349</v>
+        <v>2.96299886703491</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.49459791183472</v>
       </c>
       <c r="G386" t="n">
-        <v>2.89083814620972</v>
+        <v>2.89083790779114</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.45187306404114</v>
       </c>
       <c r="G388" t="n">
-        <v>2.85549449920654</v>
+        <v>2.85549473762512</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.48925805091858</v>
       </c>
       <c r="G391" t="n">
-        <v>2.88642072677612</v>
+        <v>2.8864209651947</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.50349903106689</v>
       </c>
       <c r="G394" t="n">
-        <v>2.89820122718811</v>
+        <v>2.89820098876953</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.804358959198</v>
       </c>
       <c r="G405" t="n">
-        <v>3.14708209037781</v>
+        <v>3.14708185195923</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.65838003158569</v>
       </c>
       <c r="G409" t="n">
-        <v>3.02632355690002</v>
+        <v>3.0263237953186</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G414" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G415" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>3.57826900482178</v>
       </c>
       <c r="G420" t="n">
-        <v>2.96005344390869</v>
+        <v>2.96005320549011</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G423" t="n">
-        <v>2.98950672149658</v>
+        <v>2.98950695991516</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.57292890548706</v>
       </c>
       <c r="G424" t="n">
-        <v>2.95563578605652</v>
+        <v>2.95563554763794</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.55690598487854</v>
       </c>
       <c r="G426" t="n">
-        <v>2.94238114356995</v>
+        <v>2.94238090515137</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.55690598487854</v>
       </c>
       <c r="G427" t="n">
-        <v>2.94238114356995</v>
+        <v>2.94238090515137</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G428" t="n">
-        <v>2.90114712715149</v>
+        <v>2.90114736557007</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G429" t="n">
-        <v>2.90114712715149</v>
+        <v>2.90114736557007</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.47323489189148</v>
       </c>
       <c r="G432" t="n">
-        <v>2.87316584587097</v>
+        <v>2.87316608428955</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.49281811714172</v>
       </c>
       <c r="G433" t="n">
-        <v>2.88936543464661</v>
+        <v>2.88936567306519</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.4394109249115</v>
       </c>
       <c r="G435" t="n">
-        <v>2.84518599510193</v>
+        <v>2.84518551826477</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.43407011032104</v>
       </c>
       <c r="G442" t="n">
-        <v>2.84076738357544</v>
+        <v>2.84076762199402</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G446" t="n">
-        <v>2.7965874671936</v>
+        <v>2.79658770561218</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G447" t="n">
-        <v>2.7965874671936</v>
+        <v>2.79658770561218</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.33971810340881</v>
       </c>
       <c r="G448" t="n">
-        <v>2.76271653175354</v>
+        <v>2.76271677017212</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.24714589118958</v>
       </c>
       <c r="G450" t="n">
-        <v>2.68613815307617</v>
+        <v>2.68613839149475</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G454" t="n">
-        <v>2.7965874671936</v>
+        <v>2.79658770561218</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.27919006347656</v>
       </c>
       <c r="G456" t="n">
-        <v>2.71264624595642</v>
+        <v>2.71264600753784</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G459" t="n">
-        <v>2.73915362358093</v>
+        <v>2.73915386199951</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G460" t="n">
-        <v>2.73915362358093</v>
+        <v>2.73915386199951</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73915362358093</v>
+        <v>2.73915386199951</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.24714589118958</v>
       </c>
       <c r="G462" t="n">
-        <v>2.68613815307617</v>
+        <v>2.68613839149475</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.08158397674561</v>
       </c>
       <c r="G464" t="n">
-        <v>2.54918026924133</v>
+        <v>2.54918003082275</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G465" t="n">
-        <v>2.73915362358093</v>
+        <v>2.73915386199951</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.20798110961914</v>
       </c>
       <c r="G466" t="n">
-        <v>2.65373969078064</v>
+        <v>2.65373992919922</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.21510195732117</v>
       </c>
       <c r="G468" t="n">
-        <v>2.65963053703308</v>
+        <v>2.6596302986145</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.20798110961914</v>
       </c>
       <c r="G469" t="n">
-        <v>2.65373969078064</v>
+        <v>2.65373992919922</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.19373893737793</v>
       </c>
       <c r="G472" t="n">
-        <v>2.64195823669434</v>
+        <v>2.64195799827576</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.29343199729919</v>
       </c>
       <c r="G473" t="n">
-        <v>2.72442746162415</v>
+        <v>2.72442770004272</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.074462890625</v>
       </c>
       <c r="G480" t="n">
-        <v>2.54328942298889</v>
+        <v>2.54328966140747</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.15101289749146</v>
       </c>
       <c r="G481" t="n">
-        <v>2.60661387443542</v>
+        <v>2.606614112854</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.02105593681335</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49910950660706</v>
+        <v>2.49910974502563</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.02105593681335</v>
       </c>
       <c r="G484" t="n">
-        <v>2.49910950660706</v>
+        <v>2.49910974502563</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.90712094306946</v>
       </c>
       <c r="G485" t="n">
-        <v>2.40485882759094</v>
+        <v>2.40485906600952</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G488" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.02639698982239</v>
       </c>
       <c r="G491" t="n">
-        <v>2.50352787971497</v>
+        <v>2.50352764129639</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.02639698982239</v>
       </c>
       <c r="G492" t="n">
-        <v>2.50352787971497</v>
+        <v>2.50352764129639</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.93738508224487</v>
       </c>
       <c r="G493" t="n">
-        <v>2.42989468574524</v>
+        <v>2.42989444732666</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G495" t="n">
-        <v>2.35920643806458</v>
+        <v>2.35920691490173</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G496" t="n">
-        <v>2.35920643806458</v>
+        <v>2.35920691490173</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G497" t="n">
-        <v>2.35920643806458</v>
+        <v>2.35920691490173</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.95518708229065</v>
       </c>
       <c r="G501" t="n">
-        <v>2.44462084770203</v>
+        <v>2.44462060928345</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G518" t="n">
-        <v>2.64713764190674</v>
+        <v>2.64713740348816</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G520" t="n">
-        <v>2.46101069450378</v>
+        <v>2.46101093292236</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G522" t="n">
-        <v>2.31624507904053</v>
+        <v>2.31624555587769</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.19216108322144</v>
+        <v>2.19216084480286</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G525" t="n">
-        <v>2.13011860847473</v>
+        <v>2.13011837005615</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G529" t="n">
-        <v>2.00603413581848</v>
+        <v>2.0060338973999</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G531" t="n">
-        <v>1.86540484428406</v>
+        <v>1.86540472507477</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>1.82817935943604</v>
+        <v>1.82817947864532</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G533" t="n">
-        <v>1.84886026382446</v>
+        <v>1.84886002540588</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G537" t="n">
-        <v>1.74545621871948</v>
+        <v>1.74545609951019</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G539" t="n">
-        <v>1.7495926618576</v>
+        <v>1.74959254264832</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G541" t="n">
-        <v>1.6792778968811</v>
+        <v>1.67927801609039</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G547" t="n">
-        <v>1.774409532547</v>
+        <v>1.77440941333771</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G548" t="n">
-        <v>1.74545621871948</v>
+        <v>1.74545609951019</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G549" t="n">
-        <v>1.73718416690826</v>
+        <v>1.73718404769897</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G551" t="n">
-        <v>1.774409532547</v>
+        <v>1.77440941333771</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G554" t="n">
-        <v>1.73304796218872</v>
+        <v>1.73304784297943</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>1.774409532547</v>
+        <v>1.77440941333771</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G560" t="n">
-        <v>1.79509043693542</v>
+        <v>1.79509031772614</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G562" t="n">
-        <v>1.83645188808441</v>
+        <v>1.83645164966583</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G563" t="n">
-        <v>1.75372838973999</v>
+        <v>1.75372850894928</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G565" t="n">
-        <v>1.774409532547</v>
+        <v>1.77440941333771</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G566" t="n">
-        <v>1.73718416690826</v>
+        <v>1.73718404769897</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G568" t="n">
-        <v>1.74545621871948</v>
+        <v>1.74545609951019</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G571" t="n">
-        <v>1.79509043693542</v>
+        <v>1.79509031772614</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G572" t="n">
-        <v>1.74545621871948</v>
+        <v>1.74545609951019</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G573" t="n">
-        <v>1.73304796218872</v>
+        <v>1.73304784297943</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G574" t="n">
-        <v>1.774409532547</v>
+        <v>1.77440941333771</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>1.7992262840271</v>
+        <v>1.79922640323639</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G578" t="n">
-        <v>1.84886026382446</v>
+        <v>1.84886002540588</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G579" t="n">
-        <v>1.9191746711731</v>
+        <v>1.91917490959167</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G581" t="n">
-        <v>2.00189805030823</v>
+        <v>2.00189781188965</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G582" t="n">
-        <v>2.00603413581848</v>
+        <v>2.0060338973999</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.73749995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.26454329490662</v>
+        <v>2.2645435333252</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.53749990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>2.09909725189209</v>
+        <v>2.09909749031067</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.31624507904053</v>
+        <v>2.31624555587769</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>2.31624507904053</v>
+        <v>2.31624555587769</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.78749990463257</v>
       </c>
       <c r="G593" t="n">
-        <v>2.30590510368347</v>
+        <v>2.30590486526489</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.63750004768372</v>
       </c>
       <c r="G596" t="n">
-        <v>2.18182039260864</v>
+        <v>2.18182063102722</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>2.19216108322144</v>
+        <v>2.19216084480286</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.63750004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>2.18182039260864</v>
+        <v>2.18182063102722</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.71250009536743</v>
       </c>
       <c r="G600" t="n">
-        <v>2.24386310577393</v>
+        <v>2.24386286735535</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>2.19216108322144</v>
+        <v>2.19216084480286</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G604" t="n">
-        <v>2.150799036026</v>
+        <v>2.15079927444458</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G607" t="n">
-        <v>2.03498673439026</v>
+        <v>2.03498697280884</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>2.00189805030823</v>
+        <v>2.00189781188965</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G611" t="n">
-        <v>2.00603413581848</v>
+        <v>2.0060338973999</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>1.92744708061218</v>
+        <v>1.9274468421936</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G614" t="n">
-        <v>1.86540484428406</v>
+        <v>1.86540472507477</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>1.84472417831421</v>
+        <v>1.84472393989563</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G616" t="n">
-        <v>1.9191746711731</v>
+        <v>1.91917490959167</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G617" t="n">
-        <v>2.00189805030823</v>
+        <v>2.00189781188965</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G618" t="n">
-        <v>1.96880853176117</v>
+        <v>1.96880877017975</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G621" t="n">
-        <v>1.94812786579132</v>
+        <v>1.94812762737274</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G622" t="n">
-        <v>1.86540484428406</v>
+        <v>1.86540472507477</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G624" t="n">
-        <v>1.9191746711731</v>
+        <v>1.91917490959167</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G634" t="n">
-        <v>1.83645188808441</v>
+        <v>1.83645164966583</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G638" t="n">
-        <v>1.84886026382446</v>
+        <v>1.84886002540588</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G641" t="n">
-        <v>1.78681814670563</v>
+        <v>1.78681790828705</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G643" t="n">
-        <v>1.7992262840271</v>
+        <v>1.79922640323639</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G645" t="n">
-        <v>1.78681814670563</v>
+        <v>1.78681790828705</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>1.774409532547</v>
+        <v>1.77440941333771</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G647" t="n">
-        <v>1.80749845504761</v>
+        <v>1.80749869346619</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G648" t="n">
-        <v>1.73718416690826</v>
+        <v>1.73718404769897</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.75372838973999</v>
+        <v>1.75372850894928</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G651" t="n">
-        <v>1.78268182277679</v>
+        <v>1.7826817035675</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>1.79509043693542</v>
+        <v>1.79509031772614</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G655" t="n">
-        <v>1.79591751098633</v>
+        <v>1.79591739177704</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G656" t="n">
-        <v>1.80998039245605</v>
+        <v>1.80998027324677</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G657" t="n">
-        <v>1.85134172439575</v>
+        <v>1.85134196281433</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G660" t="n">
-        <v>1.79839897155762</v>
+        <v>1.79839932918549</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.20650005340576</v>
       </c>
       <c r="G662" t="n">
-        <v>1.82528436183929</v>
+        <v>1.82528424263</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>1.7992262840271</v>
+        <v>1.79922640323639</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.17650008201599</v>
       </c>
       <c r="G664" t="n">
-        <v>1.80046725273132</v>
+        <v>1.80046713352203</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G668" t="n">
-        <v>1.83645188808441</v>
+        <v>1.83645164966583</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G671" t="n">
-        <v>1.77192759513855</v>
+        <v>1.77192771434784</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G672" t="n">
-        <v>1.75372838973999</v>
+        <v>1.75372850894928</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>1.69168651103973</v>
+        <v>1.69168639183044</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G676" t="n">
-        <v>1.68920469284058</v>
+        <v>1.68920457363129</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G677" t="n">
-        <v>1.57008349895477</v>
+        <v>1.57008337974548</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G681" t="n">
-        <v>1.41042804718018</v>
+        <v>1.41042792797089</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.75960004329681</v>
       </c>
       <c r="G683" t="n">
-        <v>1.4555948972702</v>
+        <v>1.45559477806091</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.72140002250671</v>
       </c>
       <c r="G686" t="n">
-        <v>1.42399477958679</v>
+        <v>1.4239946603775</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>1.47247016429901</v>
+        <v>1.4724702835083</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.73459994792938</v>
       </c>
       <c r="G691" t="n">
-        <v>1.43491411209106</v>
+        <v>1.43491399288177</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G693" t="n">
-        <v>1.42283642292023</v>
+        <v>1.42283630371094</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>1.73539996147156</v>
       </c>
       <c r="G695" t="n">
-        <v>1.43557596206665</v>
+        <v>1.43557584285736</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G696" t="n">
-        <v>1.4253181219101</v>
+        <v>1.42531824111938</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G697" t="n">
-        <v>1.4253181219101</v>
+        <v>1.42531824111938</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G698" t="n">
-        <v>1.41952764987946</v>
+        <v>1.41952753067017</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>1.72440004348755</v>
       </c>
       <c r="G699" t="n">
-        <v>1.42647635936737</v>
+        <v>1.42647624015808</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1.74479997158051</v>
       </c>
       <c r="G700" t="n">
-        <v>1.44335174560547</v>
+        <v>1.44335186481476</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G706" t="n">
-        <v>1.41952764987946</v>
+        <v>1.41952753067017</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.71539998054504</v>
       </c>
       <c r="G707" t="n">
-        <v>1.41903102397919</v>
+        <v>1.41903114318848</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G709" t="n">
-        <v>1.37320268154144</v>
+        <v>1.37320256233215</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G710" t="n">
-        <v>1.35665786266327</v>
+        <v>1.35665810108185</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.66460001468658</v>
       </c>
       <c r="G711" t="n">
-        <v>1.37700796127319</v>
+        <v>1.3770078420639</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.72019994258881</v>
       </c>
       <c r="G712" t="n">
-        <v>1.42300188541412</v>
+        <v>1.42300200462341</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G713" t="n">
-        <v>1.45592570304871</v>
+        <v>1.45592558383942</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.83959996700287</v>
       </c>
       <c r="G714" t="n">
-        <v>1.52177309989929</v>
+        <v>1.52177321910858</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.73459994792938</v>
       </c>
       <c r="G717" t="n">
-        <v>1.43491411209106</v>
+        <v>1.43491399288177</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.72979998588562</v>
       </c>
       <c r="G718" t="n">
-        <v>1.43094336986542</v>
+        <v>1.43094325065613</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G719" t="n">
-        <v>1.43028140068054</v>
+        <v>1.43028151988983</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.73539996147156</v>
       </c>
       <c r="G720" t="n">
-        <v>1.43557596206665</v>
+        <v>1.43557584285736</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G728" t="n">
-        <v>1.51383185386658</v>
+        <v>1.51383173465729</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G733" t="n">
-        <v>1.51383185386658</v>
+        <v>1.51383173465729</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.7985999584198</v>
       </c>
       <c r="G734" t="n">
-        <v>1.48785662651062</v>
+        <v>1.48785674571991</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>1.48074245452881</v>
+        <v>1.4807425737381</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.84179997444153</v>
       </c>
       <c r="G738" t="n">
-        <v>1.52359306812286</v>
+        <v>1.52359294891357</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G739" t="n">
-        <v>1.48884952068329</v>
+        <v>1.488849401474</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G740" t="n">
-        <v>1.46419811248779</v>
+        <v>1.4641979932785</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>1.48074245452881</v>
+        <v>1.4807425737381</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.77240002155304</v>
       </c>
       <c r="G742" t="n">
-        <v>1.46618342399597</v>
+        <v>1.46618330478668</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G743" t="n">
-        <v>1.48156976699829</v>
+        <v>1.48156988620758</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.78120005130768</v>
       </c>
       <c r="G748" t="n">
-        <v>1.47346305847168</v>
+        <v>1.47346293926239</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G749" t="n">
-        <v>1.48156976699829</v>
+        <v>1.48156988620758</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G752" t="n">
-        <v>1.48884952068329</v>
+        <v>1.488849401474</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.88940000534058</v>
       </c>
       <c r="G756" t="n">
-        <v>1.56296944618225</v>
+        <v>1.56296932697296</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.90240001678467</v>
       </c>
       <c r="G757" t="n">
-        <v>1.64630568027496</v>
+        <v>1.64630579948425</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>1.67884421348572</v>
+        <v>1.67884409427643</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.95819997787476</v>
       </c>
       <c r="G764" t="n">
-        <v>1.69459402561188</v>
+        <v>1.69459414482117</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>1.69615185260773</v>
+        <v>1.69615197181702</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.94760000705719</v>
       </c>
       <c r="G770" t="n">
-        <v>1.68542110919952</v>
+        <v>1.68542098999023</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.89979994297028</v>
       </c>
       <c r="G773" t="n">
-        <v>1.64405572414398</v>
+        <v>1.64405560493469</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G775" t="n">
-        <v>1.67884421348572</v>
+        <v>1.67884409427643</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>1.95819997787476</v>
       </c>
       <c r="G777" t="n">
-        <v>1.69459402561188</v>
+        <v>1.69459414482117</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>1.69615185260773</v>
+        <v>1.69615197181702</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.95959997177124</v>
       </c>
       <c r="G781" t="n">
-        <v>1.69580566883087</v>
+        <v>1.69580554962158</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G782" t="n">
-        <v>1.68126726150513</v>
+        <v>1.68126714229584</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G783" t="n">
-        <v>1.68126726150513</v>
+        <v>1.68126714229584</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G786" t="n">
-        <v>1.68749785423279</v>
+        <v>1.68749797344208</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.90859997272491</v>
       </c>
       <c r="G787" t="n">
-        <v>1.65167105197906</v>
+        <v>1.65167117118835</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G788" t="n">
-        <v>1.68126726150513</v>
+        <v>1.68126714229584</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G789" t="n">
-        <v>1.66759419441223</v>
+        <v>1.66759407520294</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.89859998226166</v>
       </c>
       <c r="G790" t="n">
-        <v>1.64301717281342</v>
+        <v>1.64301729202271</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.89979994297028</v>
       </c>
       <c r="G791" t="n">
-        <v>1.64405572414398</v>
+        <v>1.64405560493469</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G797" t="n">
-        <v>1.5983635187149</v>
+        <v>1.59836363792419</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.89979994297028</v>
       </c>
       <c r="G801" t="n">
-        <v>1.64405572414398</v>
+        <v>1.64405560493469</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G806" t="n">
-        <v>1.59230601787567</v>
+        <v>1.59230589866638</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G812" t="n">
-        <v>1.60095965862274</v>
+        <v>1.60095977783203</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G815" t="n">
-        <v>1.54211354255676</v>
+        <v>1.54211342334747</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G816" t="n">
-        <v>1.50144052505493</v>
+        <v>1.50144040584564</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G817" t="n">
-        <v>1.50144052505493</v>
+        <v>1.50144040584564</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.75</v>
       </c>
       <c r="G822" t="n">
-        <v>1.51442122459412</v>
+        <v>1.51442134380341</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G825" t="n">
-        <v>1.50576758384705</v>
+        <v>1.50576746463776</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.72560000419617</v>
       </c>
       <c r="G826" t="n">
-        <v>1.49330592155457</v>
+        <v>1.49330604076385</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G830" t="n">
-        <v>1.50144052505493</v>
+        <v>1.50144040584564</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.75</v>
       </c>
       <c r="G837" t="n">
-        <v>1.51442122459412</v>
+        <v>1.51442134380341</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G842" t="n">
-        <v>1.44519066810608</v>
+        <v>1.44519054889679</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G843" t="n">
-        <v>1.44519066810608</v>
+        <v>1.44519054889679</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G849" t="n">
-        <v>1.45817136764526</v>
+        <v>1.45817124843597</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G853" t="n">
-        <v>1.44519066810608</v>
+        <v>1.44519054889679</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G854" t="n">
-        <v>1.43653678894043</v>
+        <v>1.43653666973114</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G857" t="n">
-        <v>1.36730599403381</v>
+        <v>1.3673061132431</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G859" t="n">
-        <v>1.43653678894043</v>
+        <v>1.43653666973114</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G862" t="n">
-        <v>1.43653678894043</v>
+        <v>1.43653666973114</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G865" t="n">
-        <v>1.41922891139984</v>
+        <v>1.41922903060913</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G866" t="n">
-        <v>1.41922891139984</v>
+        <v>1.41922903060913</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G867" t="n">
-        <v>1.43653678894043</v>
+        <v>1.43653666973114</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G873" t="n">
-        <v>1.41922891139984</v>
+        <v>1.41922903060913</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G874" t="n">
-        <v>1.4149022102356</v>
+        <v>1.41490209102631</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>1.33269059658051</v>
+        <v>1.33269071578979</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G877" t="n">
-        <v>1.3846138715744</v>
+        <v>1.38461375236511</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G883" t="n">
-        <v>1.3846138715744</v>
+        <v>1.38461375236511</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G884" t="n">
-        <v>1.3846138715744</v>
+        <v>1.38461375236511</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G886" t="n">
-        <v>1.3846138715744</v>
+        <v>1.38461375236511</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G887" t="n">
-        <v>1.37163305282593</v>
+        <v>1.37163293361664</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>1.3499983549118</v>
+        <v>1.34999823570251</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>1.33269059658051</v>
+        <v>1.33269071578979</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31105613708496</v>
+        <v>1.31105601787567</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>3.0699999332428</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>17042</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -551,7 +551,7 @@
         <v>4.84223508834839</v>
       </c>
       <c r="G7" t="n">
-        <v>4.00564432144165</v>
+        <v>4.00564384460449</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.80663108825684</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9761917591095</v>
+        <v>3.97619152069092</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.81019115447998</v>
       </c>
       <c r="G9" t="n">
-        <v>3.97913694381714</v>
+        <v>3.97913646697998</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G12" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G15" t="n">
-        <v>3.09259295463562</v>
+        <v>3.0925931930542</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.53959512710571</v>
       </c>
       <c r="G23" t="n">
-        <v>3.755291223526</v>
+        <v>3.75529170036316</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.19957113265991</v>
       </c>
       <c r="G25" t="n">
-        <v>3.47401332855225</v>
+        <v>3.47401309013367</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.53959512710571</v>
       </c>
       <c r="G26" t="n">
-        <v>3.755291223526</v>
+        <v>3.75529170036316</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.52891397476196</v>
       </c>
       <c r="G27" t="n">
-        <v>3.74645566940308</v>
+        <v>3.74645614624023</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G30" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638586044312</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G31" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638586044312</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G32" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638586044312</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G33" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638586044312</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G34" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638586044312</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G35" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638586044312</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G36" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638586044312</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G37" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638586044312</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.03222894668579</v>
       </c>
       <c r="G40" t="n">
-        <v>3.3355827331543</v>
+        <v>3.33558297157288</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.08563613891602</v>
       </c>
       <c r="G41" t="n">
-        <v>3.37976264953613</v>
+        <v>3.37976288795471</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.30816507339478</v>
       </c>
       <c r="G42" t="n">
-        <v>3.56384563446045</v>
+        <v>3.56384539604187</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G43" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.40785789489746</v>
       </c>
       <c r="G45" t="n">
-        <v>3.64631462097168</v>
+        <v>3.6463143825531</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.40785789489746</v>
       </c>
       <c r="G46" t="n">
-        <v>3.64631462097168</v>
+        <v>3.6463143825531</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G47" t="n">
-        <v>3.49315786361694</v>
+        <v>3.49315762519836</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G48" t="n">
-        <v>3.49315786361694</v>
+        <v>3.49315762519836</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G49" t="n">
-        <v>3.49315786361694</v>
+        <v>3.49315762519836</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G50" t="n">
-        <v>3.49315786361694</v>
+        <v>3.49315762519836</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.21915292739868</v>
       </c>
       <c r="G59" t="n">
-        <v>3.49021196365356</v>
+        <v>3.49021220207214</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.21915292739868</v>
       </c>
       <c r="G60" t="n">
-        <v>3.49021196365356</v>
+        <v>3.49021220207214</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.08563613891602</v>
       </c>
       <c r="G62" t="n">
-        <v>3.37976264953613</v>
+        <v>3.37976288795471</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G63" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G64" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G65" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G66" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G67" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G68" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.85064506530762</v>
       </c>
       <c r="G70" t="n">
-        <v>3.1853711605072</v>
+        <v>3.18537139892578</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.04113006591797</v>
       </c>
       <c r="G71" t="n">
-        <v>3.34294581413269</v>
+        <v>3.34294605255127</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.04113006591797</v>
       </c>
       <c r="G72" t="n">
-        <v>3.34294581413269</v>
+        <v>3.34294605255127</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.91295289993286</v>
       </c>
       <c r="G73" t="n">
-        <v>3.23691415786743</v>
+        <v>3.23691391944885</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G76" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G77" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.16574621200562</v>
       </c>
       <c r="G83" t="n">
-        <v>3.44603228569031</v>
+        <v>3.44603204727173</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G84" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G85" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G86" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.9254150390625</v>
       </c>
       <c r="G89" t="n">
-        <v>3.24722290039062</v>
+        <v>3.2472231388092</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G93" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G94" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G95" t="n">
-        <v>3.09259295463562</v>
+        <v>3.0925931930542</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G96" t="n">
-        <v>3.09259295463562</v>
+        <v>3.0925931930542</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.41804790496826</v>
       </c>
       <c r="G99" t="n">
-        <v>2.82751369476318</v>
+        <v>2.8275134563446</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G111" t="n">
-        <v>2.90409231185913</v>
+        <v>2.90409183502197</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G114" t="n">
-        <v>2.90114736557007</v>
+        <v>2.90114712715149</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G115" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G119" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G120" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.20442008972168</v>
       </c>
       <c r="G121" t="n">
-        <v>2.65079402923584</v>
+        <v>2.65079426765442</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.95518708229065</v>
       </c>
       <c r="G127" t="n">
-        <v>2.44462060928345</v>
+        <v>2.44462084770203</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.40331506729126</v>
       </c>
       <c r="G134" t="n">
-        <v>1.98809552192688</v>
+        <v>1.9880952835083</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G135" t="n">
-        <v>1.76719617843628</v>
+        <v>1.76719605922699</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G136" t="n">
-        <v>1.76719617843628</v>
+        <v>1.76719605922699</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.04726791381836</v>
       </c>
       <c r="G137" t="n">
-        <v>1.69356250762939</v>
+        <v>1.6935623884201</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.86924505233765</v>
       </c>
       <c r="G138" t="n">
-        <v>1.54629647731781</v>
+        <v>1.5462965965271</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.41043591499329</v>
       </c>
       <c r="G140" t="n">
-        <v>1.99398624897003</v>
+        <v>1.99398601055145</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.25199508666992</v>
       </c>
       <c r="G141" t="n">
-        <v>1.86291897296906</v>
+        <v>1.86291921138763</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.17010402679443</v>
       </c>
       <c r="G142" t="n">
-        <v>1.7951762676239</v>
+        <v>1.79517614841461</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.23241305351257</v>
       </c>
       <c r="G143" t="n">
-        <v>1.84671998023987</v>
+        <v>1.84672021865845</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.07753205299377</v>
       </c>
       <c r="G146" t="n">
-        <v>1.71859800815582</v>
+        <v>1.71859788894653</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.21461009979248</v>
       </c>
       <c r="G147" t="n">
-        <v>1.83199298381805</v>
+        <v>1.83199310302734</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.21817088127136</v>
       </c>
       <c r="G148" t="n">
-        <v>1.83493864536285</v>
+        <v>1.83493852615356</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.28582000732422</v>
       </c>
       <c r="G150" t="n">
-        <v>1.89090013504028</v>
+        <v>1.89090001583099</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.28582000732422</v>
       </c>
       <c r="G151" t="n">
-        <v>1.89090013504028</v>
+        <v>1.89090001583099</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.28582000732422</v>
       </c>
       <c r="G152" t="n">
-        <v>1.89090013504028</v>
+        <v>1.89090001583099</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.97071802616119</v>
       </c>
       <c r="G153" t="n">
-        <v>1.63023817539215</v>
+        <v>1.63023805618286</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.01166391372681</v>
       </c>
       <c r="G155" t="n">
-        <v>1.66410970687866</v>
+        <v>1.66410982608795</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.09711503982544</v>
       </c>
       <c r="G156" t="n">
-        <v>1.73479759693146</v>
+        <v>1.73479747772217</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G159" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.97961902618408</v>
       </c>
       <c r="G162" t="n">
-        <v>1.63760125637054</v>
+        <v>1.63760113716125</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G163" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.94935500621796</v>
       </c>
       <c r="G164" t="n">
-        <v>1.61256575584412</v>
+        <v>1.61256587505341</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G165" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G166" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.86924505233765</v>
       </c>
       <c r="G170" t="n">
-        <v>1.54629647731781</v>
+        <v>1.5462965965271</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.86924505233765</v>
       </c>
       <c r="G171" t="n">
-        <v>1.54629647731781</v>
+        <v>1.5462965965271</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.83542001247406</v>
       </c>
       <c r="G172" t="n">
-        <v>1.51831543445587</v>
+        <v>1.51831531524658</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.83542001247406</v>
       </c>
       <c r="G173" t="n">
-        <v>1.51831543445587</v>
+        <v>1.51831531524658</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.83542001247406</v>
       </c>
       <c r="G174" t="n">
-        <v>1.51831543445587</v>
+        <v>1.51831531524658</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.13983988761902</v>
       </c>
       <c r="G176" t="n">
-        <v>1.77014076709747</v>
+        <v>1.77014088630676</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.17188501358032</v>
       </c>
       <c r="G177" t="n">
-        <v>1.79664969444275</v>
+        <v>1.79664957523346</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.11313700675964</v>
       </c>
       <c r="G178" t="n">
-        <v>1.748051404953</v>
+        <v>1.74805152416229</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.08287310600281</v>
       </c>
       <c r="G180" t="n">
-        <v>1.72301614284515</v>
+        <v>1.72301602363586</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.09177398681641</v>
       </c>
       <c r="G181" t="n">
-        <v>1.73037934303284</v>
+        <v>1.73037922382355</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.05082893371582</v>
       </c>
       <c r="G184" t="n">
-        <v>1.69650828838348</v>
+        <v>1.69650840759277</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.90485000610352</v>
       </c>
       <c r="G186" t="n">
-        <v>1.57575011253357</v>
+        <v>1.57574999332428</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.90485000610352</v>
       </c>
       <c r="G189" t="n">
-        <v>1.57575011253357</v>
+        <v>1.57574999332428</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.99386096000671</v>
       </c>
       <c r="G190" t="n">
-        <v>1.64938247203827</v>
+        <v>1.64938259124756</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G194" t="n">
-        <v>1.76719617843628</v>
+        <v>1.76719605922699</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.40331506729126</v>
       </c>
       <c r="G196" t="n">
-        <v>1.98809552192688</v>
+        <v>1.9880952835083</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.31608390808105</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91593539714813</v>
+        <v>1.91593515872955</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.41577696800232</v>
       </c>
       <c r="G198" t="n">
-        <v>1.99840474128723</v>
+        <v>1.99840450286865</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.52437090873718</v>
       </c>
       <c r="G199" t="n">
-        <v>2.0882363319397</v>
+        <v>2.08823657035828</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.35880899429321</v>
       </c>
       <c r="G201" t="n">
-        <v>1.95127892494202</v>
+        <v>1.95127868652344</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.27869892120361</v>
       </c>
       <c r="G203" t="n">
-        <v>1.88500928878784</v>
+        <v>1.88500905036926</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G205" t="n">
-        <v>1.76719617843628</v>
+        <v>1.76719605922699</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.14340090751648</v>
       </c>
       <c r="G207" t="n">
-        <v>1.77308654785156</v>
+        <v>1.77308666706085</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.16298294067383</v>
       </c>
       <c r="G208" t="n">
-        <v>1.78928542137146</v>
+        <v>1.78928554058075</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.12025809288025</v>
       </c>
       <c r="G210" t="n">
-        <v>1.75394225120544</v>
+        <v>1.75394201278687</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.09177398681641</v>
       </c>
       <c r="G211" t="n">
-        <v>1.73037934303284</v>
+        <v>1.73037922382355</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.11313700675964</v>
       </c>
       <c r="G214" t="n">
-        <v>1.748051404953</v>
+        <v>1.74805152416229</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.07397198677063</v>
       </c>
       <c r="G216" t="n">
-        <v>1.71565294265747</v>
+        <v>1.71565282344818</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.02412509918213</v>
       </c>
       <c r="G218" t="n">
-        <v>1.67441809177399</v>
+        <v>1.6744179725647</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.02412509918213</v>
       </c>
       <c r="G219" t="n">
-        <v>1.67441809177399</v>
+        <v>1.6744179725647</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.09711503982544</v>
       </c>
       <c r="G221" t="n">
-        <v>1.73479759693146</v>
+        <v>1.73479747772217</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.15052199363708</v>
       </c>
       <c r="G224" t="n">
-        <v>1.778977394104</v>
+        <v>1.77897727489471</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.13806009292603</v>
       </c>
       <c r="G228" t="n">
-        <v>1.76866853237152</v>
+        <v>1.76866841316223</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G229" t="n">
-        <v>1.76425015926361</v>
+        <v>1.7642502784729</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G230" t="n">
-        <v>1.76425015926361</v>
+        <v>1.7642502784729</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.01166391372681</v>
       </c>
       <c r="G232" t="n">
-        <v>1.66410970687866</v>
+        <v>1.66410982608795</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.01166391372681</v>
       </c>
       <c r="G233" t="n">
-        <v>1.66410970687866</v>
+        <v>1.66410982608795</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.01166391372681</v>
       </c>
       <c r="G234" t="n">
-        <v>1.66410970687866</v>
+        <v>1.66410982608795</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.97249805927277</v>
       </c>
       <c r="G235" t="n">
-        <v>1.63171052932739</v>
+        <v>1.63171064853668</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.04726791381836</v>
       </c>
       <c r="G236" t="n">
-        <v>1.69356250762939</v>
+        <v>1.6935623884201</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.04726791381836</v>
       </c>
       <c r="G237" t="n">
-        <v>1.69356250762939</v>
+        <v>1.6935623884201</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G238" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G239" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.07041096687317</v>
       </c>
       <c r="G240" t="n">
-        <v>1.7127069234848</v>
+        <v>1.71270704269409</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.07041096687317</v>
       </c>
       <c r="G241" t="n">
-        <v>1.7127069234848</v>
+        <v>1.71270704269409</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G243" t="n">
-        <v>1.76425015926361</v>
+        <v>1.7642502784729</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G245" t="n">
-        <v>1.76425015926361</v>
+        <v>1.7642502784729</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.04726791381836</v>
       </c>
       <c r="G249" t="n">
-        <v>1.69356250762939</v>
+        <v>1.6935623884201</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G250" t="n">
-        <v>1.76719617843628</v>
+        <v>1.76719605922699</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.03124594688416</v>
       </c>
       <c r="G251" t="n">
-        <v>1.68030846118927</v>
+        <v>1.68030858039856</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.36415004730225</v>
       </c>
       <c r="G255" t="n">
-        <v>1.95569694042206</v>
+        <v>1.95569717884064</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.34456706047058</v>
       </c>
       <c r="G257" t="n">
-        <v>1.93949735164642</v>
+        <v>1.939497590065</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.74155902862549</v>
       </c>
       <c r="G258" t="n">
-        <v>2.26790118217468</v>
+        <v>2.26790142059326</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.93738508224487</v>
       </c>
       <c r="G259" t="n">
-        <v>2.42989444732666</v>
+        <v>2.42989468574524</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.79318594932556</v>
       </c>
       <c r="G260" t="n">
-        <v>2.31060886383057</v>
+        <v>2.31060862541199</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.23824501037598</v>
       </c>
       <c r="G262" t="n">
-        <v>2.67877507209778</v>
+        <v>2.67877531051636</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G263" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>4.67133283615112</v>
       </c>
       <c r="G265" t="n">
-        <v>3.86426877975464</v>
+        <v>3.8642692565918</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>4.40073680877686</v>
       </c>
       <c r="G267" t="n">
-        <v>3.64042377471924</v>
+        <v>3.64042353630066</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>4.3793740272522</v>
       </c>
       <c r="G269" t="n">
-        <v>3.62275195121765</v>
+        <v>3.62275171279907</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.16574621200562</v>
       </c>
       <c r="G270" t="n">
-        <v>3.44603228569031</v>
+        <v>3.44603204727173</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.42210006713867</v>
       </c>
       <c r="G274" t="n">
-        <v>3.65809607505798</v>
+        <v>3.65809631347656</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.3241868019104</v>
       </c>
       <c r="G275" t="n">
-        <v>3.57709908485413</v>
+        <v>3.57709884643555</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.43278121948242</v>
       </c>
       <c r="G276" t="n">
-        <v>3.66693186759949</v>
+        <v>3.66693210601807</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.25653791427612</v>
       </c>
       <c r="G277" t="n">
-        <v>3.52113795280457</v>
+        <v>3.52113771438599</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25475788116455</v>
       </c>
       <c r="G278" t="n">
-        <v>3.51966571807861</v>
+        <v>3.51966547966003</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G281" t="n">
-        <v>3.49315786361694</v>
+        <v>3.49315762519836</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.3241868019104</v>
       </c>
       <c r="G282" t="n">
-        <v>3.57709908485413</v>
+        <v>3.57709884643555</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.07495403289795</v>
       </c>
       <c r="G286" t="n">
-        <v>3.37092638015747</v>
+        <v>3.37092614173889</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.94677805900574</v>
       </c>
       <c r="G287" t="n">
-        <v>3.26489496231079</v>
+        <v>3.26489520072937</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G290" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.75629305839539</v>
       </c>
       <c r="G291" t="n">
-        <v>3.10731983184814</v>
+        <v>3.10732007026672</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G295" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.04113006591797</v>
       </c>
       <c r="G299" t="n">
-        <v>3.34294581413269</v>
+        <v>3.34294605255127</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.99306392669678</v>
       </c>
       <c r="G301" t="n">
-        <v>3.30318427085876</v>
+        <v>3.30318403244019</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G302" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G303" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G304" t="n">
-        <v>3.18831562995911</v>
+        <v>3.18831610679626</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G305" t="n">
-        <v>3.18831562995911</v>
+        <v>3.18831610679626</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G306" t="n">
-        <v>3.18831562995911</v>
+        <v>3.18831610679626</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G307" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G309" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G311" t="n">
-        <v>3.18831562995911</v>
+        <v>3.18831610679626</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.69576501846313</v>
       </c>
       <c r="G314" t="n">
-        <v>3.05724954605103</v>
+        <v>3.05724930763245</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.65303897857666</v>
       </c>
       <c r="G318" t="n">
-        <v>3.02190542221069</v>
+        <v>3.02190518379211</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.56580805778503</v>
       </c>
       <c r="G322" t="n">
-        <v>2.94974517822266</v>
+        <v>2.94974541664124</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G327" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.21381282806396</v>
       </c>
       <c r="G329" t="n">
-        <v>3.48579430580139</v>
+        <v>3.48579478263855</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.79189705848694</v>
       </c>
       <c r="G347" t="n">
-        <v>3.13677310943604</v>
+        <v>3.13677287101746</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G348" t="n">
-        <v>3.09259295463562</v>
+        <v>3.0925931930542</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G349" t="n">
-        <v>3.09259295463562</v>
+        <v>3.0925931930542</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.70822596549988</v>
       </c>
       <c r="G351" t="n">
-        <v>3.0675573348999</v>
+        <v>3.06755781173706</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G352" t="n">
-        <v>3.09259295463562</v>
+        <v>3.0925931930542</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G353" t="n">
-        <v>3.09259295463562</v>
+        <v>3.0925931930542</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G354" t="n">
-        <v>3.09259295463562</v>
+        <v>3.0925931930542</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.83462309837341</v>
       </c>
       <c r="G355" t="n">
-        <v>3.17211675643921</v>
+        <v>3.17211723327637</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.80970001220703</v>
       </c>
       <c r="G357" t="n">
-        <v>3.15150022506714</v>
+        <v>3.15149998664856</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.79189705848694</v>
       </c>
       <c r="G360" t="n">
-        <v>3.13677310943604</v>
+        <v>3.13677287101746</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.79189705848694</v>
       </c>
       <c r="G361" t="n">
-        <v>3.13677310943604</v>
+        <v>3.13677287101746</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.87200808525085</v>
       </c>
       <c r="G362" t="n">
-        <v>3.20304322242737</v>
+        <v>3.20304346084595</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G363" t="n">
-        <v>3.09259295463562</v>
+        <v>3.0925931930542</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.81682109832764</v>
       </c>
       <c r="G366" t="n">
-        <v>3.157390832901</v>
+        <v>3.15739107131958</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.54800510406494</v>
       </c>
       <c r="G370" t="n">
-        <v>2.93501782417297</v>
+        <v>2.93501806259155</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.8114800453186</v>
       </c>
       <c r="G372" t="n">
-        <v>3.15297269821167</v>
+        <v>3.15297245979309</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G373" t="n">
-        <v>3.09259295463562</v>
+        <v>3.0925931930542</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.72068810462952</v>
       </c>
       <c r="G374" t="n">
-        <v>3.07786655426025</v>
+        <v>3.07786679267883</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G377" t="n">
-        <v>2.94827222824097</v>
+        <v>2.94827198982239</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.58183002471924</v>
       </c>
       <c r="G379" t="n">
-        <v>2.96299886703491</v>
+        <v>2.96299910545349</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.61565399169922</v>
       </c>
       <c r="G383" t="n">
-        <v>2.99097919464111</v>
+        <v>2.99097943305969</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.49459791183472</v>
       </c>
       <c r="G386" t="n">
-        <v>2.89083790779114</v>
+        <v>2.89083814620972</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.45187306404114</v>
       </c>
       <c r="G388" t="n">
-        <v>2.85549473762512</v>
+        <v>2.8554949760437</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.49815893173218</v>
       </c>
       <c r="G390" t="n">
-        <v>2.89378380775452</v>
+        <v>2.89378356933594</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.48925805091858</v>
       </c>
       <c r="G391" t="n">
-        <v>2.8864209651947</v>
+        <v>2.88642048835754</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.52486205101013</v>
       </c>
       <c r="G392" t="n">
-        <v>2.91587352752686</v>
+        <v>2.91587328910828</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G395" t="n">
-        <v>2.84224057197571</v>
+        <v>2.84224081039429</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G396" t="n">
-        <v>2.84224057197571</v>
+        <v>2.84224081039429</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G402" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.56580805778503</v>
       </c>
       <c r="G413" t="n">
-        <v>2.94974517822266</v>
+        <v>2.94974541664124</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G414" t="n">
-        <v>2.94679951667786</v>
+        <v>2.94679927825928</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G415" t="n">
-        <v>2.94679951667786</v>
+        <v>2.94679927825928</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G417" t="n">
-        <v>2.94827222824097</v>
+        <v>2.94827198982239</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G418" t="n">
-        <v>2.94827222824097</v>
+        <v>2.94827198982239</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.51418089866638</v>
       </c>
       <c r="G425" t="n">
-        <v>2.90703749656677</v>
+        <v>2.90703773498535</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.55690598487854</v>
       </c>
       <c r="G426" t="n">
-        <v>2.94238090515137</v>
+        <v>2.94238114356995</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.55690598487854</v>
       </c>
       <c r="G427" t="n">
-        <v>2.94238090515137</v>
+        <v>2.94238114356995</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G428" t="n">
-        <v>2.90114736557007</v>
+        <v>2.90114712715149</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G429" t="n">
-        <v>2.90114736557007</v>
+        <v>2.90114712715149</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G430" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.49281811714172</v>
       </c>
       <c r="G433" t="n">
-        <v>2.88936567306519</v>
+        <v>2.88936543464661</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G434" t="n">
-        <v>2.84224057197571</v>
+        <v>2.84224081039429</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.4394109249115</v>
       </c>
       <c r="G435" t="n">
-        <v>2.84518551826477</v>
+        <v>2.84518575668335</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.52486205101013</v>
       </c>
       <c r="G438" t="n">
-        <v>2.91587352752686</v>
+        <v>2.91587328910828</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.51418089866638</v>
       </c>
       <c r="G439" t="n">
-        <v>2.90703749656677</v>
+        <v>2.90703773498535</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.51418089866638</v>
       </c>
       <c r="G440" t="n">
-        <v>2.90703749656677</v>
+        <v>2.90703773498535</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.41092705726624</v>
       </c>
       <c r="G441" t="n">
-        <v>2.82162308692932</v>
+        <v>2.82162284851074</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G445" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G446" t="n">
-        <v>2.79658770561218</v>
+        <v>2.7965874671936</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G447" t="n">
-        <v>2.79658770561218</v>
+        <v>2.7965874671936</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3.33615708351135</v>
       </c>
       <c r="G449" t="n">
-        <v>2.75977087020874</v>
+        <v>2.75977110862732</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.24714589118958</v>
       </c>
       <c r="G450" t="n">
-        <v>2.68613839149475</v>
+        <v>2.68613791465759</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G452" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G453" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G454" t="n">
-        <v>2.79658770561218</v>
+        <v>2.7965874671936</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.27919006347656</v>
       </c>
       <c r="G456" t="n">
-        <v>2.71264600753784</v>
+        <v>2.71264624595642</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G457" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G458" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G459" t="n">
-        <v>2.73915386199951</v>
+        <v>2.73915362358093</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G460" t="n">
-        <v>2.73915386199951</v>
+        <v>2.73915362358093</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73915386199951</v>
+        <v>2.73915362358093</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.24714589118958</v>
       </c>
       <c r="G462" t="n">
-        <v>2.68613839149475</v>
+        <v>2.68613791465759</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.24536609649658</v>
       </c>
       <c r="G463" t="n">
-        <v>2.68466591835022</v>
+        <v>2.68466567993164</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.08158397674561</v>
       </c>
       <c r="G464" t="n">
-        <v>2.54918003082275</v>
+        <v>2.54918026924133</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G465" t="n">
-        <v>2.73915386199951</v>
+        <v>2.73915362358093</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.21510195732117</v>
       </c>
       <c r="G468" t="n">
-        <v>2.6596302986145</v>
+        <v>2.65963053703308</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.19373893737793</v>
       </c>
       <c r="G472" t="n">
-        <v>2.64195799827576</v>
+        <v>2.64195823669434</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.29343199729919</v>
       </c>
       <c r="G473" t="n">
-        <v>2.72442770004272</v>
+        <v>2.72442746162415</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.15457391738892</v>
       </c>
       <c r="G475" t="n">
-        <v>2.60955953598022</v>
+        <v>2.60956001281738</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.20442008972168</v>
       </c>
       <c r="G476" t="n">
-        <v>2.65079402923584</v>
+        <v>2.65079426765442</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>3.20442008972168</v>
       </c>
       <c r="G478" t="n">
-        <v>2.65079402923584</v>
+        <v>2.65079426765442</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.15101289749146</v>
       </c>
       <c r="G481" t="n">
-        <v>2.606614112854</v>
+        <v>2.60661387443542</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.02105593681335</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49910974502563</v>
+        <v>2.49910950660706</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.02105593681335</v>
       </c>
       <c r="G484" t="n">
-        <v>2.49910974502563</v>
+        <v>2.49910950660706</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>2.39896869659424</v>
+        <v>2.39896845817566</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>2.39896869659424</v>
+        <v>2.39896845817566</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G488" t="n">
-        <v>2.39896869659424</v>
+        <v>2.39896845817566</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.10828804969788</v>
       </c>
       <c r="G490" t="n">
-        <v>2.57127070426941</v>
+        <v>2.57127094268799</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.02639698982239</v>
       </c>
       <c r="G491" t="n">
-        <v>2.50352764129639</v>
+        <v>2.50352787971497</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.02639698982239</v>
       </c>
       <c r="G492" t="n">
-        <v>2.50352764129639</v>
+        <v>2.50352787971497</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.93738508224487</v>
       </c>
       <c r="G493" t="n">
-        <v>2.42989444732666</v>
+        <v>2.42989468574524</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G495" t="n">
-        <v>2.35920691490173</v>
+        <v>2.35920667648315</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G496" t="n">
-        <v>2.35920691490173</v>
+        <v>2.35920667648315</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G497" t="n">
-        <v>2.35920691490173</v>
+        <v>2.35920667648315</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.79496598243713</v>
       </c>
       <c r="G499" t="n">
-        <v>2.31208086013794</v>
+        <v>2.31208109855652</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.95518708229065</v>
       </c>
       <c r="G501" t="n">
-        <v>2.44462060928345</v>
+        <v>2.44462084770203</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.9195830821991</v>
       </c>
       <c r="G505" t="n">
-        <v>2.41516804695129</v>
+        <v>2.41516828536987</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>2.39896869659424</v>
+        <v>2.39896845817566</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.21250009536743</v>
       </c>
       <c r="G515" t="n">
-        <v>2.65747785568237</v>
+        <v>2.65747809410095</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G521" t="n">
-        <v>2.33692646026611</v>
+        <v>2.33692622184753</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G522" t="n">
-        <v>2.31624555587769</v>
+        <v>2.31624531745911</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.29556488990784</v>
+        <v>2.29556465148926</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.19216084480286</v>
+        <v>2.19216108322144</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G525" t="n">
-        <v>2.13011837005615</v>
+        <v>2.13011860847473</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G526" t="n">
-        <v>2.0473952293396</v>
+        <v>2.04739570617676</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.5625</v>
       </c>
       <c r="G527" t="n">
-        <v>2.1197783946991</v>
+        <v>2.11977815628052</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G531" t="n">
-        <v>1.86540472507477</v>
+        <v>1.86540508270264</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>1.82817947864532</v>
+        <v>1.82817959785461</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G533" t="n">
-        <v>1.84886002540588</v>
+        <v>1.84886014461517</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84058773517609</v>
+        <v>1.8405876159668</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G535" t="n">
-        <v>1.8157707452774</v>
+        <v>1.81577098369598</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G537" t="n">
-        <v>1.74545609951019</v>
+        <v>1.74545621871948</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G541" t="n">
-        <v>1.67927801609039</v>
+        <v>1.6792778968811</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G542" t="n">
-        <v>1.67514193058014</v>
+        <v>1.67514181137085</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G544" t="n">
-        <v>1.67514193058014</v>
+        <v>1.67514181137085</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G545" t="n">
-        <v>1.8157707452774</v>
+        <v>1.81577098369598</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G548" t="n">
-        <v>1.74545609951019</v>
+        <v>1.74545621871948</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G549" t="n">
-        <v>1.73718404769897</v>
+        <v>1.73718392848969</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.125</v>
       </c>
       <c r="G552" t="n">
-        <v>1.75786483287811</v>
+        <v>1.75786471366882</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G553" t="n">
-        <v>1.76613700389862</v>
+        <v>1.7661372423172</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G554" t="n">
-        <v>1.73304784297943</v>
+        <v>1.73304796218872</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G555" t="n">
-        <v>1.71650326251984</v>
+        <v>1.71650314331055</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G562" t="n">
-        <v>1.83645164966583</v>
+        <v>1.83645176887512</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G563" t="n">
-        <v>1.75372850894928</v>
+        <v>1.75372838973999</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G564" t="n">
-        <v>1.76613700389862</v>
+        <v>1.7661372423172</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G566" t="n">
-        <v>1.73718404769897</v>
+        <v>1.73718392848969</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.125</v>
       </c>
       <c r="G567" t="n">
-        <v>1.75786483287811</v>
+        <v>1.75786471366882</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G568" t="n">
-        <v>1.74545609951019</v>
+        <v>1.74545621871948</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G572" t="n">
-        <v>1.74545609951019</v>
+        <v>1.74545621871948</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G573" t="n">
-        <v>1.73304784297943</v>
+        <v>1.73304796218872</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>1.8943578004837</v>
+        <v>1.89435791969299</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G578" t="n">
-        <v>1.84886002540588</v>
+        <v>1.84886014461517</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G579" t="n">
-        <v>1.91917490959167</v>
+        <v>1.91917479038239</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G580" t="n">
-        <v>1.89022195339203</v>
+        <v>1.89022183418274</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.5</v>
       </c>
       <c r="G588" t="n">
-        <v>2.06807637214661</v>
+        <v>2.06807613372803</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.31624555587769</v>
+        <v>2.31624531745911</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>2.31624555587769</v>
+        <v>2.31624531745911</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.78749990463257</v>
       </c>
       <c r="G593" t="n">
-        <v>2.30590486526489</v>
+        <v>2.30590462684631</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.6875</v>
       </c>
       <c r="G594" t="n">
-        <v>2.2231822013855</v>
+        <v>2.22318196296692</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.6875</v>
       </c>
       <c r="G595" t="n">
-        <v>2.2231822013855</v>
+        <v>2.22318196296692</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.63750004768372</v>
       </c>
       <c r="G596" t="n">
-        <v>2.18182063102722</v>
+        <v>2.18182039260864</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.61249995231628</v>
       </c>
       <c r="G597" t="n">
-        <v>2.16113948822021</v>
+        <v>2.16113972663879</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>2.19216084480286</v>
+        <v>2.19216108322144</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.63750004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>2.18182063102722</v>
+        <v>2.18182039260864</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.6875</v>
       </c>
       <c r="G601" t="n">
-        <v>2.2231822013855</v>
+        <v>2.22318196296692</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>2.19216084480286</v>
+        <v>2.19216108322144</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.61249995231628</v>
       </c>
       <c r="G603" t="n">
-        <v>2.16113948822021</v>
+        <v>2.16113972663879</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G605" t="n">
-        <v>2.08875703811646</v>
+        <v>2.08875727653503</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G606" t="n">
-        <v>2.1094377040863</v>
+        <v>2.10943746566772</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G607" t="n">
-        <v>2.03498697280884</v>
+        <v>2.03498673439026</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>1.98535311222076</v>
+        <v>1.98535323143005</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G613" t="n">
-        <v>1.8943578004837</v>
+        <v>1.89435791969299</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G614" t="n">
-        <v>1.86540472507477</v>
+        <v>1.86540508270264</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G616" t="n">
-        <v>1.91917490959167</v>
+        <v>1.91917479038239</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G619" t="n">
-        <v>1.89022195339203</v>
+        <v>1.89022183418274</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G621" t="n">
-        <v>1.94812762737274</v>
+        <v>1.9481281042099</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G622" t="n">
-        <v>1.86540472507477</v>
+        <v>1.86540508270264</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G624" t="n">
-        <v>1.91917490959167</v>
+        <v>1.91917479038239</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>1.88608551025391</v>
+        <v>1.88608527183533</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.25</v>
       </c>
       <c r="G628" t="n">
-        <v>1.86126863956451</v>
+        <v>1.86126852035522</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.25</v>
       </c>
       <c r="G629" t="n">
-        <v>1.86126863956451</v>
+        <v>1.86126852035522</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.25</v>
       </c>
       <c r="G631" t="n">
-        <v>1.86126863956451</v>
+        <v>1.86126852035522</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>1.8943578004837</v>
+        <v>1.89435791969299</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G634" t="n">
-        <v>1.83645164966583</v>
+        <v>1.83645176887512</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>1.9109023809433</v>
+        <v>1.91090250015259</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G637" t="n">
-        <v>1.8778133392334</v>
+        <v>1.87781322002411</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G638" t="n">
-        <v>1.84886002540588</v>
+        <v>1.84886014461517</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G639" t="n">
-        <v>1.85299634933472</v>
+        <v>1.85299623012543</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G641" t="n">
-        <v>1.78681790828705</v>
+        <v>1.78681778907776</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G645" t="n">
-        <v>1.78681790828705</v>
+        <v>1.78681778907776</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G647" t="n">
-        <v>1.80749869346619</v>
+        <v>1.80749845504761</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G648" t="n">
-        <v>1.73718404769897</v>
+        <v>1.73718392848969</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.75372850894928</v>
+        <v>1.75372838973999</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.125</v>
       </c>
       <c r="G650" t="n">
-        <v>1.75786483287811</v>
+        <v>1.75786471366882</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G651" t="n">
-        <v>1.7826817035675</v>
+        <v>1.78268182277679</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.125</v>
       </c>
       <c r="G652" t="n">
-        <v>1.75786483287811</v>
+        <v>1.75786471366882</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G656" t="n">
-        <v>1.80998027324677</v>
+        <v>1.80998015403748</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G657" t="n">
-        <v>1.85134196281433</v>
+        <v>1.85134184360504</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G658" t="n">
-        <v>1.85299634933472</v>
+        <v>1.85299623012543</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G660" t="n">
-        <v>1.79839932918549</v>
+        <v>1.79839897155762</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.20650005340576</v>
       </c>
       <c r="G662" t="n">
-        <v>1.82528424263</v>
+        <v>1.82528400421143</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.17650008201599</v>
       </c>
       <c r="G664" t="n">
-        <v>1.80046713352203</v>
+        <v>1.80046725273132</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G666" t="n">
-        <v>1.83976078033447</v>
+        <v>1.83976066112518</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G667" t="n">
-        <v>1.83727884292603</v>
+        <v>1.83727896213531</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G668" t="n">
-        <v>1.83645164966583</v>
+        <v>1.83645176887512</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.18700003623962</v>
       </c>
       <c r="G670" t="n">
-        <v>1.80915307998657</v>
+        <v>1.80915319919586</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G672" t="n">
-        <v>1.75372850894928</v>
+        <v>1.75372838973999</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G674" t="n">
-        <v>1.75207412242889</v>
+        <v>1.75207424163818</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G676" t="n">
-        <v>1.68920457363129</v>
+        <v>1.68920469284058</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G677" t="n">
-        <v>1.57008337974548</v>
+        <v>1.57008349895477</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>1.82879996299744</v>
       </c>
       <c r="G678" t="n">
-        <v>1.5128390789032</v>
+        <v>1.51283919811249</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.75479996204376</v>
       </c>
       <c r="G679" t="n">
-        <v>1.45162415504456</v>
+        <v>1.45162403583527</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>1.79139995574951</v>
       </c>
       <c r="G680" t="n">
-        <v>1.48190069198608</v>
+        <v>1.48190057277679</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G681" t="n">
-        <v>1.41042792797089</v>
+        <v>1.41042804718018</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.75960004329681</v>
       </c>
       <c r="G683" t="n">
-        <v>1.45559477806091</v>
+        <v>1.4555948972702</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G684" t="n">
-        <v>1.47329747676849</v>
+        <v>1.47329759597778</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>1.74440002441406</v>
       </c>
       <c r="G688" t="n">
-        <v>1.44302093982697</v>
+        <v>1.44302082061768</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.76979994773865</v>
       </c>
       <c r="G690" t="n">
-        <v>1.46403253078461</v>
+        <v>1.46403241157532</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>1.71580004692078</v>
       </c>
       <c r="G692" t="n">
-        <v>1.41936218738556</v>
+        <v>1.41936206817627</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G693" t="n">
-        <v>1.42283630371094</v>
+        <v>1.42283642292023</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.7305999994278</v>
       </c>
       <c r="G694" t="n">
-        <v>1.43160510063171</v>
+        <v>1.43160498142242</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1.74479997158051</v>
       </c>
       <c r="G700" t="n">
-        <v>1.44335186481476</v>
+        <v>1.44335174560547</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>1.73759996891022</v>
       </c>
       <c r="G701" t="n">
-        <v>1.43739569187164</v>
+        <v>1.43739557266235</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G702" t="n">
-        <v>1.43524491786957</v>
+        <v>1.43524503707886</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.71539998054504</v>
       </c>
       <c r="G707" t="n">
-        <v>1.41903114318848</v>
+        <v>1.41903126239777</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G709" t="n">
-        <v>1.37320256233215</v>
+        <v>1.37320268154144</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G710" t="n">
-        <v>1.35665810108185</v>
+        <v>1.35665798187256</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.66460001468658</v>
       </c>
       <c r="G711" t="n">
-        <v>1.3770078420639</v>
+        <v>1.37700796127319</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.83959996700287</v>
       </c>
       <c r="G714" t="n">
-        <v>1.52177321910858</v>
+        <v>1.52177333831787</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.72979998588562</v>
       </c>
       <c r="G718" t="n">
-        <v>1.43094325065613</v>
+        <v>1.43094313144684</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.81980001926422</v>
       </c>
       <c r="G726" t="n">
-        <v>1.50539410114288</v>
+        <v>1.50539398193359</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.79120004177094</v>
       </c>
       <c r="G727" t="n">
-        <v>1.48173522949219</v>
+        <v>1.48173534870148</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G728" t="n">
-        <v>1.51383173465729</v>
+        <v>1.51383197307587</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G729" t="n">
-        <v>1.51796793937683</v>
+        <v>1.51796805858612</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.83159995079041</v>
       </c>
       <c r="G732" t="n">
-        <v>1.51515531539917</v>
+        <v>1.51515519618988</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G733" t="n">
-        <v>1.51383173465729</v>
+        <v>1.51383197307587</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.84179997444153</v>
       </c>
       <c r="G738" t="n">
-        <v>1.52359294891357</v>
+        <v>1.52359318733215</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.77240002155304</v>
       </c>
       <c r="G742" t="n">
-        <v>1.46618330478668</v>
+        <v>1.46618342399597</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G743" t="n">
-        <v>1.48156988620758</v>
+        <v>1.48157000541687</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G746" t="n">
-        <v>1.47329747676849</v>
+        <v>1.47329759597778</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.78120005130768</v>
       </c>
       <c r="G748" t="n">
-        <v>1.47346293926239</v>
+        <v>1.47346305847168</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G749" t="n">
-        <v>1.48156988620758</v>
+        <v>1.48157000541687</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G750" t="n">
-        <v>1.47329747676849</v>
+        <v>1.47329759597778</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G753" t="n">
-        <v>1.47329747676849</v>
+        <v>1.47329759597778</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.78639996051788</v>
       </c>
       <c r="G754" t="n">
-        <v>1.47776448726654</v>
+        <v>1.47776460647583</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.86979997158051</v>
       </c>
       <c r="G755" t="n">
-        <v>1.54675567150116</v>
+        <v>1.54675555229187</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.88940000534058</v>
       </c>
       <c r="G756" t="n">
-        <v>1.56296932697296</v>
+        <v>1.56296944618225</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.92260003089905</v>
       </c>
       <c r="G758" t="n">
-        <v>1.6637864112854</v>
+        <v>1.66378664970398</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.94959998130798</v>
       </c>
       <c r="G766" t="n">
-        <v>1.68715178966522</v>
+        <v>1.68715190887451</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.94959998130798</v>
       </c>
       <c r="G768" t="n">
-        <v>1.68715178966522</v>
+        <v>1.68715190887451</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.94959998130798</v>
       </c>
       <c r="G769" t="n">
-        <v>1.68715178966522</v>
+        <v>1.68715190887451</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.94760000705719</v>
       </c>
       <c r="G770" t="n">
-        <v>1.68542098999023</v>
+        <v>1.68542110919952</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.95860004425049</v>
       </c>
       <c r="G776" t="n">
-        <v>1.69494044780731</v>
+        <v>1.69494032859802</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.95959997177124</v>
       </c>
       <c r="G781" t="n">
-        <v>1.69580554962158</v>
+        <v>1.69580566883087</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G786" t="n">
-        <v>1.68749797344208</v>
+        <v>1.68749809265137</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G789" t="n">
-        <v>1.66759407520294</v>
+        <v>1.66759419441223</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G794" t="n">
-        <v>1.66240179538727</v>
+        <v>1.66240191459656</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G795" t="n">
-        <v>1.65980565547943</v>
+        <v>1.65980577468872</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.84860002994537</v>
       </c>
       <c r="G796" t="n">
-        <v>1.59974825382233</v>
+        <v>1.59974813461304</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G797" t="n">
-        <v>1.59836363792419</v>
+        <v>1.5983635187149</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G798" t="n">
-        <v>1.6191326379776</v>
+        <v>1.61913275718689</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G802" t="n">
-        <v>1.62345957756042</v>
+        <v>1.62345969676971</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G810" t="n">
-        <v>1.60355591773987</v>
+        <v>1.60355579853058</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G812" t="n">
-        <v>1.60095977783203</v>
+        <v>1.60095965862274</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>1.75220000743866</v>
       </c>
       <c r="G814" t="n">
-        <v>1.51632523536682</v>
+        <v>1.51632511615753</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G815" t="n">
-        <v>1.54211342334747</v>
+        <v>1.54211354255676</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G816" t="n">
-        <v>1.50144040584564</v>
+        <v>1.50144052505493</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G817" t="n">
-        <v>1.50144040584564</v>
+        <v>1.50144052505493</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G818" t="n">
-        <v>1.52913284301758</v>
+        <v>1.52913272380829</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.75</v>
       </c>
       <c r="G822" t="n">
-        <v>1.51442134380341</v>
+        <v>1.51442122459412</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.72560000419617</v>
       </c>
       <c r="G826" t="n">
-        <v>1.49330604076385</v>
+        <v>1.49330592155457</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G829" t="n">
-        <v>1.47115218639374</v>
+        <v>1.47115206718445</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G830" t="n">
-        <v>1.50144040584564</v>
+        <v>1.50144052505493</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G834" t="n">
-        <v>1.47115218639374</v>
+        <v>1.47115206718445</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>1.47115218639374</v>
+        <v>1.47115206718445</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.75</v>
       </c>
       <c r="G837" t="n">
-        <v>1.51442134380341</v>
+        <v>1.51442122459412</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G844" t="n">
-        <v>1.47115218639374</v>
+        <v>1.47115206718445</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G845" t="n">
-        <v>1.47115218639374</v>
+        <v>1.47115206718445</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G846" t="n">
-        <v>1.46682524681091</v>
+        <v>1.4668253660202</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G849" t="n">
-        <v>1.45817124843597</v>
+        <v>1.45817136764526</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G850" t="n">
-        <v>1.47115218639374</v>
+        <v>1.47115206718445</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G854" t="n">
-        <v>1.43653666973114</v>
+        <v>1.43653678894043</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G856" t="n">
-        <v>1.34134447574615</v>
+        <v>1.34134459495544</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G857" t="n">
-        <v>1.3673061132431</v>
+        <v>1.36730599403381</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G859" t="n">
-        <v>1.43653666973114</v>
+        <v>1.43653678894043</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G862" t="n">
-        <v>1.43653666973114</v>
+        <v>1.43653678894043</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G867" t="n">
-        <v>1.43653666973114</v>
+        <v>1.43653678894043</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G868" t="n">
-        <v>1.41057527065277</v>
+        <v>1.41057515144348</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G869" t="n">
-        <v>1.41057527065277</v>
+        <v>1.41057515144348</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G871" t="n">
-        <v>1.41057527065277</v>
+        <v>1.41057515144348</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G872" t="n">
-        <v>1.41057527065277</v>
+        <v>1.41057515144348</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G874" t="n">
-        <v>1.41490209102631</v>
+        <v>1.4149022102356</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G875" t="n">
-        <v>1.41057527065277</v>
+        <v>1.41057515144348</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>1.33269071578979</v>
+        <v>1.33269059658051</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G878" t="n">
-        <v>1.38028681278229</v>
+        <v>1.38028693199158</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G879" t="n">
-        <v>1.38028681278229</v>
+        <v>1.38028693199158</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G880" t="n">
-        <v>1.37595999240875</v>
+        <v>1.37595987319946</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G881" t="n">
-        <v>1.37595999240875</v>
+        <v>1.37595987319946</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G885" t="n">
-        <v>1.37595999240875</v>
+        <v>1.37595987319946</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G887" t="n">
-        <v>1.37163293361664</v>
+        <v>1.37163305282593</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>1.34999823570251</v>
+        <v>1.3499983549118</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G890" t="n">
-        <v>1.31970989704132</v>
+        <v>1.31971001625061</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>1.33269071578979</v>
+        <v>1.33269059658051</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31105601787567</v>
+        <v>1.31105613708496</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G893" t="n">
-        <v>1.31970989704132</v>
+        <v>1.31971001625061</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G903" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G905" t="n">
-        <v>1.43948984146118</v>
+        <v>1.43948972225189</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G908" t="n">
-        <v>1.4128326177597</v>
+        <v>1.41283249855042</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G914" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G915" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G916" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G920" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G921" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G922" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G923" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G924" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G927" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G929" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.625</v>
       </c>
       <c r="G930" t="n">
-        <v>1.44393253326416</v>
+        <v>1.44393265247345</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G931" t="n">
-        <v>1.43948984146118</v>
+        <v>1.43948972225189</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G936" t="n">
-        <v>1.43948984146118</v>
+        <v>1.43948972225189</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G937" t="n">
-        <v>1.45726132392883</v>
+        <v>1.45726120471954</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G939" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G942" t="n">
-        <v>1.4128326177597</v>
+        <v>1.41283249855042</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G943" t="n">
-        <v>1.4128326177597</v>
+        <v>1.41283249855042</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G944" t="n">
-        <v>1.4128326177597</v>
+        <v>1.41283249855042</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G949" t="n">
-        <v>1.4128326177597</v>
+        <v>1.41283249855042</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G950" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G953" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G954" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G957" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G967" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G968" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G971" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G995" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.30176079273224</v>
+        <v>1.30176091194153</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.45726132392883</v>
+        <v>1.45726120471954</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.25</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.15958881378174</v>
+        <v>1.15958893299103</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>1.25</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.25</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.25</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.25</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.25</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.10627448558807</v>
+        <v>1.10627460479736</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.05740308761597</v>
+        <v>1.05740296840668</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.15070331096649</v>
+        <v>1.1507031917572</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.21290338039398</v>
+        <v>1.21290349960327</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.21290338039398</v>
+        <v>1.21290349960327</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.21290338039398</v>
+        <v>1.21290349960327</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.15070331096649</v>
+        <v>1.1507031917572</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.16403186321259</v>
+        <v>1.1640317440033</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.10627448558807</v>
+        <v>1.10627460479736</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.15958881378174</v>
+        <v>1.15958893299103</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.15958881378174</v>
+        <v>1.15958893299103</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.15070331096649</v>
+        <v>1.1507031917572</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.16403186321259</v>
+        <v>1.1640317440033</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.25</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.02186000347137</v>
+        <v>1.02185988426208</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.00853145122528</v>
+        <v>1.00853133201599</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.964102685451508</v>
+        <v>0.964102804660797</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.933002650737762</v>
+        <v>0.933002531528473</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.968545615673065</v>
+        <v>0.96854555606842</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.25</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.10627448558807</v>
+        <v>1.10627460479736</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.10627448558807</v>
+        <v>1.10627460479736</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.25</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.25</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.25</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.25</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.10627448558807</v>
+        <v>1.10627460479736</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.10627448558807</v>
+        <v>1.10627460479736</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.25</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.46170401573181</v>
+        <v>1.4617041349411</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.55056142807007</v>
+        <v>1.55056154727936</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.69273316860199</v>
+        <v>1.69273328781128</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.71050477027893</v>
+        <v>1.71050488948822</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.652747631073</v>
+        <v>1.65274751186371</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.68384754657745</v>
+        <v>1.68384766578674</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.58610427379608</v>
+        <v>1.58610439300537</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.63941884040833</v>
+        <v>1.63941895961761</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.5949901342392</v>
+        <v>1.59499025344849</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.5949901342392</v>
+        <v>1.59499025344849</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.58610427379608</v>
+        <v>1.58610439300537</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.62164747714996</v>
+        <v>1.62164759635925</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.55056142807007</v>
+        <v>1.55056154727936</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.59943306446075</v>
+        <v>1.59943294525146</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.59943306446075</v>
+        <v>1.59943294525146</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.68384754657745</v>
+        <v>1.68384766578674</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.71050477027893</v>
+        <v>1.71050488948822</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.68384754657745</v>
+        <v>1.68384766578674</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1415" t="n">
-        <v>2.01706290245056</v>
+        <v>2.01706266403198</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.85711932182312</v>
+        <v>1.85711944103241</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.90154826641083</v>
+        <v>1.90154814720154</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.90154826641083</v>
+        <v>1.90154814720154</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.90154826641083</v>
+        <v>1.90154814720154</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.04372000694275</v>
+        <v>2.04371976852417</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.11480617523193</v>
+        <v>2.11480593681335</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.04372000694275</v>
+        <v>2.04371976852417</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.91931974887848</v>
+        <v>1.91931962966919</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.04372000694275</v>
+        <v>2.04371976852417</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.04372000694275</v>
+        <v>2.04371976852417</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.03483414649963</v>
+        <v>2.03483438491821</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1486" t="n">
-        <v>2.01706290245056</v>
+        <v>2.01706266403198</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.03483414649963</v>
+        <v>2.03483438491821</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.01706290245056</v>
+        <v>2.01706266403198</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.91931974887848</v>
+        <v>1.91931962966919</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709111213684</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.85711932182312</v>
+        <v>1.85711944103241</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.83934783935547</v>
+        <v>1.83934795856476</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.92820537090302</v>
+        <v>1.92820560932159</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.92820537090302</v>
+        <v>1.92820560932159</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.83934783935547</v>
+        <v>1.83934795856476</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.83934783935547</v>
+        <v>1.83934795856476</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.90154826641083</v>
+        <v>1.90154814720154</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.92820537090302</v>
+        <v>1.92820560932159</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.90154826641083</v>
+        <v>1.90154814720154</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.90154826641083</v>
+        <v>1.90154814720154</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.85711932182312</v>
+        <v>1.85711944103241</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.04372000694275</v>
+        <v>2.04371976852417</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.83934783935547</v>
+        <v>1.83934795856476</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.85711932182312</v>
+        <v>1.85711944103241</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.80380499362946</v>
+        <v>1.80380511283875</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.80380499362946</v>
+        <v>1.80380511283875</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.74160504341125</v>
+        <v>1.74160492420197</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.74604773521423</v>
+        <v>1.74604785442352</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.73716199398041</v>
+        <v>1.7371621131897</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.54167568683624</v>
+        <v>1.54167580604553</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.56833291053772</v>
+        <v>1.56833302974701</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1577" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.652747631073</v>
+        <v>1.65274751186371</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.60387587547302</v>
+        <v>1.60387599468231</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.60387587547302</v>
+        <v>1.60387599468231</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.5949901342392</v>
+        <v>1.59499025344849</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.54611873626709</v>
+        <v>1.5461186170578</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.55056142807007</v>
+        <v>1.55056154727936</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.55056142807007</v>
+        <v>1.55056154727936</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1596" t="n">
-        <v>1.54611873626709</v>
+        <v>1.5461186170578</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.54167568683624</v>
+        <v>1.54167580604553</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.54167568683624</v>
+        <v>1.54167580604553</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.5949901342392</v>
+        <v>1.59499025344849</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.58610427379608</v>
+        <v>1.58610439300537</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.71050477027893</v>
+        <v>1.71050488948822</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>2.5</v>
       </c>
       <c r="G1612" t="n">
-        <v>2.22143483161926</v>
+        <v>2.22143459320068</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.91931974887848</v>
+        <v>1.91931962966919</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1622" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1625" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1626" t="n">
-        <v>1.80380499362946</v>
+        <v>1.80380511283875</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1629" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709111213684</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>1.92820537090302</v>
+        <v>1.92820560932159</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1632" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709111213684</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.90154826641083</v>
+        <v>1.90154814720154</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1634" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709111213684</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1638" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.71050477027893</v>
+        <v>1.71050488948822</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1644" t="n">
-        <v>1.74160504341125</v>
+        <v>1.74160492420197</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1645" t="n">
-        <v>1.79491937160492</v>
+        <v>1.79491925239563</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709111213684</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1653" t="n">
-        <v>1.85711932182312</v>
+        <v>1.85711944103241</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1654" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.79491937160492</v>
+        <v>1.79491925239563</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.69273316860199</v>
+        <v>1.69273328781128</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1670" t="n">
-        <v>1.74160504341125</v>
+        <v>1.74160492420197</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1672" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1677" t="n">
-        <v>1.80380499362946</v>
+        <v>1.80380511283875</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.79491937160492</v>
+        <v>1.79491925239563</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.76381921768188</v>
+        <v>1.76381933689117</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.73716199398041</v>
+        <v>1.7371621131897</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.62164747714996</v>
+        <v>1.62164759635925</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1705" t="n">
-        <v>1.68384754657745</v>
+        <v>1.68384766578674</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1706" t="n">
-        <v>1.68384754657745</v>
+        <v>1.68384766578674</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.51057577133179</v>
+        <v>1.5105756521225</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1721" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1722" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1723" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1724" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1734" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.21290338039398</v>
+        <v>1.21290349960327</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1749" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1753" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1756" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1765" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1773" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1789" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1797" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1800" t="n">
-        <v>1.30176079273224</v>
+        <v>1.30176091194153</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1805" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1809" t="n">
-        <v>1.30176079273224</v>
+        <v>1.30176091194153</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1822" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.30176079273224</v>
+        <v>1.30176091194153</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1845" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1850" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.21290338039398</v>
+        <v>1.21290349960327</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1862" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.15070331096649</v>
+        <v>1.1507031917572</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1939" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1965" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.30176079273224</v>
+        <v>1.30176091194153</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1979" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51927,7 +51927,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1983" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1983" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.16403186321259</v>
+        <v>1.1640317440033</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.16403186321259</v>
+        <v>1.1640317440033</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52733,7 +52733,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G2014" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H2014" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.30176079273224</v>
+        <v>1.30176091194153</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2018" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2025" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53097,7 +53097,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2028" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H2028" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G2030" t="n">
-        <v>1.30176079273224</v>
+        <v>1.30176091194153</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.51501858234406</v>
+        <v>1.51501870155334</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2037" t="n">
-        <v>1.652747631073</v>
+        <v>1.65274751186371</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2039" t="n">
-        <v>1.69273316860199</v>
+        <v>1.69273328781128</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2040" t="n">
-        <v>1.652747631073</v>
+        <v>1.65274751186371</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53513,7 +53513,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2044" t="n">
-        <v>1.54167568683624</v>
+        <v>1.54167580604553</v>
       </c>
       <c r="H2044" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2045" t="n">
-        <v>1.54611873626709</v>
+        <v>1.5461186170578</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2048" t="n">
-        <v>1.56833291053772</v>
+        <v>1.56833302974701</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G2050" t="n">
-        <v>1.49724698066711</v>
+        <v>1.4972470998764</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.51057577133179</v>
+        <v>1.5105756521225</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2053" t="n">
-        <v>1.49280416965485</v>
+        <v>1.49280405044556</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>1.625</v>
       </c>
       <c r="G2056" t="n">
-        <v>1.44393253326416</v>
+        <v>1.44393265247345</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2058" t="n">
-        <v>1.43948984146118</v>
+        <v>1.43948972225189</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2060" t="n">
-        <v>1.49280416965485</v>
+        <v>1.49280405044556</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2061" t="n">
-        <v>1.49280416965485</v>
+        <v>1.49280405044556</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54007,7 +54007,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2063" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H2063" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2087" t="n">
-        <v>1.43948984146118</v>
+        <v>1.43948972225189</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2095" t="n">
-        <v>1.43948984146118</v>
+        <v>1.43948972225189</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54969,7 +54969,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2100" t="n">
-        <v>1.63941884040833</v>
+        <v>1.63941895961761</v>
       </c>
       <c r="H2100" t="s">
         <v>8</v>
@@ -54995,7 +54995,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2101" t="n">
-        <v>1.63941884040833</v>
+        <v>1.63941895961761</v>
       </c>
       <c r="H2101" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2102" t="n">
-        <v>1.60387587547302</v>
+        <v>1.60387599468231</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2108" t="n">
-        <v>1.51501858234406</v>
+        <v>1.51501870155334</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.4128326177597</v>
+        <v>1.41283249855042</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2115" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55437,7 +55437,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G2118" t="n">
-        <v>1.45726132392883</v>
+        <v>1.45726120471954</v>
       </c>
       <c r="H2118" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2125" t="n">
-        <v>1.63329350948334</v>
+        <v>1.63329362869263</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2132" t="n">
-        <v>1.55463635921478</v>
+        <v>1.55463624000549</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55827,7 +55827,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2133" t="n">
-        <v>1.55463635921478</v>
+        <v>1.55463624000549</v>
       </c>
       <c r="H2133" t="s">
         <v>8</v>
@@ -55879,7 +55879,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G2135" t="n">
-        <v>1.55926311016083</v>
+        <v>1.55926322937012</v>
       </c>
       <c r="H2135" t="s">
         <v>8</v>
@@ -55905,7 +55905,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.51762127876282</v>
+        <v>1.51762115955353</v>
       </c>
       <c r="H2136" t="s">
         <v>8</v>
@@ -56009,7 +56009,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2140" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2141" t="n">
-        <v>1.46672534942627</v>
+        <v>1.46672546863556</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2143" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56139,7 +56139,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2145" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2145" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.47135233879089</v>
+        <v>1.4713522195816</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56451,7 +56451,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2157" t="s">
         <v>8</v>
@@ -56503,7 +56503,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2159" t="s">
         <v>8</v>
@@ -56555,7 +56555,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2161" t="n">
-        <v>1.47135233879089</v>
+        <v>1.4713522195816</v>
       </c>
       <c r="H2161" t="s">
         <v>8</v>
@@ -56581,7 +56581,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2162" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2162" t="s">
         <v>8</v>
@@ -56607,7 +56607,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2163" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2163" t="s">
         <v>8</v>
@@ -56737,7 +56737,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2168" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2168" t="s">
         <v>8</v>
@@ -56841,7 +56841,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2172" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2172" t="s">
         <v>8</v>
@@ -56867,7 +56867,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2173" t="n">
-        <v>1.46672534942627</v>
+        <v>1.46672546863556</v>
       </c>
       <c r="H2173" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2174" t="n">
-        <v>1.46672534942627</v>
+        <v>1.46672546863556</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2175" t="n">
-        <v>1.47135233879089</v>
+        <v>1.4713522195816</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -56945,7 +56945,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2176" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2176" t="s">
         <v>8</v>
@@ -56971,7 +56971,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2177" t="n">
-        <v>1.46672534942627</v>
+        <v>1.46672546863556</v>
       </c>
       <c r="H2177" t="s">
         <v>8</v>
@@ -57023,7 +57023,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2179" t="n">
-        <v>1.47135233879089</v>
+        <v>1.4713522195816</v>
       </c>
       <c r="H2179" t="s">
         <v>8</v>
@@ -57049,7 +57049,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2180" t="n">
-        <v>1.47135233879089</v>
+        <v>1.4713522195816</v>
       </c>
       <c r="H2180" t="s">
         <v>8</v>
@@ -57075,7 +57075,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2181" t="n">
-        <v>1.46672534942627</v>
+        <v>1.46672546863556</v>
       </c>
       <c r="H2181" t="s">
         <v>8</v>
@@ -57127,7 +57127,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2183" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2183" t="s">
         <v>8</v>
@@ -57153,7 +57153,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2184" t="s">
         <v>8</v>
@@ -57179,7 +57179,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2185" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2185" t="s">
         <v>8</v>
@@ -57205,7 +57205,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2186" t="s">
         <v>8</v>
@@ -57231,7 +57231,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2187" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2187" t="s">
         <v>8</v>
@@ -57257,7 +57257,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G2188" t="n">
-        <v>1.31866466999054</v>
+        <v>1.31866478919983</v>
       </c>
       <c r="H2188" t="s">
         <v>8</v>
@@ -57361,7 +57361,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G2192" t="n">
-        <v>1.37418746948242</v>
+        <v>1.37418758869171</v>
       </c>
       <c r="H2192" t="s">
         <v>8</v>
@@ -57387,7 +57387,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G2193" t="n">
-        <v>1.37418746948242</v>
+        <v>1.37418758869171</v>
       </c>
       <c r="H2193" t="s">
         <v>8</v>
@@ -57595,7 +57595,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2201" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2201" t="s">
         <v>8</v>
@@ -57621,7 +57621,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2202" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57699,7 +57699,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2205" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2205" t="s">
         <v>8</v>
@@ -57725,7 +57725,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2206" t="s">
         <v>8</v>
@@ -57777,7 +57777,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2208" t="s">
         <v>8</v>
@@ -57803,7 +57803,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2209" t="s">
         <v>8</v>
@@ -57881,7 +57881,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2212" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2212" t="s">
         <v>8</v>
@@ -57933,7 +57933,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.32329165935516</v>
+        <v>1.32329154014587</v>
       </c>
       <c r="H2214" t="s">
         <v>8</v>
@@ -57959,7 +57959,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G2215" t="n">
-        <v>1.31866466999054</v>
+        <v>1.31866478919983</v>
       </c>
       <c r="H2215" t="s">
         <v>8</v>
@@ -58089,7 +58089,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2220" t="n">
-        <v>1.41120254993439</v>
+        <v>1.41120266914368</v>
       </c>
       <c r="H2220" t="s">
         <v>8</v>
@@ -58115,7 +58115,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2221" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2221" t="s">
         <v>8</v>
@@ -58141,7 +58141,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2222" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2222" t="s">
         <v>8</v>
@@ -58193,7 +58193,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2224" t="s">
         <v>8</v>
@@ -58219,7 +58219,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2225" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2225" t="s">
         <v>8</v>
@@ -58297,7 +58297,7 @@
         <v>1.625</v>
       </c>
       <c r="G2228" t="n">
-        <v>1.50374042987823</v>
+        <v>1.50374054908752</v>
       </c>
       <c r="H2228" t="s">
         <v>8</v>
@@ -58375,7 +58375,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2231" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2231" t="s">
         <v>8</v>
@@ -58401,7 +58401,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2232" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2232" t="s">
         <v>8</v>
@@ -58479,7 +58479,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.52224802970886</v>
+        <v>1.52224814891815</v>
       </c>
       <c r="H2235" t="s">
         <v>8</v>
@@ -58505,7 +58505,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2236" t="n">
-        <v>1.52224802970886</v>
+        <v>1.52224814891815</v>
       </c>
       <c r="H2236" t="s">
         <v>8</v>
@@ -58635,7 +58635,7 @@
         <v>1.625</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.50374042987823</v>
+        <v>1.50374054908752</v>
       </c>
       <c r="H2241" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.51762127876282</v>
+        <v>1.51762115955353</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58921,7 +58921,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2252" t="s">
         <v>8</v>
@@ -58999,7 +58999,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2255" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2255" t="s">
         <v>8</v>
@@ -59051,7 +59051,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2257" t="n">
-        <v>1.41120254993439</v>
+        <v>1.41120266914368</v>
       </c>
       <c r="H2257" t="s">
         <v>8</v>
@@ -59077,7 +59077,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G2258" t="n">
-        <v>1.37418746948242</v>
+        <v>1.37418758869171</v>
       </c>
       <c r="H2258" t="s">
         <v>8</v>
@@ -59155,7 +59155,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2261" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2261" t="s">
         <v>8</v>
@@ -59181,7 +59181,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2262" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2262" t="s">
         <v>8</v>
@@ -59285,7 +59285,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2266" t="n">
-        <v>1.65180099010468</v>
+        <v>1.65180110931396</v>
       </c>
       <c r="H2266" t="s">
         <v>8</v>
@@ -59415,7 +59415,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2271" t="n">
-        <v>1.61015915870667</v>
+        <v>1.61015903949738</v>
       </c>
       <c r="H2271" t="s">
         <v>8</v>
@@ -59467,7 +59467,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G2273" t="n">
-        <v>1.61478590965271</v>
+        <v>1.614786028862</v>
       </c>
       <c r="H2273" t="s">
         <v>8</v>
@@ -59597,7 +59597,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2278" t="n">
-        <v>1.66568183898926</v>
+        <v>1.66568171977997</v>
       </c>
       <c r="H2278" t="s">
         <v>8</v>
@@ -59623,7 +59623,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2279" t="n">
-        <v>1.66568183898926</v>
+        <v>1.66568171977997</v>
       </c>
       <c r="H2279" t="s">
         <v>8</v>
@@ -59779,7 +59779,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G2285" t="n">
-        <v>1.61478590965271</v>
+        <v>1.614786028862</v>
       </c>
       <c r="H2285" t="s">
         <v>8</v>
@@ -59935,7 +59935,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2291" t="n">
-        <v>1.66568183898926</v>
+        <v>1.66568171977997</v>
       </c>
       <c r="H2291" t="s">
         <v>8</v>
@@ -60065,7 +60065,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2296" t="n">
-        <v>1.60553216934204</v>
+        <v>1.60553228855133</v>
       </c>
       <c r="H2296" t="s">
         <v>8</v>
@@ -60221,7 +60221,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G2302" t="n">
-        <v>1.51762127876282</v>
+        <v>1.51762115955353</v>
       </c>
       <c r="H2302" t="s">
         <v>8</v>
@@ -60273,7 +60273,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2304" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2304" t="s">
         <v>8</v>
@@ -60299,7 +60299,7 @@
         <v>1.625</v>
       </c>
       <c r="G2305" t="n">
-        <v>1.50374042987823</v>
+        <v>1.50374054908752</v>
       </c>
       <c r="H2305" t="s">
         <v>8</v>
@@ -60325,7 +60325,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2306" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2306" t="s">
         <v>8</v>
@@ -60455,7 +60455,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2311" t="n">
-        <v>1.46672534942627</v>
+        <v>1.46672546863556</v>
       </c>
       <c r="H2311" t="s">
         <v>8</v>
@@ -60533,7 +60533,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2314" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2314" t="s">
         <v>8</v>
@@ -60559,7 +60559,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2315" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2315" t="s">
         <v>8</v>
@@ -60637,7 +60637,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2318" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2318" t="s">
         <v>8</v>
@@ -60689,7 +60689,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2320" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2320" t="s">
         <v>8</v>
@@ -60741,7 +60741,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2322" t="n">
-        <v>1.47135233879089</v>
+        <v>1.4713522195816</v>
       </c>
       <c r="H2322" t="s">
         <v>8</v>
@@ -60819,7 +60819,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2325" t="n">
-        <v>1.46672534942627</v>
+        <v>1.46672546863556</v>
       </c>
       <c r="H2325" t="s">
         <v>8</v>
@@ -60871,7 +60871,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2327" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2327" t="s">
         <v>8</v>
@@ -60949,7 +60949,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2330" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2330" t="s">
         <v>8</v>
@@ -61053,7 +61053,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2334" t="n">
-        <v>1.41120254993439</v>
+        <v>1.41120266914368</v>
       </c>
       <c r="H2334" t="s">
         <v>8</v>
@@ -61209,7 +61209,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2340" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2340" t="s">
         <v>8</v>
@@ -61287,7 +61287,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2343" t="s">
         <v>8</v>
@@ -61313,7 +61313,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2344" t="s">
         <v>8</v>
@@ -61339,7 +61339,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2345" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2345" t="s">
         <v>8</v>
@@ -61495,7 +61495,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2351" t="n">
-        <v>1.6703085899353</v>
+        <v>1.67030870914459</v>
       </c>
       <c r="H2351" t="s">
         <v>8</v>
@@ -61521,7 +61521,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2352" t="n">
-        <v>1.68881630897522</v>
+        <v>1.68881642818451</v>
       </c>
       <c r="H2352" t="s">
         <v>8</v>
@@ -61599,7 +61599,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.60553216934204</v>
+        <v>1.60553228855133</v>
       </c>
       <c r="H2355" t="s">
         <v>8</v>
@@ -61729,7 +61729,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2360" t="n">
-        <v>1.5731440782547</v>
+        <v>1.57314395904541</v>
       </c>
       <c r="H2360" t="s">
         <v>8</v>
@@ -61859,7 +61859,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2365" t="n">
-        <v>1.65180099010468</v>
+        <v>1.65180110931396</v>
       </c>
       <c r="H2365" t="s">
         <v>8</v>
@@ -61911,7 +61911,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2367" t="n">
-        <v>1.65180099010468</v>
+        <v>1.65180110931396</v>
       </c>
       <c r="H2367" t="s">
         <v>8</v>
@@ -61963,7 +61963,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2369" t="n">
-        <v>1.66568183898926</v>
+        <v>1.66568171977997</v>
       </c>
       <c r="H2369" t="s">
         <v>8</v>
@@ -61989,7 +61989,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2370" t="n">
-        <v>1.66105484962463</v>
+        <v>1.66105496883392</v>
       </c>
       <c r="H2370" t="s">
         <v>8</v>
@@ -62015,7 +62015,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.70732378959656</v>
+        <v>1.70732390880585</v>
       </c>
       <c r="H2371" t="s">
         <v>8</v>
@@ -62041,7 +62041,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2372" t="n">
-        <v>1.72120463848114</v>
+        <v>1.72120451927185</v>
       </c>
       <c r="H2372" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>3.0699999332428</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>24535</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>3.07999992370605</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>3.07999992370605</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>37408</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>3.08999991416931</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>3.07999992370605</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>260117</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>3.07999992370605</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>3.0699999332428</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>90367</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>3.08999991416931</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>3.09999990463257</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>46409</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>148012</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>3.10999989509583</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -499,7 +499,7 @@
         <v>5.16267681121826</v>
       </c>
       <c r="G5" t="n">
-        <v>4.27072429656982</v>
+        <v>4.27072381973267</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>5.07366609573364</v>
       </c>
       <c r="G6" t="n">
-        <v>4.19709157943726</v>
+        <v>4.19709205627441</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.80663108825684</v>
       </c>
       <c r="G8" t="n">
-        <v>3.97619199752808</v>
+        <v>3.97619152069092</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.81019115447998</v>
       </c>
       <c r="G9" t="n">
-        <v>3.97913694381714</v>
+        <v>3.97913646697998</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G12" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.18354892730713</v>
       </c>
       <c r="G13" t="n">
-        <v>3.46075940132141</v>
+        <v>3.46075916290283</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.77409505844116</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12204670906067</v>
+        <v>3.12204647064209</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G16" t="n">
-        <v>3.38712549209595</v>
+        <v>3.38712573051453</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G17" t="n">
-        <v>3.38712549209595</v>
+        <v>3.38712573051453</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.11233901977539</v>
       </c>
       <c r="G18" t="n">
-        <v>3.40185236930847</v>
+        <v>3.40185189247131</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.11233901977539</v>
       </c>
       <c r="G19" t="n">
-        <v>3.40185236930847</v>
+        <v>3.40185189247131</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.11233901977539</v>
       </c>
       <c r="G20" t="n">
-        <v>3.40185236930847</v>
+        <v>3.40185189247131</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.53959512710571</v>
       </c>
       <c r="G23" t="n">
-        <v>3.755291223526</v>
+        <v>3.75529146194458</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.19957113265991</v>
       </c>
       <c r="G25" t="n">
-        <v>3.47401332855225</v>
+        <v>3.47401309013367</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.53959512710571</v>
       </c>
       <c r="G26" t="n">
-        <v>3.755291223526</v>
+        <v>3.75529146194458</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G43" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G63" t="n">
-        <v>3.35030937194824</v>
+        <v>3.35030913352966</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G64" t="n">
-        <v>3.35030937194824</v>
+        <v>3.35030913352966</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G65" t="n">
-        <v>3.35030937194824</v>
+        <v>3.35030913352966</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G66" t="n">
-        <v>3.35030937194824</v>
+        <v>3.35030913352966</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G67" t="n">
-        <v>3.35030937194824</v>
+        <v>3.35030913352966</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G68" t="n">
-        <v>3.35030937194824</v>
+        <v>3.35030913352966</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.18354892730713</v>
       </c>
       <c r="G74" t="n">
-        <v>3.46075940132141</v>
+        <v>3.46075916290283</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G76" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G77" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.94321703910828</v>
       </c>
       <c r="G78" t="n">
-        <v>3.26194930076599</v>
+        <v>3.26194953918457</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.29036283493042</v>
       </c>
       <c r="G82" t="n">
-        <v>3.5491189956665</v>
+        <v>3.54911923408508</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.16574621200562</v>
       </c>
       <c r="G83" t="n">
-        <v>3.44603276252747</v>
+        <v>3.44603228569031</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G84" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G85" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G86" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.20313119888306</v>
       </c>
       <c r="G87" t="n">
-        <v>3.47695827484131</v>
+        <v>3.47695803642273</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.20313119888306</v>
       </c>
       <c r="G88" t="n">
-        <v>3.47695827484131</v>
+        <v>3.47695803642273</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.2102518081665</v>
       </c>
       <c r="G90" t="n">
-        <v>3.48284912109375</v>
+        <v>3.48284864425659</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.38422393798828</v>
       </c>
       <c r="G98" t="n">
-        <v>2.79953289031982</v>
+        <v>2.79953336715698</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.41804790496826</v>
       </c>
       <c r="G99" t="n">
-        <v>2.82751369476318</v>
+        <v>2.8275134563446</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.38778400421143</v>
       </c>
       <c r="G100" t="n">
-        <v>2.80247831344604</v>
+        <v>2.80247855186462</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G101" t="n">
-        <v>2.85696697235107</v>
+        <v>2.85696721076965</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.90583205223083</v>
       </c>
       <c r="G102" t="n">
-        <v>3.23102331161499</v>
+        <v>3.23102355003357</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.77231502532959</v>
       </c>
       <c r="G112" t="n">
-        <v>3.12057423591614</v>
+        <v>3.12057399749756</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.64947891235352</v>
       </c>
       <c r="G113" t="n">
-        <v>3.01896047592163</v>
+        <v>3.01896023750305</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G115" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G119" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G120" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.3005530834198</v>
       </c>
       <c r="G123" t="n">
-        <v>2.73031830787659</v>
+        <v>2.73031806945801</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.95518708229065</v>
       </c>
       <c r="G127" t="n">
-        <v>2.44462060928345</v>
+        <v>2.44462084770203</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.40331506729126</v>
       </c>
       <c r="G134" t="n">
-        <v>1.98809552192688</v>
+        <v>1.9880952835083</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G135" t="n">
-        <v>1.76719605922699</v>
+        <v>1.7671959400177</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G136" t="n">
-        <v>1.76719605922699</v>
+        <v>1.7671959400177</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.04726791381836</v>
       </c>
       <c r="G137" t="n">
-        <v>1.6935623884201</v>
+        <v>1.69356250762939</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.17010402679443</v>
       </c>
       <c r="G142" t="n">
-        <v>1.7951762676239</v>
+        <v>1.79517638683319</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.26267695426941</v>
       </c>
       <c r="G144" t="n">
-        <v>1.8717554807663</v>
+        <v>1.87175524234772</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.15408205986023</v>
       </c>
       <c r="G145" t="n">
-        <v>1.78192222118378</v>
+        <v>1.78192234039307</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.21461009979248</v>
       </c>
       <c r="G147" t="n">
-        <v>1.83199286460876</v>
+        <v>1.83199298381805</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.97071802616119</v>
       </c>
       <c r="G153" t="n">
-        <v>1.63023817539215</v>
+        <v>1.63023805618286</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.05438899993896</v>
       </c>
       <c r="G154" t="n">
-        <v>1.69945323467255</v>
+        <v>1.69945311546326</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.95647597312927</v>
       </c>
       <c r="G160" t="n">
-        <v>1.61845648288727</v>
+        <v>1.61845660209656</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.97961902618408</v>
       </c>
       <c r="G162" t="n">
-        <v>1.63760125637054</v>
+        <v>1.63760113716125</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.83542001247406</v>
       </c>
       <c r="G172" t="n">
-        <v>1.51831543445587</v>
+        <v>1.51831531524658</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.83542001247406</v>
       </c>
       <c r="G173" t="n">
-        <v>1.51831543445587</v>
+        <v>1.51831531524658</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.83542001247406</v>
       </c>
       <c r="G174" t="n">
-        <v>1.51831543445587</v>
+        <v>1.51831531524658</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.83363997936249</v>
       </c>
       <c r="G175" t="n">
-        <v>1.51684296131134</v>
+        <v>1.51684284210205</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.13983988761902</v>
       </c>
       <c r="G176" t="n">
-        <v>1.77014088630676</v>
+        <v>1.77014064788818</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.17188501358032</v>
       </c>
       <c r="G177" t="n">
-        <v>1.79664957523346</v>
+        <v>1.79664945602417</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.08287310600281</v>
       </c>
       <c r="G180" t="n">
-        <v>1.72301638126373</v>
+        <v>1.72301614284515</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.09177398681641</v>
       </c>
       <c r="G181" t="n">
-        <v>1.73037922382355</v>
+        <v>1.73037910461426</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.97605895996094</v>
       </c>
       <c r="G182" t="n">
-        <v>1.63465631008148</v>
+        <v>1.63465619087219</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.11847805976868</v>
       </c>
       <c r="G183" t="n">
-        <v>1.75246953964233</v>
+        <v>1.75246965885162</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.99386096000671</v>
       </c>
       <c r="G190" t="n">
-        <v>1.64938259124756</v>
+        <v>1.64938247203827</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.24309396743774</v>
       </c>
       <c r="G193" t="n">
-        <v>1.85555589199066</v>
+        <v>1.85555565357208</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G194" t="n">
-        <v>1.76719605922699</v>
+        <v>1.7671959400177</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.40331506729126</v>
       </c>
       <c r="G196" t="n">
-        <v>1.98809552192688</v>
+        <v>1.9880952835083</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.41577696800232</v>
       </c>
       <c r="G198" t="n">
-        <v>1.99840426445007</v>
+        <v>1.99840438365936</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.52437090873718</v>
       </c>
       <c r="G199" t="n">
-        <v>2.08823680877686</v>
+        <v>2.08823657035828</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.35880899429321</v>
       </c>
       <c r="G201" t="n">
-        <v>1.95127892494202</v>
+        <v>1.95127868652344</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.27869892120361</v>
       </c>
       <c r="G203" t="n">
-        <v>1.88500940799713</v>
+        <v>1.88500916957855</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G205" t="n">
-        <v>1.76719605922699</v>
+        <v>1.7671959400177</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.09533500671387</v>
       </c>
       <c r="G206" t="n">
-        <v>1.73332488536835</v>
+        <v>1.73332500457764</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.14340090751648</v>
       </c>
       <c r="G207" t="n">
-        <v>1.77308666706085</v>
+        <v>1.77308678627014</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.12025809288025</v>
       </c>
       <c r="G210" t="n">
-        <v>1.75394213199615</v>
+        <v>1.75394225120544</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.09177398681641</v>
       </c>
       <c r="G211" t="n">
-        <v>1.73037922382355</v>
+        <v>1.73037910461426</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.11669707298279</v>
       </c>
       <c r="G215" t="n">
-        <v>1.75099647045135</v>
+        <v>1.75099635124207</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.07397198677063</v>
       </c>
       <c r="G216" t="n">
-        <v>1.71565282344818</v>
+        <v>1.71565294265747</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.15408205986023</v>
       </c>
       <c r="G223" t="n">
-        <v>1.78192222118378</v>
+        <v>1.78192234039307</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.15052199363708</v>
       </c>
       <c r="G224" t="n">
-        <v>1.77897751331329</v>
+        <v>1.778977394104</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.13806009292603</v>
       </c>
       <c r="G228" t="n">
-        <v>1.76866865158081</v>
+        <v>1.76866841316223</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G229" t="n">
-        <v>1.76425015926361</v>
+        <v>1.7642502784729</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G230" t="n">
-        <v>1.76425015926361</v>
+        <v>1.7642502784729</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.04726791381836</v>
       </c>
       <c r="G236" t="n">
-        <v>1.6935623884201</v>
+        <v>1.69356250762939</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.04726791381836</v>
       </c>
       <c r="G237" t="n">
-        <v>1.6935623884201</v>
+        <v>1.69356250762939</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.07041096687317</v>
       </c>
       <c r="G240" t="n">
-        <v>1.71270716190338</v>
+        <v>1.71270704269409</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.07041096687317</v>
       </c>
       <c r="G241" t="n">
-        <v>1.71270716190338</v>
+        <v>1.71270704269409</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.11847805976868</v>
       </c>
       <c r="G242" t="n">
-        <v>1.75246953964233</v>
+        <v>1.75246965885162</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G243" t="n">
-        <v>1.76425015926361</v>
+        <v>1.7642502784729</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.15408205986023</v>
       </c>
       <c r="G244" t="n">
-        <v>1.78192222118378</v>
+        <v>1.78192234039307</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G245" t="n">
-        <v>1.76425015926361</v>
+        <v>1.7642502784729</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.08109307289124</v>
       </c>
       <c r="G247" t="n">
-        <v>1.72154378890991</v>
+        <v>1.72154366970062</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.0846529006958</v>
       </c>
       <c r="G248" t="n">
-        <v>1.72448837757111</v>
+        <v>1.7244884967804</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.04726791381836</v>
       </c>
       <c r="G249" t="n">
-        <v>1.6935623884201</v>
+        <v>1.69356250762939</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G250" t="n">
-        <v>1.76719605922699</v>
+        <v>1.7671959400177</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.45672202110291</v>
       </c>
       <c r="G254" t="n">
-        <v>2.03227543830872</v>
+        <v>2.03227519989014</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.93738508224487</v>
       </c>
       <c r="G259" t="n">
-        <v>2.42989444732666</v>
+        <v>2.42989468574524</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.85905504226685</v>
       </c>
       <c r="G261" t="n">
-        <v>2.36509776115417</v>
+        <v>2.3650975227356</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>4.67133283615112</v>
       </c>
       <c r="G265" t="n">
-        <v>3.86426901817322</v>
+        <v>3.86426854133606</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.35445117950439</v>
       </c>
       <c r="G266" t="n">
-        <v>3.60213470458984</v>
+        <v>3.60213494300842</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>4.40073680877686</v>
       </c>
       <c r="G267" t="n">
-        <v>3.64042329788208</v>
+        <v>3.64042353630066</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>4.3793740272522</v>
       </c>
       <c r="G269" t="n">
-        <v>3.62275147438049</v>
+        <v>3.62275171279907</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.16574621200562</v>
       </c>
       <c r="G270" t="n">
-        <v>3.44603276252747</v>
+        <v>3.44603228569031</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.3953971862793</v>
       </c>
       <c r="G273" t="n">
-        <v>3.6360068321228</v>
+        <v>3.63600659370422</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.42210006713867</v>
       </c>
       <c r="G274" t="n">
-        <v>3.6580958366394</v>
+        <v>3.65809631347656</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.3241868019104</v>
       </c>
       <c r="G275" t="n">
-        <v>3.57709908485413</v>
+        <v>3.57709932327271</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.43278121948242</v>
       </c>
       <c r="G276" t="n">
-        <v>3.66693162918091</v>
+        <v>3.66693186759949</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.25653791427612</v>
       </c>
       <c r="G277" t="n">
-        <v>3.52113819122314</v>
+        <v>3.52113795280457</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25475788116455</v>
       </c>
       <c r="G278" t="n">
-        <v>3.51966547966003</v>
+        <v>3.51966571807861</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.35979223251343</v>
       </c>
       <c r="G280" t="n">
-        <v>3.60655283927917</v>
+        <v>3.60655307769775</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.3241868019104</v>
       </c>
       <c r="G282" t="n">
-        <v>3.57709908485413</v>
+        <v>3.57709932327271</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.32596683502197</v>
       </c>
       <c r="G283" t="n">
-        <v>3.57857179641724</v>
+        <v>3.57857155799866</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.32774782180786</v>
       </c>
       <c r="G284" t="n">
-        <v>3.5800449848175</v>
+        <v>3.58004522323608</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>4.11233901977539</v>
       </c>
       <c r="G285" t="n">
-        <v>3.40185236930847</v>
+        <v>3.40185189247131</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.69932508468628</v>
       </c>
       <c r="G292" t="n">
-        <v>3.06019449234009</v>
+        <v>3.06019425392151</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G293" t="n">
-        <v>3.38712549209595</v>
+        <v>3.38712573051453</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.54266500473022</v>
       </c>
       <c r="G298" t="n">
-        <v>2.93060088157654</v>
+        <v>2.93060064315796</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G300" t="n">
-        <v>3.38712549209595</v>
+        <v>3.38712573051453</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.09275722503662</v>
       </c>
       <c r="G308" t="n">
-        <v>3.38565373420715</v>
+        <v>3.38565349578857</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.77231502532959</v>
       </c>
       <c r="G312" t="n">
-        <v>3.12057423591614</v>
+        <v>3.12057399749756</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.69576501846313</v>
       </c>
       <c r="G314" t="n">
-        <v>3.0572497844696</v>
+        <v>3.05724954605103</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G327" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.41319894790649</v>
       </c>
       <c r="G328" t="n">
-        <v>3.65073299407959</v>
+        <v>3.65073323249817</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.21381282806396</v>
       </c>
       <c r="G329" t="n">
-        <v>3.48579430580139</v>
+        <v>3.48579478263855</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.32596683502197</v>
       </c>
       <c r="G330" t="n">
-        <v>3.57857179641724</v>
+        <v>3.57857155799866</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.77409505844116</v>
       </c>
       <c r="G332" t="n">
-        <v>3.12204670906067</v>
+        <v>3.12204647064209</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.0055251121521</v>
       </c>
       <c r="G337" t="n">
-        <v>3.31349277496338</v>
+        <v>3.3134925365448</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.93609595298767</v>
       </c>
       <c r="G338" t="n">
-        <v>3.25605893135071</v>
+        <v>3.25605869293213</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.93609595298767</v>
       </c>
       <c r="G339" t="n">
-        <v>3.25605893135071</v>
+        <v>3.25605869293213</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>3.85598611831665</v>
       </c>
       <c r="G340" t="n">
-        <v>3.18978953361511</v>
+        <v>3.18978929519653</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.95211791992188</v>
       </c>
       <c r="G359" t="n">
-        <v>3.26931262016296</v>
+        <v>3.26931238174438</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.78299593925476</v>
       </c>
       <c r="G365" t="n">
-        <v>3.12940955162048</v>
+        <v>3.12940979003906</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.69220399856567</v>
       </c>
       <c r="G367" t="n">
-        <v>3.05430388450623</v>
+        <v>3.0543041229248</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.8114800453186</v>
       </c>
       <c r="G372" t="n">
-        <v>3.15297269821167</v>
+        <v>3.15297245979309</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.72068810462952</v>
       </c>
       <c r="G374" t="n">
-        <v>3.07786655426025</v>
+        <v>3.07786679267883</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.64947891235352</v>
       </c>
       <c r="G375" t="n">
-        <v>3.01896047592163</v>
+        <v>3.01896023750305</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.60675311088562</v>
       </c>
       <c r="G376" t="n">
-        <v>2.98361611366272</v>
+        <v>2.9836163520813</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G377" t="n">
-        <v>2.94827175140381</v>
+        <v>2.94827198982239</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.60675311088562</v>
       </c>
       <c r="G378" t="n">
-        <v>2.98361611366272</v>
+        <v>2.9836163520813</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.61565399169922</v>
       </c>
       <c r="G383" t="n">
-        <v>2.99097919464111</v>
+        <v>2.99097943305969</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.45187306404114</v>
       </c>
       <c r="G388" t="n">
-        <v>2.8554949760437</v>
+        <v>2.85549473762512</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.52486205101013</v>
       </c>
       <c r="G392" t="n">
-        <v>2.91587328910828</v>
+        <v>2.91587352752686</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.50884008407593</v>
       </c>
       <c r="G393" t="n">
-        <v>2.90261960029602</v>
+        <v>2.9026198387146</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G397" t="n">
-        <v>2.85696697235107</v>
+        <v>2.85696721076965</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G398" t="n">
-        <v>2.85696697235107</v>
+        <v>2.85696721076965</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G399" t="n">
-        <v>2.85696697235107</v>
+        <v>2.85696721076965</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G400" t="n">
-        <v>2.85696697235107</v>
+        <v>2.85696721076965</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G401" t="n">
-        <v>2.85696697235107</v>
+        <v>2.85696721076965</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.64947891235352</v>
       </c>
       <c r="G406" t="n">
-        <v>3.01896047592163</v>
+        <v>3.01896023750305</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.64947891235352</v>
       </c>
       <c r="G407" t="n">
-        <v>3.01896047592163</v>
+        <v>3.01896023750305</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.59785199165344</v>
       </c>
       <c r="G410" t="n">
-        <v>2.97625303268433</v>
+        <v>2.97625279426575</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G417" t="n">
-        <v>2.94827175140381</v>
+        <v>2.94827198982239</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G418" t="n">
-        <v>2.94827175140381</v>
+        <v>2.94827198982239</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G423" t="n">
-        <v>2.98950672149658</v>
+        <v>2.989506483078</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.51418089866638</v>
       </c>
       <c r="G425" t="n">
-        <v>2.90703749656677</v>
+        <v>2.90703773498535</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G430" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.4394109249115</v>
       </c>
       <c r="G435" t="n">
-        <v>2.84518551826477</v>
+        <v>2.84518575668335</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.52486205101013</v>
       </c>
       <c r="G438" t="n">
-        <v>2.91587328910828</v>
+        <v>2.91587352752686</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.51418089866638</v>
       </c>
       <c r="G439" t="n">
-        <v>2.90703749656677</v>
+        <v>2.90703773498535</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.51418089866638</v>
       </c>
       <c r="G440" t="n">
-        <v>2.90703749656677</v>
+        <v>2.90703773498535</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.41092705726624</v>
       </c>
       <c r="G441" t="n">
-        <v>2.82162284851074</v>
+        <v>2.82162308692932</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.43407011032104</v>
       </c>
       <c r="G442" t="n">
-        <v>2.84076762199402</v>
+        <v>2.84076738357544</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G445" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G446" t="n">
-        <v>2.79658770561218</v>
+        <v>2.7965874671936</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G447" t="n">
-        <v>2.79658770561218</v>
+        <v>2.7965874671936</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.33971810340881</v>
       </c>
       <c r="G448" t="n">
-        <v>2.76271653175354</v>
+        <v>2.76271629333496</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.25426697731018</v>
       </c>
       <c r="G451" t="n">
-        <v>2.69202899932861</v>
+        <v>2.69202876091003</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G452" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G453" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G454" t="n">
-        <v>2.79658770561218</v>
+        <v>2.7965874671936</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.32903695106506</v>
       </c>
       <c r="G455" t="n">
-        <v>2.75388073921204</v>
+        <v>2.75388097763062</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G457" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G458" t="n">
-        <v>2.79806089401245</v>
+        <v>2.79806065559387</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G459" t="n">
-        <v>2.73915410041809</v>
+        <v>2.73915386199951</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G460" t="n">
-        <v>2.73915410041809</v>
+        <v>2.73915386199951</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73915410041809</v>
+        <v>2.73915386199951</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G465" t="n">
-        <v>2.73915410041809</v>
+        <v>2.73915386199951</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.21332097053528</v>
       </c>
       <c r="G467" t="n">
-        <v>2.65815711021423</v>
+        <v>2.65815687179565</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.21510195732117</v>
       </c>
       <c r="G468" t="n">
-        <v>2.6596302986145</v>
+        <v>2.65963006019592</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.22222304344177</v>
       </c>
       <c r="G471" t="n">
-        <v>2.66552114486694</v>
+        <v>2.66552138328552</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.19373893737793</v>
       </c>
       <c r="G472" t="n">
-        <v>2.64195847511292</v>
+        <v>2.64195823669434</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.15457391738892</v>
       </c>
       <c r="G475" t="n">
-        <v>2.60955953598022</v>
+        <v>2.6095597743988</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.074462890625</v>
       </c>
       <c r="G480" t="n">
-        <v>2.54328942298889</v>
+        <v>2.54328918457031</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.15101289749146</v>
       </c>
       <c r="G481" t="n">
-        <v>2.60661435127258</v>
+        <v>2.606614112854</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.04419898986816</v>
       </c>
       <c r="G482" t="n">
-        <v>2.51825404167175</v>
+        <v>2.51825428009033</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.90712094306946</v>
       </c>
       <c r="G485" t="n">
-        <v>2.4048593044281</v>
+        <v>2.40485906600952</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G488" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.10828804969788</v>
       </c>
       <c r="G490" t="n">
-        <v>2.57127046585083</v>
+        <v>2.57127070426941</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.93738508224487</v>
       </c>
       <c r="G493" t="n">
-        <v>2.42989444732666</v>
+        <v>2.42989468574524</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.94094610214233</v>
       </c>
       <c r="G494" t="n">
-        <v>2.43284034729004</v>
+        <v>2.43284010887146</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G495" t="n">
-        <v>2.35920667648315</v>
+        <v>2.35920643806458</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G496" t="n">
-        <v>2.35920667648315</v>
+        <v>2.35920643806458</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G497" t="n">
-        <v>2.35920667648315</v>
+        <v>2.35920643806458</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.95518708229065</v>
       </c>
       <c r="G501" t="n">
-        <v>2.44462060928345</v>
+        <v>2.44462084770203</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.85905504226685</v>
       </c>
       <c r="G508" t="n">
-        <v>2.36509776115417</v>
+        <v>2.3650975227356</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>3.33750009536743</v>
       </c>
       <c r="G514" t="n">
-        <v>2.76088166236877</v>
+        <v>2.76088190078735</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G517" t="n">
-        <v>2.70917987823486</v>
+        <v>2.70918011665344</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G528" t="n">
-        <v>2.0432596206665</v>
+        <v>2.04325938224792</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G531" t="n">
-        <v>1.86540484428406</v>
+        <v>1.86540508270264</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>1.82817947864532</v>
+        <v>1.82817935943604</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84058785438538</v>
+        <v>1.8405876159668</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G535" t="n">
-        <v>1.81577086448669</v>
+        <v>1.8157707452774</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G537" t="n">
-        <v>1.74545621871948</v>
+        <v>1.74545633792877</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>1.77854585647583</v>
+        <v>1.77854561805725</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G545" t="n">
-        <v>1.81577086448669</v>
+        <v>1.8157707452774</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G547" t="n">
-        <v>1.77440941333771</v>
+        <v>1.774409532547</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G548" t="n">
-        <v>1.74545621871948</v>
+        <v>1.74545633792877</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>1.80336260795593</v>
+        <v>1.80336236953735</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G551" t="n">
-        <v>1.77440941333771</v>
+        <v>1.774409532547</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G553" t="n">
-        <v>1.76613712310791</v>
+        <v>1.76613700389862</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G554" t="n">
-        <v>1.73304784297943</v>
+        <v>1.73304796218872</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G555" t="n">
-        <v>1.71650338172913</v>
+        <v>1.71650326251984</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>1.77440941333771</v>
+        <v>1.774409532547</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>1.77854585647583</v>
+        <v>1.77854561805725</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>1.77854585647583</v>
+        <v>1.77854561805725</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G559" t="n">
-        <v>1.80336260795593</v>
+        <v>1.80336236953735</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G560" t="n">
-        <v>1.79509019851685</v>
+        <v>1.79509031772614</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G563" t="n">
-        <v>1.75372838973999</v>
+        <v>1.75372850894928</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G564" t="n">
-        <v>1.76613712310791</v>
+        <v>1.76613700389862</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G565" t="n">
-        <v>1.77440941333771</v>
+        <v>1.774409532547</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G568" t="n">
-        <v>1.74545621871948</v>
+        <v>1.74545633792877</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>1.72477555274963</v>
+        <v>1.72477579116821</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>1.72477555274963</v>
+        <v>1.72477579116821</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G571" t="n">
-        <v>1.79509019851685</v>
+        <v>1.79509031772614</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G572" t="n">
-        <v>1.74545621871948</v>
+        <v>1.74545633792877</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G573" t="n">
-        <v>1.73304784297943</v>
+        <v>1.73304796218872</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G574" t="n">
-        <v>1.77440941333771</v>
+        <v>1.774409532547</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G576" t="n">
-        <v>1.77854585647583</v>
+        <v>1.77854561805725</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G580" t="n">
-        <v>1.89022159576416</v>
+        <v>1.89022207260132</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G584" t="n">
-        <v>1.9894894361496</v>
+        <v>1.98948967456818</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>1.99362540245056</v>
+        <v>1.99362564086914</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G589" t="n">
-        <v>2.34726667404175</v>
+        <v>2.34726643562317</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>2.34726667404175</v>
+        <v>2.34726643562317</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.63750004768372</v>
       </c>
       <c r="G596" t="n">
-        <v>2.18182039260864</v>
+        <v>2.18182015419006</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.63750004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>2.18182039260864</v>
+        <v>2.18182015419006</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.71250009536743</v>
       </c>
       <c r="G600" t="n">
-        <v>2.24386262893677</v>
+        <v>2.24386286735535</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G605" t="n">
-        <v>2.08875703811646</v>
+        <v>2.08875727653503</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G614" t="n">
-        <v>1.86540484428406</v>
+        <v>1.86540508270264</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>1.8447242975235</v>
+        <v>1.84472405910492</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G618" t="n">
-        <v>1.96880865097046</v>
+        <v>1.96880841255188</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G619" t="n">
-        <v>1.89022159576416</v>
+        <v>1.89022207260132</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G620" t="n">
-        <v>1.98121726512909</v>
+        <v>1.98121702671051</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G621" t="n">
-        <v>1.9481281042099</v>
+        <v>1.94812786579132</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G622" t="n">
-        <v>1.86540484428406</v>
+        <v>1.86540508270264</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G625" t="n">
-        <v>1.9398558139801</v>
+        <v>1.93985557556152</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.25</v>
       </c>
       <c r="G628" t="n">
-        <v>1.8612687587738</v>
+        <v>1.86126852035522</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.25</v>
       </c>
       <c r="G629" t="n">
-        <v>1.8612687587738</v>
+        <v>1.86126852035522</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.25</v>
       </c>
       <c r="G631" t="n">
-        <v>1.8612687587738</v>
+        <v>1.86126852035522</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G639" t="n">
-        <v>1.85299623012543</v>
+        <v>1.85299646854401</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>1.79095387458801</v>
+        <v>1.7909539937973</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G642" t="n">
-        <v>1.81163489818573</v>
+        <v>1.81163501739502</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G644" t="n">
-        <v>1.81163489818573</v>
+        <v>1.81163501739502</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>1.77440941333771</v>
+        <v>1.774409532547</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G647" t="n">
-        <v>1.80749869346619</v>
+        <v>1.8074985742569</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.75372838973999</v>
+        <v>1.75372850894928</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G651" t="n">
-        <v>1.7826817035675</v>
+        <v>1.78268158435822</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>1.79509019851685</v>
+        <v>1.79509031772614</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G655" t="n">
-        <v>1.79591727256775</v>
+        <v>1.79591739177704</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G657" t="n">
-        <v>1.85134184360504</v>
+        <v>1.85134160518646</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G658" t="n">
-        <v>1.85299623012543</v>
+        <v>1.85299646854401</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G660" t="n">
-        <v>1.79839909076691</v>
+        <v>1.79839897155762</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.17549991607666</v>
       </c>
       <c r="G661" t="n">
-        <v>1.79964005947113</v>
+        <v>1.79963982105255</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>1.79095387458801</v>
+        <v>1.7909539937973</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G667" t="n">
-        <v>1.83727872371674</v>
+        <v>1.83727896213531</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G669" t="n">
-        <v>1.832315325737</v>
+        <v>1.83231544494629</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G672" t="n">
-        <v>1.75372838973999</v>
+        <v>1.75372850894928</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G673" t="n">
-        <v>1.76200103759766</v>
+        <v>1.76200115680695</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G674" t="n">
-        <v>1.75207436084747</v>
+        <v>1.75207412242889</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.75479996204376</v>
       </c>
       <c r="G679" t="n">
-        <v>1.45162403583527</v>
+        <v>1.45162391662598</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>1.73259997367859</v>
       </c>
       <c r="G682" t="n">
-        <v>1.43325960636139</v>
+        <v>1.4332594871521</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.75960004329681</v>
       </c>
       <c r="G683" t="n">
-        <v>1.4555948972702</v>
+        <v>1.45559501647949</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G684" t="n">
-        <v>1.47329759597778</v>
+        <v>1.47329747676849</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>1.74440002441406</v>
       </c>
       <c r="G688" t="n">
-        <v>1.44302093982697</v>
+        <v>1.44302082061768</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>1.47247040271759</v>
+        <v>1.4724702835083</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.76979994773865</v>
       </c>
       <c r="G690" t="n">
-        <v>1.46403253078461</v>
+        <v>1.46403241157532</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.73459994792938</v>
       </c>
       <c r="G691" t="n">
-        <v>1.43491399288177</v>
+        <v>1.43491411209106</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>1.73539996147156</v>
       </c>
       <c r="G695" t="n">
-        <v>1.43557572364807</v>
+        <v>1.43557584285736</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G696" t="n">
-        <v>1.42531836032867</v>
+        <v>1.42531824111938</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G697" t="n">
-        <v>1.42531836032867</v>
+        <v>1.42531824111938</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G698" t="n">
-        <v>1.41952741146088</v>
+        <v>1.41952753067017</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>1.67960000038147</v>
       </c>
       <c r="G704" t="n">
-        <v>1.38941621780396</v>
+        <v>1.38941633701324</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G706" t="n">
-        <v>1.41952741146088</v>
+        <v>1.41952753067017</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.71539998054504</v>
       </c>
       <c r="G707" t="n">
-        <v>1.41903114318848</v>
+        <v>1.41903126239777</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G710" t="n">
-        <v>1.35665810108185</v>
+        <v>1.35665786266327</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.72019994258881</v>
       </c>
       <c r="G712" t="n">
-        <v>1.42300200462341</v>
+        <v>1.42300188541412</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G713" t="n">
-        <v>1.45592570304871</v>
+        <v>1.45592558383942</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.73459994792938</v>
       </c>
       <c r="G717" t="n">
-        <v>1.43491399288177</v>
+        <v>1.43491411209106</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.73539996147156</v>
       </c>
       <c r="G720" t="n">
-        <v>1.43557572364807</v>
+        <v>1.43557584285736</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.81120002269745</v>
       </c>
       <c r="G724" t="n">
-        <v>1.49827992916107</v>
+        <v>1.49827980995178</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.81980001926422</v>
       </c>
       <c r="G726" t="n">
-        <v>1.50539422035217</v>
+        <v>1.50539410114288</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.79120004177094</v>
       </c>
       <c r="G727" t="n">
-        <v>1.48173534870148</v>
+        <v>1.48173522949219</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G729" t="n">
-        <v>1.51796805858612</v>
+        <v>1.51796793937683</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G730" t="n">
-        <v>1.48653340339661</v>
+        <v>1.48653328418732</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G731" t="n">
-        <v>1.48653340339661</v>
+        <v>1.48653328418732</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.7985999584198</v>
       </c>
       <c r="G734" t="n">
-        <v>1.4878568649292</v>
+        <v>1.48785674571991</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G739" t="n">
-        <v>1.48884952068329</v>
+        <v>1.48884963989258</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.77240002155304</v>
       </c>
       <c r="G742" t="n">
-        <v>1.46618330478668</v>
+        <v>1.46618342399597</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G743" t="n">
-        <v>1.48156976699829</v>
+        <v>1.48156988620758</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G746" t="n">
-        <v>1.47329759597778</v>
+        <v>1.47329747676849</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G747" t="n">
-        <v>1.46916127204895</v>
+        <v>1.46916139125824</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.78120005130768</v>
       </c>
       <c r="G748" t="n">
-        <v>1.47346305847168</v>
+        <v>1.47346317768097</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G749" t="n">
-        <v>1.48156976699829</v>
+        <v>1.48156988620758</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G750" t="n">
-        <v>1.47329759597778</v>
+        <v>1.47329747676849</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G752" t="n">
-        <v>1.48884952068329</v>
+        <v>1.48884963989258</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G753" t="n">
-        <v>1.47329759597778</v>
+        <v>1.47329747676849</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.88940000534058</v>
       </c>
       <c r="G756" t="n">
-        <v>1.56296932697296</v>
+        <v>1.56296944618225</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.90240001678467</v>
       </c>
       <c r="G757" t="n">
-        <v>1.64630579948425</v>
+        <v>1.64630568027496</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.94959998130798</v>
       </c>
       <c r="G766" t="n">
-        <v>1.68715178966522</v>
+        <v>1.68715190887451</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.94959998130798</v>
       </c>
       <c r="G768" t="n">
-        <v>1.68715178966522</v>
+        <v>1.68715190887451</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.94959998130798</v>
       </c>
       <c r="G769" t="n">
-        <v>1.68715178966522</v>
+        <v>1.68715190887451</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.94760000705719</v>
       </c>
       <c r="G770" t="n">
-        <v>1.68542098999023</v>
+        <v>1.68542110919952</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.94980001449585</v>
       </c>
       <c r="G774" t="n">
-        <v>1.68732500076294</v>
+        <v>1.68732488155365</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.95860004425049</v>
       </c>
       <c r="G776" t="n">
-        <v>1.69494044780731</v>
+        <v>1.69494032859802</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.87839996814728</v>
       </c>
       <c r="G784" t="n">
-        <v>1.62553644180298</v>
+        <v>1.62553656101227</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.87220001220703</v>
       </c>
       <c r="G785" t="n">
-        <v>1.62017130851746</v>
+        <v>1.62017118930817</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.89859998226166</v>
       </c>
       <c r="G790" t="n">
-        <v>1.64301729202271</v>
+        <v>1.64301717281342</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.84860002994537</v>
       </c>
       <c r="G796" t="n">
-        <v>1.59974825382233</v>
+        <v>1.59974813461304</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G798" t="n">
-        <v>1.6191326379776</v>
+        <v>1.61913275718689</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.84959995746613</v>
       </c>
       <c r="G799" t="n">
-        <v>1.6006133556366</v>
+        <v>1.60061347484589</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G802" t="n">
-        <v>1.62345957756042</v>
+        <v>1.62345969676971</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G811" t="n">
-        <v>1.57932507991791</v>
+        <v>1.5793251991272</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G815" t="n">
-        <v>1.54211342334747</v>
+        <v>1.54211354255676</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G818" t="n">
-        <v>1.52913284301758</v>
+        <v>1.52913272380829</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.76960003376007</v>
       </c>
       <c r="G819" t="n">
-        <v>1.53138291835785</v>
+        <v>1.53138279914856</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.75</v>
       </c>
       <c r="G822" t="n">
-        <v>1.51442134380341</v>
+        <v>1.51442122459412</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.72560000419617</v>
       </c>
       <c r="G826" t="n">
-        <v>1.49330604076385</v>
+        <v>1.49330592155457</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G829" t="n">
-        <v>1.47115218639374</v>
+        <v>1.47115206718445</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G832" t="n">
-        <v>1.49711358547211</v>
+        <v>1.4971137046814</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G834" t="n">
-        <v>1.47115218639374</v>
+        <v>1.47115206718445</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>1.47115218639374</v>
+        <v>1.47115206718445</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G836" t="n">
-        <v>1.47547900676727</v>
+        <v>1.47547912597656</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.75</v>
       </c>
       <c r="G837" t="n">
-        <v>1.51442134380341</v>
+        <v>1.51442122459412</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G842" t="n">
-        <v>1.44519054889679</v>
+        <v>1.44519066810608</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G843" t="n">
-        <v>1.44519054889679</v>
+        <v>1.44519066810608</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G844" t="n">
-        <v>1.47115218639374</v>
+        <v>1.47115206718445</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G845" t="n">
-        <v>1.47115218639374</v>
+        <v>1.47115206718445</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G849" t="n">
-        <v>1.45817124843597</v>
+        <v>1.45817136764526</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G850" t="n">
-        <v>1.47115218639374</v>
+        <v>1.47115206718445</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G853" t="n">
-        <v>1.44519054889679</v>
+        <v>1.44519066810608</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G856" t="n">
-        <v>1.34134447574615</v>
+        <v>1.34134459495544</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G857" t="n">
-        <v>1.3673061132431</v>
+        <v>1.36730599403381</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G865" t="n">
-        <v>1.41922914981842</v>
+        <v>1.41922891139984</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G866" t="n">
-        <v>1.41922914981842</v>
+        <v>1.41922891139984</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G873" t="n">
-        <v>1.41922914981842</v>
+        <v>1.41922891139984</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>1.33269083499908</v>
+        <v>1.33269059658051</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G887" t="n">
-        <v>1.37163293361664</v>
+        <v>1.37163317203522</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G888" t="n">
-        <v>1.33701753616333</v>
+        <v>1.33701765537262</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G890" t="n">
-        <v>1.31970989704132</v>
+        <v>1.31971001625061</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>1.33269083499908</v>
+        <v>1.33269059658051</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G893" t="n">
-        <v>1.31970989704132</v>
+        <v>1.31971001625061</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G903" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G905" t="n">
-        <v>1.43948984146118</v>
+        <v>1.43948972225189</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G908" t="n">
-        <v>1.4128326177597</v>
+        <v>1.41283249855042</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G914" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G915" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G916" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G920" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G921" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G922" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G923" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G924" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G927" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G929" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.625</v>
       </c>
       <c r="G930" t="n">
-        <v>1.44393253326416</v>
+        <v>1.44393265247345</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G931" t="n">
-        <v>1.43948984146118</v>
+        <v>1.43948972225189</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G936" t="n">
-        <v>1.43948984146118</v>
+        <v>1.43948972225189</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G937" t="n">
-        <v>1.45726132392883</v>
+        <v>1.45726120471954</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G939" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G942" t="n">
-        <v>1.4128326177597</v>
+        <v>1.41283249855042</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G943" t="n">
-        <v>1.4128326177597</v>
+        <v>1.41283249855042</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G944" t="n">
-        <v>1.4128326177597</v>
+        <v>1.41283249855042</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G949" t="n">
-        <v>1.4128326177597</v>
+        <v>1.41283249855042</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G950" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G953" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G954" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G957" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G967" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G968" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G971" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G973" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G974" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G995" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.30176079273224</v>
+        <v>1.30176091194153</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.45726132392883</v>
+        <v>1.45726120471954</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.25</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.15958881378174</v>
+        <v>1.15958893299103</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>1.25</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.25</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.25</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.25</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.25</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.10627448558807</v>
+        <v>1.10627460479736</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.05740308761597</v>
+        <v>1.05740296840668</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.15070331096649</v>
+        <v>1.1507031917572</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.21290338039398</v>
+        <v>1.21290349960327</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.21290338039398</v>
+        <v>1.21290349960327</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.21290338039398</v>
+        <v>1.21290349960327</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.15070331096649</v>
+        <v>1.1507031917572</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.16403186321259</v>
+        <v>1.1640317440033</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.10627448558807</v>
+        <v>1.10627460479736</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.15958881378174</v>
+        <v>1.15958893299103</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.15958881378174</v>
+        <v>1.15958893299103</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.15070331096649</v>
+        <v>1.1507031917572</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.16403186321259</v>
+        <v>1.1640317440033</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.25</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.02186000347137</v>
+        <v>1.02185988426208</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.00853145122528</v>
+        <v>1.00853133201599</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.964102685451508</v>
+        <v>0.964102804660797</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.933002650737762</v>
+        <v>0.933002531528473</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.968545615673065</v>
+        <v>0.96854555606842</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.25</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.12848889827728</v>
+        <v>1.12848877906799</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.10627448558807</v>
+        <v>1.10627460479736</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.10627448558807</v>
+        <v>1.10627460479736</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.25</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.25</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.25</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.25</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.10627448558807</v>
+        <v>1.10627460479736</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.10627448558807</v>
+        <v>1.10627460479736</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.25</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.11071741580963</v>
+        <v>1.11071729660034</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.09738886356354</v>
+        <v>1.09738874435425</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.46170401573181</v>
+        <v>1.4617041349411</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.55056142807007</v>
+        <v>1.55056154727936</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.69273316860199</v>
+        <v>1.69273328781128</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.71050477027893</v>
+        <v>1.71050488948822</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.652747631073</v>
+        <v>1.65274751186371</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.68384754657745</v>
+        <v>1.68384766578674</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.58610427379608</v>
+        <v>1.58610439300537</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.63941884040833</v>
+        <v>1.63941895961761</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.5949901342392</v>
+        <v>1.59499025344849</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.5949901342392</v>
+        <v>1.59499025344849</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.58610427379608</v>
+        <v>1.58610439300537</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.62164747714996</v>
+        <v>1.62164759635925</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.55056142807007</v>
+        <v>1.55056154727936</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.59943306446075</v>
+        <v>1.59943294525146</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.59943306446075</v>
+        <v>1.59943294525146</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.68384754657745</v>
+        <v>1.68384766578674</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.71050477027893</v>
+        <v>1.71050488948822</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.68384754657745</v>
+        <v>1.68384766578674</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1415" t="n">
-        <v>2.01706290245056</v>
+        <v>2.01706266403198</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.85711932182312</v>
+        <v>1.85711944103241</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.90154826641083</v>
+        <v>1.90154814720154</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.90154826641083</v>
+        <v>1.90154814720154</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.90154826641083</v>
+        <v>1.90154814720154</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.04372000694275</v>
+        <v>2.04371976852417</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.11480617523193</v>
+        <v>2.11480593681335</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.04372000694275</v>
+        <v>2.04371976852417</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.91931974887848</v>
+        <v>1.91931962966919</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.04372000694275</v>
+        <v>2.04371976852417</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.04372000694275</v>
+        <v>2.04371976852417</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.03483414649963</v>
+        <v>2.03483438491821</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1486" t="n">
-        <v>2.01706290245056</v>
+        <v>2.01706266403198</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.03483414649963</v>
+        <v>2.03483438491821</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.01706290245056</v>
+        <v>2.01706266403198</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.91931974887848</v>
+        <v>1.91931962966919</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709111213684</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.85711932182312</v>
+        <v>1.85711944103241</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.83934783935547</v>
+        <v>1.83934795856476</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.92820537090302</v>
+        <v>1.92820560932159</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.92820537090302</v>
+        <v>1.92820560932159</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.83934783935547</v>
+        <v>1.83934795856476</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.83934783935547</v>
+        <v>1.83934795856476</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.90154826641083</v>
+        <v>1.90154814720154</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.92820537090302</v>
+        <v>1.92820560932159</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.90154826641083</v>
+        <v>1.90154814720154</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.90154826641083</v>
+        <v>1.90154814720154</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.85711932182312</v>
+        <v>1.85711944103241</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.04372000694275</v>
+        <v>2.04371976852417</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.83934783935547</v>
+        <v>1.83934795856476</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.85711932182312</v>
+        <v>1.85711944103241</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.80380499362946</v>
+        <v>1.80380511283875</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.80380499362946</v>
+        <v>1.80380511283875</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.74160504341125</v>
+        <v>1.74160492420197</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.74604773521423</v>
+        <v>1.74604785442352</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.73716199398041</v>
+        <v>1.7371621131897</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.54167568683624</v>
+        <v>1.54167580604553</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.56833291053772</v>
+        <v>1.56833302974701</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1577" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.652747631073</v>
+        <v>1.65274751186371</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.60387587547302</v>
+        <v>1.60387599468231</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.60387587547302</v>
+        <v>1.60387599468231</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.5949901342392</v>
+        <v>1.59499025344849</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.54611873626709</v>
+        <v>1.5461186170578</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.55056142807007</v>
+        <v>1.55056154727936</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.55056142807007</v>
+        <v>1.55056154727936</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1596" t="n">
-        <v>1.54611873626709</v>
+        <v>1.5461186170578</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.54167568683624</v>
+        <v>1.54167580604553</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.54167568683624</v>
+        <v>1.54167580604553</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.5949901342392</v>
+        <v>1.59499025344849</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.58610427379608</v>
+        <v>1.58610439300537</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.71050477027893</v>
+        <v>1.71050488948822</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>2.5</v>
       </c>
       <c r="G1612" t="n">
-        <v>2.22143483161926</v>
+        <v>2.22143459320068</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.91931974887848</v>
+        <v>1.91931962966919</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1622" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1625" t="n">
-        <v>1.84823381900787</v>
+        <v>1.84823369979858</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1626" t="n">
-        <v>1.80380499362946</v>
+        <v>1.80380511283875</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1629" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709111213684</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>1.92820537090302</v>
+        <v>1.92820560932159</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1632" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709111213684</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.90154826641083</v>
+        <v>1.90154814720154</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1634" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709111213684</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1638" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.71050477027893</v>
+        <v>1.71050488948822</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1644" t="n">
-        <v>1.74160504341125</v>
+        <v>1.74160492420197</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1645" t="n">
-        <v>1.79491937160492</v>
+        <v>1.79491925239563</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709111213684</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1653" t="n">
-        <v>1.85711932182312</v>
+        <v>1.85711944103241</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1654" t="n">
-        <v>1.86600530147552</v>
+        <v>1.86600506305695</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.79491937160492</v>
+        <v>1.79491925239563</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.69273316860199</v>
+        <v>1.69273328781128</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1670" t="n">
-        <v>1.74160504341125</v>
+        <v>1.74160492420197</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1672" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1677" t="n">
-        <v>1.80380499362946</v>
+        <v>1.80380511283875</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.79491937160492</v>
+        <v>1.79491925239563</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.76381921768188</v>
+        <v>1.76381933689117</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.73716199398041</v>
+        <v>1.7371621131897</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.62164747714996</v>
+        <v>1.62164759635925</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1705" t="n">
-        <v>1.68384754657745</v>
+        <v>1.68384766578674</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1706" t="n">
-        <v>1.68384754657745</v>
+        <v>1.68384766578674</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.51057577133179</v>
+        <v>1.5105756521225</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1721" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1722" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1723" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1724" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1734" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.21290338039398</v>
+        <v>1.21290349960327</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1749" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1753" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1756" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1765" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1773" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1789" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1797" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1800" t="n">
-        <v>1.30176079273224</v>
+        <v>1.30176091194153</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1805" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.38617527484894</v>
+        <v>1.38617515563965</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1809" t="n">
-        <v>1.30176079273224</v>
+        <v>1.30176091194153</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1822" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.30176079273224</v>
+        <v>1.30176091194153</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.27954638004303</v>
+        <v>1.27954649925232</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1845" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1850" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.21290338039398</v>
+        <v>1.21290349960327</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1862" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.15070331096649</v>
+        <v>1.1507031917572</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1939" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1965" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.30176079273224</v>
+        <v>1.30176091194153</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1979" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.27066075801849</v>
+        <v>1.2706606388092</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51927,7 +51927,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1983" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1983" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.21734631061554</v>
+        <v>1.21734619140625</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.16403186321259</v>
+        <v>1.1640317440033</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.16403186321259</v>
+        <v>1.1640317440033</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52733,7 +52733,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G2014" t="n">
-        <v>1.22623193264008</v>
+        <v>1.22623205184937</v>
       </c>
       <c r="H2014" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.30176079273224</v>
+        <v>1.30176091194153</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2018" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2025" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53097,7 +53097,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2028" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H2028" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G2030" t="n">
-        <v>1.30176079273224</v>
+        <v>1.30176091194153</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.51501858234406</v>
+        <v>1.51501870155334</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2037" t="n">
-        <v>1.652747631073</v>
+        <v>1.65274751186371</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2039" t="n">
-        <v>1.69273316860199</v>
+        <v>1.69273328781128</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2040" t="n">
-        <v>1.652747631073</v>
+        <v>1.65274751186371</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53513,7 +53513,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2044" t="n">
-        <v>1.54167568683624</v>
+        <v>1.54167580604553</v>
       </c>
       <c r="H2044" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2045" t="n">
-        <v>1.54611873626709</v>
+        <v>1.5461186170578</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2048" t="n">
-        <v>1.56833291053772</v>
+        <v>1.56833302974701</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G2050" t="n">
-        <v>1.49724698066711</v>
+        <v>1.4972470998764</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.51057577133179</v>
+        <v>1.5105756521225</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2053" t="n">
-        <v>1.49280416965485</v>
+        <v>1.49280405044556</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>1.625</v>
       </c>
       <c r="G2056" t="n">
-        <v>1.44393253326416</v>
+        <v>1.44393265247345</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2058" t="n">
-        <v>1.43948984146118</v>
+        <v>1.43948972225189</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2060" t="n">
-        <v>1.49280416965485</v>
+        <v>1.49280405044556</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2061" t="n">
-        <v>1.49280416965485</v>
+        <v>1.49280405044556</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54007,7 +54007,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2063" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H2063" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.35063242912292</v>
+        <v>1.35063230991364</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.31953227519989</v>
+        <v>1.31953239440918</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2087" t="n">
-        <v>1.43948984146118</v>
+        <v>1.43948972225189</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.36840391159058</v>
+        <v>1.36840379238129</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2095" t="n">
-        <v>1.43948984146118</v>
+        <v>1.43948972225189</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54969,7 +54969,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2100" t="n">
-        <v>1.63941884040833</v>
+        <v>1.63941895961761</v>
       </c>
       <c r="H2100" t="s">
         <v>8</v>
@@ -54995,7 +54995,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2101" t="n">
-        <v>1.63941884040833</v>
+        <v>1.63941895961761</v>
       </c>
       <c r="H2101" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2102" t="n">
-        <v>1.60387587547302</v>
+        <v>1.60387599468231</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G2108" t="n">
-        <v>1.51501858234406</v>
+        <v>1.51501870155334</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.4128326177597</v>
+        <v>1.41283249855042</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2115" t="n">
-        <v>1.40394687652588</v>
+        <v>1.40394675731659</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.40838968753815</v>
+        <v>1.40838980674744</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55437,7 +55437,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G2118" t="n">
-        <v>1.45726132392883</v>
+        <v>1.45726120471954</v>
       </c>
       <c r="H2118" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G2125" t="n">
-        <v>1.63329350948334</v>
+        <v>1.63329362869263</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2132" t="n">
-        <v>1.55463635921478</v>
+        <v>1.55463624000549</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55827,7 +55827,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2133" t="n">
-        <v>1.55463635921478</v>
+        <v>1.55463624000549</v>
       </c>
       <c r="H2133" t="s">
         <v>8</v>
@@ -55879,7 +55879,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G2135" t="n">
-        <v>1.55926311016083</v>
+        <v>1.55926322937012</v>
       </c>
       <c r="H2135" t="s">
         <v>8</v>
@@ -55905,7 +55905,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.51762127876282</v>
+        <v>1.51762115955353</v>
       </c>
       <c r="H2136" t="s">
         <v>8</v>
@@ -56009,7 +56009,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2140" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2141" t="n">
-        <v>1.46672534942627</v>
+        <v>1.46672546863556</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2143" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56139,7 +56139,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2145" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2145" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2146" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.47135233879089</v>
+        <v>1.4713522195816</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56451,7 +56451,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2157" t="s">
         <v>8</v>
@@ -56503,7 +56503,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2159" t="s">
         <v>8</v>
@@ -56555,7 +56555,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2161" t="n">
-        <v>1.47135233879089</v>
+        <v>1.4713522195816</v>
       </c>
       <c r="H2161" t="s">
         <v>8</v>
@@ -56581,7 +56581,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2162" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2162" t="s">
         <v>8</v>
@@ -56607,7 +56607,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2163" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2163" t="s">
         <v>8</v>
@@ -56737,7 +56737,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2168" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2168" t="s">
         <v>8</v>
@@ -56841,7 +56841,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2172" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2172" t="s">
         <v>8</v>
@@ -56867,7 +56867,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2173" t="n">
-        <v>1.46672534942627</v>
+        <v>1.46672546863556</v>
       </c>
       <c r="H2173" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2174" t="n">
-        <v>1.46672534942627</v>
+        <v>1.46672546863556</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2175" t="n">
-        <v>1.47135233879089</v>
+        <v>1.4713522195816</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -56945,7 +56945,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2176" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2176" t="s">
         <v>8</v>
@@ -56971,7 +56971,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2177" t="n">
-        <v>1.46672534942627</v>
+        <v>1.46672546863556</v>
       </c>
       <c r="H2177" t="s">
         <v>8</v>
@@ -57023,7 +57023,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2179" t="n">
-        <v>1.47135233879089</v>
+        <v>1.4713522195816</v>
       </c>
       <c r="H2179" t="s">
         <v>8</v>
@@ -57049,7 +57049,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2180" t="n">
-        <v>1.47135233879089</v>
+        <v>1.4713522195816</v>
       </c>
       <c r="H2180" t="s">
         <v>8</v>
@@ -57075,7 +57075,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2181" t="n">
-        <v>1.46672534942627</v>
+        <v>1.46672546863556</v>
       </c>
       <c r="H2181" t="s">
         <v>8</v>
@@ -57127,7 +57127,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2183" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2183" t="s">
         <v>8</v>
@@ -57153,7 +57153,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2184" t="s">
         <v>8</v>
@@ -57179,7 +57179,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2185" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2185" t="s">
         <v>8</v>
@@ -57205,7 +57205,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2186" t="s">
         <v>8</v>
@@ -57231,7 +57231,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2187" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2187" t="s">
         <v>8</v>
@@ -57257,7 +57257,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G2188" t="n">
-        <v>1.31866466999054</v>
+        <v>1.31866478919983</v>
       </c>
       <c r="H2188" t="s">
         <v>8</v>
@@ -57361,7 +57361,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G2192" t="n">
-        <v>1.37418746948242</v>
+        <v>1.37418758869171</v>
       </c>
       <c r="H2192" t="s">
         <v>8</v>
@@ -57387,7 +57387,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G2193" t="n">
-        <v>1.37418746948242</v>
+        <v>1.37418758869171</v>
       </c>
       <c r="H2193" t="s">
         <v>8</v>
@@ -57595,7 +57595,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2201" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2201" t="s">
         <v>8</v>
@@ -57621,7 +57621,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2202" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57699,7 +57699,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2205" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2205" t="s">
         <v>8</v>
@@ -57725,7 +57725,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2206" t="s">
         <v>8</v>
@@ -57777,7 +57777,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2208" t="s">
         <v>8</v>
@@ -57803,7 +57803,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2209" t="s">
         <v>8</v>
@@ -57881,7 +57881,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2212" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2212" t="s">
         <v>8</v>
@@ -57933,7 +57933,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.32329165935516</v>
+        <v>1.32329154014587</v>
       </c>
       <c r="H2214" t="s">
         <v>8</v>
@@ -57959,7 +57959,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G2215" t="n">
-        <v>1.31866466999054</v>
+        <v>1.31866478919983</v>
       </c>
       <c r="H2215" t="s">
         <v>8</v>
@@ -58089,7 +58089,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2220" t="n">
-        <v>1.41120254993439</v>
+        <v>1.41120266914368</v>
       </c>
       <c r="H2220" t="s">
         <v>8</v>
@@ -58115,7 +58115,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2221" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2221" t="s">
         <v>8</v>
@@ -58141,7 +58141,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2222" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2222" t="s">
         <v>8</v>
@@ -58193,7 +58193,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2224" t="s">
         <v>8</v>
@@ -58219,7 +58219,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2225" t="n">
-        <v>1.46209859848022</v>
+        <v>1.46209847927094</v>
       </c>
       <c r="H2225" t="s">
         <v>8</v>
@@ -58297,7 +58297,7 @@
         <v>1.625</v>
       </c>
       <c r="G2228" t="n">
-        <v>1.50374042987823</v>
+        <v>1.50374054908752</v>
       </c>
       <c r="H2228" t="s">
         <v>8</v>
@@ -58375,7 +58375,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2231" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2231" t="s">
         <v>8</v>
@@ -58401,7 +58401,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2232" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2232" t="s">
         <v>8</v>
@@ -58479,7 +58479,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.52224802970886</v>
+        <v>1.52224814891815</v>
       </c>
       <c r="H2235" t="s">
         <v>8</v>
@@ -58505,7 +58505,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2236" t="n">
-        <v>1.52224802970886</v>
+        <v>1.52224814891815</v>
       </c>
       <c r="H2236" t="s">
         <v>8</v>
@@ -58635,7 +58635,7 @@
         <v>1.625</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.50374042987823</v>
+        <v>1.50374054908752</v>
       </c>
       <c r="H2241" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.51762127876282</v>
+        <v>1.51762115955353</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58921,7 +58921,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2252" t="s">
         <v>8</v>
@@ -58999,7 +58999,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2255" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2255" t="s">
         <v>8</v>
@@ -59051,7 +59051,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2257" t="n">
-        <v>1.41120254993439</v>
+        <v>1.41120266914368</v>
       </c>
       <c r="H2257" t="s">
         <v>8</v>
@@ -59077,7 +59077,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G2258" t="n">
-        <v>1.37418746948242</v>
+        <v>1.37418758869171</v>
       </c>
       <c r="H2258" t="s">
         <v>8</v>
@@ -59155,7 +59155,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2261" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2261" t="s">
         <v>8</v>
@@ -59181,7 +59181,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2262" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2262" t="s">
         <v>8</v>
@@ -59285,7 +59285,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2266" t="n">
-        <v>1.65180099010468</v>
+        <v>1.65180110931396</v>
       </c>
       <c r="H2266" t="s">
         <v>8</v>
@@ -59415,7 +59415,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2271" t="n">
-        <v>1.61015915870667</v>
+        <v>1.61015903949738</v>
       </c>
       <c r="H2271" t="s">
         <v>8</v>
@@ -59467,7 +59467,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G2273" t="n">
-        <v>1.61478590965271</v>
+        <v>1.614786028862</v>
       </c>
       <c r="H2273" t="s">
         <v>8</v>
@@ -59597,7 +59597,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2278" t="n">
-        <v>1.66568183898926</v>
+        <v>1.66568171977997</v>
       </c>
       <c r="H2278" t="s">
         <v>8</v>
@@ -59623,7 +59623,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2279" t="n">
-        <v>1.66568183898926</v>
+        <v>1.66568171977997</v>
       </c>
       <c r="H2279" t="s">
         <v>8</v>
@@ -59779,7 +59779,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G2285" t="n">
-        <v>1.61478590965271</v>
+        <v>1.614786028862</v>
       </c>
       <c r="H2285" t="s">
         <v>8</v>
@@ -59935,7 +59935,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2291" t="n">
-        <v>1.66568183898926</v>
+        <v>1.66568171977997</v>
       </c>
       <c r="H2291" t="s">
         <v>8</v>
@@ -60065,7 +60065,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2296" t="n">
-        <v>1.60553216934204</v>
+        <v>1.60553228855133</v>
       </c>
       <c r="H2296" t="s">
         <v>8</v>
@@ -60221,7 +60221,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G2302" t="n">
-        <v>1.51762127876282</v>
+        <v>1.51762115955353</v>
       </c>
       <c r="H2302" t="s">
         <v>8</v>
@@ -60273,7 +60273,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2304" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2304" t="s">
         <v>8</v>
@@ -60299,7 +60299,7 @@
         <v>1.625</v>
       </c>
       <c r="G2305" t="n">
-        <v>1.50374042987823</v>
+        <v>1.50374054908752</v>
       </c>
       <c r="H2305" t="s">
         <v>8</v>
@@ -60325,7 +60325,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2306" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2306" t="s">
         <v>8</v>
@@ -60455,7 +60455,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2311" t="n">
-        <v>1.46672534942627</v>
+        <v>1.46672546863556</v>
       </c>
       <c r="H2311" t="s">
         <v>8</v>
@@ -60533,7 +60533,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2314" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2314" t="s">
         <v>8</v>
@@ -60559,7 +60559,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G2315" t="n">
-        <v>1.42508339881897</v>
+        <v>1.42508327960968</v>
       </c>
       <c r="H2315" t="s">
         <v>8</v>
@@ -60637,7 +60637,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2318" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2318" t="s">
         <v>8</v>
@@ -60689,7 +60689,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2320" t="n">
-        <v>1.49911367893219</v>
+        <v>1.4991135597229</v>
       </c>
       <c r="H2320" t="s">
         <v>8</v>
@@ -60741,7 +60741,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2322" t="n">
-        <v>1.47135233879089</v>
+        <v>1.4713522195816</v>
       </c>
       <c r="H2322" t="s">
         <v>8</v>
@@ -60819,7 +60819,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2325" t="n">
-        <v>1.46672534942627</v>
+        <v>1.46672546863556</v>
       </c>
       <c r="H2325" t="s">
         <v>8</v>
@@ -60871,7 +60871,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2327" t="n">
-        <v>1.44359087944031</v>
+        <v>1.44359076023102</v>
       </c>
       <c r="H2327" t="s">
         <v>8</v>
@@ -60949,7 +60949,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2330" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2330" t="s">
         <v>8</v>
@@ -61053,7 +61053,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2334" t="n">
-        <v>1.41120254993439</v>
+        <v>1.41120266914368</v>
       </c>
       <c r="H2334" t="s">
         <v>8</v>
@@ -61209,7 +61209,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2340" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2340" t="s">
         <v>8</v>
@@ -61287,7 +61287,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2343" t="s">
         <v>8</v>
@@ -61313,7 +61313,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2344" t="s">
         <v>8</v>
@@ -61339,7 +61339,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2345" t="n">
-        <v>1.40657579898834</v>
+        <v>1.40657567977905</v>
       </c>
       <c r="H2345" t="s">
         <v>8</v>
@@ -61495,7 +61495,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2351" t="n">
-        <v>1.6703085899353</v>
+        <v>1.67030870914459</v>
       </c>
       <c r="H2351" t="s">
         <v>8</v>
@@ -61521,7 +61521,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2352" t="n">
-        <v>1.68881630897522</v>
+        <v>1.68881642818451</v>
       </c>
       <c r="H2352" t="s">
         <v>8</v>
@@ -61599,7 +61599,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.60553216934204</v>
+        <v>1.60553228855133</v>
       </c>
       <c r="H2355" t="s">
         <v>8</v>
@@ -61729,7 +61729,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2360" t="n">
-        <v>1.5731440782547</v>
+        <v>1.57314395904541</v>
       </c>
       <c r="H2360" t="s">
         <v>8</v>
@@ -61859,7 +61859,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2365" t="n">
-        <v>1.65180099010468</v>
+        <v>1.65180110931396</v>
       </c>
       <c r="H2365" t="s">
         <v>8</v>
@@ -61911,7 +61911,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2367" t="n">
-        <v>1.65180099010468</v>
+        <v>1.65180110931396</v>
       </c>
       <c r="H2367" t="s">
         <v>8</v>
@@ -61963,7 +61963,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2369" t="n">
-        <v>1.66568183898926</v>
+        <v>1.66568171977997</v>
       </c>
       <c r="H2369" t="s">
         <v>8</v>
@@ -61989,7 +61989,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2370" t="n">
-        <v>1.66105484962463</v>
+        <v>1.66105496883392</v>
       </c>
       <c r="H2370" t="s">
         <v>8</v>
@@ -62015,7 +62015,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.70732378959656</v>
+        <v>1.70732390880585</v>
       </c>
       <c r="H2371" t="s">
         <v>8</v>
@@ -62041,7 +62041,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2372" t="n">
-        <v>1.72120463848114</v>
+        <v>1.72120451927185</v>
       </c>
       <c r="H2372" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>3.10999989509583</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>347360</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -543,7 +543,7 @@
         <v>5.07366609573364</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1970911026001</v>
+        <v>4.19709157943726</v>
       </c>
       <c r="H6" t="n">
         <v>112</v>
@@ -572,7 +572,7 @@
         <v>4.84223508834839</v>
       </c>
       <c r="G7" t="n">
-        <v>4.00564479827881</v>
+        <v>4.00564527511597</v>
       </c>
       <c r="H7" t="n">
         <v>871</v>
@@ -659,7 +659,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G10" t="n">
-        <v>3.68165874481201</v>
+        <v>3.68165898323059</v>
       </c>
       <c r="H10" t="n">
         <v>1371</v>
@@ -688,7 +688,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G11" t="n">
-        <v>3.68165874481201</v>
+        <v>3.68165898323059</v>
       </c>
       <c r="H11" t="n">
         <v>5201</v>
@@ -804,7 +804,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H15" t="n">
         <v>2158</v>
@@ -978,7 +978,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G21" t="n">
-        <v>3.68165874481201</v>
+        <v>3.68165898323059</v>
       </c>
       <c r="H21" t="n">
         <v>978</v>
@@ -1065,7 +1065,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G24" t="n">
-        <v>3.68165874481201</v>
+        <v>3.68165898323059</v>
       </c>
       <c r="H24" t="n">
         <v>56</v>
@@ -1181,7 +1181,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G28" t="n">
-        <v>3.68165874481201</v>
+        <v>3.68165898323059</v>
       </c>
       <c r="H28" t="n">
         <v>1864</v>
@@ -1210,7 +1210,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G29" t="n">
-        <v>3.68165874481201</v>
+        <v>3.68165898323059</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>4.03044891357422</v>
       </c>
       <c r="G39" t="n">
-        <v>3.33411049842834</v>
+        <v>3.33411026000977</v>
       </c>
       <c r="H39" t="n">
         <v>151</v>
@@ -1529,7 +1529,7 @@
         <v>4.03222894668579</v>
       </c>
       <c r="G40" t="n">
-        <v>3.3355827331543</v>
+        <v>3.33558297157288</v>
       </c>
       <c r="H40" t="n">
         <v>50</v>
@@ -1587,7 +1587,7 @@
         <v>4.30816507339478</v>
       </c>
       <c r="G42" t="n">
-        <v>3.56384563446045</v>
+        <v>3.56384539604187</v>
       </c>
       <c r="H42" t="n">
         <v>589</v>
@@ -1877,7 +1877,7 @@
         <v>4.59300184249878</v>
       </c>
       <c r="G52" t="n">
-        <v>3.79947113990784</v>
+        <v>3.79947090148926</v>
       </c>
       <c r="H52" t="n">
         <v>1124</v>
@@ -2022,7 +2022,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G57" t="n">
-        <v>3.68165874481201</v>
+        <v>3.68165898323059</v>
       </c>
       <c r="H57" t="n">
         <v>148</v>
@@ -2051,7 +2051,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G58" t="n">
-        <v>3.68165874481201</v>
+        <v>3.68165898323059</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>4.21915292739868</v>
       </c>
       <c r="G59" t="n">
-        <v>3.49021244049072</v>
+        <v>3.49021220207214</v>
       </c>
       <c r="H59" t="n">
         <v>364</v>
@@ -2109,7 +2109,7 @@
         <v>4.21915292739868</v>
       </c>
       <c r="G60" t="n">
-        <v>3.49021244049072</v>
+        <v>3.49021220207214</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>4.01620721817017</v>
       </c>
       <c r="G61" t="n">
-        <v>3.32232928276062</v>
+        <v>3.32232904434204</v>
       </c>
       <c r="H61" t="n">
         <v>874</v>
@@ -2196,7 +2196,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G63" t="n">
-        <v>3.35030961036682</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H63" t="n">
         <v>524</v>
@@ -2225,7 +2225,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G64" t="n">
-        <v>3.35030961036682</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G65" t="n">
-        <v>3.35030961036682</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H65" t="n">
         <v>578</v>
@@ -2283,7 +2283,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G66" t="n">
-        <v>3.35030961036682</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H66" t="n">
         <v>1585</v>
@@ -2312,7 +2312,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G67" t="n">
-        <v>3.35030961036682</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H67" t="n">
         <v>140</v>
@@ -2341,7 +2341,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G68" t="n">
-        <v>3.35030961036682</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H68" t="n">
         <v>70</v>
@@ -2486,7 +2486,7 @@
         <v>3.91295289993286</v>
       </c>
       <c r="G73" t="n">
-        <v>3.23691391944885</v>
+        <v>3.23691368103027</v>
       </c>
       <c r="H73" t="n">
         <v>759</v>
@@ -2631,7 +2631,7 @@
         <v>3.94321703910828</v>
       </c>
       <c r="G78" t="n">
-        <v>3.26194930076599</v>
+        <v>3.26194953918457</v>
       </c>
       <c r="H78" t="n">
         <v>55</v>
@@ -2776,7 +2776,7 @@
         <v>4.16574621200562</v>
       </c>
       <c r="G83" t="n">
-        <v>3.44603228569031</v>
+        <v>3.44603204727173</v>
       </c>
       <c r="H83" t="n">
         <v>10265</v>
@@ -2892,7 +2892,7 @@
         <v>4.20313119888306</v>
       </c>
       <c r="G87" t="n">
-        <v>3.47695827484131</v>
+        <v>3.47695851325989</v>
       </c>
       <c r="H87" t="n">
         <v>2430</v>
@@ -2921,7 +2921,7 @@
         <v>4.20313119888306</v>
       </c>
       <c r="G88" t="n">
-        <v>3.47695827484131</v>
+        <v>3.47695851325989</v>
       </c>
       <c r="H88" t="n">
         <v>109</v>
@@ -3008,7 +3008,7 @@
         <v>3.96101999282837</v>
       </c>
       <c r="G91" t="n">
-        <v>3.27667689323425</v>
+        <v>3.27667665481567</v>
       </c>
       <c r="H91" t="n">
         <v>3492</v>
@@ -3037,7 +3037,7 @@
         <v>3.89871096611023</v>
       </c>
       <c r="G92" t="n">
-        <v>3.22513270378113</v>
+        <v>3.22513246536255</v>
       </c>
       <c r="H92" t="n">
         <v>292</v>
@@ -3066,7 +3066,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G93" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H93" t="n">
         <v>661</v>
@@ -3095,7 +3095,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G94" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G95" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H95" t="n">
         <v>1</v>
@@ -3153,7 +3153,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G96" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H96" t="n">
         <v>1123</v>
@@ -3182,7 +3182,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G97" t="n">
-        <v>2.94532704353333</v>
+        <v>2.94532680511475</v>
       </c>
       <c r="H97" t="n">
         <v>561</v>
@@ -3269,7 +3269,7 @@
         <v>3.38778400421143</v>
       </c>
       <c r="G100" t="n">
-        <v>2.80247807502747</v>
+        <v>2.80247831344604</v>
       </c>
       <c r="H100" t="n">
         <v>7</v>
@@ -3356,7 +3356,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G103" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H103" t="n">
         <v>356</v>
@@ -3385,7 +3385,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G104" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G105" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G106" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G107" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G108" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G109" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G110" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G114" t="n">
-        <v>2.90114712715149</v>
+        <v>2.90114688873291</v>
       </c>
       <c r="H114" t="n">
         <v>254</v>
@@ -3733,7 +3733,7 @@
         <v>3.34683895111084</v>
       </c>
       <c r="G116" t="n">
-        <v>2.76860737800598</v>
+        <v>2.7686071395874</v>
       </c>
       <c r="H116" t="n">
         <v>252</v>
@@ -3762,7 +3762,7 @@
         <v>3.34683895111084</v>
       </c>
       <c r="G117" t="n">
-        <v>2.76860737800598</v>
+        <v>2.7686071395874</v>
       </c>
       <c r="H117" t="n">
         <v>588</v>
@@ -3791,7 +3791,7 @@
         <v>3.34683895111084</v>
       </c>
       <c r="G118" t="n">
-        <v>2.76860737800598</v>
+        <v>2.7686071395874</v>
       </c>
       <c r="H118" t="n">
         <v>254</v>
@@ -3907,7 +3907,7 @@
         <v>3.29521203041077</v>
       </c>
       <c r="G122" t="n">
-        <v>2.72589993476868</v>
+        <v>2.72590017318726</v>
       </c>
       <c r="H122" t="n">
         <v>1954</v>
@@ -3936,7 +3936,7 @@
         <v>3.3005530834198</v>
       </c>
       <c r="G123" t="n">
-        <v>2.73031854629517</v>
+        <v>2.73031830787659</v>
       </c>
       <c r="H123" t="n">
         <v>190</v>
@@ -4168,7 +4168,7 @@
         <v>2.88041806221008</v>
       </c>
       <c r="G131" t="n">
-        <v>2.38276982307434</v>
+        <v>2.38276958465576</v>
       </c>
       <c r="H131" t="n">
         <v>337</v>
@@ -4371,7 +4371,7 @@
         <v>1.86924505233765</v>
       </c>
       <c r="G138" t="n">
-        <v>1.5462965965271</v>
+        <v>1.54629647731781</v>
       </c>
       <c r="H138" t="n">
         <v>19365</v>
@@ -4429,7 +4429,7 @@
         <v>2.41043591499329</v>
       </c>
       <c r="G140" t="n">
-        <v>1.99398601055145</v>
+        <v>1.99398589134216</v>
       </c>
       <c r="H140" t="n">
         <v>25915</v>
@@ -4458,7 +4458,7 @@
         <v>2.25199508666992</v>
       </c>
       <c r="G141" t="n">
-        <v>1.86291909217834</v>
+        <v>1.86291897296906</v>
       </c>
       <c r="H141" t="n">
         <v>9636</v>
@@ -4516,7 +4516,7 @@
         <v>2.23241305351257</v>
       </c>
       <c r="G143" t="n">
-        <v>1.84672021865845</v>
+        <v>1.84672033786774</v>
       </c>
       <c r="H143" t="n">
         <v>16023</v>
@@ -4661,7 +4661,7 @@
         <v>2.21817088127136</v>
       </c>
       <c r="G148" t="n">
-        <v>1.83493864536285</v>
+        <v>1.83493852615356</v>
       </c>
       <c r="H148" t="n">
         <v>337</v>
@@ -4690,7 +4690,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G149" t="n">
-        <v>1.73774254322052</v>
+        <v>1.73774242401123</v>
       </c>
       <c r="H149" t="n">
         <v>918</v>
@@ -4864,7 +4864,7 @@
         <v>2.01166391372681</v>
       </c>
       <c r="G155" t="n">
-        <v>1.66410970687866</v>
+        <v>1.66410958766937</v>
       </c>
       <c r="H155" t="n">
         <v>1874</v>
@@ -4980,7 +4980,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G159" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H159" t="n">
         <v>2151</v>
@@ -5038,7 +5038,7 @@
         <v>2.02946591377258</v>
       </c>
       <c r="G161" t="n">
-        <v>1.67883598804474</v>
+        <v>1.67883610725403</v>
       </c>
       <c r="H161" t="n">
         <v>5715</v>
@@ -5067,7 +5067,7 @@
         <v>1.97961902618408</v>
       </c>
       <c r="G162" t="n">
-        <v>1.63760137557983</v>
+        <v>1.63760125637054</v>
       </c>
       <c r="H162" t="n">
         <v>645</v>
@@ -5096,7 +5096,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G163" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H163" t="n">
         <v>2241</v>
@@ -5154,7 +5154,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G165" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H165" t="n">
         <v>123</v>
@@ -5183,7 +5183,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G166" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H166" t="n">
         <v>1048</v>
@@ -5299,7 +5299,7 @@
         <v>1.86924505233765</v>
       </c>
       <c r="G170" t="n">
-        <v>1.5462965965271</v>
+        <v>1.54629647731781</v>
       </c>
       <c r="H170" t="n">
         <v>690</v>
@@ -5328,7 +5328,7 @@
         <v>1.86924505233765</v>
       </c>
       <c r="G171" t="n">
-        <v>1.5462965965271</v>
+        <v>1.54629647731781</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>2.17188501358032</v>
       </c>
       <c r="G177" t="n">
-        <v>1.79664945602417</v>
+        <v>1.79664957523346</v>
       </c>
       <c r="H177" t="n">
         <v>17162</v>
@@ -5589,7 +5589,7 @@
         <v>2.08287310600281</v>
       </c>
       <c r="G180" t="n">
-        <v>1.72301614284515</v>
+        <v>1.72301602363586</v>
       </c>
       <c r="H180" t="n">
         <v>674</v>
@@ -5879,7 +5879,7 @@
         <v>1.99386096000671</v>
       </c>
       <c r="G190" t="n">
-        <v>1.64938259124756</v>
+        <v>1.64938247203827</v>
       </c>
       <c r="H190" t="n">
         <v>619</v>
@@ -5908,7 +5908,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G191" t="n">
-        <v>1.73774254322052</v>
+        <v>1.73774242401123</v>
       </c>
       <c r="H191" t="n">
         <v>4547</v>
@@ -5937,7 +5937,7 @@
         <v>2.29650092124939</v>
       </c>
       <c r="G192" t="n">
-        <v>1.89973556995392</v>
+        <v>1.89973545074463</v>
       </c>
       <c r="H192" t="n">
         <v>5945</v>
@@ -6024,7 +6024,7 @@
         <v>2.30362200737</v>
       </c>
       <c r="G195" t="n">
-        <v>1.90562653541565</v>
+        <v>1.90562641620636</v>
       </c>
       <c r="H195" t="n">
         <v>8629</v>
@@ -6140,7 +6140,7 @@
         <v>2.52437090873718</v>
       </c>
       <c r="G199" t="n">
-        <v>2.08823657035828</v>
+        <v>2.08823680877686</v>
       </c>
       <c r="H199" t="n">
         <v>365</v>
@@ -6285,7 +6285,7 @@
         <v>2.15764307975769</v>
       </c>
       <c r="G204" t="n">
-        <v>1.78486812114716</v>
+        <v>1.78486824035645</v>
       </c>
       <c r="H204" t="n">
         <v>5715</v>
@@ -6633,7 +6633,7 @@
         <v>2.07397198677063</v>
       </c>
       <c r="G216" t="n">
-        <v>1.71565282344818</v>
+        <v>1.71565294265747</v>
       </c>
       <c r="H216" t="n">
         <v>128</v>
@@ -6691,7 +6691,7 @@
         <v>2.02412509918213</v>
       </c>
       <c r="G218" t="n">
-        <v>1.67441809177399</v>
+        <v>1.6744179725647</v>
       </c>
       <c r="H218" t="n">
         <v>2724</v>
@@ -6720,7 +6720,7 @@
         <v>2.02412509918213</v>
       </c>
       <c r="G219" t="n">
-        <v>1.67441809177399</v>
+        <v>1.6744179725647</v>
       </c>
       <c r="H219" t="n">
         <v>56</v>
@@ -6749,7 +6749,7 @@
         <v>2.02946591377258</v>
       </c>
       <c r="G220" t="n">
-        <v>1.67883598804474</v>
+        <v>1.67883610725403</v>
       </c>
       <c r="H220" t="n">
         <v>898</v>
@@ -6894,7 +6894,7 @@
         <v>2.00098204612732</v>
       </c>
       <c r="G225" t="n">
-        <v>1.65527331829071</v>
+        <v>1.65527319908142</v>
       </c>
       <c r="H225" t="n">
         <v>56</v>
@@ -7097,7 +7097,7 @@
         <v>2.01166391372681</v>
       </c>
       <c r="G232" t="n">
-        <v>1.66410970687866</v>
+        <v>1.66410958766937</v>
       </c>
       <c r="H232" t="n">
         <v>2171</v>
@@ -7126,7 +7126,7 @@
         <v>2.01166391372681</v>
       </c>
       <c r="G233" t="n">
-        <v>1.66410970687866</v>
+        <v>1.66410958766937</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>2.01166391372681</v>
       </c>
       <c r="G234" t="n">
-        <v>1.66410970687866</v>
+        <v>1.66410958766937</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>1.97249805927277</v>
       </c>
       <c r="G235" t="n">
-        <v>1.63171064853668</v>
+        <v>1.63171052932739</v>
       </c>
       <c r="H235" t="n">
         <v>14</v>
@@ -7271,7 +7271,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G238" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H238" t="n">
         <v>654</v>
@@ -7300,7 +7300,7 @@
         <v>1.95825695991516</v>
       </c>
       <c r="G239" t="n">
-        <v>1.61992979049683</v>
+        <v>1.61992990970612</v>
       </c>
       <c r="H239" t="n">
         <v>224</v>
@@ -7503,7 +7503,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G246" t="n">
-        <v>1.73774254322052</v>
+        <v>1.73774242401123</v>
       </c>
       <c r="H246" t="n">
         <v>664</v>
@@ -7648,7 +7648,7 @@
         <v>2.03124594688416</v>
       </c>
       <c r="G251" t="n">
-        <v>1.68030869960785</v>
+        <v>1.68030858039856</v>
       </c>
       <c r="H251" t="n">
         <v>849</v>
@@ -7677,7 +7677,7 @@
         <v>2.04904794692993</v>
       </c>
       <c r="G252" t="n">
-        <v>1.69503509998322</v>
+        <v>1.69503498077393</v>
       </c>
       <c r="H252" t="n">
         <v>16761</v>
@@ -7764,7 +7764,7 @@
         <v>2.36415004730225</v>
       </c>
       <c r="G255" t="n">
-        <v>1.95569717884064</v>
+        <v>1.95569694042206</v>
       </c>
       <c r="H255" t="n">
         <v>38762</v>
@@ -7793,7 +7793,7 @@
         <v>2.41221594810486</v>
       </c>
       <c r="G256" t="n">
-        <v>1.99545860290527</v>
+        <v>1.99545836448669</v>
       </c>
       <c r="H256" t="n">
         <v>7030</v>
@@ -7909,7 +7909,7 @@
         <v>2.79318594932556</v>
       </c>
       <c r="G260" t="n">
-        <v>2.31060862541199</v>
+        <v>2.31060886383057</v>
       </c>
       <c r="H260" t="n">
         <v>17760</v>
@@ -7967,7 +7967,7 @@
         <v>3.23824501037598</v>
       </c>
       <c r="G262" t="n">
-        <v>2.67877507209778</v>
+        <v>2.6787748336792</v>
       </c>
       <c r="H262" t="n">
         <v>34397</v>
@@ -7996,7 +7996,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G263" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H263" t="n">
         <v>23256</v>
@@ -8025,7 +8025,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G264" t="n">
-        <v>3.68165874481201</v>
+        <v>3.68165898323059</v>
       </c>
       <c r="H264" t="n">
         <v>7281</v>
@@ -8054,7 +8054,7 @@
         <v>4.67133283615112</v>
       </c>
       <c r="G265" t="n">
-        <v>3.86426901817322</v>
+        <v>3.86426877975464</v>
       </c>
       <c r="H265" t="n">
         <v>108992</v>
@@ -8112,7 +8112,7 @@
         <v>4.40073680877686</v>
       </c>
       <c r="G267" t="n">
-        <v>3.64042401313782</v>
+        <v>3.64042377471924</v>
       </c>
       <c r="H267" t="n">
         <v>57818</v>
@@ -8141,7 +8141,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G268" t="n">
-        <v>3.68165874481201</v>
+        <v>3.68165898323059</v>
       </c>
       <c r="H268" t="n">
         <v>8984</v>
@@ -8199,7 +8199,7 @@
         <v>4.16574621200562</v>
       </c>
       <c r="G270" t="n">
-        <v>3.44603228569031</v>
+        <v>3.44603204727173</v>
       </c>
       <c r="H270" t="n">
         <v>17616</v>
@@ -8228,7 +8228,7 @@
         <v>4.05893182754517</v>
       </c>
       <c r="G271" t="n">
-        <v>3.35767197608948</v>
+        <v>3.35767221450806</v>
       </c>
       <c r="H271" t="n">
         <v>19224</v>
@@ -8257,7 +8257,7 @@
         <v>4.59300184249878</v>
       </c>
       <c r="G272" t="n">
-        <v>3.79947113990784</v>
+        <v>3.79947090148926</v>
       </c>
       <c r="H272" t="n">
         <v>58292</v>
@@ -8402,7 +8402,7 @@
         <v>4.25653791427612</v>
       </c>
       <c r="G277" t="n">
-        <v>3.52113795280457</v>
+        <v>3.52113771438599</v>
       </c>
       <c r="H277" t="n">
         <v>9571</v>
@@ -8431,7 +8431,7 @@
         <v>4.25475788116455</v>
       </c>
       <c r="G278" t="n">
-        <v>3.51966547966003</v>
+        <v>3.51966571807861</v>
       </c>
       <c r="H278" t="n">
         <v>10019</v>
@@ -8489,7 +8489,7 @@
         <v>4.35979223251343</v>
       </c>
       <c r="G280" t="n">
-        <v>3.60655331611633</v>
+        <v>3.60655307769775</v>
       </c>
       <c r="H280" t="n">
         <v>2930</v>
@@ -8663,7 +8663,7 @@
         <v>4.07495403289795</v>
       </c>
       <c r="G286" t="n">
-        <v>3.37092638015747</v>
+        <v>3.37092614173889</v>
       </c>
       <c r="H286" t="n">
         <v>6601</v>
@@ -8692,7 +8692,7 @@
         <v>3.94677805900574</v>
       </c>
       <c r="G287" t="n">
-        <v>3.26489520072937</v>
+        <v>3.26489496231079</v>
       </c>
       <c r="H287" t="n">
         <v>2309</v>
@@ -8779,7 +8779,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G290" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H290" t="n">
         <v>14</v>
@@ -8837,7 +8837,7 @@
         <v>3.69932508468628</v>
       </c>
       <c r="G292" t="n">
-        <v>3.06019425392151</v>
+        <v>3.06019449234009</v>
       </c>
       <c r="H292" t="n">
         <v>4324</v>
@@ -8924,7 +8924,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G295" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H295" t="n">
         <v>2785</v>
@@ -8953,7 +8953,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G296" t="n">
-        <v>2.94532704353333</v>
+        <v>2.94532680511475</v>
       </c>
       <c r="H296" t="n">
         <v>1256</v>
@@ -8982,7 +8982,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G297" t="n">
-        <v>2.94532704353333</v>
+        <v>2.94532680511475</v>
       </c>
       <c r="H297" t="n">
         <v>2543</v>
@@ -9127,7 +9127,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G302" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H302" t="n">
         <v>1569</v>
@@ -9156,7 +9156,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G303" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G307" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H307" t="n">
         <v>4172</v>
@@ -9301,7 +9301,7 @@
         <v>4.09275722503662</v>
       </c>
       <c r="G308" t="n">
-        <v>3.38565349578857</v>
+        <v>3.38565373420715</v>
       </c>
       <c r="H308" t="n">
         <v>112</v>
@@ -9330,7 +9330,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G309" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H309" t="n">
         <v>2275</v>
@@ -9620,7 +9620,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G319" t="n">
-        <v>2.94532704353333</v>
+        <v>2.94532680511475</v>
       </c>
       <c r="H319" t="n">
         <v>3638</v>
@@ -9678,7 +9678,7 @@
         <v>3.53376293182373</v>
       </c>
       <c r="G321" t="n">
-        <v>2.92323660850525</v>
+        <v>2.92323637008667</v>
       </c>
       <c r="H321" t="n">
         <v>3459</v>
@@ -9765,7 +9765,7 @@
         <v>3.48213696479797</v>
       </c>
       <c r="G324" t="n">
-        <v>2.88053011894226</v>
+        <v>2.88052988052368</v>
       </c>
       <c r="H324" t="n">
         <v>29</v>
@@ -9910,7 +9910,7 @@
         <v>4.21381282806396</v>
       </c>
       <c r="G329" t="n">
-        <v>3.48579454421997</v>
+        <v>3.48579478263855</v>
       </c>
       <c r="H329" t="n">
         <v>5440</v>
@@ -10084,7 +10084,7 @@
         <v>3.98772311210632</v>
       </c>
       <c r="G335" t="n">
-        <v>3.29876637458801</v>
+        <v>3.29876613616943</v>
       </c>
       <c r="H335" t="n">
         <v>8933</v>
@@ -10113,7 +10113,7 @@
         <v>3.99662399291992</v>
       </c>
       <c r="G336" t="n">
-        <v>3.30612945556641</v>
+        <v>3.30612921714783</v>
       </c>
       <c r="H336" t="n">
         <v>4587</v>
@@ -10287,7 +10287,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G342" t="n">
-        <v>3.16033577919006</v>
+        <v>3.16033554077148</v>
       </c>
       <c r="H342" t="n">
         <v>731</v>
@@ -10461,7 +10461,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G348" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H348" t="n">
         <v>682</v>
@@ -10490,7 +10490,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G349" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H349" t="n">
         <v>2665</v>
@@ -10519,7 +10519,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G350" t="n">
-        <v>3.16033577919006</v>
+        <v>3.16033554077148</v>
       </c>
       <c r="H350" t="n">
         <v>2507</v>
@@ -10548,7 +10548,7 @@
         <v>3.70822596549988</v>
       </c>
       <c r="G351" t="n">
-        <v>3.0675573348999</v>
+        <v>3.06755757331848</v>
       </c>
       <c r="H351" t="n">
         <v>1095</v>
@@ -10577,7 +10577,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G352" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H352" t="n">
         <v>2010</v>
@@ -10606,7 +10606,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G353" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G354" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H354" t="n">
         <v>3131</v>
@@ -10664,7 +10664,7 @@
         <v>3.83462309837341</v>
       </c>
       <c r="G355" t="n">
-        <v>3.17211723327637</v>
+        <v>3.17211699485779</v>
       </c>
       <c r="H355" t="n">
         <v>2162</v>
@@ -10867,7 +10867,7 @@
         <v>3.87200808525085</v>
       </c>
       <c r="G362" t="n">
-        <v>3.20304322242737</v>
+        <v>3.20304298400879</v>
       </c>
       <c r="H362" t="n">
         <v>224</v>
@@ -10896,7 +10896,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G363" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H363" t="n">
         <v>716</v>
@@ -11099,7 +11099,7 @@
         <v>3.54800510406494</v>
       </c>
       <c r="G370" t="n">
-        <v>2.93501806259155</v>
+        <v>2.93501782417297</v>
       </c>
       <c r="H370" t="n">
         <v>3053</v>
@@ -11186,7 +11186,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G373" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H373" t="n">
         <v>6892</v>
@@ -11302,7 +11302,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G377" t="n">
-        <v>2.94827175140381</v>
+        <v>2.94827198982239</v>
       </c>
       <c r="H377" t="n">
         <v>672</v>
@@ -11447,7 +11447,7 @@
         <v>3.62989592552185</v>
       </c>
       <c r="G382" t="n">
-        <v>3.00276064872742</v>
+        <v>3.00276041030884</v>
       </c>
       <c r="H382" t="n">
         <v>112</v>
@@ -11505,7 +11505,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G384" t="n">
-        <v>2.94532704353333</v>
+        <v>2.94532680511475</v>
       </c>
       <c r="H384" t="n">
         <v>572</v>
@@ -11795,7 +11795,7 @@
         <v>3.50349903106689</v>
       </c>
       <c r="G394" t="n">
-        <v>2.89820122718811</v>
+        <v>2.89820146560669</v>
       </c>
       <c r="H394" t="n">
         <v>921</v>
@@ -12027,7 +12027,7 @@
         <v>3.91651391983032</v>
       </c>
       <c r="G402" t="n">
-        <v>3.23985958099365</v>
+        <v>3.23985981941223</v>
       </c>
       <c r="H402" t="n">
         <v>22226</v>
@@ -12056,7 +12056,7 @@
         <v>4.046471118927</v>
       </c>
       <c r="G403" t="n">
-        <v>3.3473641872406</v>
+        <v>3.34736442565918</v>
       </c>
       <c r="H403" t="n">
         <v>98461</v>
@@ -12201,7 +12201,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G408" t="n">
-        <v>2.94532704353333</v>
+        <v>2.94532680511475</v>
       </c>
       <c r="H408" t="n">
         <v>7539</v>
@@ -12230,7 +12230,7 @@
         <v>3.65838003158569</v>
       </c>
       <c r="G409" t="n">
-        <v>3.02632355690002</v>
+        <v>3.02632331848145</v>
       </c>
       <c r="H409" t="n">
         <v>1995</v>
@@ -12462,7 +12462,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G417" t="n">
-        <v>2.94827175140381</v>
+        <v>2.94827198982239</v>
       </c>
       <c r="H417" t="n">
         <v>561</v>
@@ -12491,7 +12491,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G418" t="n">
-        <v>2.94827175140381</v>
+        <v>2.94827198982239</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>3.62989592552185</v>
       </c>
       <c r="G419" t="n">
-        <v>3.00276064872742</v>
+        <v>3.00276041030884</v>
       </c>
       <c r="H419" t="n">
         <v>481</v>
@@ -12549,7 +12549,7 @@
         <v>3.57826900482178</v>
       </c>
       <c r="G420" t="n">
-        <v>2.96005320549011</v>
+        <v>2.96005344390869</v>
       </c>
       <c r="H420" t="n">
         <v>11998</v>
@@ -12578,7 +12578,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G421" t="n">
-        <v>2.94532704353333</v>
+        <v>2.94532680511475</v>
       </c>
       <c r="H421" t="n">
         <v>1850</v>
@@ -12723,7 +12723,7 @@
         <v>3.55690598487854</v>
       </c>
       <c r="G426" t="n">
-        <v>2.94238114356995</v>
+        <v>2.94238138198853</v>
       </c>
       <c r="H426" t="n">
         <v>651</v>
@@ -12752,7 +12752,7 @@
         <v>3.55690598487854</v>
       </c>
       <c r="G427" t="n">
-        <v>2.94238114356995</v>
+        <v>2.94238138198853</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -12781,7 +12781,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G428" t="n">
-        <v>2.90114712715149</v>
+        <v>2.90114688873291</v>
       </c>
       <c r="H428" t="n">
         <v>1147</v>
@@ -12810,7 +12810,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G429" t="n">
-        <v>2.90114712715149</v>
+        <v>2.90114688873291</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G431" t="n">
-        <v>2.94532704353333</v>
+        <v>2.94532680511475</v>
       </c>
       <c r="H431" t="n">
         <v>2306</v>
@@ -12984,7 +12984,7 @@
         <v>3.4394109249115</v>
       </c>
       <c r="G435" t="n">
-        <v>2.84518527984619</v>
+        <v>2.84518551826477</v>
       </c>
       <c r="H435" t="n">
         <v>1937</v>
@@ -13158,7 +13158,7 @@
         <v>3.41092705726624</v>
       </c>
       <c r="G441" t="n">
-        <v>2.82162284851074</v>
+        <v>2.82162308692932</v>
       </c>
       <c r="H441" t="n">
         <v>21711</v>
@@ -13361,7 +13361,7 @@
         <v>3.33971810340881</v>
       </c>
       <c r="G448" t="n">
-        <v>2.7627170085907</v>
+        <v>2.76271677017212</v>
       </c>
       <c r="H448" t="n">
         <v>1290</v>
@@ -13390,7 +13390,7 @@
         <v>3.33615708351135</v>
       </c>
       <c r="G449" t="n">
-        <v>2.75977087020874</v>
+        <v>2.75977110862732</v>
       </c>
       <c r="H449" t="n">
         <v>863</v>
@@ -13419,7 +13419,7 @@
         <v>3.24714589118958</v>
       </c>
       <c r="G450" t="n">
-        <v>2.68613791465759</v>
+        <v>2.68613815307617</v>
       </c>
       <c r="H450" t="n">
         <v>4906</v>
@@ -13593,7 +13593,7 @@
         <v>3.27919006347656</v>
       </c>
       <c r="G456" t="n">
-        <v>2.71264624595642</v>
+        <v>2.71264600753784</v>
       </c>
       <c r="H456" t="n">
         <v>2696</v>
@@ -13767,7 +13767,7 @@
         <v>3.24714589118958</v>
       </c>
       <c r="G462" t="n">
-        <v>2.68613791465759</v>
+        <v>2.68613815307617</v>
       </c>
       <c r="H462" t="n">
         <v>280</v>
@@ -13796,7 +13796,7 @@
         <v>3.24536609649658</v>
       </c>
       <c r="G463" t="n">
-        <v>2.68466591835022</v>
+        <v>2.68466567993164</v>
       </c>
       <c r="H463" t="n">
         <v>4256</v>
@@ -13999,7 +13999,7 @@
         <v>3.18483805656433</v>
       </c>
       <c r="G470" t="n">
-        <v>2.63459539413452</v>
+        <v>2.63459515571594</v>
       </c>
       <c r="H470" t="n">
         <v>1182</v>
@@ -14057,7 +14057,7 @@
         <v>3.19373893737793</v>
       </c>
       <c r="G472" t="n">
-        <v>2.64195823669434</v>
+        <v>2.64195847511292</v>
       </c>
       <c r="H472" t="n">
         <v>2530</v>
@@ -14115,7 +14115,7 @@
         <v>3.24002504348755</v>
       </c>
       <c r="G474" t="n">
-        <v>2.68024754524231</v>
+        <v>2.68024778366089</v>
       </c>
       <c r="H474" t="n">
         <v>2632</v>
@@ -14202,7 +14202,7 @@
         <v>3.18483805656433</v>
       </c>
       <c r="G477" t="n">
-        <v>2.63459539413452</v>
+        <v>2.63459515571594</v>
       </c>
       <c r="H477" t="n">
         <v>839</v>
@@ -14318,7 +14318,7 @@
         <v>3.15101289749146</v>
       </c>
       <c r="G481" t="n">
-        <v>2.60661387443542</v>
+        <v>2.606614112854</v>
       </c>
       <c r="H481" t="n">
         <v>1291</v>
@@ -14463,7 +14463,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>2.39896869659424</v>
+        <v>2.39896845817566</v>
       </c>
       <c r="H486" t="n">
         <v>84</v>
@@ -14492,7 +14492,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>2.39896869659424</v>
+        <v>2.39896845817566</v>
       </c>
       <c r="H487" t="n">
         <v>246</v>
@@ -14521,7 +14521,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G488" t="n">
-        <v>2.39896869659424</v>
+        <v>2.39896845817566</v>
       </c>
       <c r="H488" t="n">
         <v>786</v>
@@ -14608,7 +14608,7 @@
         <v>3.02639698982239</v>
       </c>
       <c r="G491" t="n">
-        <v>2.50352764129639</v>
+        <v>2.50352787971497</v>
       </c>
       <c r="H491" t="n">
         <v>3010</v>
@@ -14637,7 +14637,7 @@
         <v>3.02639698982239</v>
       </c>
       <c r="G492" t="n">
-        <v>2.50352764129639</v>
+        <v>2.50352787971497</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -14695,7 +14695,7 @@
         <v>2.94094610214233</v>
       </c>
       <c r="G494" t="n">
-        <v>2.43284034729004</v>
+        <v>2.43284010887146</v>
       </c>
       <c r="H494" t="n">
         <v>73</v>
@@ -14724,7 +14724,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G495" t="n">
-        <v>2.35920667648315</v>
+        <v>2.35920643806458</v>
       </c>
       <c r="H495" t="n">
         <v>466</v>
@@ -14753,7 +14753,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G496" t="n">
-        <v>2.35920667648315</v>
+        <v>2.35920643806458</v>
       </c>
       <c r="H496" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G497" t="n">
-        <v>2.35920667648315</v>
+        <v>2.35920643806458</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14840,7 +14840,7 @@
         <v>2.79496598243713</v>
       </c>
       <c r="G499" t="n">
-        <v>2.3120813369751</v>
+        <v>2.31208109855652</v>
       </c>
       <c r="H499" t="n">
         <v>1177</v>
@@ -15043,7 +15043,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>2.39896869659424</v>
+        <v>2.39896845817566</v>
       </c>
       <c r="H506" t="n">
         <v>1522</v>
@@ -15072,7 +15072,7 @@
         <v>2.86617588996887</v>
       </c>
       <c r="G507" t="n">
-        <v>2.37098813056946</v>
+        <v>2.37098789215088</v>
       </c>
       <c r="H507" t="n">
         <v>1021</v>
@@ -15304,7 +15304,7 @@
         <v>3.21250009536743</v>
       </c>
       <c r="G515" t="n">
-        <v>2.65747785568237</v>
+        <v>2.65747809410095</v>
       </c>
       <c r="H515" t="n">
         <v>26540</v>
@@ -15449,7 +15449,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G520" t="n">
-        <v>2.46101045608521</v>
+        <v>2.46101069450378</v>
       </c>
       <c r="H520" t="n">
         <v>15414</v>
@@ -15507,7 +15507,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G522" t="n">
-        <v>2.31624555587769</v>
+        <v>2.31624531745911</v>
       </c>
       <c r="H522" t="n">
         <v>15526</v>
@@ -15565,7 +15565,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.19216084480286</v>
+        <v>2.19216108322144</v>
       </c>
       <c r="H524" t="n">
         <v>25151</v>
@@ -15594,7 +15594,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G525" t="n">
-        <v>2.13011837005615</v>
+        <v>2.13011860847473</v>
       </c>
       <c r="H525" t="n">
         <v>29040</v>
@@ -15652,7 +15652,7 @@
         <v>2.5625</v>
       </c>
       <c r="G527" t="n">
-        <v>2.11977815628052</v>
+        <v>2.11977791786194</v>
       </c>
       <c r="H527" t="n">
         <v>17500</v>
@@ -15681,7 +15681,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G528" t="n">
-        <v>2.04325938224792</v>
+        <v>2.04325914382935</v>
       </c>
       <c r="H528" t="n">
         <v>172096</v>
@@ -16000,7 +16000,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G539" t="n">
-        <v>1.74959242343903</v>
+        <v>1.74959254264832</v>
       </c>
       <c r="H539" t="n">
         <v>9531</v>
@@ -16029,7 +16029,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>1.72063946723938</v>
+        <v>1.72063934803009</v>
       </c>
       <c r="H540" t="n">
         <v>15673</v>
@@ -16116,7 +16116,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G543" t="n">
-        <v>1.64618873596191</v>
+        <v>1.64618861675262</v>
       </c>
       <c r="H543" t="n">
         <v>14522</v>
@@ -16290,7 +16290,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G549" t="n">
-        <v>1.7371838092804</v>
+        <v>1.73718392848969</v>
       </c>
       <c r="H549" t="n">
         <v>6788</v>
@@ -16377,7 +16377,7 @@
         <v>2.125</v>
       </c>
       <c r="G552" t="n">
-        <v>1.7578649520874</v>
+        <v>1.75786483287811</v>
       </c>
       <c r="H552" t="n">
         <v>4581</v>
@@ -16406,7 +16406,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G553" t="n">
-        <v>1.76613712310791</v>
+        <v>1.76613700389862</v>
       </c>
       <c r="H553" t="n">
         <v>14755</v>
@@ -16464,7 +16464,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G555" t="n">
-        <v>1.71650338172913</v>
+        <v>1.71650326251984</v>
       </c>
       <c r="H555" t="n">
         <v>11105</v>
@@ -16725,7 +16725,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G564" t="n">
-        <v>1.76613712310791</v>
+        <v>1.76613700389862</v>
       </c>
       <c r="H564" t="n">
         <v>6751</v>
@@ -16783,7 +16783,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G566" t="n">
-        <v>1.7371838092804</v>
+        <v>1.73718392848969</v>
       </c>
       <c r="H566" t="n">
         <v>1701</v>
@@ -16812,7 +16812,7 @@
         <v>2.125</v>
       </c>
       <c r="G567" t="n">
-        <v>1.7578649520874</v>
+        <v>1.75786483287811</v>
       </c>
       <c r="H567" t="n">
         <v>9117</v>
@@ -16870,7 +16870,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>1.72477543354034</v>
+        <v>1.72477555274963</v>
       </c>
       <c r="H569" t="n">
         <v>2737</v>
@@ -16899,7 +16899,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>1.72477543354034</v>
+        <v>1.72477555274963</v>
       </c>
       <c r="H570" t="n">
         <v>11694</v>
@@ -17305,7 +17305,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G584" t="n">
-        <v>1.98948931694031</v>
+        <v>1.98948955535889</v>
       </c>
       <c r="H584" t="n">
         <v>98188</v>
@@ -17363,7 +17363,7 @@
         <v>2.73749995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.26454329490662</v>
+        <v>2.2645435333252</v>
       </c>
       <c r="H586" t="n">
         <v>241077</v>
@@ -17392,7 +17392,7 @@
         <v>2.53749990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>2.09909725189209</v>
+        <v>2.09909749031067</v>
       </c>
       <c r="H587" t="n">
         <v>383922</v>
@@ -17421,7 +17421,7 @@
         <v>2.5</v>
       </c>
       <c r="G588" t="n">
-        <v>2.06807589530945</v>
+        <v>2.06807613372803</v>
       </c>
       <c r="H588" t="n">
         <v>93249</v>
@@ -17508,7 +17508,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.31624555587769</v>
+        <v>2.31624531745911</v>
       </c>
       <c r="H591" t="n">
         <v>50643</v>
@@ -17537,7 +17537,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>2.31624555587769</v>
+        <v>2.31624531745911</v>
       </c>
       <c r="H592" t="n">
         <v>191122</v>
@@ -17711,7 +17711,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>2.19216084480286</v>
+        <v>2.19216108322144</v>
       </c>
       <c r="H598" t="n">
         <v>52517</v>
@@ -17769,7 +17769,7 @@
         <v>2.71250009536743</v>
       </c>
       <c r="G600" t="n">
-        <v>2.24386262893677</v>
+        <v>2.24386239051819</v>
       </c>
       <c r="H600" t="n">
         <v>116767</v>
@@ -17827,7 +17827,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>2.19216084480286</v>
+        <v>2.19216108322144</v>
       </c>
       <c r="H602" t="n">
         <v>23329</v>
@@ -17914,7 +17914,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G605" t="n">
-        <v>2.08875703811646</v>
+        <v>2.08875679969788</v>
       </c>
       <c r="H605" t="n">
         <v>41989</v>
@@ -18552,7 +18552,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>1.8860856294632</v>
+        <v>1.88608551025391</v>
       </c>
       <c r="H627" t="n">
         <v>13640</v>
@@ -18581,7 +18581,7 @@
         <v>2.25</v>
       </c>
       <c r="G628" t="n">
-        <v>1.8612687587738</v>
+        <v>1.86126863956451</v>
       </c>
       <c r="H628" t="n">
         <v>1406</v>
@@ -18610,7 +18610,7 @@
         <v>2.25</v>
       </c>
       <c r="G629" t="n">
-        <v>1.8612687587738</v>
+        <v>1.86126863956451</v>
       </c>
       <c r="H629" t="n">
         <v>1064</v>
@@ -18668,7 +18668,7 @@
         <v>2.25</v>
       </c>
       <c r="G631" t="n">
-        <v>1.8612687587738</v>
+        <v>1.86126863956451</v>
       </c>
       <c r="H631" t="n">
         <v>760</v>
@@ -18784,7 +18784,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G635" t="n">
-        <v>1.90676617622375</v>
+        <v>1.90676629543304</v>
       </c>
       <c r="H635" t="n">
         <v>9833</v>
@@ -18813,7 +18813,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>1.91090250015259</v>
+        <v>1.9109023809433</v>
       </c>
       <c r="H636" t="n">
         <v>24468</v>
@@ -18929,7 +18929,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>1.7909539937973</v>
+        <v>1.79095411300659</v>
       </c>
       <c r="H640" t="n">
         <v>28706</v>
@@ -18958,7 +18958,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G641" t="n">
-        <v>1.78681790828705</v>
+        <v>1.78681802749634</v>
       </c>
       <c r="H641" t="n">
         <v>25425</v>
@@ -19074,7 +19074,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G645" t="n">
-        <v>1.78681790828705</v>
+        <v>1.78681802749634</v>
       </c>
       <c r="H645" t="n">
         <v>5814</v>
@@ -19132,7 +19132,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G647" t="n">
-        <v>1.80749845504761</v>
+        <v>1.80749833583832</v>
       </c>
       <c r="H647" t="n">
         <v>10121</v>
@@ -19161,7 +19161,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G648" t="n">
-        <v>1.7371838092804</v>
+        <v>1.73718392848969</v>
       </c>
       <c r="H648" t="n">
         <v>16400</v>
@@ -19219,7 +19219,7 @@
         <v>2.125</v>
       </c>
       <c r="G650" t="n">
-        <v>1.7578649520874</v>
+        <v>1.75786483287811</v>
       </c>
       <c r="H650" t="n">
         <v>15747</v>
@@ -19248,7 +19248,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G651" t="n">
-        <v>1.78268182277679</v>
+        <v>1.7826817035675</v>
       </c>
       <c r="H651" t="n">
         <v>9355</v>
@@ -19277,7 +19277,7 @@
         <v>2.125</v>
       </c>
       <c r="G652" t="n">
-        <v>1.7578649520874</v>
+        <v>1.75786483287811</v>
       </c>
       <c r="H652" t="n">
         <v>6777</v>
@@ -19364,7 +19364,7 @@
         <v>2.1710000038147</v>
       </c>
       <c r="G655" t="n">
-        <v>1.79591739177704</v>
+        <v>1.79591751098633</v>
       </c>
       <c r="H655" t="n">
         <v>7457</v>
@@ -19422,7 +19422,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G657" t="n">
-        <v>1.85134172439575</v>
+        <v>1.85134184360504</v>
       </c>
       <c r="H657" t="n">
         <v>9372</v>
@@ -19654,7 +19654,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>1.7909539937973</v>
+        <v>1.79095411300659</v>
       </c>
       <c r="H665" t="n">
         <v>1007</v>
@@ -19683,7 +19683,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G666" t="n">
-        <v>1.83976078033447</v>
+        <v>1.83976066112518</v>
       </c>
       <c r="H666" t="n">
         <v>28805</v>
@@ -19712,7 +19712,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G667" t="n">
-        <v>1.83727896213531</v>
+        <v>1.83727884292603</v>
       </c>
       <c r="H667" t="n">
         <v>1138</v>
@@ -19799,7 +19799,7 @@
         <v>2.18700003623962</v>
       </c>
       <c r="G670" t="n">
-        <v>1.80915307998657</v>
+        <v>1.80915319919586</v>
       </c>
       <c r="H670" t="n">
         <v>1019</v>
@@ -20060,7 +20060,7 @@
         <v>1.75479996204376</v>
       </c>
       <c r="G679" t="n">
-        <v>1.45162403583527</v>
+        <v>1.45162415504456</v>
       </c>
       <c r="H679" t="n">
         <v>77393</v>
@@ -20176,7 +20176,7 @@
         <v>1.75960004329681</v>
       </c>
       <c r="G683" t="n">
-        <v>1.45559501647949</v>
+        <v>1.4555948972702</v>
       </c>
       <c r="H683" t="n">
         <v>9557</v>
@@ -20205,7 +20205,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G684" t="n">
-        <v>1.47329759597778</v>
+        <v>1.47329747676849</v>
       </c>
       <c r="H684" t="n">
         <v>524</v>
@@ -20263,7 +20263,7 @@
         <v>1.72140002250671</v>
       </c>
       <c r="G686" t="n">
-        <v>1.4239946603775</v>
+        <v>1.42399477958679</v>
       </c>
       <c r="H686" t="n">
         <v>1520</v>
@@ -20379,7 +20379,7 @@
         <v>1.76979994773865</v>
       </c>
       <c r="G690" t="n">
-        <v>1.46403241157532</v>
+        <v>1.46403253078461</v>
       </c>
       <c r="H690" t="n">
         <v>3320</v>
@@ -20611,7 +20611,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G698" t="n">
-        <v>1.41952753067017</v>
+        <v>1.41952741146088</v>
       </c>
       <c r="H698" t="n">
         <v>9959</v>
@@ -20698,7 +20698,7 @@
         <v>1.73759996891022</v>
       </c>
       <c r="G701" t="n">
-        <v>1.43739581108093</v>
+        <v>1.43739569187164</v>
       </c>
       <c r="H701" t="n">
         <v>8466</v>
@@ -20727,7 +20727,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G702" t="n">
-        <v>1.43524491786957</v>
+        <v>1.43524503707886</v>
       </c>
       <c r="H702" t="n">
         <v>4220</v>
@@ -20814,7 +20814,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>1.41456425189972</v>
+        <v>1.41456413269043</v>
       </c>
       <c r="H705" t="n">
         <v>2040</v>
@@ -20843,7 +20843,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G706" t="n">
-        <v>1.41952753067017</v>
+        <v>1.41952741146088</v>
       </c>
       <c r="H706" t="n">
         <v>2390</v>
@@ -20872,7 +20872,7 @@
         <v>1.71539998054504</v>
       </c>
       <c r="G707" t="n">
-        <v>1.41903114318848</v>
+        <v>1.41903126239777</v>
       </c>
       <c r="H707" t="n">
         <v>1650</v>
@@ -21017,7 +21017,7 @@
         <v>1.72019994258881</v>
       </c>
       <c r="G712" t="n">
-        <v>1.42300176620483</v>
+        <v>1.42300188541412</v>
       </c>
       <c r="H712" t="n">
         <v>4691</v>
@@ -21046,7 +21046,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G713" t="n">
-        <v>1.45592570304871</v>
+        <v>1.45592558383942</v>
       </c>
       <c r="H713" t="n">
         <v>6546</v>
@@ -21075,7 +21075,7 @@
         <v>1.83959996700287</v>
       </c>
       <c r="G714" t="n">
-        <v>1.52177321910858</v>
+        <v>1.52177333831787</v>
       </c>
       <c r="H714" t="n">
         <v>24405</v>
@@ -21104,7 +21104,7 @@
         <v>1.78960001468658</v>
       </c>
       <c r="G715" t="n">
-        <v>1.48041164875031</v>
+        <v>1.48041176795959</v>
       </c>
       <c r="H715" t="n">
         <v>5445</v>
@@ -21191,7 +21191,7 @@
         <v>1.72979998588562</v>
       </c>
       <c r="G718" t="n">
-        <v>1.43094325065613</v>
+        <v>1.43094313144684</v>
       </c>
       <c r="H718" t="n">
         <v>566</v>
@@ -21278,7 +21278,7 @@
         <v>1.81140005588531</v>
       </c>
       <c r="G721" t="n">
-        <v>1.49844527244568</v>
+        <v>1.49844539165497</v>
       </c>
       <c r="H721" t="n">
         <v>7281</v>
@@ -21307,7 +21307,7 @@
         <v>1.81140005588531</v>
       </c>
       <c r="G722" t="n">
-        <v>1.49844527244568</v>
+        <v>1.49844539165497</v>
       </c>
       <c r="H722" t="n">
         <v>0</v>
@@ -21336,7 +21336,7 @@
         <v>1.81140005588531</v>
       </c>
       <c r="G723" t="n">
-        <v>1.49844527244568</v>
+        <v>1.49844539165497</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21423,7 +21423,7 @@
         <v>1.81980001926422</v>
       </c>
       <c r="G726" t="n">
-        <v>1.50539410114288</v>
+        <v>1.50539422035217</v>
       </c>
       <c r="H726" t="n">
         <v>2000</v>
@@ -21771,7 +21771,7 @@
         <v>1.84179997444153</v>
       </c>
       <c r="G738" t="n">
-        <v>1.52359306812286</v>
+        <v>1.52359318733215</v>
       </c>
       <c r="H738" t="n">
         <v>1530</v>
@@ -21974,7 +21974,7 @@
         <v>1.78960001468658</v>
       </c>
       <c r="G745" t="n">
-        <v>1.48041164875031</v>
+        <v>1.48041176795959</v>
       </c>
       <c r="H745" t="n">
         <v>219</v>
@@ -22003,7 +22003,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G746" t="n">
-        <v>1.47329759597778</v>
+        <v>1.47329747676849</v>
       </c>
       <c r="H746" t="n">
         <v>2400</v>
@@ -22061,7 +22061,7 @@
         <v>1.78120005130768</v>
       </c>
       <c r="G748" t="n">
-        <v>1.47346305847168</v>
+        <v>1.47346293926239</v>
       </c>
       <c r="H748" t="n">
         <v>198</v>
@@ -22119,7 +22119,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G750" t="n">
-        <v>1.47329759597778</v>
+        <v>1.47329747676849</v>
       </c>
       <c r="H750" t="n">
         <v>470</v>
@@ -22206,7 +22206,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G753" t="n">
-        <v>1.47329759597778</v>
+        <v>1.47329747676849</v>
       </c>
       <c r="H753" t="n">
         <v>225</v>
@@ -22293,7 +22293,7 @@
         <v>1.88940000534058</v>
       </c>
       <c r="G756" t="n">
-        <v>1.56296932697296</v>
+        <v>1.56296920776367</v>
       </c>
       <c r="H756" t="n">
         <v>4631</v>
@@ -80038,6 +80038,35 @@
         <v>30466</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>35812</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -514,7 +514,7 @@
         <v>5.16267681121826</v>
       </c>
       <c r="G5" t="n">
-        <v>4.27072381973267</v>
+        <v>4.27072334289551</v>
       </c>
       <c r="H5" t="n">
         <v>140</v>
@@ -572,7 +572,7 @@
         <v>4.84223508834839</v>
       </c>
       <c r="G7" t="n">
-        <v>4.00564527511597</v>
+        <v>4.00564479827881</v>
       </c>
       <c r="H7" t="n">
         <v>871</v>
@@ -717,7 +717,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G12" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H12" t="n">
         <v>4083</v>
@@ -833,7 +833,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G16" t="n">
-        <v>3.38712573051453</v>
+        <v>3.38712596893311</v>
       </c>
       <c r="H16" t="n">
         <v>1287</v>
@@ -862,7 +862,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G17" t="n">
-        <v>3.38712573051453</v>
+        <v>3.38712596893311</v>
       </c>
       <c r="H17" t="n">
         <v>1333</v>
@@ -1152,7 +1152,7 @@
         <v>4.52891397476196</v>
       </c>
       <c r="G27" t="n">
-        <v>3.74645590782166</v>
+        <v>3.74645566940308</v>
       </c>
       <c r="H27" t="n">
         <v>1269</v>
@@ -1239,7 +1239,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G30" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H30" t="n">
         <v>333</v>
@@ -1268,7 +1268,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G31" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H31" t="n">
         <v>33</v>
@@ -1297,7 +1297,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G32" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G33" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G34" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G35" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G36" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G37" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H37" t="n">
         <v>168</v>
@@ -1529,7 +1529,7 @@
         <v>4.03222894668579</v>
       </c>
       <c r="G40" t="n">
-        <v>3.33558297157288</v>
+        <v>3.3355827331543</v>
       </c>
       <c r="H40" t="n">
         <v>50</v>
@@ -1587,7 +1587,7 @@
         <v>4.30816507339478</v>
       </c>
       <c r="G42" t="n">
-        <v>3.56384539604187</v>
+        <v>3.56384515762329</v>
       </c>
       <c r="H42" t="n">
         <v>589</v>
@@ -1616,7 +1616,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G43" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H43" t="n">
         <v>112</v>
@@ -1645,7 +1645,7 @@
         <v>4.03400897979736</v>
       </c>
       <c r="G44" t="n">
-        <v>3.33705544471741</v>
+        <v>3.33705520629883</v>
       </c>
       <c r="H44" t="n">
         <v>1197</v>
@@ -1674,7 +1674,7 @@
         <v>4.40785789489746</v>
       </c>
       <c r="G45" t="n">
-        <v>3.6463143825531</v>
+        <v>3.64631462097168</v>
       </c>
       <c r="H45" t="n">
         <v>280</v>
@@ -1703,7 +1703,7 @@
         <v>4.40785789489746</v>
       </c>
       <c r="G46" t="n">
-        <v>3.6463143825531</v>
+        <v>3.64631462097168</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>4.26722002029419</v>
       </c>
       <c r="G51" t="n">
-        <v>3.52997422218323</v>
+        <v>3.52997446060181</v>
       </c>
       <c r="H51" t="n">
         <v>91</v>
@@ -1877,7 +1877,7 @@
         <v>4.59300184249878</v>
       </c>
       <c r="G52" t="n">
-        <v>3.79947090148926</v>
+        <v>3.79947113990784</v>
       </c>
       <c r="H52" t="n">
         <v>1124</v>
@@ -1906,7 +1906,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G53" t="n">
-        <v>3.82892441749573</v>
+        <v>3.82892489433289</v>
       </c>
       <c r="H53" t="n">
         <v>4</v>
@@ -1935,7 +1935,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G54" t="n">
-        <v>3.82892441749573</v>
+        <v>3.82892489433289</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G55" t="n">
-        <v>3.82892441749573</v>
+        <v>3.82892489433289</v>
       </c>
       <c r="H55" t="n">
         <v>56</v>
@@ -1993,7 +1993,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G56" t="n">
-        <v>3.82892441749573</v>
+        <v>3.82892489433289</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>4.21915292739868</v>
       </c>
       <c r="G59" t="n">
-        <v>3.49021220207214</v>
+        <v>3.49021196365356</v>
       </c>
       <c r="H59" t="n">
         <v>364</v>
@@ -2109,7 +2109,7 @@
         <v>4.21915292739868</v>
       </c>
       <c r="G60" t="n">
-        <v>3.49021220207214</v>
+        <v>3.49021196365356</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>4.01620721817017</v>
       </c>
       <c r="G61" t="n">
-        <v>3.32232904434204</v>
+        <v>3.32232928276062</v>
       </c>
       <c r="H61" t="n">
         <v>874</v>
@@ -2428,7 +2428,7 @@
         <v>4.04113006591797</v>
       </c>
       <c r="G71" t="n">
-        <v>3.34294605255127</v>
+        <v>3.34294629096985</v>
       </c>
       <c r="H71" t="n">
         <v>879</v>
@@ -2457,7 +2457,7 @@
         <v>4.04113006591797</v>
       </c>
       <c r="G72" t="n">
-        <v>3.34294605255127</v>
+        <v>3.34294629096985</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>3.91295289993286</v>
       </c>
       <c r="G73" t="n">
-        <v>3.23691368103027</v>
+        <v>3.23691391944885</v>
       </c>
       <c r="H73" t="n">
         <v>759</v>
@@ -2544,7 +2544,7 @@
         <v>4.18176794052124</v>
       </c>
       <c r="G75" t="n">
-        <v>3.45928621292114</v>
+        <v>3.45928573608398</v>
       </c>
       <c r="H75" t="n">
         <v>1353</v>
@@ -2573,7 +2573,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G76" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H76" t="n">
         <v>224</v>
@@ -2602,7 +2602,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G77" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>4.29036283493042</v>
       </c>
       <c r="G82" t="n">
-        <v>3.5491189956665</v>
+        <v>3.54911875724792</v>
       </c>
       <c r="H82" t="n">
         <v>2234</v>
@@ -2776,7 +2776,7 @@
         <v>4.16574621200562</v>
       </c>
       <c r="G83" t="n">
-        <v>3.44603204727173</v>
+        <v>3.44603228569031</v>
       </c>
       <c r="H83" t="n">
         <v>10265</v>
@@ -2805,7 +2805,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G84" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H84" t="n">
         <v>1299</v>
@@ -2834,7 +2834,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G85" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H85" t="n">
         <v>940</v>
@@ -2863,7 +2863,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G86" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>4.20313119888306</v>
       </c>
       <c r="G87" t="n">
-        <v>3.47695851325989</v>
+        <v>3.47695827484131</v>
       </c>
       <c r="H87" t="n">
         <v>2430</v>
@@ -2921,7 +2921,7 @@
         <v>4.20313119888306</v>
       </c>
       <c r="G88" t="n">
-        <v>3.47695851325989</v>
+        <v>3.47695827484131</v>
       </c>
       <c r="H88" t="n">
         <v>109</v>
@@ -3037,7 +3037,7 @@
         <v>3.89871096611023</v>
       </c>
       <c r="G92" t="n">
-        <v>3.22513246536255</v>
+        <v>3.22513270378113</v>
       </c>
       <c r="H92" t="n">
         <v>292</v>
@@ -3182,7 +3182,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G97" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H97" t="n">
         <v>561</v>
@@ -3211,7 +3211,7 @@
         <v>3.38422393798828</v>
       </c>
       <c r="G98" t="n">
-        <v>2.7995331287384</v>
+        <v>2.79953336715698</v>
       </c>
       <c r="H98" t="n">
         <v>581</v>
@@ -3240,7 +3240,7 @@
         <v>3.41804790496826</v>
       </c>
       <c r="G99" t="n">
-        <v>2.82751369476318</v>
+        <v>2.8275134563446</v>
       </c>
       <c r="H99" t="n">
         <v>129</v>
@@ -3327,7 +3327,7 @@
         <v>3.90583205223083</v>
       </c>
       <c r="G102" t="n">
-        <v>3.23102331161499</v>
+        <v>3.23102355003357</v>
       </c>
       <c r="H102" t="n">
         <v>112</v>
@@ -3617,7 +3617,7 @@
         <v>3.77231502532959</v>
       </c>
       <c r="G112" t="n">
-        <v>3.12057375907898</v>
+        <v>3.12057399749756</v>
       </c>
       <c r="H112" t="n">
         <v>1916</v>
@@ -3704,7 +3704,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G115" t="n">
-        <v>2.79806065559387</v>
+        <v>2.79806041717529</v>
       </c>
       <c r="H115" t="n">
         <v>400</v>
@@ -3820,7 +3820,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G119" t="n">
-        <v>2.79806065559387</v>
+        <v>2.79806041717529</v>
       </c>
       <c r="H119" t="n">
         <v>682</v>
@@ -3849,7 +3849,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G120" t="n">
-        <v>2.79806065559387</v>
+        <v>2.79806041717529</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>3.29521203041077</v>
       </c>
       <c r="G122" t="n">
-        <v>2.72590017318726</v>
+        <v>2.7258996963501</v>
       </c>
       <c r="H122" t="n">
         <v>1954</v>
@@ -3936,7 +3936,7 @@
         <v>3.3005530834198</v>
       </c>
       <c r="G123" t="n">
-        <v>2.73031830787659</v>
+        <v>2.73031854629517</v>
       </c>
       <c r="H123" t="n">
         <v>190</v>
@@ -4255,7 +4255,7 @@
         <v>2.40331506729126</v>
       </c>
       <c r="G134" t="n">
-        <v>1.98809540271759</v>
+        <v>1.98809564113617</v>
       </c>
       <c r="H134" t="n">
         <v>22668</v>
@@ -4284,7 +4284,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G135" t="n">
-        <v>1.76719605922699</v>
+        <v>1.7671959400177</v>
       </c>
       <c r="H135" t="n">
         <v>7586</v>
@@ -4313,7 +4313,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G136" t="n">
-        <v>1.76719605922699</v>
+        <v>1.7671959400177</v>
       </c>
       <c r="H136" t="n">
         <v>6199</v>
@@ -4400,7 +4400,7 @@
         <v>2.13450002670288</v>
       </c>
       <c r="G139" t="n">
-        <v>1.76572358608246</v>
+        <v>1.76572346687317</v>
       </c>
       <c r="H139" t="n">
         <v>11343</v>
@@ -4429,7 +4429,7 @@
         <v>2.41043591499329</v>
       </c>
       <c r="G140" t="n">
-        <v>1.99398589134216</v>
+        <v>1.99398624897003</v>
       </c>
       <c r="H140" t="n">
         <v>25915</v>
@@ -4516,7 +4516,7 @@
         <v>2.23241305351257</v>
       </c>
       <c r="G143" t="n">
-        <v>1.84672033786774</v>
+        <v>1.84672009944916</v>
       </c>
       <c r="H143" t="n">
         <v>16023</v>
@@ -4545,7 +4545,7 @@
         <v>2.26267695426941</v>
       </c>
       <c r="G144" t="n">
-        <v>1.87175524234772</v>
+        <v>1.87175559997559</v>
       </c>
       <c r="H144" t="n">
         <v>2313</v>
@@ -4574,7 +4574,7 @@
         <v>2.15408205986023</v>
       </c>
       <c r="G145" t="n">
-        <v>1.78192245960236</v>
+        <v>1.78192222118378</v>
       </c>
       <c r="H145" t="n">
         <v>4435</v>
@@ -4603,7 +4603,7 @@
         <v>2.07753205299377</v>
       </c>
       <c r="G146" t="n">
-        <v>1.71859788894653</v>
+        <v>1.71859776973724</v>
       </c>
       <c r="H146" t="n">
         <v>6315</v>
@@ -4690,7 +4690,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G149" t="n">
-        <v>1.73774242401123</v>
+        <v>1.73774266242981</v>
       </c>
       <c r="H149" t="n">
         <v>918</v>
@@ -4864,7 +4864,7 @@
         <v>2.01166391372681</v>
       </c>
       <c r="G155" t="n">
-        <v>1.66410958766937</v>
+        <v>1.66410970687866</v>
       </c>
       <c r="H155" t="n">
         <v>1874</v>
@@ -4893,7 +4893,7 @@
         <v>2.09711503982544</v>
       </c>
       <c r="G156" t="n">
-        <v>1.73479747772217</v>
+        <v>1.73479735851288</v>
       </c>
       <c r="H156" t="n">
         <v>280</v>
@@ -4922,7 +4922,7 @@
         <v>2.02590489387512</v>
       </c>
       <c r="G157" t="n">
-        <v>1.67589032649994</v>
+        <v>1.67589044570923</v>
       </c>
       <c r="H157" t="n">
         <v>1033</v>
@@ -5009,7 +5009,7 @@
         <v>1.95647597312927</v>
       </c>
       <c r="G160" t="n">
-        <v>1.61845648288727</v>
+        <v>1.61845660209656</v>
       </c>
       <c r="H160" t="n">
         <v>1797</v>
@@ -5038,7 +5038,7 @@
         <v>2.02946591377258</v>
       </c>
       <c r="G161" t="n">
-        <v>1.67883610725403</v>
+        <v>1.67883598804474</v>
       </c>
       <c r="H161" t="n">
         <v>5715</v>
@@ -5125,7 +5125,7 @@
         <v>1.94935500621796</v>
       </c>
       <c r="G164" t="n">
-        <v>1.6125659942627</v>
+        <v>1.61256587505341</v>
       </c>
       <c r="H164" t="n">
         <v>829</v>
@@ -5473,7 +5473,7 @@
         <v>2.13983988761902</v>
       </c>
       <c r="G176" t="n">
-        <v>1.77014088630676</v>
+        <v>1.77014076709747</v>
       </c>
       <c r="H176" t="n">
         <v>7689</v>
@@ -5531,7 +5531,7 @@
         <v>2.11313700675964</v>
       </c>
       <c r="G178" t="n">
-        <v>1.748051404953</v>
+        <v>1.74805152416229</v>
       </c>
       <c r="H178" t="n">
         <v>2418</v>
@@ -5560,7 +5560,7 @@
         <v>2.12203788757324</v>
       </c>
       <c r="G179" t="n">
-        <v>1.7554144859314</v>
+        <v>1.75541436672211</v>
       </c>
       <c r="H179" t="n">
         <v>1487</v>
@@ -5589,7 +5589,7 @@
         <v>2.08287310600281</v>
       </c>
       <c r="G180" t="n">
-        <v>1.72301602363586</v>
+        <v>1.72301614284515</v>
       </c>
       <c r="H180" t="n">
         <v>674</v>
@@ -5618,7 +5618,7 @@
         <v>2.09177398681641</v>
       </c>
       <c r="G181" t="n">
-        <v>1.73037910461426</v>
+        <v>1.73037922382355</v>
       </c>
       <c r="H181" t="n">
         <v>1713</v>
@@ -5734,7 +5734,7 @@
         <v>1.93155300617218</v>
       </c>
       <c r="G185" t="n">
-        <v>1.59783971309662</v>
+        <v>1.59783959388733</v>
       </c>
       <c r="H185" t="n">
         <v>494</v>
@@ -5792,7 +5792,7 @@
         <v>1.87992596626282</v>
       </c>
       <c r="G187" t="n">
-        <v>1.55513203144073</v>
+        <v>1.55513215065002</v>
       </c>
       <c r="H187" t="n">
         <v>674</v>
@@ -5821,7 +5821,7 @@
         <v>1.93155300617218</v>
       </c>
       <c r="G188" t="n">
-        <v>1.59783971309662</v>
+        <v>1.59783959388733</v>
       </c>
       <c r="H188" t="n">
         <v>95</v>
@@ -5879,7 +5879,7 @@
         <v>1.99386096000671</v>
       </c>
       <c r="G190" t="n">
-        <v>1.64938247203827</v>
+        <v>1.64938271045685</v>
       </c>
       <c r="H190" t="n">
         <v>619</v>
@@ -5908,7 +5908,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G191" t="n">
-        <v>1.73774242401123</v>
+        <v>1.73774266242981</v>
       </c>
       <c r="H191" t="n">
         <v>4547</v>
@@ -5937,7 +5937,7 @@
         <v>2.29650092124939</v>
       </c>
       <c r="G192" t="n">
-        <v>1.89973545074463</v>
+        <v>1.89973556995392</v>
       </c>
       <c r="H192" t="n">
         <v>5945</v>
@@ -5966,7 +5966,7 @@
         <v>2.24309396743774</v>
       </c>
       <c r="G193" t="n">
-        <v>1.85555565357208</v>
+        <v>1.85555577278137</v>
       </c>
       <c r="H193" t="n">
         <v>7335</v>
@@ -5995,7 +5995,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G194" t="n">
-        <v>1.76719605922699</v>
+        <v>1.7671959400177</v>
       </c>
       <c r="H194" t="n">
         <v>1123</v>
@@ -6024,7 +6024,7 @@
         <v>2.30362200737</v>
       </c>
       <c r="G195" t="n">
-        <v>1.90562641620636</v>
+        <v>1.90562629699707</v>
       </c>
       <c r="H195" t="n">
         <v>8629</v>
@@ -6053,7 +6053,7 @@
         <v>2.40331506729126</v>
       </c>
       <c r="G196" t="n">
-        <v>1.98809540271759</v>
+        <v>1.98809564113617</v>
       </c>
       <c r="H196" t="n">
         <v>7857</v>
@@ -6082,7 +6082,7 @@
         <v>2.31608390808105</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91593515872955</v>
+        <v>1.91593539714813</v>
       </c>
       <c r="H197" t="n">
         <v>4776</v>
@@ -6111,7 +6111,7 @@
         <v>2.41577696800232</v>
       </c>
       <c r="G198" t="n">
-        <v>1.99840462207794</v>
+        <v>1.99840438365936</v>
       </c>
       <c r="H198" t="n">
         <v>1058</v>
@@ -6140,7 +6140,7 @@
         <v>2.52437090873718</v>
       </c>
       <c r="G199" t="n">
-        <v>2.08823680877686</v>
+        <v>2.08823657035828</v>
       </c>
       <c r="H199" t="n">
         <v>365</v>
@@ -6198,7 +6198,7 @@
         <v>2.35880899429321</v>
       </c>
       <c r="G201" t="n">
-        <v>1.95127904415131</v>
+        <v>1.95127856731415</v>
       </c>
       <c r="H201" t="n">
         <v>224</v>
@@ -6227,7 +6227,7 @@
         <v>2.13450002670288</v>
       </c>
       <c r="G202" t="n">
-        <v>1.76572358608246</v>
+        <v>1.76572346687317</v>
       </c>
       <c r="H202" t="n">
         <v>7171</v>
@@ -6256,7 +6256,7 @@
         <v>2.27869892120361</v>
       </c>
       <c r="G203" t="n">
-        <v>1.88500928878784</v>
+        <v>1.88500940799713</v>
       </c>
       <c r="H203" t="n">
         <v>9785</v>
@@ -6285,7 +6285,7 @@
         <v>2.15764307975769</v>
       </c>
       <c r="G204" t="n">
-        <v>1.78486824035645</v>
+        <v>1.78486835956573</v>
       </c>
       <c r="H204" t="n">
         <v>5715</v>
@@ -6314,7 +6314,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G205" t="n">
-        <v>1.76719605922699</v>
+        <v>1.7671959400177</v>
       </c>
       <c r="H205" t="n">
         <v>16748</v>
@@ -6343,7 +6343,7 @@
         <v>2.09533500671387</v>
       </c>
       <c r="G206" t="n">
-        <v>1.73332500457764</v>
+        <v>1.73332512378693</v>
       </c>
       <c r="H206" t="n">
         <v>2548</v>
@@ -6372,7 +6372,7 @@
         <v>2.14340090751648</v>
       </c>
       <c r="G207" t="n">
-        <v>1.77308666706085</v>
+        <v>1.77308678627014</v>
       </c>
       <c r="H207" t="n">
         <v>2034</v>
@@ -6430,7 +6430,7 @@
         <v>2.10245609283447</v>
       </c>
       <c r="G209" t="n">
-        <v>1.73921573162079</v>
+        <v>1.73921597003937</v>
       </c>
       <c r="H209" t="n">
         <v>730</v>
@@ -6488,7 +6488,7 @@
         <v>2.09177398681641</v>
       </c>
       <c r="G211" t="n">
-        <v>1.73037910461426</v>
+        <v>1.73037922382355</v>
       </c>
       <c r="H211" t="n">
         <v>845</v>
@@ -6517,7 +6517,7 @@
         <v>2.059730052948</v>
       </c>
       <c r="G212" t="n">
-        <v>1.70387148857117</v>
+        <v>1.70387160778046</v>
       </c>
       <c r="H212" t="n">
         <v>973</v>
@@ -6546,7 +6546,7 @@
         <v>2.059730052948</v>
       </c>
       <c r="G213" t="n">
-        <v>1.70387148857117</v>
+        <v>1.70387160778046</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>2.11313700675964</v>
       </c>
       <c r="G214" t="n">
-        <v>1.748051404953</v>
+        <v>1.74805152416229</v>
       </c>
       <c r="H214" t="n">
         <v>364</v>
@@ -6604,7 +6604,7 @@
         <v>2.11669707298279</v>
       </c>
       <c r="G215" t="n">
-        <v>1.75099647045135</v>
+        <v>1.75099635124207</v>
       </c>
       <c r="H215" t="n">
         <v>561</v>
@@ -6749,7 +6749,7 @@
         <v>2.02946591377258</v>
       </c>
       <c r="G220" t="n">
-        <v>1.67883610725403</v>
+        <v>1.67883598804474</v>
       </c>
       <c r="H220" t="n">
         <v>898</v>
@@ -6778,7 +6778,7 @@
         <v>2.09711503982544</v>
       </c>
       <c r="G221" t="n">
-        <v>1.73479747772217</v>
+        <v>1.73479735851288</v>
       </c>
       <c r="H221" t="n">
         <v>56</v>
@@ -6836,7 +6836,7 @@
         <v>2.15408205986023</v>
       </c>
       <c r="G223" t="n">
-        <v>1.78192245960236</v>
+        <v>1.78192222118378</v>
       </c>
       <c r="H223" t="n">
         <v>1893</v>
@@ -6865,7 +6865,7 @@
         <v>2.15052199363708</v>
       </c>
       <c r="G224" t="n">
-        <v>1.77897727489471</v>
+        <v>1.778977394104</v>
       </c>
       <c r="H224" t="n">
         <v>522</v>
@@ -6894,7 +6894,7 @@
         <v>2.00098204612732</v>
       </c>
       <c r="G225" t="n">
-        <v>1.65527319908142</v>
+        <v>1.6552734375</v>
       </c>
       <c r="H225" t="n">
         <v>56</v>
@@ -6923,7 +6923,7 @@
         <v>2.00454306602478</v>
       </c>
       <c r="G226" t="n">
-        <v>1.65821897983551</v>
+        <v>1.6582190990448</v>
       </c>
       <c r="H226" t="n">
         <v>472</v>
@@ -7010,7 +7010,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G229" t="n">
-        <v>1.7642502784729</v>
+        <v>1.76425015926361</v>
       </c>
       <c r="H229" t="n">
         <v>1647</v>
@@ -7039,7 +7039,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G230" t="n">
-        <v>1.7642502784729</v>
+        <v>1.76425015926361</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>2.059730052948</v>
       </c>
       <c r="G231" t="n">
-        <v>1.70387148857117</v>
+        <v>1.70387160778046</v>
       </c>
       <c r="H231" t="n">
         <v>648</v>
@@ -7097,7 +7097,7 @@
         <v>2.01166391372681</v>
       </c>
       <c r="G232" t="n">
-        <v>1.66410958766937</v>
+        <v>1.66410970687866</v>
       </c>
       <c r="H232" t="n">
         <v>2171</v>
@@ -7126,7 +7126,7 @@
         <v>2.01166391372681</v>
       </c>
       <c r="G233" t="n">
-        <v>1.66410958766937</v>
+        <v>1.66410970687866</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>2.01166391372681</v>
       </c>
       <c r="G234" t="n">
-        <v>1.66410958766937</v>
+        <v>1.66410970687866</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>2.07041096687317</v>
       </c>
       <c r="G240" t="n">
-        <v>1.71270716190338</v>
+        <v>1.7127069234848</v>
       </c>
       <c r="H240" t="n">
         <v>281</v>
@@ -7358,7 +7358,7 @@
         <v>2.07041096687317</v>
       </c>
       <c r="G241" t="n">
-        <v>1.71270716190338</v>
+        <v>1.7127069234848</v>
       </c>
       <c r="H241" t="n">
         <v>112</v>
@@ -7416,7 +7416,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G243" t="n">
-        <v>1.7642502784729</v>
+        <v>1.76425015926361</v>
       </c>
       <c r="H243" t="n">
         <v>907</v>
@@ -7445,7 +7445,7 @@
         <v>2.15408205986023</v>
       </c>
       <c r="G244" t="n">
-        <v>1.78192245960236</v>
+        <v>1.78192222118378</v>
       </c>
       <c r="H244" t="n">
         <v>6094</v>
@@ -7474,7 +7474,7 @@
         <v>2.13271903991699</v>
       </c>
       <c r="G245" t="n">
-        <v>1.7642502784729</v>
+        <v>1.76425015926361</v>
       </c>
       <c r="H245" t="n">
         <v>5117</v>
@@ -7503,7 +7503,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G246" t="n">
-        <v>1.73774242401123</v>
+        <v>1.73774266242981</v>
       </c>
       <c r="H246" t="n">
         <v>664</v>
@@ -7561,7 +7561,7 @@
         <v>2.0846529006958</v>
       </c>
       <c r="G248" t="n">
-        <v>1.72448837757111</v>
+        <v>1.7244884967804</v>
       </c>
       <c r="H248" t="n">
         <v>449</v>
@@ -7619,7 +7619,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G250" t="n">
-        <v>1.76719605922699</v>
+        <v>1.7671959400177</v>
       </c>
       <c r="H250" t="n">
         <v>5386</v>
@@ -7706,7 +7706,7 @@
         <v>2.16654396057129</v>
       </c>
       <c r="G253" t="n">
-        <v>1.79223120212555</v>
+        <v>1.79223132133484</v>
       </c>
       <c r="H253" t="n">
         <v>9056</v>
@@ -7735,7 +7735,7 @@
         <v>2.45672202110291</v>
       </c>
       <c r="G254" t="n">
-        <v>2.03227543830872</v>
+        <v>2.03227519989014</v>
       </c>
       <c r="H254" t="n">
         <v>27479</v>
@@ -7793,7 +7793,7 @@
         <v>2.41221594810486</v>
       </c>
       <c r="G256" t="n">
-        <v>1.99545836448669</v>
+        <v>1.99545884132385</v>
       </c>
       <c r="H256" t="n">
         <v>7030</v>
@@ -7822,7 +7822,7 @@
         <v>2.34456706047058</v>
       </c>
       <c r="G257" t="n">
-        <v>1.93949747085571</v>
+        <v>1.93949723243713</v>
       </c>
       <c r="H257" t="n">
         <v>4814</v>
@@ -7851,7 +7851,7 @@
         <v>2.74155902862549</v>
       </c>
       <c r="G258" t="n">
-        <v>2.26790118217468</v>
+        <v>2.26790142059326</v>
       </c>
       <c r="H258" t="n">
         <v>17046</v>
@@ -7909,7 +7909,7 @@
         <v>2.79318594932556</v>
       </c>
       <c r="G260" t="n">
-        <v>2.31060886383057</v>
+        <v>2.31060862541199</v>
       </c>
       <c r="H260" t="n">
         <v>17760</v>
@@ -7938,7 +7938,7 @@
         <v>2.85905504226685</v>
       </c>
       <c r="G261" t="n">
-        <v>2.36509728431702</v>
+        <v>2.3650975227356</v>
       </c>
       <c r="H261" t="n">
         <v>7738</v>
@@ -7967,7 +7967,7 @@
         <v>3.23824501037598</v>
       </c>
       <c r="G262" t="n">
-        <v>2.6787748336792</v>
+        <v>2.67877531051636</v>
       </c>
       <c r="H262" t="n">
         <v>34397</v>
@@ -8054,7 +8054,7 @@
         <v>4.67133283615112</v>
       </c>
       <c r="G265" t="n">
-        <v>3.86426877975464</v>
+        <v>3.86426854133606</v>
       </c>
       <c r="H265" t="n">
         <v>108992</v>
@@ -8112,7 +8112,7 @@
         <v>4.40073680877686</v>
       </c>
       <c r="G267" t="n">
-        <v>3.64042377471924</v>
+        <v>3.64042353630066</v>
       </c>
       <c r="H267" t="n">
         <v>57818</v>
@@ -8199,7 +8199,7 @@
         <v>4.16574621200562</v>
       </c>
       <c r="G270" t="n">
-        <v>3.44603204727173</v>
+        <v>3.44603228569031</v>
       </c>
       <c r="H270" t="n">
         <v>17616</v>
@@ -8228,7 +8228,7 @@
         <v>4.05893182754517</v>
       </c>
       <c r="G271" t="n">
-        <v>3.35767221450806</v>
+        <v>3.35767197608948</v>
       </c>
       <c r="H271" t="n">
         <v>19224</v>
@@ -8257,7 +8257,7 @@
         <v>4.59300184249878</v>
       </c>
       <c r="G272" t="n">
-        <v>3.79947090148926</v>
+        <v>3.79947113990784</v>
       </c>
       <c r="H272" t="n">
         <v>58292</v>
@@ -8286,7 +8286,7 @@
         <v>4.3953971862793</v>
       </c>
       <c r="G273" t="n">
-        <v>3.63600659370422</v>
+        <v>3.63600635528564</v>
       </c>
       <c r="H273" t="n">
         <v>30650</v>
@@ -8315,7 +8315,7 @@
         <v>4.42210006713867</v>
       </c>
       <c r="G274" t="n">
-        <v>3.6580958366394</v>
+        <v>3.65809631347656</v>
       </c>
       <c r="H274" t="n">
         <v>7239</v>
@@ -8344,7 +8344,7 @@
         <v>4.3241868019104</v>
       </c>
       <c r="G275" t="n">
-        <v>3.57709932327271</v>
+        <v>3.57709956169128</v>
       </c>
       <c r="H275" t="n">
         <v>4632</v>
@@ -8373,7 +8373,7 @@
         <v>4.43278121948242</v>
       </c>
       <c r="G276" t="n">
-        <v>3.66693210601807</v>
+        <v>3.66693186759949</v>
       </c>
       <c r="H276" t="n">
         <v>12359</v>
@@ -8431,7 +8431,7 @@
         <v>4.25475788116455</v>
       </c>
       <c r="G278" t="n">
-        <v>3.51966571807861</v>
+        <v>3.51966547966003</v>
       </c>
       <c r="H278" t="n">
         <v>10019</v>
@@ -8489,7 +8489,7 @@
         <v>4.35979223251343</v>
       </c>
       <c r="G280" t="n">
-        <v>3.60655307769775</v>
+        <v>3.60655331611633</v>
       </c>
       <c r="H280" t="n">
         <v>2930</v>
@@ -8547,7 +8547,7 @@
         <v>4.3241868019104</v>
       </c>
       <c r="G282" t="n">
-        <v>3.57709932327271</v>
+        <v>3.57709956169128</v>
       </c>
       <c r="H282" t="n">
         <v>3567</v>
@@ -8576,7 +8576,7 @@
         <v>4.32596683502197</v>
       </c>
       <c r="G283" t="n">
-        <v>3.57857179641724</v>
+        <v>3.57857155799866</v>
       </c>
       <c r="H283" t="n">
         <v>27176</v>
@@ -8605,7 +8605,7 @@
         <v>4.32774782180786</v>
       </c>
       <c r="G284" t="n">
-        <v>3.58004522323608</v>
+        <v>3.58004546165466</v>
       </c>
       <c r="H284" t="n">
         <v>731</v>
@@ -8692,7 +8692,7 @@
         <v>3.94677805900574</v>
       </c>
       <c r="G287" t="n">
-        <v>3.26489496231079</v>
+        <v>3.26489520072937</v>
       </c>
       <c r="H287" t="n">
         <v>2309</v>
@@ -8721,7 +8721,7 @@
         <v>3.92007398605347</v>
       </c>
       <c r="G288" t="n">
-        <v>3.24280500411987</v>
+        <v>3.24280476570129</v>
       </c>
       <c r="H288" t="n">
         <v>728</v>
@@ -8750,7 +8750,7 @@
         <v>3.92007398605347</v>
       </c>
       <c r="G289" t="n">
-        <v>3.24280500411987</v>
+        <v>3.24280476570129</v>
       </c>
       <c r="H289" t="n">
         <v>1247</v>
@@ -8808,7 +8808,7 @@
         <v>3.75629305839539</v>
       </c>
       <c r="G291" t="n">
-        <v>3.1073203086853</v>
+        <v>3.10732007026672</v>
       </c>
       <c r="H291" t="n">
         <v>2984</v>
@@ -8837,7 +8837,7 @@
         <v>3.69932508468628</v>
       </c>
       <c r="G292" t="n">
-        <v>3.06019449234009</v>
+        <v>3.06019425392151</v>
       </c>
       <c r="H292" t="n">
         <v>4324</v>
@@ -8866,7 +8866,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G293" t="n">
-        <v>3.38712573051453</v>
+        <v>3.38712596893311</v>
       </c>
       <c r="H293" t="n">
         <v>9236</v>
@@ -8895,7 +8895,7 @@
         <v>3.85954594612122</v>
       </c>
       <c r="G294" t="n">
-        <v>3.19273400306702</v>
+        <v>3.1927342414856</v>
       </c>
       <c r="H294" t="n">
         <v>2137</v>
@@ -8953,7 +8953,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G296" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H296" t="n">
         <v>1256</v>
@@ -8982,7 +8982,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G297" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H297" t="n">
         <v>2543</v>
@@ -9040,7 +9040,7 @@
         <v>4.04113006591797</v>
       </c>
       <c r="G299" t="n">
-        <v>3.34294605255127</v>
+        <v>3.34294629096985</v>
       </c>
       <c r="H299" t="n">
         <v>3903</v>
@@ -9069,7 +9069,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G300" t="n">
-        <v>3.38712573051453</v>
+        <v>3.38712596893311</v>
       </c>
       <c r="H300" t="n">
         <v>13458</v>
@@ -9185,7 +9185,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G304" t="n">
-        <v>3.18831586837769</v>
+        <v>3.18831562995911</v>
       </c>
       <c r="H304" t="n">
         <v>1235</v>
@@ -9214,7 +9214,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G305" t="n">
-        <v>3.18831586837769</v>
+        <v>3.18831562995911</v>
       </c>
       <c r="H305" t="n">
         <v>1282</v>
@@ -9243,7 +9243,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G306" t="n">
-        <v>3.18831586837769</v>
+        <v>3.18831562995911</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>4.09275722503662</v>
       </c>
       <c r="G308" t="n">
-        <v>3.38565373420715</v>
+        <v>3.38565349578857</v>
       </c>
       <c r="H308" t="n">
         <v>112</v>
@@ -9359,7 +9359,7 @@
         <v>3.9093930721283</v>
       </c>
       <c r="G310" t="n">
-        <v>3.23396944999695</v>
+        <v>3.23396921157837</v>
       </c>
       <c r="H310" t="n">
         <v>842</v>
@@ -9388,7 +9388,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G311" t="n">
-        <v>3.18831586837769</v>
+        <v>3.18831562995911</v>
       </c>
       <c r="H311" t="n">
         <v>2222</v>
@@ -9417,7 +9417,7 @@
         <v>3.77231502532959</v>
       </c>
       <c r="G312" t="n">
-        <v>3.12057375907898</v>
+        <v>3.12057399749756</v>
       </c>
       <c r="H312" t="n">
         <v>207</v>
@@ -9446,7 +9446,7 @@
         <v>3.70644593238831</v>
       </c>
       <c r="G313" t="n">
-        <v>3.06608510017395</v>
+        <v>3.06608533859253</v>
       </c>
       <c r="H313" t="n">
         <v>2608</v>
@@ -9504,7 +9504,7 @@
         <v>3.65481901168823</v>
       </c>
       <c r="G315" t="n">
-        <v>3.02337789535522</v>
+        <v>3.0233781337738</v>
       </c>
       <c r="H315" t="n">
         <v>57</v>
@@ -9591,7 +9591,7 @@
         <v>3.65303897857666</v>
       </c>
       <c r="G318" t="n">
-        <v>3.02190542221069</v>
+        <v>3.02190518379211</v>
       </c>
       <c r="H318" t="n">
         <v>112</v>
@@ -9620,7 +9620,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G319" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H319" t="n">
         <v>3638</v>
@@ -9707,7 +9707,7 @@
         <v>3.56580805778503</v>
       </c>
       <c r="G322" t="n">
-        <v>2.94974517822266</v>
+        <v>2.94974541664124</v>
       </c>
       <c r="H322" t="n">
         <v>1994</v>
@@ -9765,7 +9765,7 @@
         <v>3.48213696479797</v>
       </c>
       <c r="G324" t="n">
-        <v>2.88052988052368</v>
+        <v>2.88053011894226</v>
       </c>
       <c r="H324" t="n">
         <v>29</v>
@@ -9823,7 +9823,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G326" t="n">
-        <v>3.82892441749573</v>
+        <v>3.82892489433289</v>
       </c>
       <c r="H326" t="n">
         <v>278520</v>
@@ -9852,7 +9852,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G327" t="n">
-        <v>3.53439211845398</v>
+        <v>3.5343918800354</v>
       </c>
       <c r="H327" t="n">
         <v>72071</v>
@@ -9881,7 +9881,7 @@
         <v>4.41319894790649</v>
       </c>
       <c r="G328" t="n">
-        <v>3.65073251724243</v>
+        <v>3.65073275566101</v>
       </c>
       <c r="H328" t="n">
         <v>30835</v>
@@ -9910,7 +9910,7 @@
         <v>4.21381282806396</v>
       </c>
       <c r="G329" t="n">
-        <v>3.48579478263855</v>
+        <v>3.48579502105713</v>
       </c>
       <c r="H329" t="n">
         <v>5440</v>
@@ -9939,7 +9939,7 @@
         <v>4.32596683502197</v>
       </c>
       <c r="G330" t="n">
-        <v>3.57857179641724</v>
+        <v>3.57857155799866</v>
       </c>
       <c r="H330" t="n">
         <v>34372</v>
@@ -9968,7 +9968,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G331" t="n">
-        <v>3.24575066566467</v>
+        <v>3.24575018882751</v>
       </c>
       <c r="H331" t="n">
         <v>39316</v>
@@ -10055,7 +10055,7 @@
         <v>3.98950290679932</v>
       </c>
       <c r="G334" t="n">
-        <v>3.30023837089539</v>
+        <v>3.30023860931396</v>
       </c>
       <c r="H334" t="n">
         <v>5942</v>
@@ -10171,7 +10171,7 @@
         <v>3.93609595298767</v>
       </c>
       <c r="G338" t="n">
-        <v>3.25605869293213</v>
+        <v>3.25605845451355</v>
       </c>
       <c r="H338" t="n">
         <v>7661</v>
@@ -10200,7 +10200,7 @@
         <v>3.93609595298767</v>
       </c>
       <c r="G339" t="n">
-        <v>3.25605869293213</v>
+        <v>3.25605845451355</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>3.8915901184082</v>
       </c>
       <c r="G341" t="n">
-        <v>3.21924209594727</v>
+        <v>3.21924233436584</v>
       </c>
       <c r="H341" t="n">
         <v>1665</v>
@@ -10287,7 +10287,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G342" t="n">
-        <v>3.16033554077148</v>
+        <v>3.16033577919006</v>
       </c>
       <c r="H342" t="n">
         <v>731</v>
@@ -10345,7 +10345,7 @@
         <v>3.86844706535339</v>
       </c>
       <c r="G344" t="n">
-        <v>3.20009756088257</v>
+        <v>3.20009732246399</v>
       </c>
       <c r="H344" t="n">
         <v>2777</v>
@@ -10403,7 +10403,7 @@
         <v>3.85954594612122</v>
       </c>
       <c r="G346" t="n">
-        <v>3.19273400306702</v>
+        <v>3.1927342414856</v>
       </c>
       <c r="H346" t="n">
         <v>320</v>
@@ -10432,7 +10432,7 @@
         <v>3.79189705848694</v>
       </c>
       <c r="G347" t="n">
-        <v>3.13677310943604</v>
+        <v>3.13677287101746</v>
       </c>
       <c r="H347" t="n">
         <v>1464</v>
@@ -10519,7 +10519,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G350" t="n">
-        <v>3.16033554077148</v>
+        <v>3.16033577919006</v>
       </c>
       <c r="H350" t="n">
         <v>2507</v>
@@ -10664,7 +10664,7 @@
         <v>3.83462309837341</v>
       </c>
       <c r="G355" t="n">
-        <v>3.17211699485779</v>
+        <v>3.17211723327637</v>
       </c>
       <c r="H355" t="n">
         <v>2162</v>
@@ -10809,7 +10809,7 @@
         <v>3.79189705848694</v>
       </c>
       <c r="G360" t="n">
-        <v>3.13677310943604</v>
+        <v>3.13677287101746</v>
       </c>
       <c r="H360" t="n">
         <v>319</v>
@@ -10838,7 +10838,7 @@
         <v>3.79189705848694</v>
       </c>
       <c r="G361" t="n">
-        <v>3.13677310943604</v>
+        <v>3.13677287101746</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>3.87200808525085</v>
       </c>
       <c r="G362" t="n">
-        <v>3.20304298400879</v>
+        <v>3.20304322242737</v>
       </c>
       <c r="H362" t="n">
         <v>224</v>
@@ -10954,7 +10954,7 @@
         <v>3.78299593925476</v>
       </c>
       <c r="G365" t="n">
-        <v>3.12940955162048</v>
+        <v>3.1294093132019</v>
       </c>
       <c r="H365" t="n">
         <v>1274</v>
@@ -10983,7 +10983,7 @@
         <v>3.81682109832764</v>
       </c>
       <c r="G366" t="n">
-        <v>3.157390832901</v>
+        <v>3.15739107131958</v>
       </c>
       <c r="H366" t="n">
         <v>6042</v>
@@ -11012,7 +11012,7 @@
         <v>3.69220399856567</v>
       </c>
       <c r="G367" t="n">
-        <v>3.05430364608765</v>
+        <v>3.05430388450623</v>
       </c>
       <c r="H367" t="n">
         <v>1012</v>
@@ -11041,7 +11041,7 @@
         <v>3.58004903793335</v>
       </c>
       <c r="G368" t="n">
-        <v>2.96152567863464</v>
+        <v>2.96152591705322</v>
       </c>
       <c r="H368" t="n">
         <v>2763</v>
@@ -11070,7 +11070,7 @@
         <v>3.59607195854187</v>
       </c>
       <c r="G369" t="n">
-        <v>2.97478032112122</v>
+        <v>2.97478055953979</v>
       </c>
       <c r="H369" t="n">
         <v>1067</v>
@@ -11099,7 +11099,7 @@
         <v>3.54800510406494</v>
       </c>
       <c r="G370" t="n">
-        <v>2.93501782417297</v>
+        <v>2.93501806259155</v>
       </c>
       <c r="H370" t="n">
         <v>3053</v>
@@ -11157,7 +11157,7 @@
         <v>3.8114800453186</v>
       </c>
       <c r="G372" t="n">
-        <v>3.15297269821167</v>
+        <v>3.15297245979309</v>
       </c>
       <c r="H372" t="n">
         <v>56763</v>
@@ -11273,7 +11273,7 @@
         <v>3.60675311088562</v>
       </c>
       <c r="G376" t="n">
-        <v>2.98361611366272</v>
+        <v>2.9836163520813</v>
       </c>
       <c r="H376" t="n">
         <v>874</v>
@@ -11302,7 +11302,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G377" t="n">
-        <v>2.94827198982239</v>
+        <v>2.94827175140381</v>
       </c>
       <c r="H377" t="n">
         <v>672</v>
@@ -11331,7 +11331,7 @@
         <v>3.60675311088562</v>
       </c>
       <c r="G378" t="n">
-        <v>2.98361611366272</v>
+        <v>2.9836163520813</v>
       </c>
       <c r="H378" t="n">
         <v>22</v>
@@ -11505,7 +11505,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G384" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H384" t="n">
         <v>572</v>
@@ -11534,7 +11534,7 @@
         <v>3.57114791870117</v>
       </c>
       <c r="G385" t="n">
-        <v>2.95416283607483</v>
+        <v>2.95416259765625</v>
       </c>
       <c r="H385" t="n">
         <v>1159</v>
@@ -11563,7 +11563,7 @@
         <v>3.49459791183472</v>
       </c>
       <c r="G386" t="n">
-        <v>2.89083790779114</v>
+        <v>2.89083814620972</v>
       </c>
       <c r="H386" t="n">
         <v>848</v>
@@ -11650,7 +11650,7 @@
         <v>3.47145509719849</v>
       </c>
       <c r="G389" t="n">
-        <v>2.87169337272644</v>
+        <v>2.87169361114502</v>
       </c>
       <c r="H389" t="n">
         <v>649</v>
@@ -11708,7 +11708,7 @@
         <v>3.48925805091858</v>
       </c>
       <c r="G391" t="n">
-        <v>2.88642048835754</v>
+        <v>2.88642072677612</v>
       </c>
       <c r="H391" t="n">
         <v>642</v>
@@ -11766,7 +11766,7 @@
         <v>3.50884008407593</v>
       </c>
       <c r="G393" t="n">
-        <v>2.90261960029602</v>
+        <v>2.9026198387146</v>
       </c>
       <c r="H393" t="n">
         <v>12647</v>
@@ -11795,7 +11795,7 @@
         <v>3.50349903106689</v>
       </c>
       <c r="G394" t="n">
-        <v>2.89820146560669</v>
+        <v>2.89820122718811</v>
       </c>
       <c r="H394" t="n">
         <v>921</v>
@@ -11824,7 +11824,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G395" t="n">
-        <v>2.84224104881287</v>
+        <v>2.84224081039429</v>
       </c>
       <c r="H395" t="n">
         <v>954</v>
@@ -11853,7 +11853,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G396" t="n">
-        <v>2.84224104881287</v>
+        <v>2.84224081039429</v>
       </c>
       <c r="H396" t="n">
         <v>421</v>
@@ -12085,7 +12085,7 @@
         <v>3.70644593238831</v>
       </c>
       <c r="G404" t="n">
-        <v>3.06608510017395</v>
+        <v>3.06608533859253</v>
       </c>
       <c r="H404" t="n">
         <v>38976</v>
@@ -12114,7 +12114,7 @@
         <v>3.804358959198</v>
       </c>
       <c r="G405" t="n">
-        <v>3.14708185195923</v>
+        <v>3.14708209037781</v>
       </c>
       <c r="H405" t="n">
         <v>42911</v>
@@ -12201,7 +12201,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G408" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H408" t="n">
         <v>7539</v>
@@ -12230,7 +12230,7 @@
         <v>3.65838003158569</v>
       </c>
       <c r="G409" t="n">
-        <v>3.02632331848145</v>
+        <v>3.02632355690002</v>
       </c>
       <c r="H409" t="n">
         <v>1995</v>
@@ -12259,7 +12259,7 @@
         <v>3.59785199165344</v>
       </c>
       <c r="G410" t="n">
-        <v>2.97625303268433</v>
+        <v>2.97625279426575</v>
       </c>
       <c r="H410" t="n">
         <v>2148</v>
@@ -12346,7 +12346,7 @@
         <v>3.56580805778503</v>
       </c>
       <c r="G413" t="n">
-        <v>2.94974517822266</v>
+        <v>2.94974541664124</v>
       </c>
       <c r="H413" t="n">
         <v>449</v>
@@ -12375,7 +12375,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G414" t="n">
-        <v>2.94679951667786</v>
+        <v>2.94679927825928</v>
       </c>
       <c r="H414" t="n">
         <v>393</v>
@@ -12404,7 +12404,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G415" t="n">
-        <v>2.94679951667786</v>
+        <v>2.94679927825928</v>
       </c>
       <c r="H415" t="n">
         <v>140</v>
@@ -12433,7 +12433,7 @@
         <v>3.59607195854187</v>
       </c>
       <c r="G416" t="n">
-        <v>2.97478032112122</v>
+        <v>2.97478055953979</v>
       </c>
       <c r="H416" t="n">
         <v>168</v>
@@ -12462,7 +12462,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G417" t="n">
-        <v>2.94827198982239</v>
+        <v>2.94827175140381</v>
       </c>
       <c r="H417" t="n">
         <v>561</v>
@@ -12491,7 +12491,7 @@
         <v>3.56402707099915</v>
       </c>
       <c r="G418" t="n">
-        <v>2.94827198982239</v>
+        <v>2.94827175140381</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>3.57826900482178</v>
       </c>
       <c r="G420" t="n">
-        <v>2.96005344390869</v>
+        <v>2.96005320549011</v>
       </c>
       <c r="H420" t="n">
         <v>11998</v>
@@ -12578,7 +12578,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G421" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H421" t="n">
         <v>1850</v>
@@ -12607,7 +12607,7 @@
         <v>3.61209392547607</v>
       </c>
       <c r="G422" t="n">
-        <v>2.98803448677063</v>
+        <v>2.98803424835205</v>
       </c>
       <c r="H422" t="n">
         <v>991</v>
@@ -12665,7 +12665,7 @@
         <v>3.57292890548706</v>
       </c>
       <c r="G424" t="n">
-        <v>2.9556360244751</v>
+        <v>2.95563578605652</v>
       </c>
       <c r="H424" t="n">
         <v>3529</v>
@@ -12723,7 +12723,7 @@
         <v>3.55690598487854</v>
       </c>
       <c r="G426" t="n">
-        <v>2.94238138198853</v>
+        <v>2.94238114356995</v>
       </c>
       <c r="H426" t="n">
         <v>651</v>
@@ -12752,7 +12752,7 @@
         <v>3.55690598487854</v>
       </c>
       <c r="G427" t="n">
-        <v>2.94238138198853</v>
+        <v>2.94238114356995</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G430" t="n">
-        <v>2.79806065559387</v>
+        <v>2.79806041717529</v>
       </c>
       <c r="H430" t="n">
         <v>6347</v>
@@ -12868,7 +12868,7 @@
         <v>3.560467004776</v>
       </c>
       <c r="G431" t="n">
-        <v>2.94532680511475</v>
+        <v>2.94532704353333</v>
       </c>
       <c r="H431" t="n">
         <v>2306</v>
@@ -12897,7 +12897,7 @@
         <v>3.47323489189148</v>
       </c>
       <c r="G432" t="n">
-        <v>2.87316560745239</v>
+        <v>2.87316584587097</v>
       </c>
       <c r="H432" t="n">
         <v>3521</v>
@@ -12926,7 +12926,7 @@
         <v>3.49281811714172</v>
       </c>
       <c r="G433" t="n">
-        <v>2.88936567306519</v>
+        <v>2.88936543464661</v>
       </c>
       <c r="H433" t="n">
         <v>2375</v>
@@ -12955,7 +12955,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G434" t="n">
-        <v>2.84224104881287</v>
+        <v>2.84224081039429</v>
       </c>
       <c r="H434" t="n">
         <v>5513</v>
@@ -13013,7 +13013,7 @@
         <v>3.47145509719849</v>
       </c>
       <c r="G436" t="n">
-        <v>2.87169337272644</v>
+        <v>2.87169361114502</v>
       </c>
       <c r="H436" t="n">
         <v>1</v>
@@ -13042,7 +13042,7 @@
         <v>3.47145509719849</v>
       </c>
       <c r="G437" t="n">
-        <v>2.87169337272644</v>
+        <v>2.87169361114502</v>
       </c>
       <c r="H437" t="n">
         <v>1866</v>
@@ -13187,7 +13187,7 @@
         <v>3.43407011032104</v>
       </c>
       <c r="G442" t="n">
-        <v>2.84076738357544</v>
+        <v>2.84076762199402</v>
       </c>
       <c r="H442" t="n">
         <v>1933</v>
@@ -13274,7 +13274,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G445" t="n">
-        <v>2.79806065559387</v>
+        <v>2.79806041717529</v>
       </c>
       <c r="H445" t="n">
         <v>910</v>
@@ -13390,7 +13390,7 @@
         <v>3.33615708351135</v>
       </c>
       <c r="G449" t="n">
-        <v>2.75977110862732</v>
+        <v>2.75977087020874</v>
       </c>
       <c r="H449" t="n">
         <v>863</v>
@@ -13419,7 +13419,7 @@
         <v>3.24714589118958</v>
       </c>
       <c r="G450" t="n">
-        <v>2.68613815307617</v>
+        <v>2.68613791465759</v>
       </c>
       <c r="H450" t="n">
         <v>4906</v>
@@ -13477,7 +13477,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G452" t="n">
-        <v>2.79806065559387</v>
+        <v>2.79806041717529</v>
       </c>
       <c r="H452" t="n">
         <v>2274</v>
@@ -13506,7 +13506,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G453" t="n">
-        <v>2.79806065559387</v>
+        <v>2.79806041717529</v>
       </c>
       <c r="H453" t="n">
         <v>712</v>
@@ -13622,7 +13622,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G457" t="n">
-        <v>2.79806065559387</v>
+        <v>2.79806041717529</v>
       </c>
       <c r="H457" t="n">
         <v>1958</v>
@@ -13651,7 +13651,7 @@
         <v>3.38244390487671</v>
       </c>
       <c r="G458" t="n">
-        <v>2.79806065559387</v>
+        <v>2.79806041717529</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G459" t="n">
-        <v>2.73915362358093</v>
+        <v>2.73915386199951</v>
       </c>
       <c r="H459" t="n">
         <v>2136</v>
@@ -13709,7 +13709,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G460" t="n">
-        <v>2.73915362358093</v>
+        <v>2.73915386199951</v>
       </c>
       <c r="H460" t="n">
         <v>1123</v>
@@ -13738,7 +13738,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G461" t="n">
-        <v>2.73915362358093</v>
+        <v>2.73915386199951</v>
       </c>
       <c r="H461" t="n">
         <v>40</v>
@@ -13767,7 +13767,7 @@
         <v>3.24714589118958</v>
       </c>
       <c r="G462" t="n">
-        <v>2.68613815307617</v>
+        <v>2.68613791465759</v>
       </c>
       <c r="H462" t="n">
         <v>280</v>
@@ -13796,7 +13796,7 @@
         <v>3.24536609649658</v>
       </c>
       <c r="G463" t="n">
-        <v>2.68466567993164</v>
+        <v>2.68466591835022</v>
       </c>
       <c r="H463" t="n">
         <v>4256</v>
@@ -13825,7 +13825,7 @@
         <v>3.08158397674561</v>
       </c>
       <c r="G464" t="n">
-        <v>2.54918026924133</v>
+        <v>2.54918050765991</v>
       </c>
       <c r="H464" t="n">
         <v>5308</v>
@@ -13854,7 +13854,7 @@
         <v>3.31123399734497</v>
       </c>
       <c r="G465" t="n">
-        <v>2.73915362358093</v>
+        <v>2.73915386199951</v>
       </c>
       <c r="H465" t="n">
         <v>5647</v>
@@ -13883,7 +13883,7 @@
         <v>3.20798110961914</v>
       </c>
       <c r="G466" t="n">
-        <v>2.65373992919922</v>
+        <v>2.65373969078064</v>
       </c>
       <c r="H466" t="n">
         <v>3873</v>
@@ -13970,7 +13970,7 @@
         <v>3.20798110961914</v>
       </c>
       <c r="G469" t="n">
-        <v>2.65373992919922</v>
+        <v>2.65373969078064</v>
       </c>
       <c r="H469" t="n">
         <v>19</v>
@@ -13999,7 +13999,7 @@
         <v>3.18483805656433</v>
       </c>
       <c r="G470" t="n">
-        <v>2.63459515571594</v>
+        <v>2.63459491729736</v>
       </c>
       <c r="H470" t="n">
         <v>1182</v>
@@ -14028,7 +14028,7 @@
         <v>3.22222304344177</v>
       </c>
       <c r="G471" t="n">
-        <v>2.66552114486694</v>
+        <v>2.66552138328552</v>
       </c>
       <c r="H471" t="n">
         <v>990</v>
@@ -14057,7 +14057,7 @@
         <v>3.19373893737793</v>
       </c>
       <c r="G472" t="n">
-        <v>2.64195847511292</v>
+        <v>2.64195823669434</v>
       </c>
       <c r="H472" t="n">
         <v>2530</v>
@@ -14086,7 +14086,7 @@
         <v>3.29343199729919</v>
       </c>
       <c r="G473" t="n">
-        <v>2.72442722320557</v>
+        <v>2.72442746162415</v>
       </c>
       <c r="H473" t="n">
         <v>5172</v>
@@ -14115,7 +14115,7 @@
         <v>3.24002504348755</v>
       </c>
       <c r="G474" t="n">
-        <v>2.68024778366089</v>
+        <v>2.68024754524231</v>
       </c>
       <c r="H474" t="n">
         <v>2632</v>
@@ -14202,7 +14202,7 @@
         <v>3.18483805656433</v>
       </c>
       <c r="G477" t="n">
-        <v>2.63459515571594</v>
+        <v>2.63459491729736</v>
       </c>
       <c r="H477" t="n">
         <v>839</v>
@@ -14289,7 +14289,7 @@
         <v>3.074462890625</v>
       </c>
       <c r="G480" t="n">
-        <v>2.54328966140747</v>
+        <v>2.54328942298889</v>
       </c>
       <c r="H480" t="n">
         <v>577</v>
@@ -14347,7 +14347,7 @@
         <v>3.04419898986816</v>
       </c>
       <c r="G482" t="n">
-        <v>2.51825428009033</v>
+        <v>2.51825404167175</v>
       </c>
       <c r="H482" t="n">
         <v>589</v>
@@ -14463,7 +14463,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H486" t="n">
         <v>84</v>
@@ -14492,7 +14492,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H487" t="n">
         <v>246</v>
@@ -14521,7 +14521,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G488" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H488" t="n">
         <v>786</v>
@@ -14695,7 +14695,7 @@
         <v>2.94094610214233</v>
       </c>
       <c r="G494" t="n">
-        <v>2.43284010887146</v>
+        <v>2.43284034729004</v>
       </c>
       <c r="H494" t="n">
         <v>73</v>
@@ -14724,7 +14724,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G495" t="n">
-        <v>2.35920643806458</v>
+        <v>2.35920667648315</v>
       </c>
       <c r="H495" t="n">
         <v>466</v>
@@ -14753,7 +14753,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G496" t="n">
-        <v>2.35920643806458</v>
+        <v>2.35920667648315</v>
       </c>
       <c r="H496" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G497" t="n">
-        <v>2.35920643806458</v>
+        <v>2.35920667648315</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>2.98011088371277</v>
       </c>
       <c r="G503" t="n">
-        <v>2.46523857116699</v>
+        <v>2.46523880958557</v>
       </c>
       <c r="H503" t="n">
         <v>1171</v>
@@ -14985,7 +14985,7 @@
         <v>2.98011088371277</v>
       </c>
       <c r="G504" t="n">
-        <v>2.46523857116699</v>
+        <v>2.46523880958557</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H506" t="n">
         <v>1522</v>
@@ -15072,7 +15072,7 @@
         <v>2.86617588996887</v>
       </c>
       <c r="G507" t="n">
-        <v>2.37098789215088</v>
+        <v>2.37098836898804</v>
       </c>
       <c r="H507" t="n">
         <v>1021</v>
@@ -15101,7 +15101,7 @@
         <v>2.85905504226685</v>
       </c>
       <c r="G508" t="n">
-        <v>2.36509728431702</v>
+        <v>2.3650975227356</v>
       </c>
       <c r="H508" t="n">
         <v>561</v>
@@ -15159,7 +15159,7 @@
         <v>2.71307611465454</v>
       </c>
       <c r="G510" t="n">
-        <v>2.24433922767639</v>
+        <v>2.24433898925781</v>
       </c>
       <c r="H510" t="n">
         <v>11079</v>
@@ -15188,7 +15188,7 @@
         <v>3.25</v>
       </c>
       <c r="G511" t="n">
-        <v>2.68849897384644</v>
+        <v>2.68849921226501</v>
       </c>
       <c r="H511" t="n">
         <v>28967</v>
@@ -15217,7 +15217,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G512" t="n">
-        <v>3.06075310707092</v>
+        <v>3.06075263023376</v>
       </c>
       <c r="H512" t="n">
         <v>27810</v>
@@ -15246,7 +15246,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G513" t="n">
-        <v>2.85394501686096</v>
+        <v>2.85394525527954</v>
       </c>
       <c r="H513" t="n">
         <v>64973</v>
@@ -15275,7 +15275,7 @@
         <v>3.33750009536743</v>
       </c>
       <c r="G514" t="n">
-        <v>2.76088190078735</v>
+        <v>2.76088166236877</v>
       </c>
       <c r="H514" t="n">
         <v>17816</v>
@@ -15333,7 +15333,7 @@
         <v>3.25</v>
       </c>
       <c r="G516" t="n">
-        <v>2.68849897384644</v>
+        <v>2.68849921226501</v>
       </c>
       <c r="H516" t="n">
         <v>10298</v>
@@ -15420,7 +15420,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G519" t="n">
-        <v>2.50237274169922</v>
+        <v>2.50237226486206</v>
       </c>
       <c r="H519" t="n">
         <v>83407</v>
@@ -15449,7 +15449,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G520" t="n">
-        <v>2.46101069450378</v>
+        <v>2.46101093292236</v>
       </c>
       <c r="H520" t="n">
         <v>15414</v>
@@ -15536,7 +15536,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.29556465148926</v>
+        <v>2.29556488990784</v>
       </c>
       <c r="H523" t="n">
         <v>6084</v>
@@ -15565,7 +15565,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.19216108322144</v>
+        <v>2.19216084480286</v>
       </c>
       <c r="H524" t="n">
         <v>25151</v>
@@ -15623,7 +15623,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G526" t="n">
-        <v>2.04739546775818</v>
+        <v>2.0473952293396</v>
       </c>
       <c r="H526" t="n">
         <v>20378</v>
@@ -15652,7 +15652,7 @@
         <v>2.5625</v>
       </c>
       <c r="G527" t="n">
-        <v>2.11977791786194</v>
+        <v>2.11977815628052</v>
       </c>
       <c r="H527" t="n">
         <v>17500</v>
@@ -15681,7 +15681,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G528" t="n">
-        <v>2.04325914382935</v>
+        <v>2.04325938224792</v>
       </c>
       <c r="H528" t="n">
         <v>172096</v>
@@ -15710,7 +15710,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G529" t="n">
-        <v>2.0060338973999</v>
+        <v>2.00603413581848</v>
       </c>
       <c r="H529" t="n">
         <v>37032</v>
@@ -15739,7 +15739,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.96053624153137</v>
+        <v>1.96053600311279</v>
       </c>
       <c r="H530" t="n">
         <v>29220</v>
@@ -15768,7 +15768,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G531" t="n">
-        <v>1.86540496349335</v>
+        <v>1.86540508270264</v>
       </c>
       <c r="H531" t="n">
         <v>103365</v>
@@ -15797,7 +15797,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>1.82817947864532</v>
+        <v>1.82817935943604</v>
       </c>
       <c r="H532" t="n">
         <v>42692</v>
@@ -15826,7 +15826,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G533" t="n">
-        <v>1.84886014461517</v>
+        <v>1.84886002540588</v>
       </c>
       <c r="H533" t="n">
         <v>31186</v>
@@ -15855,7 +15855,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84058797359467</v>
+        <v>1.84058773517609</v>
       </c>
       <c r="H534" t="n">
         <v>86811</v>
@@ -15913,7 +15913,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G536" t="n">
-        <v>1.81990694999695</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H536" t="n">
         <v>22954</v>
@@ -15942,7 +15942,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G537" t="n">
-        <v>1.74545633792877</v>
+        <v>1.74545621871948</v>
       </c>
       <c r="H537" t="n">
         <v>25482</v>
@@ -15971,7 +15971,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>1.77854549884796</v>
+        <v>1.77854561805725</v>
       </c>
       <c r="H538" t="n">
         <v>14766</v>
@@ -16000,7 +16000,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G539" t="n">
-        <v>1.74959254264832</v>
+        <v>1.7495926618576</v>
       </c>
       <c r="H539" t="n">
         <v>9531</v>
@@ -16029,7 +16029,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>1.72063934803009</v>
+        <v>1.72063946723938</v>
       </c>
       <c r="H540" t="n">
         <v>15673</v>
@@ -16087,7 +16087,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G542" t="n">
-        <v>1.67514181137085</v>
+        <v>1.67514193058014</v>
       </c>
       <c r="H542" t="n">
         <v>46153</v>
@@ -16145,7 +16145,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G544" t="n">
-        <v>1.67514181137085</v>
+        <v>1.67514193058014</v>
       </c>
       <c r="H544" t="n">
         <v>25851</v>
@@ -16203,7 +16203,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G546" t="n">
-        <v>1.81990694999695</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H546" t="n">
         <v>72365</v>
@@ -16232,7 +16232,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G547" t="n">
-        <v>1.77440929412842</v>
+        <v>1.774409532547</v>
       </c>
       <c r="H547" t="n">
         <v>15793</v>
@@ -16261,7 +16261,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G548" t="n">
-        <v>1.74545633792877</v>
+        <v>1.74545621871948</v>
       </c>
       <c r="H548" t="n">
         <v>10957</v>
@@ -16290,7 +16290,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G549" t="n">
-        <v>1.73718392848969</v>
+        <v>1.73718404769897</v>
       </c>
       <c r="H549" t="n">
         <v>6788</v>
@@ -16348,7 +16348,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G551" t="n">
-        <v>1.77440929412842</v>
+        <v>1.774409532547</v>
       </c>
       <c r="H551" t="n">
         <v>14085</v>
@@ -16377,7 +16377,7 @@
         <v>2.125</v>
       </c>
       <c r="G552" t="n">
-        <v>1.75786483287811</v>
+        <v>1.75786471366882</v>
       </c>
       <c r="H552" t="n">
         <v>4581</v>
@@ -16493,7 +16493,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>1.77440929412842</v>
+        <v>1.774409532547</v>
       </c>
       <c r="H556" t="n">
         <v>3545</v>
@@ -16522,7 +16522,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>1.77854549884796</v>
+        <v>1.77854561805725</v>
       </c>
       <c r="H557" t="n">
         <v>10553</v>
@@ -16551,7 +16551,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>1.77854549884796</v>
+        <v>1.77854561805725</v>
       </c>
       <c r="H558" t="n">
         <v>4069</v>
@@ -16609,7 +16609,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G560" t="n">
-        <v>1.79509043693542</v>
+        <v>1.79509019851685</v>
       </c>
       <c r="H560" t="n">
         <v>2240</v>
@@ -16638,7 +16638,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G561" t="n">
-        <v>1.81990694999695</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H561" t="n">
         <v>17464</v>
@@ -16696,7 +16696,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G563" t="n">
-        <v>1.75372874736786</v>
+        <v>1.75372850894928</v>
       </c>
       <c r="H563" t="n">
         <v>4008</v>
@@ -16754,7 +16754,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G565" t="n">
-        <v>1.77440929412842</v>
+        <v>1.774409532547</v>
       </c>
       <c r="H565" t="n">
         <v>4955</v>
@@ -16783,7 +16783,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G566" t="n">
-        <v>1.73718392848969</v>
+        <v>1.73718404769897</v>
       </c>
       <c r="H566" t="n">
         <v>1701</v>
@@ -16812,7 +16812,7 @@
         <v>2.125</v>
       </c>
       <c r="G567" t="n">
-        <v>1.75786483287811</v>
+        <v>1.75786471366882</v>
       </c>
       <c r="H567" t="n">
         <v>9117</v>
@@ -16841,7 +16841,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G568" t="n">
-        <v>1.74545633792877</v>
+        <v>1.74545621871948</v>
       </c>
       <c r="H568" t="n">
         <v>10094</v>
@@ -16870,7 +16870,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>1.72477555274963</v>
+        <v>1.72477579116821</v>
       </c>
       <c r="H569" t="n">
         <v>2737</v>
@@ -16899,7 +16899,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>1.72477555274963</v>
+        <v>1.72477579116821</v>
       </c>
       <c r="H570" t="n">
         <v>11694</v>
@@ -16928,7 +16928,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G571" t="n">
-        <v>1.79509043693542</v>
+        <v>1.79509019851685</v>
       </c>
       <c r="H571" t="n">
         <v>4292</v>
@@ -16957,7 +16957,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G572" t="n">
-        <v>1.74545633792877</v>
+        <v>1.74545621871948</v>
       </c>
       <c r="H572" t="n">
         <v>2283</v>
@@ -17015,7 +17015,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G574" t="n">
-        <v>1.77440929412842</v>
+        <v>1.774409532547</v>
       </c>
       <c r="H574" t="n">
         <v>3299</v>
@@ -17073,7 +17073,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G576" t="n">
-        <v>1.77854549884796</v>
+        <v>1.77854561805725</v>
       </c>
       <c r="H576" t="n">
         <v>6528</v>
@@ -17102,7 +17102,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>1.89435756206512</v>
+        <v>1.8943578004837</v>
       </c>
       <c r="H577" t="n">
         <v>252675</v>
@@ -17131,7 +17131,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G578" t="n">
-        <v>1.84886014461517</v>
+        <v>1.84886002540588</v>
       </c>
       <c r="H578" t="n">
         <v>35013</v>
@@ -17160,7 +17160,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G579" t="n">
-        <v>1.91917455196381</v>
+        <v>1.91917479038239</v>
       </c>
       <c r="H579" t="n">
         <v>121147</v>
@@ -17189,7 +17189,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G580" t="n">
-        <v>1.89022195339203</v>
+        <v>1.89022183418274</v>
       </c>
       <c r="H580" t="n">
         <v>60138</v>
@@ -17218,7 +17218,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G581" t="n">
-        <v>2.00189781188965</v>
+        <v>2.00189805030823</v>
       </c>
       <c r="H581" t="n">
         <v>169721</v>
@@ -17247,7 +17247,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G582" t="n">
-        <v>2.0060338973999</v>
+        <v>2.00603413581848</v>
       </c>
       <c r="H582" t="n">
         <v>168479</v>
@@ -17276,7 +17276,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>1.93158328533173</v>
+        <v>1.93158340454102</v>
       </c>
       <c r="H583" t="n">
         <v>72085</v>
@@ -17305,7 +17305,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G584" t="n">
-        <v>1.98948955535889</v>
+        <v>1.98948931694031</v>
       </c>
       <c r="H584" t="n">
         <v>98188</v>
@@ -17334,7 +17334,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>1.99362552165985</v>
+        <v>1.99362576007843</v>
       </c>
       <c r="H585" t="n">
         <v>32719</v>
@@ -17363,7 +17363,7 @@
         <v>2.73749995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.2645435333252</v>
+        <v>2.26454329490662</v>
       </c>
       <c r="H586" t="n">
         <v>241077</v>
@@ -17392,7 +17392,7 @@
         <v>2.53749990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>2.09909749031067</v>
+        <v>2.09909725189209</v>
       </c>
       <c r="H587" t="n">
         <v>383922</v>
@@ -17421,7 +17421,7 @@
         <v>2.5</v>
       </c>
       <c r="G588" t="n">
-        <v>2.06807613372803</v>
+        <v>2.06807637214661</v>
       </c>
       <c r="H588" t="n">
         <v>93249</v>
@@ -17711,7 +17711,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>2.19216108322144</v>
+        <v>2.19216084480286</v>
       </c>
       <c r="H598" t="n">
         <v>52517</v>
@@ -17769,7 +17769,7 @@
         <v>2.71250009536743</v>
       </c>
       <c r="G600" t="n">
-        <v>2.24386239051819</v>
+        <v>2.24386286735535</v>
       </c>
       <c r="H600" t="n">
         <v>116767</v>
@@ -17827,7 +17827,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>2.19216108322144</v>
+        <v>2.19216084480286</v>
       </c>
       <c r="H602" t="n">
         <v>23329</v>
@@ -17914,7 +17914,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G605" t="n">
-        <v>2.08875679969788</v>
+        <v>2.08875703811646</v>
       </c>
       <c r="H605" t="n">
         <v>41989</v>
@@ -17943,7 +17943,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G606" t="n">
-        <v>2.10943794250488</v>
+        <v>2.1094377040863</v>
       </c>
       <c r="H606" t="n">
         <v>57475</v>
@@ -17972,7 +17972,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G607" t="n">
-        <v>2.03498697280884</v>
+        <v>2.03498673439026</v>
       </c>
       <c r="H607" t="n">
         <v>10511</v>
@@ -18030,7 +18030,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>2.00189781188965</v>
+        <v>2.00189805030823</v>
       </c>
       <c r="H609" t="n">
         <v>12738</v>
@@ -18059,7 +18059,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G610" t="n">
-        <v>2.03912305831909</v>
+        <v>2.03912329673767</v>
       </c>
       <c r="H610" t="n">
         <v>47299</v>
@@ -18088,7 +18088,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G611" t="n">
-        <v>2.0060338973999</v>
+        <v>2.00603413581848</v>
       </c>
       <c r="H611" t="n">
         <v>9883</v>
@@ -18117,7 +18117,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>1.92744708061218</v>
+        <v>1.92744696140289</v>
       </c>
       <c r="H612" t="n">
         <v>8870</v>
@@ -18146,7 +18146,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G613" t="n">
-        <v>1.89435756206512</v>
+        <v>1.8943578004837</v>
       </c>
       <c r="H613" t="n">
         <v>19551</v>
@@ -18175,7 +18175,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G614" t="n">
-        <v>1.86540496349335</v>
+        <v>1.86540508270264</v>
       </c>
       <c r="H614" t="n">
         <v>24381</v>
@@ -18204,7 +18204,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>1.84472405910492</v>
+        <v>1.84472393989563</v>
       </c>
       <c r="H615" t="n">
         <v>28679</v>
@@ -18233,7 +18233,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G616" t="n">
-        <v>1.91917455196381</v>
+        <v>1.91917479038239</v>
       </c>
       <c r="H616" t="n">
         <v>15467</v>
@@ -18262,7 +18262,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G617" t="n">
-        <v>2.00189781188965</v>
+        <v>2.00189805030823</v>
       </c>
       <c r="H617" t="n">
         <v>21737</v>
@@ -18320,7 +18320,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G619" t="n">
-        <v>1.89022195339203</v>
+        <v>1.89022183418274</v>
       </c>
       <c r="H619" t="n">
         <v>600</v>
@@ -18349,7 +18349,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G620" t="n">
-        <v>1.98121690750122</v>
+        <v>1.98121726512909</v>
       </c>
       <c r="H620" t="n">
         <v>4625</v>
@@ -18407,7 +18407,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G622" t="n">
-        <v>1.86540496349335</v>
+        <v>1.86540508270264</v>
       </c>
       <c r="H622" t="n">
         <v>19869</v>
@@ -18436,7 +18436,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>1.93158328533173</v>
+        <v>1.93158340454102</v>
       </c>
       <c r="H623" t="n">
         <v>16422</v>
@@ -18465,7 +18465,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G624" t="n">
-        <v>1.91917455196381</v>
+        <v>1.91917479038239</v>
       </c>
       <c r="H624" t="n">
         <v>3752</v>
@@ -18523,7 +18523,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G626" t="n">
-        <v>1.92331111431122</v>
+        <v>1.92331099510193</v>
       </c>
       <c r="H626" t="n">
         <v>11025</v>
@@ -18581,7 +18581,7 @@
         <v>2.25</v>
       </c>
       <c r="G628" t="n">
-        <v>1.86126863956451</v>
+        <v>1.8612687587738</v>
       </c>
       <c r="H628" t="n">
         <v>1406</v>
@@ -18610,7 +18610,7 @@
         <v>2.25</v>
       </c>
       <c r="G629" t="n">
-        <v>1.86126863956451</v>
+        <v>1.8612687587738</v>
       </c>
       <c r="H629" t="n">
         <v>1064</v>
@@ -18668,7 +18668,7 @@
         <v>2.25</v>
       </c>
       <c r="G631" t="n">
-        <v>1.86126863956451</v>
+        <v>1.8612687587738</v>
       </c>
       <c r="H631" t="n">
         <v>760</v>
@@ -18726,7 +18726,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>1.89435756206512</v>
+        <v>1.8943578004837</v>
       </c>
       <c r="H633" t="n">
         <v>1081</v>
@@ -18871,7 +18871,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G638" t="n">
-        <v>1.84886014461517</v>
+        <v>1.84886002540588</v>
       </c>
       <c r="H638" t="n">
         <v>7040</v>
@@ -18900,7 +18900,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G639" t="n">
-        <v>1.85299634933472</v>
+        <v>1.85299646854401</v>
       </c>
       <c r="H639" t="n">
         <v>21490</v>
@@ -18987,7 +18987,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G642" t="n">
-        <v>1.81163477897644</v>
+        <v>1.81163489818573</v>
       </c>
       <c r="H642" t="n">
         <v>11225</v>
@@ -19045,7 +19045,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G644" t="n">
-        <v>1.81163477897644</v>
+        <v>1.81163489818573</v>
       </c>
       <c r="H644" t="n">
         <v>10559</v>
@@ -19103,7 +19103,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>1.77440929412842</v>
+        <v>1.774409532547</v>
       </c>
       <c r="H646" t="n">
         <v>13135</v>
@@ -19132,7 +19132,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G647" t="n">
-        <v>1.80749833583832</v>
+        <v>1.80749845504761</v>
       </c>
       <c r="H647" t="n">
         <v>10121</v>
@@ -19161,7 +19161,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G648" t="n">
-        <v>1.73718392848969</v>
+        <v>1.73718404769897</v>
       </c>
       <c r="H648" t="n">
         <v>16400</v>
@@ -19190,7 +19190,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.75372874736786</v>
+        <v>1.75372850894928</v>
       </c>
       <c r="H649" t="n">
         <v>426</v>
@@ -19219,7 +19219,7 @@
         <v>2.125</v>
       </c>
       <c r="G650" t="n">
-        <v>1.75786483287811</v>
+        <v>1.75786471366882</v>
       </c>
       <c r="H650" t="n">
         <v>15747</v>
@@ -19277,7 +19277,7 @@
         <v>2.125</v>
       </c>
       <c r="G652" t="n">
-        <v>1.75786483287811</v>
+        <v>1.75786471366882</v>
       </c>
       <c r="H652" t="n">
         <v>6777</v>
@@ -19306,7 +19306,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>1.79509043693542</v>
+        <v>1.79509019851685</v>
       </c>
       <c r="H653" t="n">
         <v>586</v>
@@ -19335,7 +19335,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>1.81990694999695</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H654" t="n">
         <v>16533</v>
@@ -19393,7 +19393,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G656" t="n">
-        <v>1.80998027324677</v>
+        <v>1.80998039245605</v>
       </c>
       <c r="H656" t="n">
         <v>3706</v>
@@ -19422,7 +19422,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G657" t="n">
-        <v>1.85134184360504</v>
+        <v>1.85134172439575</v>
       </c>
       <c r="H657" t="n">
         <v>9372</v>
@@ -19451,7 +19451,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G658" t="n">
-        <v>1.85299634933472</v>
+        <v>1.85299646854401</v>
       </c>
       <c r="H658" t="n">
         <v>3089</v>
@@ -19480,7 +19480,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G659" t="n">
-        <v>1.81990694999695</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H659" t="n">
         <v>3423</v>
@@ -19538,7 +19538,7 @@
         <v>2.17549991607666</v>
       </c>
       <c r="G661" t="n">
-        <v>1.79963982105255</v>
+        <v>1.79963994026184</v>
       </c>
       <c r="H661" t="n">
         <v>808</v>
@@ -19625,7 +19625,7 @@
         <v>2.17650008201599</v>
       </c>
       <c r="G664" t="n">
-        <v>1.80046713352203</v>
+        <v>1.80046725273132</v>
       </c>
       <c r="H664" t="n">
         <v>4725</v>
@@ -19683,7 +19683,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G666" t="n">
-        <v>1.83976066112518</v>
+        <v>1.83976054191589</v>
       </c>
       <c r="H666" t="n">
         <v>28805</v>
@@ -19799,7 +19799,7 @@
         <v>2.18700003623962</v>
       </c>
       <c r="G670" t="n">
-        <v>1.80915319919586</v>
+        <v>1.80915307998657</v>
       </c>
       <c r="H670" t="n">
         <v>1019</v>
@@ -19828,7 +19828,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G671" t="n">
-        <v>1.77192783355713</v>
+        <v>1.77192759513855</v>
       </c>
       <c r="H671" t="n">
         <v>4215</v>
@@ -19857,7 +19857,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G672" t="n">
-        <v>1.75372874736786</v>
+        <v>1.75372850894928</v>
       </c>
       <c r="H672" t="n">
         <v>1260</v>
@@ -19886,7 +19886,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G673" t="n">
-        <v>1.76200115680695</v>
+        <v>1.76200127601624</v>
       </c>
       <c r="H673" t="n">
         <v>1302</v>
@@ -19973,7 +19973,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G676" t="n">
-        <v>1.68920469284058</v>
+        <v>1.68920481204987</v>
       </c>
       <c r="H676" t="n">
         <v>12451</v>
@@ -20031,7 +20031,7 @@
         <v>1.82879996299744</v>
       </c>
       <c r="G678" t="n">
-        <v>1.5128390789032</v>
+        <v>1.51283919811249</v>
       </c>
       <c r="H678" t="n">
         <v>26154</v>
@@ -20060,7 +20060,7 @@
         <v>1.75479996204376</v>
       </c>
       <c r="G679" t="n">
-        <v>1.45162415504456</v>
+        <v>1.45162403583527</v>
       </c>
       <c r="H679" t="n">
         <v>77393</v>
@@ -20205,7 +20205,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G684" t="n">
-        <v>1.47329747676849</v>
+        <v>1.47329759597778</v>
       </c>
       <c r="H684" t="n">
         <v>524</v>
@@ -20263,7 +20263,7 @@
         <v>1.72140002250671</v>
       </c>
       <c r="G686" t="n">
-        <v>1.42399477958679</v>
+        <v>1.4239946603775</v>
       </c>
       <c r="H686" t="n">
         <v>1520</v>
@@ -20292,7 +20292,7 @@
         <v>1.75059998035431</v>
       </c>
       <c r="G687" t="n">
-        <v>1.44814968109131</v>
+        <v>1.4481498003006</v>
       </c>
       <c r="H687" t="n">
         <v>4065</v>
@@ -20321,7 +20321,7 @@
         <v>1.74440002441406</v>
       </c>
       <c r="G688" t="n">
-        <v>1.44302093982697</v>
+        <v>1.44302082061768</v>
       </c>
       <c r="H688" t="n">
         <v>2706</v>
@@ -20350,7 +20350,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>1.47247016429901</v>
+        <v>1.47247040271759</v>
       </c>
       <c r="H689" t="n">
         <v>525</v>
@@ -20379,7 +20379,7 @@
         <v>1.76979994773865</v>
       </c>
       <c r="G690" t="n">
-        <v>1.46403253078461</v>
+        <v>1.46403241157532</v>
       </c>
       <c r="H690" t="n">
         <v>3320</v>
@@ -20437,7 +20437,7 @@
         <v>1.71580004692078</v>
       </c>
       <c r="G692" t="n">
-        <v>1.41936206817627</v>
+        <v>1.41936218738556</v>
       </c>
       <c r="H692" t="n">
         <v>2936</v>
@@ -20466,7 +20466,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G693" t="n">
-        <v>1.42283654212952</v>
+        <v>1.42283642292023</v>
       </c>
       <c r="H693" t="n">
         <v>484</v>
@@ -20495,7 +20495,7 @@
         <v>1.7305999994278</v>
       </c>
       <c r="G694" t="n">
-        <v>1.43160510063171</v>
+        <v>1.43160498142242</v>
       </c>
       <c r="H694" t="n">
         <v>5402</v>
@@ -20611,7 +20611,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G698" t="n">
-        <v>1.41952741146088</v>
+        <v>1.41952753067017</v>
       </c>
       <c r="H698" t="n">
         <v>9959</v>
@@ -20669,7 +20669,7 @@
         <v>1.74479997158051</v>
       </c>
       <c r="G700" t="n">
-        <v>1.44335174560547</v>
+        <v>1.44335186481476</v>
       </c>
       <c r="H700" t="n">
         <v>2020</v>
@@ -20727,7 +20727,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G702" t="n">
-        <v>1.43524503707886</v>
+        <v>1.43524479866028</v>
       </c>
       <c r="H702" t="n">
         <v>4220</v>
@@ -20756,7 +20756,7 @@
         <v>1.6793999671936</v>
       </c>
       <c r="G703" t="n">
-        <v>1.38925087451935</v>
+        <v>1.38925099372864</v>
       </c>
       <c r="H703" t="n">
         <v>10191</v>
@@ -20785,7 +20785,7 @@
         <v>1.67960000038147</v>
       </c>
       <c r="G704" t="n">
-        <v>1.38941633701324</v>
+        <v>1.38941645622253</v>
       </c>
       <c r="H704" t="n">
         <v>2454</v>
@@ -20814,7 +20814,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>1.41456413269043</v>
+        <v>1.41456425189972</v>
       </c>
       <c r="H705" t="n">
         <v>2040</v>
@@ -20843,7 +20843,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G706" t="n">
-        <v>1.41952741146088</v>
+        <v>1.41952753067017</v>
       </c>
       <c r="H706" t="n">
         <v>2390</v>
@@ -20872,7 +20872,7 @@
         <v>1.71539998054504</v>
       </c>
       <c r="G707" t="n">
-        <v>1.41903126239777</v>
+        <v>1.41903114318848</v>
       </c>
       <c r="H707" t="n">
         <v>1650</v>
@@ -20901,7 +20901,7 @@
         <v>1.6793999671936</v>
       </c>
       <c r="G708" t="n">
-        <v>1.38925087451935</v>
+        <v>1.38925099372864</v>
       </c>
       <c r="H708" t="n">
         <v>4417</v>
@@ -20930,7 +20930,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G709" t="n">
-        <v>1.37320256233215</v>
+        <v>1.37320268154144</v>
       </c>
       <c r="H709" t="n">
         <v>347</v>
@@ -20988,7 +20988,7 @@
         <v>1.66460001468658</v>
       </c>
       <c r="G711" t="n">
-        <v>1.3770078420639</v>
+        <v>1.37700808048248</v>
       </c>
       <c r="H711" t="n">
         <v>40</v>
@@ -21017,7 +21017,7 @@
         <v>1.72019994258881</v>
       </c>
       <c r="G712" t="n">
-        <v>1.42300188541412</v>
+        <v>1.42300176620483</v>
       </c>
       <c r="H712" t="n">
         <v>4691</v>
@@ -21046,7 +21046,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G713" t="n">
-        <v>1.45592558383942</v>
+        <v>1.45592570304871</v>
       </c>
       <c r="H713" t="n">
         <v>6546</v>
@@ -21075,7 +21075,7 @@
         <v>1.83959996700287</v>
       </c>
       <c r="G714" t="n">
-        <v>1.52177333831787</v>
+        <v>1.52177309989929</v>
       </c>
       <c r="H714" t="n">
         <v>24405</v>
@@ -21104,7 +21104,7 @@
         <v>1.78960001468658</v>
       </c>
       <c r="G715" t="n">
-        <v>1.48041176795959</v>
+        <v>1.48041164875031</v>
       </c>
       <c r="H715" t="n">
         <v>5445</v>
@@ -21191,7 +21191,7 @@
         <v>1.72979998588562</v>
       </c>
       <c r="G718" t="n">
-        <v>1.43094313144684</v>
+        <v>1.43094336986542</v>
       </c>
       <c r="H718" t="n">
         <v>566</v>
@@ -21278,7 +21278,7 @@
         <v>1.81140005588531</v>
       </c>
       <c r="G721" t="n">
-        <v>1.49844539165497</v>
+        <v>1.49844551086426</v>
       </c>
       <c r="H721" t="n">
         <v>7281</v>
@@ -21307,7 +21307,7 @@
         <v>1.81140005588531</v>
       </c>
       <c r="G722" t="n">
-        <v>1.49844539165497</v>
+        <v>1.49844551086426</v>
       </c>
       <c r="H722" t="n">
         <v>0</v>
@@ -21336,7 +21336,7 @@
         <v>1.81140005588531</v>
       </c>
       <c r="G723" t="n">
-        <v>1.49844539165497</v>
+        <v>1.49844551086426</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>1.81120002269745</v>
       </c>
       <c r="G724" t="n">
-        <v>1.49827992916107</v>
+        <v>1.49828004837036</v>
       </c>
       <c r="H724" t="n">
         <v>3000</v>
@@ -21423,7 +21423,7 @@
         <v>1.81980001926422</v>
       </c>
       <c r="G726" t="n">
-        <v>1.50539422035217</v>
+        <v>1.50539398193359</v>
       </c>
       <c r="H726" t="n">
         <v>2000</v>
@@ -21452,7 +21452,7 @@
         <v>1.79120004177094</v>
       </c>
       <c r="G727" t="n">
-        <v>1.48173534870148</v>
+        <v>1.48173522949219</v>
       </c>
       <c r="H727" t="n">
         <v>3810</v>
@@ -21481,7 +21481,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G728" t="n">
-        <v>1.51383185386658</v>
+        <v>1.51383197307587</v>
       </c>
       <c r="H728" t="n">
         <v>1067</v>
@@ -21510,7 +21510,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G729" t="n">
-        <v>1.51796793937683</v>
+        <v>1.51796782016754</v>
       </c>
       <c r="H729" t="n">
         <v>330</v>
@@ -21539,7 +21539,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G730" t="n">
-        <v>1.48653316497803</v>
+        <v>1.48653340339661</v>
       </c>
       <c r="H730" t="n">
         <v>642</v>
@@ -21568,7 +21568,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G731" t="n">
-        <v>1.48653316497803</v>
+        <v>1.48653340339661</v>
       </c>
       <c r="H731" t="n">
         <v>339</v>
@@ -21597,7 +21597,7 @@
         <v>1.83159995079041</v>
       </c>
       <c r="G732" t="n">
-        <v>1.51515543460846</v>
+        <v>1.51515531539917</v>
       </c>
       <c r="H732" t="n">
         <v>19406</v>
@@ -21626,7 +21626,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G733" t="n">
-        <v>1.51383185386658</v>
+        <v>1.51383197307587</v>
       </c>
       <c r="H733" t="n">
         <v>1869</v>
@@ -21655,7 +21655,7 @@
         <v>1.7985999584198</v>
       </c>
       <c r="G734" t="n">
-        <v>1.48785674571991</v>
+        <v>1.4878568649292</v>
       </c>
       <c r="H734" t="n">
         <v>1269</v>
@@ -21771,7 +21771,7 @@
         <v>1.84179997444153</v>
       </c>
       <c r="G738" t="n">
-        <v>1.52359318733215</v>
+        <v>1.52359306812286</v>
       </c>
       <c r="H738" t="n">
         <v>1530</v>
@@ -21800,7 +21800,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G739" t="n">
-        <v>1.488849401474</v>
+        <v>1.48884952068329</v>
       </c>
       <c r="H739" t="n">
         <v>776</v>
@@ -21974,7 +21974,7 @@
         <v>1.78960001468658</v>
       </c>
       <c r="G745" t="n">
-        <v>1.48041176795959</v>
+        <v>1.48041164875031</v>
       </c>
       <c r="H745" t="n">
         <v>219</v>
@@ -22003,7 +22003,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G746" t="n">
-        <v>1.47329747676849</v>
+        <v>1.47329759597778</v>
       </c>
       <c r="H746" t="n">
         <v>2400</v>
@@ -22061,7 +22061,7 @@
         <v>1.78120005130768</v>
       </c>
       <c r="G748" t="n">
-        <v>1.47346293926239</v>
+        <v>1.47346305847168</v>
       </c>
       <c r="H748" t="n">
         <v>198</v>
@@ -22119,7 +22119,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G750" t="n">
-        <v>1.47329747676849</v>
+        <v>1.47329759597778</v>
       </c>
       <c r="H750" t="n">
         <v>470</v>
@@ -22177,7 +22177,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G752" t="n">
-        <v>1.488849401474</v>
+        <v>1.48884952068329</v>
       </c>
       <c r="H752" t="n">
         <v>1260</v>
@@ -22206,7 +22206,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G753" t="n">
-        <v>1.47329747676849</v>
+        <v>1.47329759597778</v>
       </c>
       <c r="H753" t="n">
         <v>225</v>
@@ -22264,7 +22264,7 @@
         <v>1.86979997158051</v>
       </c>
       <c r="G755" t="n">
-        <v>1.54675567150116</v>
+        <v>1.54675555229187</v>
       </c>
       <c r="H755" t="n">
         <v>6445</v>
@@ -22293,7 +22293,7 @@
         <v>1.88940000534058</v>
       </c>
       <c r="G756" t="n">
-        <v>1.56296920776367</v>
+        <v>1.56296944618225</v>
       </c>
       <c r="H756" t="n">
         <v>4631</v>
@@ -22322,7 +22322,7 @@
         <v>1.90240001678467</v>
       </c>
       <c r="G757" t="n">
-        <v>1.64630579948425</v>
+        <v>1.64630568027496</v>
       </c>
       <c r="H757" t="n">
         <v>1697</v>
@@ -22351,7 +22351,7 @@
         <v>1.92260003089905</v>
       </c>
       <c r="G758" t="n">
-        <v>1.66378653049469</v>
+        <v>1.6637864112854</v>
       </c>
       <c r="H758" t="n">
         <v>20</v>
@@ -22380,7 +22380,7 @@
         <v>1.93239998817444</v>
       </c>
       <c r="G759" t="n">
-        <v>1.67226719856262</v>
+        <v>1.67226731777191</v>
       </c>
       <c r="H759" t="n">
         <v>3791</v>
@@ -22409,7 +22409,7 @@
         <v>1.86220002174377</v>
       </c>
       <c r="G760" t="n">
-        <v>1.61151731014252</v>
+        <v>1.61151719093323</v>
       </c>
       <c r="H760" t="n">
         <v>10183</v>
@@ -22496,7 +22496,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>1.67884421348572</v>
+        <v>1.67884433269501</v>
       </c>
       <c r="H763" t="n">
         <v>16054</v>
@@ -22554,7 +22554,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>1.69615197181702</v>
+        <v>1.69615185260773</v>
       </c>
       <c r="H765" t="n">
         <v>124</v>
@@ -22757,7 +22757,7 @@
         <v>1.92980003356934</v>
       </c>
       <c r="G772" t="n">
-        <v>1.67001724243164</v>
+        <v>1.67001736164093</v>
       </c>
       <c r="H772" t="n">
         <v>2856</v>
@@ -22815,7 +22815,7 @@
         <v>1.94980001449585</v>
       </c>
       <c r="G774" t="n">
-        <v>1.68732500076294</v>
+        <v>1.68732488155365</v>
       </c>
       <c r="H774" t="n">
         <v>1771</v>
@@ -22844,7 +22844,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G775" t="n">
-        <v>1.67884421348572</v>
+        <v>1.67884433269501</v>
       </c>
       <c r="H775" t="n">
         <v>3450</v>
@@ -22960,7 +22960,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>1.69615197181702</v>
+        <v>1.69615185260773</v>
       </c>
       <c r="H779" t="n">
         <v>2604</v>
@@ -23192,7 +23192,7 @@
         <v>1.90859997272491</v>
       </c>
       <c r="G787" t="n">
-        <v>1.65167117118835</v>
+        <v>1.65167105197906</v>
       </c>
       <c r="H787" t="n">
         <v>5503</v>
@@ -23337,7 +23337,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G792" t="n">
-        <v>1.67019033432007</v>
+        <v>1.67019021511078</v>
       </c>
       <c r="H792" t="n">
         <v>693</v>
@@ -23366,7 +23366,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G793" t="n">
-        <v>1.67019033432007</v>
+        <v>1.67019021511078</v>
       </c>
       <c r="H793" t="n">
         <v>0</v>
@@ -23424,7 +23424,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G795" t="n">
-        <v>1.65980577468872</v>
+        <v>1.65980565547943</v>
       </c>
       <c r="H795" t="n">
         <v>666</v>
@@ -23453,7 +23453,7 @@
         <v>1.84860002994537</v>
       </c>
       <c r="G796" t="n">
-        <v>1.59974825382233</v>
+        <v>1.59974813461304</v>
       </c>
       <c r="H796" t="n">
         <v>9753</v>
@@ -23482,7 +23482,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G797" t="n">
-        <v>1.5983635187149</v>
+        <v>1.59836339950562</v>
       </c>
       <c r="H797" t="n">
         <v>6802</v>
@@ -23511,7 +23511,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G798" t="n">
-        <v>1.61913275718689</v>
+        <v>1.61913287639618</v>
       </c>
       <c r="H798" t="n">
         <v>570</v>
@@ -23569,7 +23569,7 @@
         <v>1.85739994049072</v>
       </c>
       <c r="G800" t="n">
-        <v>1.60736346244812</v>
+        <v>1.60736334323883</v>
       </c>
       <c r="H800" t="n">
         <v>3716</v>
@@ -23627,7 +23627,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G802" t="n">
-        <v>1.62345957756042</v>
+        <v>1.62345969676971</v>
       </c>
       <c r="H802" t="n">
         <v>4654</v>
@@ -23743,7 +23743,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G806" t="n">
-        <v>1.59230577945709</v>
+        <v>1.59230589866638</v>
       </c>
       <c r="H806" t="n">
         <v>3639</v>
@@ -23888,7 +23888,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G811" t="n">
-        <v>1.57932507991791</v>
+        <v>1.5793251991272</v>
       </c>
       <c r="H811" t="n">
         <v>115</v>
@@ -23917,7 +23917,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G812" t="n">
-        <v>1.60095977783203</v>
+        <v>1.60095965862274</v>
       </c>
       <c r="H812" t="n">
         <v>3785</v>
@@ -23975,7 +23975,7 @@
         <v>1.75220000743866</v>
       </c>
       <c r="G814" t="n">
-        <v>1.51632511615753</v>
+        <v>1.51632523536682</v>
       </c>
       <c r="H814" t="n">
         <v>8175</v>
@@ -24004,7 +24004,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G815" t="n">
-        <v>1.54211342334747</v>
+        <v>1.54211354255676</v>
       </c>
       <c r="H815" t="n">
         <v>7327</v>
@@ -24033,7 +24033,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G816" t="n">
-        <v>1.50144052505493</v>
+        <v>1.50144040584564</v>
       </c>
       <c r="H816" t="n">
         <v>282</v>
@@ -24062,7 +24062,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G817" t="n">
-        <v>1.50144052505493</v>
+        <v>1.50144040584564</v>
       </c>
       <c r="H817" t="n">
         <v>4851</v>
@@ -24120,7 +24120,7 @@
         <v>1.76960003376007</v>
       </c>
       <c r="G819" t="n">
-        <v>1.53138279914856</v>
+        <v>1.53138291835785</v>
       </c>
       <c r="H819" t="n">
         <v>2845</v>
@@ -24236,7 +24236,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G823" t="n">
-        <v>1.46249830722809</v>
+        <v>1.4624981880188</v>
       </c>
       <c r="H823" t="n">
         <v>7377</v>
@@ -24265,7 +24265,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G824" t="n">
-        <v>1.46249830722809</v>
+        <v>1.4624981880188</v>
       </c>
       <c r="H824" t="n">
         <v>3058</v>
@@ -24410,7 +24410,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G829" t="n">
-        <v>1.47115206718445</v>
+        <v>1.47115218639374</v>
       </c>
       <c r="H829" t="n">
         <v>107</v>
@@ -24439,7 +24439,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G830" t="n">
-        <v>1.50144052505493</v>
+        <v>1.50144040584564</v>
       </c>
       <c r="H830" t="n">
         <v>4506</v>
@@ -24468,7 +24468,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G831" t="n">
-        <v>1.48845982551575</v>
+        <v>1.48845970630646</v>
       </c>
       <c r="H831" t="n">
         <v>1011</v>
@@ -24555,7 +24555,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G834" t="n">
-        <v>1.47115206718445</v>
+        <v>1.47115218639374</v>
       </c>
       <c r="H834" t="n">
         <v>1294</v>
@@ -24584,7 +24584,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>1.47115206718445</v>
+        <v>1.47115218639374</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -24671,7 +24671,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G838" t="n">
-        <v>1.55336344242096</v>
+        <v>1.55336356163025</v>
       </c>
       <c r="H838" t="n">
         <v>19702</v>
@@ -24845,7 +24845,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G844" t="n">
-        <v>1.47115206718445</v>
+        <v>1.47115218639374</v>
       </c>
       <c r="H844" t="n">
         <v>12319</v>
@@ -24874,7 +24874,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G845" t="n">
-        <v>1.47115206718445</v>
+        <v>1.47115218639374</v>
       </c>
       <c r="H845" t="n">
         <v>1152</v>
@@ -25019,7 +25019,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G850" t="n">
-        <v>1.47115206718445</v>
+        <v>1.47115218639374</v>
       </c>
       <c r="H850" t="n">
         <v>1560</v>
@@ -25164,7 +25164,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G855" t="n">
-        <v>1.4322098493576</v>
+        <v>1.43220996856689</v>
       </c>
       <c r="H855" t="n">
         <v>1512</v>
@@ -25309,7 +25309,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G860" t="n">
-        <v>1.42788290977478</v>
+        <v>1.42788302898407</v>
       </c>
       <c r="H860" t="n">
         <v>4086</v>
@@ -25338,7 +25338,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G861" t="n">
-        <v>1.4322098493576</v>
+        <v>1.43220996856689</v>
       </c>
       <c r="H861" t="n">
         <v>3911</v>
@@ -25396,7 +25396,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G863" t="n">
-        <v>1.4322098493576</v>
+        <v>1.43220996856689</v>
       </c>
       <c r="H863" t="n">
         <v>1152</v>
@@ -25425,7 +25425,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G864" t="n">
-        <v>1.42788290977478</v>
+        <v>1.42788302898407</v>
       </c>
       <c r="H864" t="n">
         <v>8157</v>
@@ -25454,7 +25454,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G865" t="n">
-        <v>1.41922914981842</v>
+        <v>1.41922903060913</v>
       </c>
       <c r="H865" t="n">
         <v>7928</v>
@@ -25483,7 +25483,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G866" t="n">
-        <v>1.41922914981842</v>
+        <v>1.41922903060913</v>
       </c>
       <c r="H866" t="n">
         <v>1621</v>
@@ -25686,7 +25686,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G873" t="n">
-        <v>1.41922914981842</v>
+        <v>1.41922903060913</v>
       </c>
       <c r="H873" t="n">
         <v>3139</v>
@@ -25715,7 +25715,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G874" t="n">
-        <v>1.4149022102356</v>
+        <v>1.41490209102631</v>
       </c>
       <c r="H874" t="n">
         <v>614</v>
@@ -25802,7 +25802,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G877" t="n">
-        <v>1.38461375236511</v>
+        <v>1.3846138715744</v>
       </c>
       <c r="H877" t="n">
         <v>3726</v>
@@ -25831,7 +25831,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G878" t="n">
-        <v>1.38028681278229</v>
+        <v>1.38028693199158</v>
       </c>
       <c r="H878" t="n">
         <v>7486</v>
@@ -25860,7 +25860,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G879" t="n">
-        <v>1.38028681278229</v>
+        <v>1.38028693199158</v>
       </c>
       <c r="H879" t="n">
         <v>2002</v>
@@ -25889,7 +25889,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G880" t="n">
-        <v>1.37595999240875</v>
+        <v>1.37595987319946</v>
       </c>
       <c r="H880" t="n">
         <v>915</v>
@@ -25918,7 +25918,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G881" t="n">
-        <v>1.37595999240875</v>
+        <v>1.37595987319946</v>
       </c>
       <c r="H881" t="n">
         <v>5522</v>
@@ -25976,7 +25976,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G883" t="n">
-        <v>1.38461375236511</v>
+        <v>1.3846138715744</v>
       </c>
       <c r="H883" t="n">
         <v>4134</v>
@@ -26005,7 +26005,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G884" t="n">
-        <v>1.38461375236511</v>
+        <v>1.3846138715744</v>
       </c>
       <c r="H884" t="n">
         <v>1525</v>
@@ -26034,7 +26034,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G885" t="n">
-        <v>1.37595999240875</v>
+        <v>1.37595987319946</v>
       </c>
       <c r="H885" t="n">
         <v>5234</v>
@@ -26063,7 +26063,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G886" t="n">
-        <v>1.38461375236511</v>
+        <v>1.3846138715744</v>
       </c>
       <c r="H886" t="n">
         <v>1608</v>
@@ -26121,7 +26121,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G888" t="n">
-        <v>1.33701753616333</v>
+        <v>1.33701765537262</v>
       </c>
       <c r="H888" t="n">
         <v>7055</v>
@@ -26237,7 +26237,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31105601787567</v>
+        <v>1.31105613708496</v>
       </c>
       <c r="H892" t="n">
         <v>200</v>
@@ -80067,6 +80067,35 @@
         <v>35812</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>160438</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.35138177871704</v>
       </c>
       <c r="G2" t="n">
-        <v>4.42682600021362</v>
+        <v>4.42682695388794</v>
       </c>
       <c r="H2" t="n">
         <v>748</v>
@@ -456,7 +456,7 @@
         <v>5.35138177871704</v>
       </c>
       <c r="G3" t="n">
-        <v>4.42682600021362</v>
+        <v>4.42682695388794</v>
       </c>
       <c r="H3" t="n">
         <v>253</v>
@@ -485,7 +485,7 @@
         <v>5.35138177871704</v>
       </c>
       <c r="G4" t="n">
-        <v>4.42682600021362</v>
+        <v>4.42682695388794</v>
       </c>
       <c r="H4" t="n">
         <v>349</v>
@@ -514,7 +514,7 @@
         <v>5.16267681121826</v>
       </c>
       <c r="G5" t="n">
-        <v>4.27072334289551</v>
+        <v>4.27072381973267</v>
       </c>
       <c r="H5" t="n">
         <v>140</v>
@@ -543,7 +543,7 @@
         <v>5.07366609573364</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1970911026001</v>
+        <v>4.19709157943726</v>
       </c>
       <c r="H6" t="n">
         <v>112</v>
@@ -601,7 +601,7 @@
         <v>4.80663108825684</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9761917591095</v>
+        <v>3.97619199752808</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -630,7 +630,7 @@
         <v>4.81019115447998</v>
       </c>
       <c r="G9" t="n">
-        <v>3.97913694381714</v>
+        <v>3.9791374206543</v>
       </c>
       <c r="H9" t="n">
         <v>912</v>
@@ -659,7 +659,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G10" t="n">
-        <v>3.68165850639343</v>
+        <v>3.68165922164917</v>
       </c>
       <c r="H10" t="n">
         <v>1371</v>
@@ -688,7 +688,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G11" t="n">
-        <v>3.68165850639343</v>
+        <v>3.68165922164917</v>
       </c>
       <c r="H11" t="n">
         <v>5201</v>
@@ -717,7 +717,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G12" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H12" t="n">
         <v>4083</v>
@@ -833,7 +833,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G16" t="n">
-        <v>3.38712573051453</v>
+        <v>3.38712549209595</v>
       </c>
       <c r="H16" t="n">
         <v>1287</v>
@@ -862,7 +862,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G17" t="n">
-        <v>3.38712573051453</v>
+        <v>3.38712549209595</v>
       </c>
       <c r="H17" t="n">
         <v>1333</v>
@@ -891,7 +891,7 @@
         <v>4.11233901977539</v>
       </c>
       <c r="G18" t="n">
-        <v>3.40185236930847</v>
+        <v>3.40185213088989</v>
       </c>
       <c r="H18" t="n">
         <v>1740</v>
@@ -920,7 +920,7 @@
         <v>4.11233901977539</v>
       </c>
       <c r="G19" t="n">
-        <v>3.40185236930847</v>
+        <v>3.40185213088989</v>
       </c>
       <c r="H19" t="n">
         <v>5</v>
@@ -949,7 +949,7 @@
         <v>4.11233901977539</v>
       </c>
       <c r="G20" t="n">
-        <v>3.40185236930847</v>
+        <v>3.40185213088989</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G21" t="n">
-        <v>3.68165850639343</v>
+        <v>3.68165922164917</v>
       </c>
       <c r="H21" t="n">
         <v>978</v>
@@ -1007,7 +1007,7 @@
         <v>4.77102613449097</v>
       </c>
       <c r="G22" t="n">
-        <v>3.94673824310303</v>
+        <v>3.94673848152161</v>
       </c>
       <c r="H22" t="n">
         <v>3421</v>
@@ -1036,7 +1036,7 @@
         <v>4.53959512710571</v>
       </c>
       <c r="G23" t="n">
-        <v>3.755291223526</v>
+        <v>3.75529170036316</v>
       </c>
       <c r="H23" t="n">
         <v>556</v>
@@ -1065,7 +1065,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G24" t="n">
-        <v>3.68165850639343</v>
+        <v>3.68165922164917</v>
       </c>
       <c r="H24" t="n">
         <v>56</v>
@@ -1094,7 +1094,7 @@
         <v>4.19957113265991</v>
       </c>
       <c r="G25" t="n">
-        <v>3.47401332855225</v>
+        <v>3.47401309013367</v>
       </c>
       <c r="H25" t="n">
         <v>50</v>
@@ -1123,7 +1123,7 @@
         <v>4.53959512710571</v>
       </c>
       <c r="G26" t="n">
-        <v>3.755291223526</v>
+        <v>3.75529170036316</v>
       </c>
       <c r="H26" t="n">
         <v>224</v>
@@ -1152,7 +1152,7 @@
         <v>4.52891397476196</v>
       </c>
       <c r="G27" t="n">
-        <v>3.74645566940308</v>
+        <v>3.74645590782166</v>
       </c>
       <c r="H27" t="n">
         <v>1269</v>
@@ -1181,7 +1181,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G28" t="n">
-        <v>3.68165850639343</v>
+        <v>3.68165922164917</v>
       </c>
       <c r="H28" t="n">
         <v>1864</v>
@@ -1210,7 +1210,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G29" t="n">
-        <v>3.68165850639343</v>
+        <v>3.68165922164917</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G30" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H30" t="n">
         <v>333</v>
@@ -1268,7 +1268,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G31" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H31" t="n">
         <v>33</v>
@@ -1297,7 +1297,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G32" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G33" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G34" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G35" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G36" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G37" t="n">
-        <v>3.69638538360596</v>
+        <v>3.69638562202454</v>
       </c>
       <c r="H37" t="n">
         <v>168</v>
@@ -1471,7 +1471,7 @@
         <v>3.99840402603149</v>
       </c>
       <c r="G38" t="n">
-        <v>3.30760169029236</v>
+        <v>3.30760192871094</v>
       </c>
       <c r="H38" t="n">
         <v>318</v>
@@ -1500,7 +1500,7 @@
         <v>4.03044891357422</v>
       </c>
       <c r="G39" t="n">
-        <v>3.33411049842834</v>
+        <v>3.33411002159119</v>
       </c>
       <c r="H39" t="n">
         <v>151</v>
@@ -1529,7 +1529,7 @@
         <v>4.03222894668579</v>
       </c>
       <c r="G40" t="n">
-        <v>3.33558297157288</v>
+        <v>3.3355827331543</v>
       </c>
       <c r="H40" t="n">
         <v>50</v>
@@ -1587,7 +1587,7 @@
         <v>4.30816507339478</v>
       </c>
       <c r="G42" t="n">
-        <v>3.56384539604187</v>
+        <v>3.56384563446045</v>
       </c>
       <c r="H42" t="n">
         <v>589</v>
@@ -1616,7 +1616,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G43" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H43" t="n">
         <v>112</v>
@@ -1645,7 +1645,7 @@
         <v>4.03400897979736</v>
       </c>
       <c r="G44" t="n">
-        <v>3.33705520629883</v>
+        <v>3.33705544471741</v>
       </c>
       <c r="H44" t="n">
         <v>1197</v>
@@ -1674,7 +1674,7 @@
         <v>4.40785789489746</v>
       </c>
       <c r="G45" t="n">
-        <v>3.64631462097168</v>
+        <v>3.64631414413452</v>
       </c>
       <c r="H45" t="n">
         <v>280</v>
@@ -1703,7 +1703,7 @@
         <v>4.40785789489746</v>
       </c>
       <c r="G46" t="n">
-        <v>3.64631462097168</v>
+        <v>3.64631414413452</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G47" t="n">
-        <v>3.49315762519836</v>
+        <v>3.49315810203552</v>
       </c>
       <c r="H47" t="n">
         <v>290</v>
@@ -1761,7 +1761,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G48" t="n">
-        <v>3.49315762519836</v>
+        <v>3.49315810203552</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G49" t="n">
-        <v>3.49315762519836</v>
+        <v>3.49315810203552</v>
       </c>
       <c r="H49" t="n">
         <v>43</v>
@@ -1819,7 +1819,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G50" t="n">
-        <v>3.49315762519836</v>
+        <v>3.49315810203552</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>4.26722002029419</v>
       </c>
       <c r="G51" t="n">
-        <v>3.52997446060181</v>
+        <v>3.52997469902039</v>
       </c>
       <c r="H51" t="n">
         <v>91</v>
@@ -1877,7 +1877,7 @@
         <v>4.59300184249878</v>
       </c>
       <c r="G52" t="n">
-        <v>3.79947113990784</v>
+        <v>3.799471616745</v>
       </c>
       <c r="H52" t="n">
         <v>1124</v>
@@ -1906,7 +1906,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G53" t="n">
-        <v>3.82892441749573</v>
+        <v>3.82892489433289</v>
       </c>
       <c r="H53" t="n">
         <v>4</v>
@@ -1935,7 +1935,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G54" t="n">
-        <v>3.82892441749573</v>
+        <v>3.82892489433289</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G55" t="n">
-        <v>3.82892441749573</v>
+        <v>3.82892489433289</v>
       </c>
       <c r="H55" t="n">
         <v>56</v>
@@ -1993,7 +1993,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G56" t="n">
-        <v>3.82892441749573</v>
+        <v>3.82892489433289</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G57" t="n">
-        <v>3.68165850639343</v>
+        <v>3.68165922164917</v>
       </c>
       <c r="H57" t="n">
         <v>148</v>
@@ -2051,7 +2051,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G58" t="n">
-        <v>3.68165850639343</v>
+        <v>3.68165922164917</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>4.21915292739868</v>
       </c>
       <c r="G59" t="n">
-        <v>3.49021172523499</v>
+        <v>3.49021196365356</v>
       </c>
       <c r="H59" t="n">
         <v>364</v>
@@ -2109,7 +2109,7 @@
         <v>4.21915292739868</v>
       </c>
       <c r="G60" t="n">
-        <v>3.49021172523499</v>
+        <v>3.49021196365356</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G63" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H63" t="n">
         <v>524</v>
@@ -2225,7 +2225,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G64" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G65" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H65" t="n">
         <v>578</v>
@@ -2283,7 +2283,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G66" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H66" t="n">
         <v>1585</v>
@@ -2312,7 +2312,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G67" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H67" t="n">
         <v>140</v>
@@ -2341,7 +2341,7 @@
         <v>4.05003118515015</v>
       </c>
       <c r="G68" t="n">
-        <v>3.35030913352966</v>
+        <v>3.35030937194824</v>
       </c>
       <c r="H68" t="n">
         <v>70</v>
@@ -2370,7 +2370,7 @@
         <v>3.82750201225281</v>
       </c>
       <c r="G69" t="n">
-        <v>3.1662266254425</v>
+        <v>3.16622614860535</v>
       </c>
       <c r="H69" t="n">
         <v>357</v>
@@ -2544,7 +2544,7 @@
         <v>4.18176794052124</v>
       </c>
       <c r="G75" t="n">
-        <v>3.45928621292114</v>
+        <v>3.45928597450256</v>
       </c>
       <c r="H75" t="n">
         <v>1353</v>
@@ -2573,7 +2573,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G76" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H76" t="n">
         <v>224</v>
@@ -2602,7 +2602,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G77" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>3.94321703910828</v>
       </c>
       <c r="G78" t="n">
-        <v>3.26194953918457</v>
+        <v>3.26194930076599</v>
       </c>
       <c r="H78" t="n">
         <v>55</v>
@@ -2660,7 +2660,7 @@
         <v>3.94499707221985</v>
       </c>
       <c r="G79" t="n">
-        <v>3.26342177391052</v>
+        <v>3.2634220123291</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>3.9343159198761</v>
       </c>
       <c r="G80" t="n">
-        <v>3.2545862197876</v>
+        <v>3.25458598136902</v>
       </c>
       <c r="H80" t="n">
         <v>445</v>
@@ -2718,7 +2718,7 @@
         <v>3.9343159198761</v>
       </c>
       <c r="G81" t="n">
-        <v>3.2545862197876</v>
+        <v>3.25458598136902</v>
       </c>
       <c r="H81" t="n">
         <v>56</v>
@@ -2747,7 +2747,7 @@
         <v>4.29036283493042</v>
       </c>
       <c r="G82" t="n">
-        <v>3.54911875724792</v>
+        <v>3.54911923408508</v>
       </c>
       <c r="H82" t="n">
         <v>2234</v>
@@ -2776,7 +2776,7 @@
         <v>4.16574621200562</v>
       </c>
       <c r="G83" t="n">
-        <v>3.44603252410889</v>
+        <v>3.44603228569031</v>
       </c>
       <c r="H83" t="n">
         <v>10265</v>
@@ -2805,7 +2805,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G84" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H84" t="n">
         <v>1299</v>
@@ -2834,7 +2834,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G85" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H85" t="n">
         <v>940</v>
@@ -2863,7 +2863,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G86" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>4.20313119888306</v>
       </c>
       <c r="G87" t="n">
-        <v>3.47695851325989</v>
+        <v>3.47695827484131</v>
       </c>
       <c r="H87" t="n">
         <v>2430</v>
@@ -2921,7 +2921,7 @@
         <v>4.20313119888306</v>
       </c>
       <c r="G88" t="n">
-        <v>3.47695851325989</v>
+        <v>3.47695827484131</v>
       </c>
       <c r="H88" t="n">
         <v>109</v>
@@ -2950,7 +2950,7 @@
         <v>3.9254150390625</v>
       </c>
       <c r="G89" t="n">
-        <v>3.24722290039062</v>
+        <v>3.2472231388092</v>
       </c>
       <c r="H89" t="n">
         <v>1760</v>
@@ -3008,7 +3008,7 @@
         <v>3.96101999282837</v>
       </c>
       <c r="G91" t="n">
-        <v>3.27667665481567</v>
+        <v>3.27667641639709</v>
       </c>
       <c r="H91" t="n">
         <v>3492</v>
@@ -3211,7 +3211,7 @@
         <v>3.38422393798828</v>
       </c>
       <c r="G98" t="n">
-        <v>2.7995331287384</v>
+        <v>2.79953336715698</v>
       </c>
       <c r="H98" t="n">
         <v>581</v>
@@ -3240,7 +3240,7 @@
         <v>3.41804790496826</v>
       </c>
       <c r="G99" t="n">
-        <v>2.82751369476318</v>
+        <v>2.8275134563446</v>
       </c>
       <c r="H99" t="n">
         <v>129</v>
@@ -3269,7 +3269,7 @@
         <v>3.38778400421143</v>
       </c>
       <c r="G100" t="n">
-        <v>2.80247807502747</v>
+        <v>2.80247831344604</v>
       </c>
       <c r="H100" t="n">
         <v>7</v>
@@ -3327,7 +3327,7 @@
         <v>3.90583205223083</v>
       </c>
       <c r="G102" t="n">
-        <v>3.23102355003357</v>
+        <v>3.23102331161499</v>
       </c>
       <c r="H102" t="n">
         <v>112</v>
@@ -3356,7 +3356,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G103" t="n">
-        <v>3.32380127906799</v>
+        <v>3.32380104064941</v>
       </c>
       <c r="H103" t="n">
         <v>356</v>
@@ -3385,7 +3385,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G104" t="n">
-        <v>3.32380127906799</v>
+        <v>3.32380104064941</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G105" t="n">
-        <v>3.32380127906799</v>
+        <v>3.32380104064941</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G106" t="n">
-        <v>3.32380127906799</v>
+        <v>3.32380104064941</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G107" t="n">
-        <v>3.32380127906799</v>
+        <v>3.32380104064941</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G108" t="n">
-        <v>3.32380127906799</v>
+        <v>3.32380104064941</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G109" t="n">
-        <v>3.32380127906799</v>
+        <v>3.32380104064941</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G110" t="n">
-        <v>3.32380127906799</v>
+        <v>3.32380104064941</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G111" t="n">
-        <v>2.90409231185913</v>
+        <v>2.90409207344055</v>
       </c>
       <c r="H111" t="n">
         <v>5</v>
@@ -3675,7 +3675,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G114" t="n">
-        <v>2.90114736557007</v>
+        <v>2.90114712715149</v>
       </c>
       <c r="H114" t="n">
         <v>254</v>
@@ -3733,7 +3733,7 @@
         <v>3.34683895111084</v>
       </c>
       <c r="G116" t="n">
-        <v>2.76860737800598</v>
+        <v>2.7686071395874</v>
       </c>
       <c r="H116" t="n">
         <v>252</v>
@@ -3762,7 +3762,7 @@
         <v>3.34683895111084</v>
       </c>
       <c r="G117" t="n">
-        <v>2.76860737800598</v>
+        <v>2.7686071395874</v>
       </c>
       <c r="H117" t="n">
         <v>588</v>
@@ -3791,7 +3791,7 @@
         <v>3.34683895111084</v>
       </c>
       <c r="G118" t="n">
-        <v>2.76860737800598</v>
+        <v>2.7686071395874</v>
       </c>
       <c r="H118" t="n">
         <v>254</v>
@@ -3878,7 +3878,7 @@
         <v>3.20442008972168</v>
       </c>
       <c r="G121" t="n">
-        <v>2.65079402923584</v>
+        <v>2.65079426765442</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>3.29521203041077</v>
       </c>
       <c r="G122" t="n">
-        <v>2.7258996963501</v>
+        <v>2.72589993476868</v>
       </c>
       <c r="H122" t="n">
         <v>1954</v>
@@ -3965,7 +3965,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G124" t="n">
-        <v>2.35626125335693</v>
+        <v>2.35626101493835</v>
       </c>
       <c r="H124" t="n">
         <v>1581</v>
@@ -3994,7 +3994,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G125" t="n">
-        <v>2.35626125335693</v>
+        <v>2.35626101493835</v>
       </c>
       <c r="H125" t="n">
         <v>1216</v>
@@ -4023,7 +4023,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G126" t="n">
-        <v>2.35626125335693</v>
+        <v>2.35626101493835</v>
       </c>
       <c r="H126" t="n">
         <v>44</v>
@@ -4052,7 +4052,7 @@
         <v>2.95518708229065</v>
       </c>
       <c r="G127" t="n">
-        <v>2.44462060928345</v>
+        <v>2.44462084770203</v>
       </c>
       <c r="H127" t="n">
         <v>702</v>
@@ -4081,7 +4081,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G128" t="n">
-        <v>2.35626125335693</v>
+        <v>2.35626101493835</v>
       </c>
       <c r="H128" t="n">
         <v>113</v>
@@ -4110,7 +4110,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G129" t="n">
-        <v>2.35626125335693</v>
+        <v>2.35626101493835</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G130" t="n">
-        <v>2.35626125335693</v>
+        <v>2.35626101493835</v>
       </c>
       <c r="H130" t="n">
         <v>206</v>
@@ -4168,7 +4168,7 @@
         <v>2.88041806221008</v>
       </c>
       <c r="G131" t="n">
-        <v>2.38276982307434</v>
+        <v>2.38276958465576</v>
       </c>
       <c r="H131" t="n">
         <v>337</v>
@@ -4197,7 +4197,7 @@
         <v>2.79852700233459</v>
       </c>
       <c r="G132" t="n">
-        <v>2.31502676010132</v>
+        <v>2.3150269985199</v>
       </c>
       <c r="H132" t="n">
         <v>112</v>
@@ -4226,7 +4226,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G133" t="n">
-        <v>2.35626125335693</v>
+        <v>2.35626101493835</v>
       </c>
       <c r="H133" t="n">
         <v>596</v>
@@ -4284,7 +4284,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G135" t="n">
-        <v>1.76719617843628</v>
+        <v>1.76719605922699</v>
       </c>
       <c r="H135" t="n">
         <v>7586</v>
@@ -4313,7 +4313,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G136" t="n">
-        <v>1.76719617843628</v>
+        <v>1.76719605922699</v>
       </c>
       <c r="H136" t="n">
         <v>6199</v>
@@ -4458,7 +4458,7 @@
         <v>2.25199508666992</v>
       </c>
       <c r="G141" t="n">
-        <v>1.86291897296906</v>
+        <v>1.86291921138763</v>
       </c>
       <c r="H141" t="n">
         <v>9636</v>
@@ -4487,7 +4487,7 @@
         <v>2.17010402679443</v>
       </c>
       <c r="G142" t="n">
-        <v>1.7951762676239</v>
+        <v>1.79517638683319</v>
       </c>
       <c r="H142" t="n">
         <v>2359</v>
@@ -4516,7 +4516,7 @@
         <v>2.23241305351257</v>
       </c>
       <c r="G143" t="n">
-        <v>1.84672021865845</v>
+        <v>1.84672009944916</v>
       </c>
       <c r="H143" t="n">
         <v>16023</v>
@@ -4545,7 +4545,7 @@
         <v>2.26267695426941</v>
       </c>
       <c r="G144" t="n">
-        <v>1.87175524234772</v>
+        <v>1.8717554807663</v>
       </c>
       <c r="H144" t="n">
         <v>2313</v>
@@ -4603,7 +4603,7 @@
         <v>2.07753205299377</v>
       </c>
       <c r="G146" t="n">
-        <v>1.71859800815582</v>
+        <v>1.71859788894653</v>
       </c>
       <c r="H146" t="n">
         <v>6315</v>
@@ -4690,7 +4690,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G149" t="n">
-        <v>1.73774242401123</v>
+        <v>1.73774254322052</v>
       </c>
       <c r="H149" t="n">
         <v>918</v>
@@ -4719,7 +4719,7 @@
         <v>2.28582000732422</v>
       </c>
       <c r="G150" t="n">
-        <v>1.89090013504028</v>
+        <v>1.89090001583099</v>
       </c>
       <c r="H150" t="n">
         <v>14195</v>
@@ -4748,7 +4748,7 @@
         <v>2.28582000732422</v>
       </c>
       <c r="G151" t="n">
-        <v>1.89090013504028</v>
+        <v>1.89090001583099</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>2.28582000732422</v>
       </c>
       <c r="G152" t="n">
-        <v>1.89090013504028</v>
+        <v>1.89090001583099</v>
       </c>
       <c r="H152" t="n">
         <v>56</v>
@@ -4893,7 +4893,7 @@
         <v>2.09711503982544</v>
       </c>
       <c r="G156" t="n">
-        <v>1.73479759693146</v>
+        <v>1.73479747772217</v>
       </c>
       <c r="H156" t="n">
         <v>280</v>
@@ -5067,7 +5067,7 @@
         <v>1.97961902618408</v>
       </c>
       <c r="G162" t="n">
-        <v>1.63760125637054</v>
+        <v>1.63760137557983</v>
       </c>
       <c r="H162" t="n">
         <v>645</v>
@@ -5212,7 +5212,7 @@
         <v>1.92265200614929</v>
       </c>
       <c r="G167" t="n">
-        <v>1.59047639369965</v>
+        <v>1.59047627449036</v>
       </c>
       <c r="H167" t="n">
         <v>926</v>
@@ -5241,7 +5241,7 @@
         <v>1.92265200614929</v>
       </c>
       <c r="G168" t="n">
-        <v>1.59047639369965</v>
+        <v>1.59047627449036</v>
       </c>
       <c r="H168" t="n">
         <v>561</v>
@@ -5270,7 +5270,7 @@
         <v>1.92265200614929</v>
       </c>
       <c r="G169" t="n">
-        <v>1.59047639369965</v>
+        <v>1.59047627449036</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.83363997936249</v>
       </c>
       <c r="G175" t="n">
-        <v>1.51684284210205</v>
+        <v>1.51684296131134</v>
       </c>
       <c r="H175" t="n">
         <v>1417</v>
@@ -5473,7 +5473,7 @@
         <v>2.13983988761902</v>
       </c>
       <c r="G176" t="n">
-        <v>1.77014088630676</v>
+        <v>1.77014076709747</v>
       </c>
       <c r="H176" t="n">
         <v>7689</v>
@@ -5502,7 +5502,7 @@
         <v>2.17188501358032</v>
       </c>
       <c r="G177" t="n">
-        <v>1.79664969444275</v>
+        <v>1.79664957523346</v>
       </c>
       <c r="H177" t="n">
         <v>17162</v>
@@ -5531,7 +5531,7 @@
         <v>2.11313700675964</v>
       </c>
       <c r="G178" t="n">
-        <v>1.748051404953</v>
+        <v>1.74805128574371</v>
       </c>
       <c r="H178" t="n">
         <v>2418</v>
@@ -5589,7 +5589,7 @@
         <v>2.08287310600281</v>
       </c>
       <c r="G180" t="n">
-        <v>1.72301626205444</v>
+        <v>1.72301614284515</v>
       </c>
       <c r="H180" t="n">
         <v>674</v>
@@ -5647,7 +5647,7 @@
         <v>1.97605895996094</v>
       </c>
       <c r="G182" t="n">
-        <v>1.63465642929077</v>
+        <v>1.63465619087219</v>
       </c>
       <c r="H182" t="n">
         <v>1404</v>
@@ -5676,7 +5676,7 @@
         <v>2.11847805976868</v>
       </c>
       <c r="G183" t="n">
-        <v>1.75246953964233</v>
+        <v>1.75246977806091</v>
       </c>
       <c r="H183" t="n">
         <v>951</v>
@@ -5763,7 +5763,7 @@
         <v>1.90485000610352</v>
       </c>
       <c r="G186" t="n">
-        <v>1.57575011253357</v>
+        <v>1.57574999332428</v>
       </c>
       <c r="H186" t="n">
         <v>3560</v>
@@ -5792,7 +5792,7 @@
         <v>1.87992596626282</v>
       </c>
       <c r="G187" t="n">
-        <v>1.55513203144073</v>
+        <v>1.55513215065002</v>
       </c>
       <c r="H187" t="n">
         <v>674</v>
@@ -5850,7 +5850,7 @@
         <v>1.90485000610352</v>
       </c>
       <c r="G189" t="n">
-        <v>1.57575011253357</v>
+        <v>1.57574999332428</v>
       </c>
       <c r="H189" t="n">
         <v>634</v>
@@ -5879,7 +5879,7 @@
         <v>1.99386096000671</v>
       </c>
       <c r="G190" t="n">
-        <v>1.64938259124756</v>
+        <v>1.64938247203827</v>
       </c>
       <c r="H190" t="n">
         <v>619</v>
@@ -5908,7 +5908,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G191" t="n">
-        <v>1.73774242401123</v>
+        <v>1.73774254322052</v>
       </c>
       <c r="H191" t="n">
         <v>4547</v>
@@ -5937,7 +5937,7 @@
         <v>2.29650092124939</v>
       </c>
       <c r="G192" t="n">
-        <v>1.89973556995392</v>
+        <v>1.8997358083725</v>
       </c>
       <c r="H192" t="n">
         <v>5945</v>
@@ -5966,7 +5966,7 @@
         <v>2.24309396743774</v>
       </c>
       <c r="G193" t="n">
-        <v>1.85555589199066</v>
+        <v>1.85555577278137</v>
       </c>
       <c r="H193" t="n">
         <v>7335</v>
@@ -5995,7 +5995,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G194" t="n">
-        <v>1.76719617843628</v>
+        <v>1.76719605922699</v>
       </c>
       <c r="H194" t="n">
         <v>1123</v>
@@ -6082,7 +6082,7 @@
         <v>2.31608390808105</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91593515872955</v>
+        <v>1.91593539714813</v>
       </c>
       <c r="H197" t="n">
         <v>4776</v>
@@ -6169,7 +6169,7 @@
         <v>2.44248008728027</v>
       </c>
       <c r="G200" t="n">
-        <v>2.02049398422241</v>
+        <v>2.02049422264099</v>
       </c>
       <c r="H200" t="n">
         <v>6150</v>
@@ -6198,7 +6198,7 @@
         <v>2.35880899429321</v>
       </c>
       <c r="G201" t="n">
-        <v>1.95127892494202</v>
+        <v>1.95127880573273</v>
       </c>
       <c r="H201" t="n">
         <v>224</v>
@@ -6256,7 +6256,7 @@
         <v>2.27869892120361</v>
       </c>
       <c r="G203" t="n">
-        <v>1.88500928878784</v>
+        <v>1.88500952720642</v>
       </c>
       <c r="H203" t="n">
         <v>9785</v>
@@ -6285,7 +6285,7 @@
         <v>2.15764307975769</v>
       </c>
       <c r="G204" t="n">
-        <v>1.78486812114716</v>
+        <v>1.78486824035645</v>
       </c>
       <c r="H204" t="n">
         <v>5715</v>
@@ -6314,7 +6314,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G205" t="n">
-        <v>1.76719617843628</v>
+        <v>1.76719605922699</v>
       </c>
       <c r="H205" t="n">
         <v>16748</v>
@@ -6401,7 +6401,7 @@
         <v>2.16298294067383</v>
       </c>
       <c r="G208" t="n">
-        <v>1.78928542137146</v>
+        <v>1.78928554058075</v>
       </c>
       <c r="H208" t="n">
         <v>7479</v>
@@ -6430,7 +6430,7 @@
         <v>2.10245609283447</v>
       </c>
       <c r="G209" t="n">
-        <v>1.73921597003937</v>
+        <v>1.73921573162079</v>
       </c>
       <c r="H209" t="n">
         <v>730</v>
@@ -6459,7 +6459,7 @@
         <v>2.12025809288025</v>
       </c>
       <c r="G210" t="n">
-        <v>1.75394201278687</v>
+        <v>1.75394225120544</v>
       </c>
       <c r="H210" t="n">
         <v>1994</v>
@@ -6575,7 +6575,7 @@
         <v>2.11313700675964</v>
       </c>
       <c r="G214" t="n">
-        <v>1.748051404953</v>
+        <v>1.74805128574371</v>
       </c>
       <c r="H214" t="n">
         <v>364</v>
@@ -6604,7 +6604,7 @@
         <v>2.11669707298279</v>
       </c>
       <c r="G215" t="n">
-        <v>1.75099647045135</v>
+        <v>1.75099635124207</v>
       </c>
       <c r="H215" t="n">
         <v>561</v>
@@ -6633,7 +6633,7 @@
         <v>2.07397198677063</v>
       </c>
       <c r="G216" t="n">
-        <v>1.71565294265747</v>
+        <v>1.71565282344818</v>
       </c>
       <c r="H216" t="n">
         <v>128</v>
@@ -6662,7 +6662,7 @@
         <v>1.99920201301575</v>
       </c>
       <c r="G217" t="n">
-        <v>1.65380084514618</v>
+        <v>1.65380096435547</v>
       </c>
       <c r="H217" t="n">
         <v>467</v>
@@ -6691,7 +6691,7 @@
         <v>2.02412509918213</v>
       </c>
       <c r="G218" t="n">
-        <v>1.6744179725647</v>
+        <v>1.67441809177399</v>
       </c>
       <c r="H218" t="n">
         <v>2724</v>
@@ -6720,7 +6720,7 @@
         <v>2.02412509918213</v>
       </c>
       <c r="G219" t="n">
-        <v>1.6744179725647</v>
+        <v>1.67441809177399</v>
       </c>
       <c r="H219" t="n">
         <v>56</v>
@@ -6778,7 +6778,7 @@
         <v>2.09711503982544</v>
       </c>
       <c r="G221" t="n">
-        <v>1.73479759693146</v>
+        <v>1.73479747772217</v>
       </c>
       <c r="H221" t="n">
         <v>56</v>
@@ -6894,7 +6894,7 @@
         <v>2.00098204612732</v>
       </c>
       <c r="G225" t="n">
-        <v>1.65527331829071</v>
+        <v>1.6552734375</v>
       </c>
       <c r="H225" t="n">
         <v>56</v>
@@ -6981,7 +6981,7 @@
         <v>2.13806009292603</v>
       </c>
       <c r="G228" t="n">
-        <v>1.76866853237152</v>
+        <v>1.76866865158081</v>
       </c>
       <c r="H228" t="n">
         <v>252</v>
@@ -7184,7 +7184,7 @@
         <v>1.97249805927277</v>
       </c>
       <c r="G235" t="n">
-        <v>1.63171052932739</v>
+        <v>1.63171064853668</v>
       </c>
       <c r="H235" t="n">
         <v>14</v>
@@ -7329,7 +7329,7 @@
         <v>2.07041096687317</v>
       </c>
       <c r="G240" t="n">
-        <v>1.71270704269409</v>
+        <v>1.71270716190338</v>
       </c>
       <c r="H240" t="n">
         <v>281</v>
@@ -7358,7 +7358,7 @@
         <v>2.07041096687317</v>
       </c>
       <c r="G241" t="n">
-        <v>1.71270704269409</v>
+        <v>1.71270716190338</v>
       </c>
       <c r="H241" t="n">
         <v>112</v>
@@ -7387,7 +7387,7 @@
         <v>2.11847805976868</v>
       </c>
       <c r="G242" t="n">
-        <v>1.75246953964233</v>
+        <v>1.75246977806091</v>
       </c>
       <c r="H242" t="n">
         <v>2937</v>
@@ -7503,7 +7503,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G246" t="n">
-        <v>1.73774242401123</v>
+        <v>1.73774254322052</v>
       </c>
       <c r="H246" t="n">
         <v>664</v>
@@ -7619,7 +7619,7 @@
         <v>2.13628005981445</v>
       </c>
       <c r="G250" t="n">
-        <v>1.76719617843628</v>
+        <v>1.76719605922699</v>
       </c>
       <c r="H250" t="n">
         <v>5386</v>
@@ -7648,7 +7648,7 @@
         <v>2.03124594688416</v>
       </c>
       <c r="G251" t="n">
-        <v>1.68030846118927</v>
+        <v>1.68030858039856</v>
       </c>
       <c r="H251" t="n">
         <v>849</v>
@@ -7677,7 +7677,7 @@
         <v>2.04904794692993</v>
       </c>
       <c r="G252" t="n">
-        <v>1.69503498077393</v>
+        <v>1.69503486156464</v>
       </c>
       <c r="H252" t="n">
         <v>16761</v>
@@ -7764,7 +7764,7 @@
         <v>2.36415004730225</v>
       </c>
       <c r="G255" t="n">
-        <v>1.95569694042206</v>
+        <v>1.95569682121277</v>
       </c>
       <c r="H255" t="n">
         <v>38762</v>
@@ -7793,7 +7793,7 @@
         <v>2.41221594810486</v>
       </c>
       <c r="G256" t="n">
-        <v>1.99545848369598</v>
+        <v>1.99545872211456</v>
       </c>
       <c r="H256" t="n">
         <v>7030</v>
@@ -7822,7 +7822,7 @@
         <v>2.34456706047058</v>
       </c>
       <c r="G257" t="n">
-        <v>1.93949711322784</v>
+        <v>1.939497590065</v>
       </c>
       <c r="H257" t="n">
         <v>4814</v>
@@ -7938,7 +7938,7 @@
         <v>2.85905504226685</v>
       </c>
       <c r="G261" t="n">
-        <v>2.36509776115417</v>
+        <v>2.3650975227356</v>
       </c>
       <c r="H261" t="n">
         <v>7738</v>
@@ -8025,7 +8025,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G264" t="n">
-        <v>3.68165850639343</v>
+        <v>3.68165922164917</v>
       </c>
       <c r="H264" t="n">
         <v>7281</v>
@@ -8083,7 +8083,7 @@
         <v>4.35445117950439</v>
       </c>
       <c r="G266" t="n">
-        <v>3.60213470458984</v>
+        <v>3.60213494300842</v>
       </c>
       <c r="H266" t="n">
         <v>67774</v>
@@ -8112,7 +8112,7 @@
         <v>4.40073680877686</v>
       </c>
       <c r="G267" t="n">
-        <v>3.64042329788208</v>
+        <v>3.64042401313782</v>
       </c>
       <c r="H267" t="n">
         <v>57818</v>
@@ -8141,7 +8141,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G268" t="n">
-        <v>3.68165850639343</v>
+        <v>3.68165922164917</v>
       </c>
       <c r="H268" t="n">
         <v>8984</v>
@@ -8170,7 +8170,7 @@
         <v>4.3793740272522</v>
       </c>
       <c r="G269" t="n">
-        <v>3.62275147438049</v>
+        <v>3.62275218963623</v>
       </c>
       <c r="H269" t="n">
         <v>7198</v>
@@ -8199,7 +8199,7 @@
         <v>4.16574621200562</v>
       </c>
       <c r="G270" t="n">
-        <v>3.44603252410889</v>
+        <v>3.44603228569031</v>
       </c>
       <c r="H270" t="n">
         <v>17616</v>
@@ -8257,7 +8257,7 @@
         <v>4.59300184249878</v>
       </c>
       <c r="G272" t="n">
-        <v>3.79947113990784</v>
+        <v>3.799471616745</v>
       </c>
       <c r="H272" t="n">
         <v>58292</v>
@@ -8286,7 +8286,7 @@
         <v>4.3953971862793</v>
       </c>
       <c r="G273" t="n">
-        <v>3.6360068321228</v>
+        <v>3.63600659370422</v>
       </c>
       <c r="H273" t="n">
         <v>30650</v>
@@ -8315,7 +8315,7 @@
         <v>4.42210006713867</v>
       </c>
       <c r="G274" t="n">
-        <v>3.65809559822083</v>
+        <v>3.6580958366394</v>
       </c>
       <c r="H274" t="n">
         <v>7239</v>
@@ -8344,7 +8344,7 @@
         <v>4.3241868019104</v>
       </c>
       <c r="G275" t="n">
-        <v>3.57709932327271</v>
+        <v>3.57709908485413</v>
       </c>
       <c r="H275" t="n">
         <v>4632</v>
@@ -8402,7 +8402,7 @@
         <v>4.25653791427612</v>
       </c>
       <c r="G277" t="n">
-        <v>3.52113819122314</v>
+        <v>3.52113795280457</v>
       </c>
       <c r="H277" t="n">
         <v>9571</v>
@@ -8460,7 +8460,7 @@
         <v>4.15506505966187</v>
       </c>
       <c r="G279" t="n">
-        <v>3.4371964931488</v>
+        <v>3.43719673156738</v>
       </c>
       <c r="H279" t="n">
         <v>3034</v>
@@ -8518,7 +8518,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G281" t="n">
-        <v>3.49315762519836</v>
+        <v>3.49315810203552</v>
       </c>
       <c r="H281" t="n">
         <v>2699</v>
@@ -8547,7 +8547,7 @@
         <v>4.3241868019104</v>
       </c>
       <c r="G282" t="n">
-        <v>3.57709932327271</v>
+        <v>3.57709908485413</v>
       </c>
       <c r="H282" t="n">
         <v>3567</v>
@@ -8576,7 +8576,7 @@
         <v>4.32596683502197</v>
       </c>
       <c r="G283" t="n">
-        <v>3.57857179641724</v>
+        <v>3.57857203483582</v>
       </c>
       <c r="H283" t="n">
         <v>27176</v>
@@ -8634,7 +8634,7 @@
         <v>4.11233901977539</v>
       </c>
       <c r="G285" t="n">
-        <v>3.40185236930847</v>
+        <v>3.40185213088989</v>
       </c>
       <c r="H285" t="n">
         <v>2305</v>
@@ -8721,7 +8721,7 @@
         <v>3.92007398605347</v>
       </c>
       <c r="G288" t="n">
-        <v>3.24280452728271</v>
+        <v>3.24280476570129</v>
       </c>
       <c r="H288" t="n">
         <v>728</v>
@@ -8750,7 +8750,7 @@
         <v>3.92007398605347</v>
       </c>
       <c r="G289" t="n">
-        <v>3.24280452728271</v>
+        <v>3.24280476570129</v>
       </c>
       <c r="H289" t="n">
         <v>1247</v>
@@ -8808,7 +8808,7 @@
         <v>3.75629305839539</v>
       </c>
       <c r="G291" t="n">
-        <v>3.10731983184814</v>
+        <v>3.10732007026672</v>
       </c>
       <c r="H291" t="n">
         <v>2984</v>
@@ -8837,7 +8837,7 @@
         <v>3.69932508468628</v>
       </c>
       <c r="G292" t="n">
-        <v>3.06019449234009</v>
+        <v>3.06019425392151</v>
       </c>
       <c r="H292" t="n">
         <v>4324</v>
@@ -8866,7 +8866,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G293" t="n">
-        <v>3.38712573051453</v>
+        <v>3.38712549209595</v>
       </c>
       <c r="H293" t="n">
         <v>9236</v>
@@ -8895,7 +8895,7 @@
         <v>3.85954594612122</v>
       </c>
       <c r="G294" t="n">
-        <v>3.19273400306702</v>
+        <v>3.1927342414856</v>
       </c>
       <c r="H294" t="n">
         <v>2137</v>
@@ -9069,7 +9069,7 @@
         <v>4.09453678131104</v>
       </c>
       <c r="G300" t="n">
-        <v>3.38712573051453</v>
+        <v>3.38712549209595</v>
       </c>
       <c r="H300" t="n">
         <v>13458</v>
@@ -9098,7 +9098,7 @@
         <v>3.99306392669678</v>
       </c>
       <c r="G301" t="n">
-        <v>3.30318427085876</v>
+        <v>3.30318450927734</v>
       </c>
       <c r="H301" t="n">
         <v>4913</v>
@@ -9185,7 +9185,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G304" t="n">
-        <v>3.18831586837769</v>
+        <v>3.18831562995911</v>
       </c>
       <c r="H304" t="n">
         <v>1235</v>
@@ -9214,7 +9214,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G305" t="n">
-        <v>3.18831586837769</v>
+        <v>3.18831562995911</v>
       </c>
       <c r="H305" t="n">
         <v>1282</v>
@@ -9243,7 +9243,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G306" t="n">
-        <v>3.18831586837769</v>
+        <v>3.18831562995911</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>4.09275722503662</v>
       </c>
       <c r="G308" t="n">
-        <v>3.38565373420715</v>
+        <v>3.38565325737</v>
       </c>
       <c r="H308" t="n">
         <v>112</v>
@@ -9388,7 +9388,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G311" t="n">
-        <v>3.18831586837769</v>
+        <v>3.18831562995911</v>
       </c>
       <c r="H311" t="n">
         <v>2222</v>
@@ -9504,7 +9504,7 @@
         <v>3.65481901168823</v>
       </c>
       <c r="G315" t="n">
-        <v>3.02337789535522</v>
+        <v>3.02337765693665</v>
       </c>
       <c r="H315" t="n">
         <v>57</v>
@@ -9533,7 +9533,7 @@
         <v>3.66728091239929</v>
       </c>
       <c r="G316" t="n">
-        <v>3.03368663787842</v>
+        <v>3.033686876297</v>
       </c>
       <c r="H316" t="n">
         <v>1969</v>
@@ -9562,7 +9562,7 @@
         <v>3.66728091239929</v>
       </c>
       <c r="G317" t="n">
-        <v>3.03368663787842</v>
+        <v>3.033686876297</v>
       </c>
       <c r="H317" t="n">
         <v>2340</v>
@@ -9591,7 +9591,7 @@
         <v>3.65303897857666</v>
       </c>
       <c r="G318" t="n">
-        <v>3.02190518379211</v>
+        <v>3.02190542221069</v>
       </c>
       <c r="H318" t="n">
         <v>112</v>
@@ -9649,7 +9649,7 @@
         <v>3.53910398483276</v>
       </c>
       <c r="G320" t="n">
-        <v>2.927654504776</v>
+        <v>2.92765498161316</v>
       </c>
       <c r="H320" t="n">
         <v>6607</v>
@@ -9707,7 +9707,7 @@
         <v>3.56580805778503</v>
       </c>
       <c r="G322" t="n">
-        <v>2.94974517822266</v>
+        <v>2.94974493980408</v>
       </c>
       <c r="H322" t="n">
         <v>1994</v>
@@ -9794,7 +9794,7 @@
         <v>4.94904899597168</v>
       </c>
       <c r="G325" t="n">
-        <v>4.09400415420532</v>
+        <v>4.09400463104248</v>
       </c>
       <c r="H325" t="n">
         <v>60949</v>
@@ -9823,7 +9823,7 @@
         <v>4.62860679626465</v>
       </c>
       <c r="G326" t="n">
-        <v>3.82892441749573</v>
+        <v>3.82892489433289</v>
       </c>
       <c r="H326" t="n">
         <v>278520</v>
@@ -9852,7 +9852,7 @@
         <v>4.27256011962891</v>
       </c>
       <c r="G327" t="n">
-        <v>3.53439235687256</v>
+        <v>3.53439211845398</v>
       </c>
       <c r="H327" t="n">
         <v>72071</v>
@@ -9881,7 +9881,7 @@
         <v>4.41319894790649</v>
       </c>
       <c r="G328" t="n">
-        <v>3.65073275566101</v>
+        <v>3.65073251724243</v>
       </c>
       <c r="H328" t="n">
         <v>30835</v>
@@ -9910,7 +9910,7 @@
         <v>4.21381282806396</v>
       </c>
       <c r="G329" t="n">
-        <v>3.48579430580139</v>
+        <v>3.48579406738281</v>
       </c>
       <c r="H329" t="n">
         <v>5440</v>
@@ -9939,7 +9939,7 @@
         <v>4.32596683502197</v>
       </c>
       <c r="G330" t="n">
-        <v>3.57857179641724</v>
+        <v>3.57857203483582</v>
       </c>
       <c r="H330" t="n">
         <v>34372</v>
@@ -10026,7 +10026,7 @@
         <v>4.00730609893799</v>
       </c>
       <c r="G333" t="n">
-        <v>3.31496572494507</v>
+        <v>3.31496596336365</v>
       </c>
       <c r="H333" t="n">
         <v>19910</v>
@@ -10055,7 +10055,7 @@
         <v>3.98950290679932</v>
       </c>
       <c r="G334" t="n">
-        <v>3.30023837089539</v>
+        <v>3.30023860931396</v>
       </c>
       <c r="H334" t="n">
         <v>5942</v>
@@ -10171,7 +10171,7 @@
         <v>3.93609595298767</v>
       </c>
       <c r="G338" t="n">
-        <v>3.25605845451355</v>
+        <v>3.25605869293213</v>
       </c>
       <c r="H338" t="n">
         <v>7661</v>
@@ -10200,7 +10200,7 @@
         <v>3.93609595298767</v>
       </c>
       <c r="G339" t="n">
-        <v>3.25605845451355</v>
+        <v>3.25605869293213</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>3.85598611831665</v>
       </c>
       <c r="G340" t="n">
-        <v>3.18978929519653</v>
+        <v>3.18978953361511</v>
       </c>
       <c r="H340" t="n">
         <v>3818</v>
@@ -10345,7 +10345,7 @@
         <v>3.86844706535339</v>
       </c>
       <c r="G344" t="n">
-        <v>3.20009732246399</v>
+        <v>3.20009756088257</v>
       </c>
       <c r="H344" t="n">
         <v>2777</v>
@@ -10374,7 +10374,7 @@
         <v>3.84530401229858</v>
       </c>
       <c r="G345" t="n">
-        <v>3.18095278739929</v>
+        <v>3.18095254898071</v>
       </c>
       <c r="H345" t="n">
         <v>842</v>
@@ -10403,7 +10403,7 @@
         <v>3.85954594612122</v>
       </c>
       <c r="G346" t="n">
-        <v>3.19273400306702</v>
+        <v>3.1927342414856</v>
       </c>
       <c r="H346" t="n">
         <v>320</v>
@@ -10548,7 +10548,7 @@
         <v>3.70822596549988</v>
       </c>
       <c r="G351" t="n">
-        <v>3.06755757331848</v>
+        <v>3.0675573348999</v>
       </c>
       <c r="H351" t="n">
         <v>1095</v>
@@ -10664,7 +10664,7 @@
         <v>3.83462309837341</v>
       </c>
       <c r="G355" t="n">
-        <v>3.17211699485779</v>
+        <v>3.17211723327637</v>
       </c>
       <c r="H355" t="n">
         <v>2162</v>
@@ -10693,7 +10693,7 @@
         <v>3.82750201225281</v>
       </c>
       <c r="G356" t="n">
-        <v>3.1662266254425</v>
+        <v>3.16622614860535</v>
       </c>
       <c r="H356" t="n">
         <v>358</v>
@@ -10722,7 +10722,7 @@
         <v>3.80970001220703</v>
       </c>
       <c r="G357" t="n">
-        <v>3.15150022506714</v>
+        <v>3.15149998664856</v>
       </c>
       <c r="H357" t="n">
         <v>1714</v>
@@ -10780,7 +10780,7 @@
         <v>3.95211791992188</v>
       </c>
       <c r="G359" t="n">
-        <v>3.26931285858154</v>
+        <v>3.26931238174438</v>
       </c>
       <c r="H359" t="n">
         <v>7949</v>
@@ -10867,7 +10867,7 @@
         <v>3.87200808525085</v>
       </c>
       <c r="G362" t="n">
-        <v>3.20304322242737</v>
+        <v>3.20304298400879</v>
       </c>
       <c r="H362" t="n">
         <v>224</v>
@@ -10925,7 +10925,7 @@
         <v>3.82750201225281</v>
       </c>
       <c r="G364" t="n">
-        <v>3.1662266254425</v>
+        <v>3.16622614860535</v>
       </c>
       <c r="H364" t="n">
         <v>196</v>
@@ -10954,7 +10954,7 @@
         <v>3.78299593925476</v>
       </c>
       <c r="G365" t="n">
-        <v>3.12940979003906</v>
+        <v>3.12940955162048</v>
       </c>
       <c r="H365" t="n">
         <v>1274</v>
@@ -11012,7 +11012,7 @@
         <v>3.69220399856567</v>
       </c>
       <c r="G367" t="n">
-        <v>3.05430388450623</v>
+        <v>3.05430364608765</v>
       </c>
       <c r="H367" t="n">
         <v>1012</v>
@@ -11041,7 +11041,7 @@
         <v>3.58004903793335</v>
       </c>
       <c r="G368" t="n">
-        <v>2.96152591705322</v>
+        <v>2.96152567863464</v>
       </c>
       <c r="H368" t="n">
         <v>2763</v>
@@ -11070,7 +11070,7 @@
         <v>3.59607195854187</v>
       </c>
       <c r="G369" t="n">
-        <v>2.97478032112122</v>
+        <v>2.97478079795837</v>
       </c>
       <c r="H369" t="n">
         <v>1067</v>
@@ -11128,7 +11128,7 @@
         <v>3.53910398483276</v>
       </c>
       <c r="G371" t="n">
-        <v>2.927654504776</v>
+        <v>2.92765498161316</v>
       </c>
       <c r="H371" t="n">
         <v>248</v>
@@ -11157,7 +11157,7 @@
         <v>3.8114800453186</v>
       </c>
       <c r="G372" t="n">
-        <v>3.15297269821167</v>
+        <v>3.15297245979309</v>
       </c>
       <c r="H372" t="n">
         <v>56763</v>
@@ -11360,7 +11360,7 @@
         <v>3.58183002471924</v>
       </c>
       <c r="G379" t="n">
-        <v>2.96299886703491</v>
+        <v>2.96299910545349</v>
       </c>
       <c r="H379" t="n">
         <v>1229</v>
@@ -11476,7 +11476,7 @@
         <v>3.61565399169922</v>
       </c>
       <c r="G383" t="n">
-        <v>2.99097895622253</v>
+        <v>2.99097919464111</v>
       </c>
       <c r="H383" t="n">
         <v>775</v>
@@ -11534,7 +11534,7 @@
         <v>3.57114791870117</v>
       </c>
       <c r="G385" t="n">
-        <v>2.95416235923767</v>
+        <v>2.95416259765625</v>
       </c>
       <c r="H385" t="n">
         <v>1159</v>
@@ -11563,7 +11563,7 @@
         <v>3.49459791183472</v>
       </c>
       <c r="G386" t="n">
-        <v>2.89083814620972</v>
+        <v>2.89083790779114</v>
       </c>
       <c r="H386" t="n">
         <v>848</v>
@@ -11592,7 +11592,7 @@
         <v>3.43763089179993</v>
       </c>
       <c r="G387" t="n">
-        <v>2.84371328353882</v>
+        <v>2.84371304512024</v>
       </c>
       <c r="H387" t="n">
         <v>2655</v>
@@ -11621,7 +11621,7 @@
         <v>3.45187306404114</v>
       </c>
       <c r="G388" t="n">
-        <v>2.85549473762512</v>
+        <v>2.85549449920654</v>
       </c>
       <c r="H388" t="n">
         <v>1441</v>
@@ -11708,7 +11708,7 @@
         <v>3.48925805091858</v>
       </c>
       <c r="G391" t="n">
-        <v>2.88642072677612</v>
+        <v>2.8864209651947</v>
       </c>
       <c r="H391" t="n">
         <v>642</v>
@@ -11737,7 +11737,7 @@
         <v>3.52486205101013</v>
       </c>
       <c r="G392" t="n">
-        <v>2.91587328910828</v>
+        <v>2.91587352752686</v>
       </c>
       <c r="H392" t="n">
         <v>2488</v>
@@ -11795,7 +11795,7 @@
         <v>3.50349903106689</v>
       </c>
       <c r="G394" t="n">
-        <v>2.89820098876953</v>
+        <v>2.89820122718811</v>
       </c>
       <c r="H394" t="n">
         <v>921</v>
@@ -11824,7 +11824,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G395" t="n">
-        <v>2.84224057197571</v>
+        <v>2.84224104881287</v>
       </c>
       <c r="H395" t="n">
         <v>954</v>
@@ -11853,7 +11853,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G396" t="n">
-        <v>2.84224057197571</v>
+        <v>2.84224104881287</v>
       </c>
       <c r="H396" t="n">
         <v>421</v>
@@ -12056,7 +12056,7 @@
         <v>4.046471118927</v>
       </c>
       <c r="G403" t="n">
-        <v>3.3473641872406</v>
+        <v>3.34736466407776</v>
       </c>
       <c r="H403" t="n">
         <v>98461</v>
@@ -12259,7 +12259,7 @@
         <v>3.59785199165344</v>
       </c>
       <c r="G410" t="n">
-        <v>2.97625327110291</v>
+        <v>2.97625279426575</v>
       </c>
       <c r="H410" t="n">
         <v>2148</v>
@@ -12346,7 +12346,7 @@
         <v>3.56580805778503</v>
       </c>
       <c r="G413" t="n">
-        <v>2.94974517822266</v>
+        <v>2.94974493980408</v>
       </c>
       <c r="H413" t="n">
         <v>449</v>
@@ -12433,7 +12433,7 @@
         <v>3.59607195854187</v>
       </c>
       <c r="G416" t="n">
-        <v>2.97478032112122</v>
+        <v>2.97478079795837</v>
       </c>
       <c r="H416" t="n">
         <v>168</v>
@@ -12549,7 +12549,7 @@
         <v>3.57826900482178</v>
       </c>
       <c r="G420" t="n">
-        <v>2.96005320549011</v>
+        <v>2.96005344390869</v>
       </c>
       <c r="H420" t="n">
         <v>11998</v>
@@ -12607,7 +12607,7 @@
         <v>3.61209392547607</v>
       </c>
       <c r="G422" t="n">
-        <v>2.98803424835205</v>
+        <v>2.98803400993347</v>
       </c>
       <c r="H422" t="n">
         <v>991</v>
@@ -12636,7 +12636,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G423" t="n">
-        <v>2.98950695991516</v>
+        <v>2.98950672149658</v>
       </c>
       <c r="H423" t="n">
         <v>1460</v>
@@ -12665,7 +12665,7 @@
         <v>3.57292890548706</v>
       </c>
       <c r="G424" t="n">
-        <v>2.95563578605652</v>
+        <v>2.95563554763794</v>
       </c>
       <c r="H424" t="n">
         <v>3529</v>
@@ -12694,7 +12694,7 @@
         <v>3.51418089866638</v>
       </c>
       <c r="G425" t="n">
-        <v>2.90703749656677</v>
+        <v>2.90703773498535</v>
       </c>
       <c r="H425" t="n">
         <v>900</v>
@@ -12781,7 +12781,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G428" t="n">
-        <v>2.90114736557007</v>
+        <v>2.90114712715149</v>
       </c>
       <c r="H428" t="n">
         <v>1147</v>
@@ -12810,7 +12810,7 @@
         <v>3.50706005096436</v>
       </c>
       <c r="G429" t="n">
-        <v>2.90114736557007</v>
+        <v>2.90114712715149</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>3.49281811714172</v>
       </c>
       <c r="G433" t="n">
-        <v>2.88936567306519</v>
+        <v>2.88936543464661</v>
       </c>
       <c r="H433" t="n">
         <v>2375</v>
@@ -12955,7 +12955,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G434" t="n">
-        <v>2.84224057197571</v>
+        <v>2.84224104881287</v>
       </c>
       <c r="H434" t="n">
         <v>5513</v>
@@ -12984,7 +12984,7 @@
         <v>3.4394109249115</v>
       </c>
       <c r="G435" t="n">
-        <v>2.84518575668335</v>
+        <v>2.84518527984619</v>
       </c>
       <c r="H435" t="n">
         <v>1937</v>
@@ -13071,7 +13071,7 @@
         <v>3.52486205101013</v>
       </c>
       <c r="G438" t="n">
-        <v>2.91587328910828</v>
+        <v>2.91587352752686</v>
       </c>
       <c r="H438" t="n">
         <v>1685</v>
@@ -13100,7 +13100,7 @@
         <v>3.51418089866638</v>
       </c>
       <c r="G439" t="n">
-        <v>2.90703749656677</v>
+        <v>2.90703773498535</v>
       </c>
       <c r="H439" t="n">
         <v>1659</v>
@@ -13129,7 +13129,7 @@
         <v>3.51418089866638</v>
       </c>
       <c r="G440" t="n">
-        <v>2.90703749656677</v>
+        <v>2.90703773498535</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>3.41092705726624</v>
       </c>
       <c r="G441" t="n">
-        <v>2.82162284851074</v>
+        <v>2.82162308692932</v>
       </c>
       <c r="H441" t="n">
         <v>21711</v>
@@ -13187,7 +13187,7 @@
         <v>3.43407011032104</v>
       </c>
       <c r="G442" t="n">
-        <v>2.84076762199402</v>
+        <v>2.84076738357544</v>
       </c>
       <c r="H442" t="n">
         <v>1933</v>
@@ -13216,7 +13216,7 @@
         <v>3.43763089179993</v>
       </c>
       <c r="G443" t="n">
-        <v>2.84371328353882</v>
+        <v>2.84371304512024</v>
       </c>
       <c r="H443" t="n">
         <v>3393</v>
@@ -13245,7 +13245,7 @@
         <v>3.43763089179993</v>
       </c>
       <c r="G444" t="n">
-        <v>2.84371328353882</v>
+        <v>2.84371304512024</v>
       </c>
       <c r="H444" t="n">
         <v>56</v>
@@ -13303,7 +13303,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G446" t="n">
-        <v>2.79658770561218</v>
+        <v>2.7965874671936</v>
       </c>
       <c r="H446" t="n">
         <v>1179</v>
@@ -13332,7 +13332,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G447" t="n">
-        <v>2.79658770561218</v>
+        <v>2.7965874671936</v>
       </c>
       <c r="H447" t="n">
         <v>1972</v>
@@ -13361,7 +13361,7 @@
         <v>3.33971810340881</v>
       </c>
       <c r="G448" t="n">
-        <v>2.76271653175354</v>
+        <v>2.76271677017212</v>
       </c>
       <c r="H448" t="n">
         <v>1290</v>
@@ -13390,7 +13390,7 @@
         <v>3.33615708351135</v>
       </c>
       <c r="G449" t="n">
-        <v>2.75977087020874</v>
+        <v>2.75977110862732</v>
       </c>
       <c r="H449" t="n">
         <v>863</v>
@@ -13419,7 +13419,7 @@
         <v>3.24714589118958</v>
       </c>
       <c r="G450" t="n">
-        <v>2.68613815307617</v>
+        <v>2.68613839149475</v>
       </c>
       <c r="H450" t="n">
         <v>4906</v>
@@ -13535,7 +13535,7 @@
         <v>3.38066291809082</v>
       </c>
       <c r="G454" t="n">
-        <v>2.79658770561218</v>
+        <v>2.7965874671936</v>
       </c>
       <c r="H454" t="n">
         <v>2146</v>
@@ -13564,7 +13564,7 @@
         <v>3.32903695106506</v>
       </c>
       <c r="G455" t="n">
-        <v>2.75388097763062</v>
+        <v>2.75388121604919</v>
       </c>
       <c r="H455" t="n">
         <v>6311</v>
@@ -13593,7 +13593,7 @@
         <v>3.27919006347656</v>
       </c>
       <c r="G456" t="n">
-        <v>2.71264600753784</v>
+        <v>2.71264576911926</v>
       </c>
       <c r="H456" t="n">
         <v>2696</v>
@@ -13767,7 +13767,7 @@
         <v>3.24714589118958</v>
       </c>
       <c r="G462" t="n">
-        <v>2.68613815307617</v>
+        <v>2.68613839149475</v>
       </c>
       <c r="H462" t="n">
         <v>280</v>
@@ -13796,7 +13796,7 @@
         <v>3.24536609649658</v>
       </c>
       <c r="G463" t="n">
-        <v>2.68466567993164</v>
+        <v>2.68466591835022</v>
       </c>
       <c r="H463" t="n">
         <v>4256</v>
@@ -13825,7 +13825,7 @@
         <v>3.08158397674561</v>
       </c>
       <c r="G464" t="n">
-        <v>2.54918026924133</v>
+        <v>2.54918003082275</v>
       </c>
       <c r="H464" t="n">
         <v>5308</v>
@@ -13883,7 +13883,7 @@
         <v>3.20798110961914</v>
       </c>
       <c r="G466" t="n">
-        <v>2.65373992919922</v>
+        <v>2.65373969078064</v>
       </c>
       <c r="H466" t="n">
         <v>3873</v>
@@ -13941,7 +13941,7 @@
         <v>3.21510195732117</v>
       </c>
       <c r="G468" t="n">
-        <v>2.65963053703308</v>
+        <v>2.6596302986145</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
         <v>3.20798110961914</v>
       </c>
       <c r="G469" t="n">
-        <v>2.65373992919922</v>
+        <v>2.65373969078064</v>
       </c>
       <c r="H469" t="n">
         <v>19</v>
@@ -13999,7 +13999,7 @@
         <v>3.18483805656433</v>
       </c>
       <c r="G470" t="n">
-        <v>2.63459515571594</v>
+        <v>2.63459539413452</v>
       </c>
       <c r="H470" t="n">
         <v>1182</v>
@@ -14028,7 +14028,7 @@
         <v>3.22222304344177</v>
       </c>
       <c r="G471" t="n">
-        <v>2.66552114486694</v>
+        <v>2.66552138328552</v>
       </c>
       <c r="H471" t="n">
         <v>990</v>
@@ -14057,7 +14057,7 @@
         <v>3.19373893737793</v>
       </c>
       <c r="G472" t="n">
-        <v>2.64195799827576</v>
+        <v>2.64195847511292</v>
       </c>
       <c r="H472" t="n">
         <v>2530</v>
@@ -14086,7 +14086,7 @@
         <v>3.29343199729919</v>
       </c>
       <c r="G473" t="n">
-        <v>2.72442770004272</v>
+        <v>2.72442722320557</v>
       </c>
       <c r="H473" t="n">
         <v>5172</v>
@@ -14144,7 +14144,7 @@
         <v>3.15457391738892</v>
       </c>
       <c r="G475" t="n">
-        <v>2.60955953598022</v>
+        <v>2.6095597743988</v>
       </c>
       <c r="H475" t="n">
         <v>7087</v>
@@ -14173,7 +14173,7 @@
         <v>3.20442008972168</v>
       </c>
       <c r="G476" t="n">
-        <v>2.65079402923584</v>
+        <v>2.65079426765442</v>
       </c>
       <c r="H476" t="n">
         <v>393</v>
@@ -14202,7 +14202,7 @@
         <v>3.18483805656433</v>
       </c>
       <c r="G477" t="n">
-        <v>2.63459515571594</v>
+        <v>2.63459539413452</v>
       </c>
       <c r="H477" t="n">
         <v>839</v>
@@ -14231,7 +14231,7 @@
         <v>3.20442008972168</v>
       </c>
       <c r="G478" t="n">
-        <v>2.65079402923584</v>
+        <v>2.65079426765442</v>
       </c>
       <c r="H478" t="n">
         <v>29</v>
@@ -14318,7 +14318,7 @@
         <v>3.15101289749146</v>
       </c>
       <c r="G481" t="n">
-        <v>2.606614112854</v>
+        <v>2.60661387443542</v>
       </c>
       <c r="H481" t="n">
         <v>1291</v>
@@ -14347,7 +14347,7 @@
         <v>3.04419898986816</v>
       </c>
       <c r="G482" t="n">
-        <v>2.51825428009033</v>
+        <v>2.51825451850891</v>
       </c>
       <c r="H482" t="n">
         <v>589</v>
@@ -14376,7 +14376,7 @@
         <v>3.02105593681335</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49910974502563</v>
+        <v>2.49910950660706</v>
       </c>
       <c r="H483" t="n">
         <v>342</v>
@@ -14405,7 +14405,7 @@
         <v>3.02105593681335</v>
       </c>
       <c r="G484" t="n">
-        <v>2.49910974502563</v>
+        <v>2.49910950660706</v>
       </c>
       <c r="H484" t="n">
         <v>151</v>
@@ -14463,7 +14463,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G486" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H486" t="n">
         <v>84</v>
@@ -14492,7 +14492,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H487" t="n">
         <v>246</v>
@@ -14521,7 +14521,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G488" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H488" t="n">
         <v>786</v>
@@ -14550,7 +14550,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G489" t="n">
-        <v>2.35626125335693</v>
+        <v>2.35626101493835</v>
       </c>
       <c r="H489" t="n">
         <v>1630</v>
@@ -14608,7 +14608,7 @@
         <v>3.02639698982239</v>
       </c>
       <c r="G491" t="n">
-        <v>2.50352764129639</v>
+        <v>2.50352787971497</v>
       </c>
       <c r="H491" t="n">
         <v>3010</v>
@@ -14637,7 +14637,7 @@
         <v>3.02639698982239</v>
       </c>
       <c r="G492" t="n">
-        <v>2.50352764129639</v>
+        <v>2.50352787971497</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G498" t="n">
-        <v>2.35626125335693</v>
+        <v>2.35626101493835</v>
       </c>
       <c r="H498" t="n">
         <v>56</v>
@@ -14840,7 +14840,7 @@
         <v>2.79496598243713</v>
       </c>
       <c r="G499" t="n">
-        <v>2.31208086013794</v>
+        <v>2.31208109855652</v>
       </c>
       <c r="H499" t="n">
         <v>1177</v>
@@ -14869,7 +14869,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G500" t="n">
-        <v>2.35626125335693</v>
+        <v>2.35626101493835</v>
       </c>
       <c r="H500" t="n">
         <v>449</v>
@@ -14898,7 +14898,7 @@
         <v>2.95518708229065</v>
       </c>
       <c r="G501" t="n">
-        <v>2.44462060928345</v>
+        <v>2.44462084770203</v>
       </c>
       <c r="H501" t="n">
         <v>1797</v>
@@ -14956,7 +14956,7 @@
         <v>2.98011088371277</v>
       </c>
       <c r="G503" t="n">
-        <v>2.46523833274841</v>
+        <v>2.46523880958557</v>
       </c>
       <c r="H503" t="n">
         <v>1171</v>
@@ -14985,7 +14985,7 @@
         <v>2.98011088371277</v>
       </c>
       <c r="G504" t="n">
-        <v>2.46523833274841</v>
+        <v>2.46523880958557</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>2.39896845817566</v>
+        <v>2.39896869659424</v>
       </c>
       <c r="H506" t="n">
         <v>1522</v>
@@ -15101,7 +15101,7 @@
         <v>2.85905504226685</v>
       </c>
       <c r="G508" t="n">
-        <v>2.36509776115417</v>
+        <v>2.3650975227356</v>
       </c>
       <c r="H508" t="n">
         <v>561</v>
@@ -15130,7 +15130,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G509" t="n">
-        <v>2.35626125335693</v>
+        <v>2.35626101493835</v>
       </c>
       <c r="H509" t="n">
         <v>5732</v>
@@ -15188,7 +15188,7 @@
         <v>3.25</v>
       </c>
       <c r="G511" t="n">
-        <v>2.68849921226501</v>
+        <v>2.68849897384644</v>
       </c>
       <c r="H511" t="n">
         <v>28967</v>
@@ -15246,7 +15246,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G513" t="n">
-        <v>2.85394549369812</v>
+        <v>2.85394525527954</v>
       </c>
       <c r="H513" t="n">
         <v>64973</v>
@@ -15275,7 +15275,7 @@
         <v>3.33750009536743</v>
       </c>
       <c r="G514" t="n">
-        <v>2.76088190078735</v>
+        <v>2.76088166236877</v>
       </c>
       <c r="H514" t="n">
         <v>17816</v>
@@ -15333,7 +15333,7 @@
         <v>3.25</v>
       </c>
       <c r="G516" t="n">
-        <v>2.68849921226501</v>
+        <v>2.68849897384644</v>
       </c>
       <c r="H516" t="n">
         <v>10298</v>
@@ -15391,7 +15391,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G518" t="n">
-        <v>2.64713740348816</v>
+        <v>2.64713764190674</v>
       </c>
       <c r="H518" t="n">
         <v>33959</v>
@@ -15420,7 +15420,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G519" t="n">
-        <v>2.50237226486206</v>
+        <v>2.50237250328064</v>
       </c>
       <c r="H519" t="n">
         <v>83407</v>
@@ -15478,7 +15478,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G521" t="n">
-        <v>2.33692646026611</v>
+        <v>2.33692622184753</v>
       </c>
       <c r="H521" t="n">
         <v>36956</v>
@@ -15536,7 +15536,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.29556488990784</v>
+        <v>2.29556465148926</v>
       </c>
       <c r="H523" t="n">
         <v>6084</v>
@@ -15565,7 +15565,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.19216108322144</v>
+        <v>2.19216084480286</v>
       </c>
       <c r="H524" t="n">
         <v>25151</v>
@@ -15594,7 +15594,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G525" t="n">
-        <v>2.13011860847473</v>
+        <v>2.13011837005615</v>
       </c>
       <c r="H525" t="n">
         <v>29040</v>
@@ -15652,7 +15652,7 @@
         <v>2.5625</v>
       </c>
       <c r="G527" t="n">
-        <v>2.1197783946991</v>
+        <v>2.11977815628052</v>
       </c>
       <c r="H527" t="n">
         <v>17500</v>
@@ -15739,7 +15739,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.96053612232208</v>
+        <v>1.96053636074066</v>
       </c>
       <c r="H530" t="n">
         <v>29220</v>
@@ -15768,7 +15768,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G531" t="n">
-        <v>1.86540484428406</v>
+        <v>1.86540472507477</v>
       </c>
       <c r="H531" t="n">
         <v>103365</v>
@@ -15826,7 +15826,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G533" t="n">
-        <v>1.84886002540588</v>
+        <v>1.84886014461517</v>
       </c>
       <c r="H533" t="n">
         <v>31186</v>
@@ -15855,7 +15855,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84058773517609</v>
+        <v>1.84058809280396</v>
       </c>
       <c r="H534" t="n">
         <v>86811</v>
@@ -15884,7 +15884,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G535" t="n">
-        <v>1.8157707452774</v>
+        <v>1.81577086448669</v>
       </c>
       <c r="H535" t="n">
         <v>32861</v>
@@ -15913,7 +15913,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G536" t="n">
-        <v>1.81990718841553</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H536" t="n">
         <v>22954</v>
@@ -15971,7 +15971,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>1.77854573726654</v>
+        <v>1.77854561805725</v>
       </c>
       <c r="H538" t="n">
         <v>14766</v>
@@ -16000,7 +16000,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G539" t="n">
-        <v>1.74959242343903</v>
+        <v>1.74959254264832</v>
       </c>
       <c r="H539" t="n">
         <v>9531</v>
@@ -16029,7 +16029,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>1.72063934803009</v>
+        <v>1.7206392288208</v>
       </c>
       <c r="H540" t="n">
         <v>15673</v>
@@ -16058,7 +16058,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G541" t="n">
-        <v>1.6792778968811</v>
+        <v>1.67927801609039</v>
       </c>
       <c r="H541" t="n">
         <v>22049</v>
@@ -16087,7 +16087,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G542" t="n">
-        <v>1.67514193058014</v>
+        <v>1.67514181137085</v>
       </c>
       <c r="H542" t="n">
         <v>46153</v>
@@ -16116,7 +16116,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G543" t="n">
-        <v>1.64618873596191</v>
+        <v>1.64618861675262</v>
       </c>
       <c r="H543" t="n">
         <v>14522</v>
@@ -16145,7 +16145,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G544" t="n">
-        <v>1.67514193058014</v>
+        <v>1.67514181137085</v>
       </c>
       <c r="H544" t="n">
         <v>25851</v>
@@ -16174,7 +16174,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G545" t="n">
-        <v>1.8157707452774</v>
+        <v>1.81577086448669</v>
       </c>
       <c r="H545" t="n">
         <v>124025</v>
@@ -16203,7 +16203,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G546" t="n">
-        <v>1.81990718841553</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H546" t="n">
         <v>72365</v>
@@ -16232,7 +16232,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G547" t="n">
-        <v>1.77440929412842</v>
+        <v>1.77440941333771</v>
       </c>
       <c r="H547" t="n">
         <v>15793</v>
@@ -16319,7 +16319,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>1.80336260795593</v>
+        <v>1.80336248874664</v>
       </c>
       <c r="H550" t="n">
         <v>51521</v>
@@ -16348,7 +16348,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G551" t="n">
-        <v>1.77440929412842</v>
+        <v>1.77440941333771</v>
       </c>
       <c r="H551" t="n">
         <v>14085</v>
@@ -16406,7 +16406,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G553" t="n">
-        <v>1.76613712310791</v>
+        <v>1.76613700389862</v>
       </c>
       <c r="H553" t="n">
         <v>14755</v>
@@ -16435,7 +16435,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G554" t="n">
-        <v>1.73304784297943</v>
+        <v>1.73304796218872</v>
       </c>
       <c r="H554" t="n">
         <v>14752</v>
@@ -16464,7 +16464,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G555" t="n">
-        <v>1.71650338172913</v>
+        <v>1.71650350093842</v>
       </c>
       <c r="H555" t="n">
         <v>11105</v>
@@ -16493,7 +16493,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>1.77440929412842</v>
+        <v>1.77440941333771</v>
       </c>
       <c r="H556" t="n">
         <v>3545</v>
@@ -16522,7 +16522,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>1.77854573726654</v>
+        <v>1.77854561805725</v>
       </c>
       <c r="H557" t="n">
         <v>10553</v>
@@ -16551,7 +16551,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>1.77854573726654</v>
+        <v>1.77854561805725</v>
       </c>
       <c r="H558" t="n">
         <v>4069</v>
@@ -16580,7 +16580,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G559" t="n">
-        <v>1.80336260795593</v>
+        <v>1.80336248874664</v>
       </c>
       <c r="H559" t="n">
         <v>10623</v>
@@ -16609,7 +16609,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G560" t="n">
-        <v>1.79509007930756</v>
+        <v>1.79509019851685</v>
       </c>
       <c r="H560" t="n">
         <v>2240</v>
@@ -16638,7 +16638,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G561" t="n">
-        <v>1.81990718841553</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H561" t="n">
         <v>17464</v>
@@ -16696,7 +16696,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G563" t="n">
-        <v>1.75372850894928</v>
+        <v>1.75372862815857</v>
       </c>
       <c r="H563" t="n">
         <v>4008</v>
@@ -16725,7 +16725,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G564" t="n">
-        <v>1.76613712310791</v>
+        <v>1.76613700389862</v>
       </c>
       <c r="H564" t="n">
         <v>6751</v>
@@ -16754,7 +16754,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G565" t="n">
-        <v>1.77440929412842</v>
+        <v>1.77440941333771</v>
       </c>
       <c r="H565" t="n">
         <v>4955</v>
@@ -16928,7 +16928,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G571" t="n">
-        <v>1.79509007930756</v>
+        <v>1.79509019851685</v>
       </c>
       <c r="H571" t="n">
         <v>4292</v>
@@ -16986,7 +16986,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G573" t="n">
-        <v>1.73304784297943</v>
+        <v>1.73304796218872</v>
       </c>
       <c r="H573" t="n">
         <v>2137</v>
@@ -17015,7 +17015,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G574" t="n">
-        <v>1.77440929412842</v>
+        <v>1.77440941333771</v>
       </c>
       <c r="H574" t="n">
         <v>3299</v>
@@ -17044,7 +17044,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>1.79922640323639</v>
+        <v>1.79922616481781</v>
       </c>
       <c r="H575" t="n">
         <v>4859</v>
@@ -17073,7 +17073,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G576" t="n">
-        <v>1.77854573726654</v>
+        <v>1.77854561805725</v>
       </c>
       <c r="H576" t="n">
         <v>6528</v>
@@ -17102,7 +17102,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>1.8943578004837</v>
+        <v>1.89435768127441</v>
       </c>
       <c r="H577" t="n">
         <v>252675</v>
@@ -17131,7 +17131,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G578" t="n">
-        <v>1.84886002540588</v>
+        <v>1.84886014461517</v>
       </c>
       <c r="H578" t="n">
         <v>35013</v>
@@ -17160,7 +17160,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G579" t="n">
-        <v>1.91917490959167</v>
+        <v>1.91917479038239</v>
       </c>
       <c r="H579" t="n">
         <v>121147</v>
@@ -17189,7 +17189,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G580" t="n">
-        <v>1.89022195339203</v>
+        <v>1.89022183418274</v>
       </c>
       <c r="H580" t="n">
         <v>60138</v>
@@ -17218,7 +17218,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G581" t="n">
-        <v>2.00189781188965</v>
+        <v>2.00189805030823</v>
       </c>
       <c r="H581" t="n">
         <v>169721</v>
@@ -17276,7 +17276,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>1.93158328533173</v>
+        <v>1.93158316612244</v>
       </c>
       <c r="H583" t="n">
         <v>72085</v>
@@ -17334,7 +17334,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>1.99362564086914</v>
+        <v>1.99362552165985</v>
       </c>
       <c r="H585" t="n">
         <v>32719</v>
@@ -17363,7 +17363,7 @@
         <v>2.73749995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.2645435333252</v>
+        <v>2.26454329490662</v>
       </c>
       <c r="H586" t="n">
         <v>241077</v>
@@ -17392,7 +17392,7 @@
         <v>2.53749990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>2.09909725189209</v>
+        <v>2.09909749031067</v>
       </c>
       <c r="H587" t="n">
         <v>383922</v>
@@ -17450,7 +17450,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G589" t="n">
-        <v>2.34726667404175</v>
+        <v>2.34726643562317</v>
       </c>
       <c r="H589" t="n">
         <v>262760</v>
@@ -17479,7 +17479,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>2.34726667404175</v>
+        <v>2.34726643562317</v>
       </c>
       <c r="H590" t="n">
         <v>113565</v>
@@ -17595,7 +17595,7 @@
         <v>2.6875</v>
       </c>
       <c r="G594" t="n">
-        <v>2.2231822013855</v>
+        <v>2.22318196296692</v>
       </c>
       <c r="H594" t="n">
         <v>48626</v>
@@ -17624,7 +17624,7 @@
         <v>2.6875</v>
       </c>
       <c r="G595" t="n">
-        <v>2.2231822013855</v>
+        <v>2.22318196296692</v>
       </c>
       <c r="H595" t="n">
         <v>129240</v>
@@ -17711,7 +17711,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>2.19216108322144</v>
+        <v>2.19216084480286</v>
       </c>
       <c r="H598" t="n">
         <v>52517</v>
@@ -17798,7 +17798,7 @@
         <v>2.6875</v>
       </c>
       <c r="G601" t="n">
-        <v>2.2231822013855</v>
+        <v>2.22318196296692</v>
       </c>
       <c r="H601" t="n">
         <v>13674</v>
@@ -17827,7 +17827,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G602" t="n">
-        <v>2.19216108322144</v>
+        <v>2.19216084480286</v>
       </c>
       <c r="H602" t="n">
         <v>23329</v>
@@ -17885,7 +17885,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G604" t="n">
-        <v>2.15079927444458</v>
+        <v>2.150799036026</v>
       </c>
       <c r="H604" t="n">
         <v>20536</v>
@@ -17943,7 +17943,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G606" t="n">
-        <v>2.1094377040863</v>
+        <v>2.10943746566772</v>
       </c>
       <c r="H606" t="n">
         <v>57475</v>
@@ -17972,7 +17972,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G607" t="n">
-        <v>2.03498697280884</v>
+        <v>2.03498673439026</v>
       </c>
       <c r="H607" t="n">
         <v>10511</v>
@@ -18001,7 +18001,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>1.98535323143005</v>
+        <v>1.98535335063934</v>
       </c>
       <c r="H608" t="n">
         <v>20331</v>
@@ -18030,7 +18030,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>2.00189781188965</v>
+        <v>2.00189805030823</v>
       </c>
       <c r="H609" t="n">
         <v>12738</v>
@@ -18117,7 +18117,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>1.92744708061218</v>
+        <v>1.92744696140289</v>
       </c>
       <c r="H612" t="n">
         <v>8870</v>
@@ -18146,7 +18146,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G613" t="n">
-        <v>1.8943578004837</v>
+        <v>1.89435768127441</v>
       </c>
       <c r="H613" t="n">
         <v>19551</v>
@@ -18175,7 +18175,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G614" t="n">
-        <v>1.86540484428406</v>
+        <v>1.86540472507477</v>
       </c>
       <c r="H614" t="n">
         <v>24381</v>
@@ -18233,7 +18233,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G616" t="n">
-        <v>1.91917490959167</v>
+        <v>1.91917479038239</v>
       </c>
       <c r="H616" t="n">
         <v>15467</v>
@@ -18262,7 +18262,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G617" t="n">
-        <v>2.00189781188965</v>
+        <v>2.00189805030823</v>
       </c>
       <c r="H617" t="n">
         <v>21737</v>
@@ -18291,7 +18291,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G618" t="n">
-        <v>1.96880877017975</v>
+        <v>1.96880865097046</v>
       </c>
       <c r="H618" t="n">
         <v>5295</v>
@@ -18320,7 +18320,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G619" t="n">
-        <v>1.89022195339203</v>
+        <v>1.89022183418274</v>
       </c>
       <c r="H619" t="n">
         <v>600</v>
@@ -18349,7 +18349,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G620" t="n">
-        <v>1.9812171459198</v>
+        <v>1.98121738433838</v>
       </c>
       <c r="H620" t="n">
         <v>4625</v>
@@ -18407,7 +18407,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G622" t="n">
-        <v>1.86540484428406</v>
+        <v>1.86540472507477</v>
       </c>
       <c r="H622" t="n">
         <v>19869</v>
@@ -18436,7 +18436,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>1.93158328533173</v>
+        <v>1.93158316612244</v>
       </c>
       <c r="H623" t="n">
         <v>16422</v>
@@ -18465,7 +18465,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G624" t="n">
-        <v>1.91917490959167</v>
+        <v>1.91917479038239</v>
       </c>
       <c r="H624" t="n">
         <v>3752</v>
@@ -18494,7 +18494,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G625" t="n">
-        <v>1.93985569477081</v>
+        <v>1.93985557556152</v>
       </c>
       <c r="H625" t="n">
         <v>4699</v>
@@ -18523,7 +18523,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G626" t="n">
-        <v>1.92331099510193</v>
+        <v>1.92331111431122</v>
       </c>
       <c r="H626" t="n">
         <v>11025</v>
@@ -18552,7 +18552,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>1.88608551025391</v>
+        <v>1.88608527183533</v>
       </c>
       <c r="H627" t="n">
         <v>13640</v>
@@ -18581,7 +18581,7 @@
         <v>2.25</v>
       </c>
       <c r="G628" t="n">
-        <v>1.86126863956451</v>
+        <v>1.86126887798309</v>
       </c>
       <c r="H628" t="n">
         <v>1406</v>
@@ -18610,7 +18610,7 @@
         <v>2.25</v>
       </c>
       <c r="G629" t="n">
-        <v>1.86126863956451</v>
+        <v>1.86126887798309</v>
       </c>
       <c r="H629" t="n">
         <v>1064</v>
@@ -18639,7 +18639,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>1.89849424362183</v>
+        <v>1.89849412441254</v>
       </c>
       <c r="H630" t="n">
         <v>8296</v>
@@ -18668,7 +18668,7 @@
         <v>2.25</v>
       </c>
       <c r="G631" t="n">
-        <v>1.86126863956451</v>
+        <v>1.86126887798309</v>
       </c>
       <c r="H631" t="n">
         <v>760</v>
@@ -18697,7 +18697,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G632" t="n">
-        <v>1.89849424362183</v>
+        <v>1.89849412441254</v>
       </c>
       <c r="H632" t="n">
         <v>1989</v>
@@ -18726,7 +18726,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>1.8943578004837</v>
+        <v>1.89435768127441</v>
       </c>
       <c r="H633" t="n">
         <v>1081</v>
@@ -18842,7 +18842,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G637" t="n">
-        <v>1.87781345844269</v>
+        <v>1.87781322002411</v>
       </c>
       <c r="H637" t="n">
         <v>5289</v>
@@ -18871,7 +18871,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G638" t="n">
-        <v>1.84886002540588</v>
+        <v>1.84886014461517</v>
       </c>
       <c r="H638" t="n">
         <v>7040</v>
@@ -18987,7 +18987,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G642" t="n">
-        <v>1.81163477897644</v>
+        <v>1.81163501739502</v>
       </c>
       <c r="H642" t="n">
         <v>11225</v>
@@ -19016,7 +19016,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G643" t="n">
-        <v>1.79922640323639</v>
+        <v>1.79922616481781</v>
       </c>
       <c r="H643" t="n">
         <v>860</v>
@@ -19045,7 +19045,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G644" t="n">
-        <v>1.81163477897644</v>
+        <v>1.81163501739502</v>
       </c>
       <c r="H644" t="n">
         <v>10559</v>
@@ -19103,7 +19103,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>1.77440929412842</v>
+        <v>1.77440941333771</v>
       </c>
       <c r="H646" t="n">
         <v>13135</v>
@@ -19132,7 +19132,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G647" t="n">
-        <v>1.80749845504761</v>
+        <v>1.80749869346619</v>
       </c>
       <c r="H647" t="n">
         <v>10121</v>
@@ -19190,7 +19190,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.75372850894928</v>
+        <v>1.75372862815857</v>
       </c>
       <c r="H649" t="n">
         <v>426</v>
@@ -19248,7 +19248,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G651" t="n">
-        <v>1.78268182277679</v>
+        <v>1.7826817035675</v>
       </c>
       <c r="H651" t="n">
         <v>9355</v>
@@ -19306,7 +19306,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>1.79509007930756</v>
+        <v>1.79509019851685</v>
       </c>
       <c r="H653" t="n">
         <v>586</v>
@@ -19335,7 +19335,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>1.81990718841553</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H654" t="n">
         <v>16533</v>
@@ -19393,7 +19393,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G656" t="n">
-        <v>1.80998051166534</v>
+        <v>1.80998027324677</v>
       </c>
       <c r="H656" t="n">
         <v>3706</v>
@@ -19422,7 +19422,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G657" t="n">
-        <v>1.85134196281433</v>
+        <v>1.85134160518646</v>
       </c>
       <c r="H657" t="n">
         <v>9372</v>
@@ -19480,7 +19480,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G659" t="n">
-        <v>1.81990718841553</v>
+        <v>1.81990706920624</v>
       </c>
       <c r="H659" t="n">
         <v>3423</v>
@@ -19509,7 +19509,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G660" t="n">
-        <v>1.79839909076691</v>
+        <v>1.7983992099762</v>
       </c>
       <c r="H660" t="n">
         <v>3407</v>
@@ -19538,7 +19538,7 @@
         <v>2.17549991607666</v>
       </c>
       <c r="G661" t="n">
-        <v>1.79963994026184</v>
+        <v>1.79963982105255</v>
       </c>
       <c r="H661" t="n">
         <v>808</v>
@@ -19567,7 +19567,7 @@
         <v>2.20650005340576</v>
       </c>
       <c r="G662" t="n">
-        <v>1.82528424263</v>
+        <v>1.82528412342072</v>
       </c>
       <c r="H662" t="n">
         <v>405</v>
@@ -19596,7 +19596,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>1.79922640323639</v>
+        <v>1.79922616481781</v>
       </c>
       <c r="H663" t="n">
         <v>2053</v>
@@ -19683,7 +19683,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G666" t="n">
-        <v>1.83976078033447</v>
+        <v>1.83976066112518</v>
       </c>
       <c r="H666" t="n">
         <v>28805</v>
@@ -19770,7 +19770,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G669" t="n">
-        <v>1.83231544494629</v>
+        <v>1.83231556415558</v>
       </c>
       <c r="H669" t="n">
         <v>57</v>
@@ -19799,7 +19799,7 @@
         <v>2.18700003623962</v>
       </c>
       <c r="G670" t="n">
-        <v>1.80915307998657</v>
+        <v>1.80915331840515</v>
       </c>
       <c r="H670" t="n">
         <v>1019</v>
@@ -19857,7 +19857,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G672" t="n">
-        <v>1.75372850894928</v>
+        <v>1.75372862815857</v>
       </c>
       <c r="H672" t="n">
         <v>1260</v>
@@ -19886,7 +19886,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G673" t="n">
-        <v>1.76200115680695</v>
+        <v>1.76200091838837</v>
       </c>
       <c r="H673" t="n">
         <v>1302</v>
@@ -19944,7 +19944,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>1.69168651103973</v>
+        <v>1.69168639183044</v>
       </c>
       <c r="H675" t="n">
         <v>10262</v>
@@ -19973,7 +19973,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G676" t="n">
-        <v>1.68920469284058</v>
+        <v>1.68920481204987</v>
       </c>
       <c r="H676" t="n">
         <v>12451</v>
@@ -20002,7 +20002,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G677" t="n">
-        <v>1.57008337974548</v>
+        <v>1.57008349895477</v>
       </c>
       <c r="H677" t="n">
         <v>17496</v>
@@ -20060,7 +20060,7 @@
         <v>1.75479996204376</v>
       </c>
       <c r="G679" t="n">
-        <v>1.45162403583527</v>
+        <v>1.45162415504456</v>
       </c>
       <c r="H679" t="n">
         <v>77393</v>
@@ -20089,7 +20089,7 @@
         <v>1.79139995574951</v>
       </c>
       <c r="G680" t="n">
-        <v>1.48190069198608</v>
+        <v>1.48190057277679</v>
       </c>
       <c r="H680" t="n">
         <v>24993</v>
@@ -20205,7 +20205,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G684" t="n">
-        <v>1.47329759597778</v>
+        <v>1.47329747676849</v>
       </c>
       <c r="H684" t="n">
         <v>524</v>
@@ -20321,7 +20321,7 @@
         <v>1.74440002441406</v>
       </c>
       <c r="G688" t="n">
-        <v>1.44302093982697</v>
+        <v>1.44302070140839</v>
       </c>
       <c r="H688" t="n">
         <v>2706</v>
@@ -20350,7 +20350,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>1.4724702835083</v>
+        <v>1.47247016429901</v>
       </c>
       <c r="H689" t="n">
         <v>525</v>
@@ -20495,7 +20495,7 @@
         <v>1.7305999994278</v>
       </c>
       <c r="G694" t="n">
-        <v>1.43160510063171</v>
+        <v>1.43160498142242</v>
       </c>
       <c r="H694" t="n">
         <v>5402</v>
@@ -20524,7 +20524,7 @@
         <v>1.73539996147156</v>
       </c>
       <c r="G695" t="n">
-        <v>1.43557584285736</v>
+        <v>1.43557572364807</v>
       </c>
       <c r="H695" t="n">
         <v>1802</v>
@@ -20669,7 +20669,7 @@
         <v>1.74479997158051</v>
       </c>
       <c r="G700" t="n">
-        <v>1.44335174560547</v>
+        <v>1.44335186481476</v>
       </c>
       <c r="H700" t="n">
         <v>2020</v>
@@ -20727,7 +20727,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G702" t="n">
-        <v>1.43524479866028</v>
+        <v>1.43524491786957</v>
       </c>
       <c r="H702" t="n">
         <v>4220</v>
@@ -20756,7 +20756,7 @@
         <v>1.6793999671936</v>
       </c>
       <c r="G703" t="n">
-        <v>1.38925099372864</v>
+        <v>1.38925087451935</v>
       </c>
       <c r="H703" t="n">
         <v>10191</v>
@@ -20785,7 +20785,7 @@
         <v>1.67960000038147</v>
       </c>
       <c r="G704" t="n">
-        <v>1.38941621780396</v>
+        <v>1.38941633701324</v>
       </c>
       <c r="H704" t="n">
         <v>2454</v>
@@ -20901,7 +20901,7 @@
         <v>1.6793999671936</v>
       </c>
       <c r="G708" t="n">
-        <v>1.38925099372864</v>
+        <v>1.38925087451935</v>
       </c>
       <c r="H708" t="n">
         <v>4417</v>
@@ -20959,7 +20959,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G710" t="n">
-        <v>1.35665798187256</v>
+        <v>1.35665810108185</v>
       </c>
       <c r="H710" t="n">
         <v>901</v>
@@ -20988,7 +20988,7 @@
         <v>1.66460001468658</v>
       </c>
       <c r="G711" t="n">
-        <v>1.3770078420639</v>
+        <v>1.37700796127319</v>
       </c>
       <c r="H711" t="n">
         <v>40</v>
@@ -21017,7 +21017,7 @@
         <v>1.72019994258881</v>
       </c>
       <c r="G712" t="n">
-        <v>1.42300200462341</v>
+        <v>1.42300188541412</v>
       </c>
       <c r="H712" t="n">
         <v>4691</v>
@@ -21046,7 +21046,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G713" t="n">
-        <v>1.45592558383942</v>
+        <v>1.45592570304871</v>
       </c>
       <c r="H713" t="n">
         <v>6546</v>
@@ -21104,7 +21104,7 @@
         <v>1.78960001468658</v>
       </c>
       <c r="G715" t="n">
-        <v>1.48041164875031</v>
+        <v>1.48041176795959</v>
       </c>
       <c r="H715" t="n">
         <v>5445</v>
@@ -21133,7 +21133,7 @@
         <v>1.78779995441437</v>
       </c>
       <c r="G716" t="n">
-        <v>1.47892260551453</v>
+        <v>1.47892272472382</v>
       </c>
       <c r="H716" t="n">
         <v>2084</v>
@@ -21220,7 +21220,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G719" t="n">
-        <v>1.43028151988983</v>
+        <v>1.43028140068054</v>
       </c>
       <c r="H719" t="n">
         <v>1706</v>
@@ -21249,7 +21249,7 @@
         <v>1.73539996147156</v>
       </c>
       <c r="G720" t="n">
-        <v>1.43557584285736</v>
+        <v>1.43557572364807</v>
       </c>
       <c r="H720" t="n">
         <v>21468</v>
@@ -21365,7 +21365,7 @@
         <v>1.81120002269745</v>
       </c>
       <c r="G724" t="n">
-        <v>1.49828004837036</v>
+        <v>1.49827992916107</v>
       </c>
       <c r="H724" t="n">
         <v>3000</v>
@@ -21394,7 +21394,7 @@
         <v>1.80120003223419</v>
       </c>
       <c r="G725" t="n">
-        <v>1.49000751972198</v>
+        <v>1.49000775814056</v>
       </c>
       <c r="H725" t="n">
         <v>100</v>
@@ -21423,7 +21423,7 @@
         <v>1.81980001926422</v>
       </c>
       <c r="G726" t="n">
-        <v>1.50539422035217</v>
+        <v>1.50539410114288</v>
       </c>
       <c r="H726" t="n">
         <v>2000</v>
@@ -21510,7 +21510,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G729" t="n">
-        <v>1.51796805858612</v>
+        <v>1.51796793937683</v>
       </c>
       <c r="H729" t="n">
         <v>330</v>
@@ -21539,7 +21539,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G730" t="n">
-        <v>1.48653328418732</v>
+        <v>1.48653340339661</v>
       </c>
       <c r="H730" t="n">
         <v>642</v>
@@ -21568,7 +21568,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G731" t="n">
-        <v>1.48653328418732</v>
+        <v>1.48653340339661</v>
       </c>
       <c r="H731" t="n">
         <v>339</v>
@@ -21597,7 +21597,7 @@
         <v>1.83159995079041</v>
       </c>
       <c r="G732" t="n">
-        <v>1.51515531539917</v>
+        <v>1.51515543460846</v>
       </c>
       <c r="H732" t="n">
         <v>19406</v>
@@ -21655,7 +21655,7 @@
         <v>1.7985999584198</v>
       </c>
       <c r="G734" t="n">
-        <v>1.4878568649292</v>
+        <v>1.48785674571991</v>
       </c>
       <c r="H734" t="n">
         <v>1269</v>
@@ -21684,7 +21684,7 @@
         <v>1.80120003223419</v>
       </c>
       <c r="G735" t="n">
-        <v>1.49000751972198</v>
+        <v>1.49000775814056</v>
       </c>
       <c r="H735" t="n">
         <v>80</v>
@@ -21742,7 +21742,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>1.4807425737381</v>
+        <v>1.48074245452881</v>
       </c>
       <c r="H737" t="n">
         <v>2570</v>
@@ -21771,7 +21771,7 @@
         <v>1.84179997444153</v>
       </c>
       <c r="G738" t="n">
-        <v>1.52359306812286</v>
+        <v>1.52359318733215</v>
       </c>
       <c r="H738" t="n">
         <v>1530</v>
@@ -21800,7 +21800,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G739" t="n">
-        <v>1.488849401474</v>
+        <v>1.48884952068329</v>
       </c>
       <c r="H739" t="n">
         <v>776</v>
@@ -21829,7 +21829,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G740" t="n">
-        <v>1.4641979932785</v>
+        <v>1.46419811248779</v>
       </c>
       <c r="H740" t="n">
         <v>2269</v>
@@ -21858,7 +21858,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>1.4807425737381</v>
+        <v>1.48074245452881</v>
       </c>
       <c r="H741" t="n">
         <v>2079</v>
@@ -21887,7 +21887,7 @@
         <v>1.77240002155304</v>
       </c>
       <c r="G742" t="n">
-        <v>1.46618330478668</v>
+        <v>1.46618342399597</v>
       </c>
       <c r="H742" t="n">
         <v>214</v>
@@ -21974,7 +21974,7 @@
         <v>1.78960001468658</v>
       </c>
       <c r="G745" t="n">
-        <v>1.48041164875031</v>
+        <v>1.48041176795959</v>
       </c>
       <c r="H745" t="n">
         <v>219</v>
@@ -22003,7 +22003,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G746" t="n">
-        <v>1.47329759597778</v>
+        <v>1.47329747676849</v>
       </c>
       <c r="H746" t="n">
         <v>2400</v>
@@ -22032,7 +22032,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G747" t="n">
-        <v>1.46916127204895</v>
+        <v>1.46916139125824</v>
       </c>
       <c r="H747" t="n">
         <v>2530</v>
@@ -22119,7 +22119,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G750" t="n">
-        <v>1.47329759597778</v>
+        <v>1.47329747676849</v>
       </c>
       <c r="H750" t="n">
         <v>470</v>
@@ -22148,7 +22148,7 @@
         <v>1.80120003223419</v>
       </c>
       <c r="G751" t="n">
-        <v>1.49000751972198</v>
+        <v>1.49000775814056</v>
       </c>
       <c r="H751" t="n">
         <v>10</v>
@@ -22177,7 +22177,7 @@
         <v>1.79980003833771</v>
       </c>
       <c r="G752" t="n">
-        <v>1.488849401474</v>
+        <v>1.48884952068329</v>
       </c>
       <c r="H752" t="n">
         <v>1260</v>
@@ -22206,7 +22206,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G753" t="n">
-        <v>1.47329759597778</v>
+        <v>1.47329747676849</v>
       </c>
       <c r="H753" t="n">
         <v>225</v>
@@ -22235,7 +22235,7 @@
         <v>1.78639996051788</v>
       </c>
       <c r="G754" t="n">
-        <v>1.47776460647583</v>
+        <v>1.47776448726654</v>
       </c>
       <c r="H754" t="n">
         <v>4001</v>
@@ -22264,7 +22264,7 @@
         <v>1.86979997158051</v>
       </c>
       <c r="G755" t="n">
-        <v>1.54675567150116</v>
+        <v>1.54675555229187</v>
       </c>
       <c r="H755" t="n">
         <v>6445</v>
@@ -22351,7 +22351,7 @@
         <v>1.92260003089905</v>
       </c>
       <c r="G758" t="n">
-        <v>1.6637864112854</v>
+        <v>1.66378653049469</v>
       </c>
       <c r="H758" t="n">
         <v>20</v>
@@ -22380,7 +22380,7 @@
         <v>1.93239998817444</v>
       </c>
       <c r="G759" t="n">
-        <v>1.67226719856262</v>
+        <v>1.67226731777191</v>
       </c>
       <c r="H759" t="n">
         <v>3791</v>
@@ -22438,7 +22438,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G761" t="n">
-        <v>1.61826729774475</v>
+        <v>1.61826741695404</v>
       </c>
       <c r="H761" t="n">
         <v>4580</v>
@@ -22496,7 +22496,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>1.67884409427643</v>
+        <v>1.67884433269501</v>
       </c>
       <c r="H763" t="n">
         <v>16054</v>
@@ -22525,7 +22525,7 @@
         <v>1.95819997787476</v>
       </c>
       <c r="G764" t="n">
-        <v>1.69459414482117</v>
+        <v>1.69459402561188</v>
       </c>
       <c r="H764" t="n">
         <v>5283</v>
@@ -22554,7 +22554,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>1.69615197181702</v>
+        <v>1.69615185260773</v>
       </c>
       <c r="H765" t="n">
         <v>124</v>
@@ -22699,7 +22699,7 @@
         <v>1.94760000705719</v>
       </c>
       <c r="G770" t="n">
-        <v>1.68542098999023</v>
+        <v>1.68542122840881</v>
       </c>
       <c r="H770" t="n">
         <v>930</v>
@@ -22728,7 +22728,7 @@
         <v>1.91380000114441</v>
       </c>
       <c r="G771" t="n">
-        <v>1.65617108345032</v>
+        <v>1.65617120265961</v>
       </c>
       <c r="H771" t="n">
         <v>1620</v>
@@ -22757,7 +22757,7 @@
         <v>1.92980003356934</v>
       </c>
       <c r="G772" t="n">
-        <v>1.67001724243164</v>
+        <v>1.67001736164093</v>
       </c>
       <c r="H772" t="n">
         <v>2856</v>
@@ -22786,7 +22786,7 @@
         <v>1.89979994297028</v>
       </c>
       <c r="G773" t="n">
-        <v>1.64405560493469</v>
+        <v>1.64405572414398</v>
       </c>
       <c r="H773" t="n">
         <v>482</v>
@@ -22844,7 +22844,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G775" t="n">
-        <v>1.67884409427643</v>
+        <v>1.67884433269501</v>
       </c>
       <c r="H775" t="n">
         <v>3450</v>
@@ -22902,7 +22902,7 @@
         <v>1.95819997787476</v>
       </c>
       <c r="G777" t="n">
-        <v>1.69459414482117</v>
+        <v>1.69459402561188</v>
       </c>
       <c r="H777" t="n">
         <v>500</v>
@@ -22960,7 +22960,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>1.69615197181702</v>
+        <v>1.69615185260773</v>
       </c>
       <c r="H779" t="n">
         <v>2604</v>
@@ -22989,7 +22989,7 @@
         <v>1.93680000305176</v>
       </c>
       <c r="G780" t="n">
-        <v>1.67607486248016</v>
+        <v>1.67607498168945</v>
       </c>
       <c r="H780" t="n">
         <v>216</v>
@@ -23018,7 +23018,7 @@
         <v>1.95959997177124</v>
       </c>
       <c r="G781" t="n">
-        <v>1.69580554962158</v>
+        <v>1.69580566883087</v>
       </c>
       <c r="H781" t="n">
         <v>2212</v>
@@ -23047,7 +23047,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G782" t="n">
-        <v>1.68126714229584</v>
+        <v>1.68126738071442</v>
       </c>
       <c r="H782" t="n">
         <v>2221</v>
@@ -23076,7 +23076,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G783" t="n">
-        <v>1.68126714229584</v>
+        <v>1.68126738071442</v>
       </c>
       <c r="H783" t="n">
         <v>0</v>
@@ -23105,7 +23105,7 @@
         <v>1.87839996814728</v>
       </c>
       <c r="G784" t="n">
-        <v>1.62553644180298</v>
+        <v>1.62553656101227</v>
       </c>
       <c r="H784" t="n">
         <v>2900</v>
@@ -23192,7 +23192,7 @@
         <v>1.90859997272491</v>
       </c>
       <c r="G787" t="n">
-        <v>1.65167117118835</v>
+        <v>1.65167105197906</v>
       </c>
       <c r="H787" t="n">
         <v>5503</v>
@@ -23221,7 +23221,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G788" t="n">
-        <v>1.68126714229584</v>
+        <v>1.68126738071442</v>
       </c>
       <c r="H788" t="n">
         <v>2080</v>
@@ -23250,7 +23250,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G789" t="n">
-        <v>1.66759407520294</v>
+        <v>1.66759431362152</v>
       </c>
       <c r="H789" t="n">
         <v>1896</v>
@@ -23279,7 +23279,7 @@
         <v>1.89859998226166</v>
       </c>
       <c r="G790" t="n">
-        <v>1.64301729202271</v>
+        <v>1.64301717281342</v>
       </c>
       <c r="H790" t="n">
         <v>3830</v>
@@ -23308,7 +23308,7 @@
         <v>1.89979994297028</v>
       </c>
       <c r="G791" t="n">
-        <v>1.64405560493469</v>
+        <v>1.64405572414398</v>
       </c>
       <c r="H791" t="n">
         <v>83</v>
@@ -23337,7 +23337,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G792" t="n">
-        <v>1.67019021511078</v>
+        <v>1.67019033432007</v>
       </c>
       <c r="H792" t="n">
         <v>693</v>
@@ -23366,7 +23366,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G793" t="n">
-        <v>1.67019021511078</v>
+        <v>1.67019033432007</v>
       </c>
       <c r="H793" t="n">
         <v>0</v>
@@ -23395,7 +23395,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G794" t="n">
-        <v>1.66240179538727</v>
+        <v>1.66240191459656</v>
       </c>
       <c r="H794" t="n">
         <v>50</v>
@@ -23424,7 +23424,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G795" t="n">
-        <v>1.65980565547943</v>
+        <v>1.65980577468872</v>
       </c>
       <c r="H795" t="n">
         <v>666</v>
@@ -23453,7 +23453,7 @@
         <v>1.84860002994537</v>
       </c>
       <c r="G796" t="n">
-        <v>1.59974825382233</v>
+        <v>1.59974813461304</v>
       </c>
       <c r="H796" t="n">
         <v>9753</v>
@@ -23482,7 +23482,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G797" t="n">
-        <v>1.59836363792419</v>
+        <v>1.59836339950562</v>
       </c>
       <c r="H797" t="n">
         <v>6802</v>
@@ -23511,7 +23511,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G798" t="n">
-        <v>1.6191326379776</v>
+        <v>1.61913275718689</v>
       </c>
       <c r="H798" t="n">
         <v>570</v>
@@ -23569,7 +23569,7 @@
         <v>1.85739994049072</v>
       </c>
       <c r="G800" t="n">
-        <v>1.60736346244812</v>
+        <v>1.60736334323883</v>
       </c>
       <c r="H800" t="n">
         <v>3716</v>
@@ -23598,7 +23598,7 @@
         <v>1.89979994297028</v>
       </c>
       <c r="G801" t="n">
-        <v>1.64405560493469</v>
+        <v>1.64405572414398</v>
       </c>
       <c r="H801" t="n">
         <v>5259</v>
@@ -23627,7 +23627,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G802" t="n">
-        <v>1.62345957756042</v>
+        <v>1.62345969676971</v>
       </c>
       <c r="H802" t="n">
         <v>4654</v>
@@ -23685,7 +23685,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G804" t="n">
-        <v>1.62086343765259</v>
+        <v>1.62086355686188</v>
       </c>
       <c r="H804" t="n">
         <v>1386</v>
@@ -23859,7 +23859,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G810" t="n">
-        <v>1.60355591773987</v>
+        <v>1.60355579853058</v>
       </c>
       <c r="H810" t="n">
         <v>1874</v>
@@ -23888,7 +23888,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G811" t="n">
-        <v>1.5793251991272</v>
+        <v>1.57932507991791</v>
       </c>
       <c r="H811" t="n">
         <v>115</v>
@@ -23917,7 +23917,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G812" t="n">
-        <v>1.60095977783203</v>
+        <v>1.60095953941345</v>
       </c>
       <c r="H812" t="n">
         <v>3785</v>
@@ -23975,7 +23975,7 @@
         <v>1.75220000743866</v>
       </c>
       <c r="G814" t="n">
-        <v>1.51632523536682</v>
+        <v>1.51632511615753</v>
       </c>
       <c r="H814" t="n">
         <v>8175</v>
@@ -24004,7 +24004,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G815" t="n">
-        <v>1.54211342334747</v>
+        <v>1.54211354255676</v>
       </c>
       <c r="H815" t="n">
         <v>7327</v>
@@ -24033,7 +24033,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G816" t="n">
-        <v>1.50144040584564</v>
+        <v>1.50144052505493</v>
       </c>
       <c r="H816" t="n">
         <v>282</v>
@@ -24062,7 +24062,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G817" t="n">
-        <v>1.50144040584564</v>
+        <v>1.50144052505493</v>
       </c>
       <c r="H817" t="n">
         <v>4851</v>
@@ -24091,7 +24091,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G818" t="n">
-        <v>1.52913284301758</v>
+        <v>1.52913272380829</v>
       </c>
       <c r="H818" t="n">
         <v>3097</v>
@@ -24120,7 +24120,7 @@
         <v>1.76960003376007</v>
       </c>
       <c r="G819" t="n">
-        <v>1.53138291835785</v>
+        <v>1.53138279914856</v>
       </c>
       <c r="H819" t="n">
         <v>2845</v>
@@ -24207,7 +24207,7 @@
         <v>1.75</v>
       </c>
       <c r="G822" t="n">
-        <v>1.51442134380341</v>
+        <v>1.51442122459412</v>
       </c>
       <c r="H822" t="n">
         <v>7919</v>
@@ -24294,7 +24294,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G825" t="n">
-        <v>1.50576746463776</v>
+        <v>1.50576758384705</v>
       </c>
       <c r="H825" t="n">
         <v>4969</v>
@@ -24323,7 +24323,7 @@
         <v>1.72560000419617</v>
       </c>
       <c r="G826" t="n">
-        <v>1.49330604076385</v>
+        <v>1.49330592155457</v>
       </c>
       <c r="H826" t="n">
         <v>6548</v>
@@ -24352,7 +24352,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>1.4798059463501</v>
+        <v>1.47980582714081</v>
       </c>
       <c r="H827" t="n">
         <v>3742</v>
@@ -24381,7 +24381,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>1.4798059463501</v>
+        <v>1.47980582714081</v>
       </c>
       <c r="H828" t="n">
         <v>3769</v>
@@ -24439,7 +24439,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G830" t="n">
-        <v>1.50144040584564</v>
+        <v>1.50144052505493</v>
       </c>
       <c r="H830" t="n">
         <v>4506</v>
@@ -24468,7 +24468,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G831" t="n">
-        <v>1.48845982551575</v>
+        <v>1.48845970630646</v>
       </c>
       <c r="H831" t="n">
         <v>1011</v>
@@ -24497,7 +24497,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G832" t="n">
-        <v>1.4971137046814</v>
+        <v>1.49711358547211</v>
       </c>
       <c r="H832" t="n">
         <v>2164</v>
@@ -24526,7 +24526,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G833" t="n">
-        <v>1.44951748847961</v>
+        <v>1.44951736927032</v>
       </c>
       <c r="H833" t="n">
         <v>2154</v>
@@ -24642,7 +24642,7 @@
         <v>1.75</v>
       </c>
       <c r="G837" t="n">
-        <v>1.51442134380341</v>
+        <v>1.51442122459412</v>
       </c>
       <c r="H837" t="n">
         <v>7450</v>
@@ -24700,7 +24700,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G839" t="n">
-        <v>1.54903662204742</v>
+        <v>1.54903650283813</v>
       </c>
       <c r="H839" t="n">
         <v>12013</v>
@@ -24729,7 +24729,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G840" t="n">
-        <v>1.4798059463501</v>
+        <v>1.47980582714081</v>
       </c>
       <c r="H840" t="n">
         <v>19618</v>
@@ -24787,7 +24787,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G842" t="n">
-        <v>1.44519054889679</v>
+        <v>1.44519066810608</v>
       </c>
       <c r="H842" t="n">
         <v>11178</v>
@@ -24816,7 +24816,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G843" t="n">
-        <v>1.44519054889679</v>
+        <v>1.44519066810608</v>
       </c>
       <c r="H843" t="n">
         <v>3119</v>
@@ -24903,7 +24903,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G846" t="n">
-        <v>1.46682524681091</v>
+        <v>1.46682512760162</v>
       </c>
       <c r="H846" t="n">
         <v>1032</v>
@@ -24932,7 +24932,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G847" t="n">
-        <v>1.4798059463501</v>
+        <v>1.47980582714081</v>
       </c>
       <c r="H847" t="n">
         <v>2642</v>
@@ -24961,7 +24961,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G848" t="n">
-        <v>1.4798059463501</v>
+        <v>1.47980582714081</v>
       </c>
       <c r="H848" t="n">
         <v>4589</v>
@@ -25048,7 +25048,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G851" t="n">
-        <v>1.44951748847961</v>
+        <v>1.44951736927032</v>
       </c>
       <c r="H851" t="n">
         <v>3089</v>
@@ -25077,7 +25077,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G852" t="n">
-        <v>1.44951748847961</v>
+        <v>1.44951736927032</v>
       </c>
       <c r="H852" t="n">
         <v>11501</v>
@@ -25106,7 +25106,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G853" t="n">
-        <v>1.44519054889679</v>
+        <v>1.44519066810608</v>
       </c>
       <c r="H853" t="n">
         <v>1626</v>
@@ -25193,7 +25193,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G856" t="n">
-        <v>1.34134447574615</v>
+        <v>1.34134459495544</v>
       </c>
       <c r="H856" t="n">
         <v>9092</v>
@@ -25251,7 +25251,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G858" t="n">
-        <v>1.44951748847961</v>
+        <v>1.44951736927032</v>
       </c>
       <c r="H858" t="n">
         <v>1469</v>
@@ -25309,7 +25309,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G860" t="n">
-        <v>1.42788290977478</v>
+        <v>1.42788279056549</v>
       </c>
       <c r="H860" t="n">
         <v>4086</v>
@@ -25425,7 +25425,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G864" t="n">
-        <v>1.42788290977478</v>
+        <v>1.42788279056549</v>
       </c>
       <c r="H864" t="n">
         <v>8157</v>
@@ -25454,7 +25454,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G865" t="n">
-        <v>1.41922903060913</v>
+        <v>1.41922891139984</v>
       </c>
       <c r="H865" t="n">
         <v>7928</v>
@@ -25483,7 +25483,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G866" t="n">
-        <v>1.41922903060913</v>
+        <v>1.41922891139984</v>
       </c>
       <c r="H866" t="n">
         <v>1621</v>
@@ -25686,7 +25686,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G873" t="n">
-        <v>1.41922903060913</v>
+        <v>1.41922891139984</v>
       </c>
       <c r="H873" t="n">
         <v>3139</v>
@@ -25773,7 +25773,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>1.33269071578979</v>
+        <v>1.33269059658051</v>
       </c>
       <c r="H876" t="n">
         <v>951</v>
@@ -25802,7 +25802,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G877" t="n">
-        <v>1.38461375236511</v>
+        <v>1.3846138715744</v>
       </c>
       <c r="H877" t="n">
         <v>3726</v>
@@ -25831,7 +25831,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G878" t="n">
-        <v>1.38028681278229</v>
+        <v>1.38028693199158</v>
       </c>
       <c r="H878" t="n">
         <v>7486</v>
@@ -25860,7 +25860,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G879" t="n">
-        <v>1.38028681278229</v>
+        <v>1.38028693199158</v>
       </c>
       <c r="H879" t="n">
         <v>2002</v>
@@ -25976,7 +25976,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G883" t="n">
-        <v>1.38461375236511</v>
+        <v>1.3846138715744</v>
       </c>
       <c r="H883" t="n">
         <v>4134</v>
@@ -26005,7 +26005,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G884" t="n">
-        <v>1.38461375236511</v>
+        <v>1.3846138715744</v>
       </c>
       <c r="H884" t="n">
         <v>1525</v>
@@ -26063,7 +26063,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G886" t="n">
-        <v>1.38461375236511</v>
+        <v>1.3846138715744</v>
       </c>
       <c r="H886" t="n">
         <v>1608</v>
@@ -26092,7 +26092,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G887" t="n">
-        <v>1.37163293361664</v>
+        <v>1.37163317203522</v>
       </c>
       <c r="H887" t="n">
         <v>8464</v>
@@ -26121,7 +26121,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G888" t="n">
-        <v>1.33701753616333</v>
+        <v>1.33701765537262</v>
       </c>
       <c r="H888" t="n">
         <v>7055</v>
@@ -26150,7 +26150,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>1.34999823570251</v>
+        <v>1.34999847412109</v>
       </c>
       <c r="H889" t="n">
         <v>10750</v>
@@ -26179,7 +26179,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G890" t="n">
-        <v>1.31970989704132</v>
+        <v>1.31971001625061</v>
       </c>
       <c r="H890" t="n">
         <v>3007</v>
@@ -26208,7 +26208,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>1.33269071578979</v>
+        <v>1.33269059658051</v>
       </c>
       <c r="H891" t="n">
         <v>4712</v>
@@ -26237,7 +26237,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31105601787567</v>
+        <v>1.31105625629425</v>
       </c>
       <c r="H892" t="n">
         <v>200</v>
@@ -26266,7 +26266,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G893" t="n">
-        <v>1.31970989704132</v>
+        <v>1.31971001625061</v>
       </c>
       <c r="H893" t="n">
         <v>7</v>
@@ -26324,7 +26324,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G895" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950382709503</v>
       </c>
       <c r="H895" t="n">
         <v>13784</v>
@@ -26353,7 +26353,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G896" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950382709503</v>
       </c>
       <c r="H896" t="n">
         <v>5979</v>
@@ -26440,7 +26440,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G899" t="n">
-        <v>1.34618949890137</v>
+        <v>1.34618937969208</v>
       </c>
       <c r="H899" t="n">
         <v>6326</v>
@@ -26643,7 +26643,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G906" t="n">
-        <v>1.3906182050705</v>
+        <v>1.39061832427979</v>
       </c>
       <c r="H906" t="n">
         <v>4064</v>
@@ -26730,7 +26730,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G909" t="n">
-        <v>1.42171835899353</v>
+        <v>1.42171823978424</v>
       </c>
       <c r="H909" t="n">
         <v>988</v>
@@ -26788,7 +26788,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G911" t="n">
-        <v>1.42171835899353</v>
+        <v>1.42171823978424</v>
       </c>
       <c r="H911" t="n">
         <v>2700</v>
@@ -27020,7 +27020,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G919" t="n">
-        <v>1.3906182050705</v>
+        <v>1.39061832427979</v>
       </c>
       <c r="H919" t="n">
         <v>4578</v>
@@ -27455,7 +27455,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G934" t="n">
-        <v>1.46614694595337</v>
+        <v>1.46614682674408</v>
       </c>
       <c r="H934" t="n">
         <v>6922</v>
@@ -27629,7 +27629,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G940" t="n">
-        <v>1.42171835899353</v>
+        <v>1.42171823978424</v>
       </c>
       <c r="H940" t="n">
         <v>13365</v>
@@ -27774,7 +27774,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>1.3906182050705</v>
+        <v>1.39061832427979</v>
       </c>
       <c r="H945" t="n">
         <v>5513</v>
@@ -27832,7 +27832,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G947" t="n">
-        <v>1.3906182050705</v>
+        <v>1.39061832427979</v>
       </c>
       <c r="H947" t="n">
         <v>2032</v>
@@ -27861,7 +27861,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G948" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950382709503</v>
       </c>
       <c r="H948" t="n">
         <v>704</v>
@@ -27948,7 +27948,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G951" t="n">
-        <v>1.38173246383667</v>
+        <v>1.38173234462738</v>
       </c>
       <c r="H951" t="n">
         <v>13177</v>
@@ -27977,7 +27977,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G952" t="n">
-        <v>1.3906182050705</v>
+        <v>1.39061832427979</v>
       </c>
       <c r="H952" t="n">
         <v>1128</v>
@@ -28093,7 +28093,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G956" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950382709503</v>
       </c>
       <c r="H956" t="n">
         <v>284</v>
@@ -28180,7 +28180,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G959" t="n">
-        <v>1.38173246383667</v>
+        <v>1.38173234462738</v>
       </c>
       <c r="H959" t="n">
         <v>562</v>
@@ -28209,7 +28209,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G960" t="n">
-        <v>1.38173246383667</v>
+        <v>1.38173234462738</v>
       </c>
       <c r="H960" t="n">
         <v>2514</v>
@@ -28238,7 +28238,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G961" t="n">
-        <v>1.38173246383667</v>
+        <v>1.38173234462738</v>
       </c>
       <c r="H961" t="n">
         <v>167</v>
@@ -28267,7 +28267,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G962" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H962" t="n">
         <v>1847</v>
@@ -28296,7 +28296,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G963" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H963" t="n">
         <v>507</v>
@@ -28325,7 +28325,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G964" t="n">
-        <v>1.36396098136902</v>
+        <v>1.36396086215973</v>
       </c>
       <c r="H964" t="n">
         <v>374</v>
@@ -28354,7 +28354,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G965" t="n">
-        <v>1.36396098136902</v>
+        <v>1.36396086215973</v>
       </c>
       <c r="H965" t="n">
         <v>14009</v>
@@ -28412,7 +28412,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G967" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H967" t="n">
         <v>17914</v>
@@ -28441,7 +28441,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G968" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H968" t="n">
         <v>54447</v>
@@ -28470,7 +28470,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G969" t="n">
-        <v>1.36396098136902</v>
+        <v>1.36396086215973</v>
       </c>
       <c r="H969" t="n">
         <v>8994</v>
@@ -28528,7 +28528,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G971" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H971" t="n">
         <v>9924</v>
@@ -28673,7 +28673,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G976" t="n">
-        <v>1.34618949890137</v>
+        <v>1.34618937969208</v>
       </c>
       <c r="H976" t="n">
         <v>1120</v>
@@ -28731,7 +28731,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G978" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H978" t="n">
         <v>8033</v>
@@ -28876,7 +28876,7 @@
         <v>1.5</v>
       </c>
       <c r="G983" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H983" t="n">
         <v>5647</v>
@@ -28905,7 +28905,7 @@
         <v>1.5</v>
       </c>
       <c r="G984" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H984" t="n">
         <v>196</v>
@@ -29021,7 +29021,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G988" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H988" t="n">
         <v>10413</v>
@@ -29137,7 +29137,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G992" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H992" t="n">
         <v>9225</v>
@@ -29224,7 +29224,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G995" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H995" t="n">
         <v>5723</v>
@@ -29311,7 +29311,7 @@
         <v>1.5</v>
       </c>
       <c r="G998" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H998" t="n">
         <v>1924</v>
@@ -29340,7 +29340,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G999" t="n">
-        <v>1.28398931026459</v>
+        <v>1.28398942947388</v>
       </c>
       <c r="H999" t="n">
         <v>561</v>
@@ -29485,7 +29485,7 @@
         <v>1.5</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1004" t="n">
         <v>1331</v>
@@ -29514,7 +29514,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H1005" t="n">
         <v>2169</v>
@@ -29543,7 +29543,7 @@
         <v>1.5</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1006" t="n">
         <v>824</v>
@@ -29601,7 +29601,7 @@
         <v>1.5</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1008" t="n">
         <v>43</v>
@@ -29630,7 +29630,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H1009" t="n">
         <v>60</v>
@@ -29659,7 +29659,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.34618949890137</v>
+        <v>1.34618937969208</v>
       </c>
       <c r="H1010" t="n">
         <v>40</v>
@@ -29688,7 +29688,7 @@
         <v>1.5</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1011" t="n">
         <v>1000</v>
@@ -29717,7 +29717,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H1012" t="n">
         <v>400</v>
@@ -29833,7 +29833,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H1016" t="n">
         <v>596</v>
@@ -29862,7 +29862,7 @@
         <v>1.5</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1017" t="n">
         <v>2108</v>
@@ -29891,7 +29891,7 @@
         <v>1.5</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1018" t="n">
         <v>5</v>
@@ -29978,7 +29978,7 @@
         <v>1.5</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1021" t="n">
         <v>1444</v>
@@ -30036,7 +30036,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.34618949890137</v>
+        <v>1.34618937969208</v>
       </c>
       <c r="H1023" t="n">
         <v>26942</v>
@@ -30065,7 +30065,7 @@
         <v>1.5</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1024" t="n">
         <v>2212</v>
@@ -30210,7 +30210,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.48391842842102</v>
+        <v>1.48391830921173</v>
       </c>
       <c r="H1029" t="n">
         <v>8880</v>
@@ -30326,7 +30326,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.42171835899353</v>
+        <v>1.42171823978424</v>
       </c>
       <c r="H1033" t="n">
         <v>16284</v>
@@ -30355,7 +30355,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.42171835899353</v>
+        <v>1.42171823978424</v>
       </c>
       <c r="H1034" t="n">
         <v>10854</v>
@@ -30558,7 +30558,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950382709503</v>
       </c>
       <c r="H1041" t="n">
         <v>7010</v>
@@ -30587,7 +30587,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950382709503</v>
       </c>
       <c r="H1042" t="n">
         <v>1800</v>
@@ -30645,7 +30645,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H1044" t="n">
         <v>3840</v>
@@ -30674,7 +30674,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.38173246383667</v>
+        <v>1.38173234462738</v>
       </c>
       <c r="H1045" t="n">
         <v>3079</v>
@@ -30703,7 +30703,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H1046" t="n">
         <v>14097</v>
@@ -30732,7 +30732,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.36396098136902</v>
+        <v>1.36396086215973</v>
       </c>
       <c r="H1047" t="n">
         <v>5752</v>
@@ -30935,7 +30935,7 @@
         <v>1.5</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1054" t="n">
         <v>270</v>
@@ -30964,7 +30964,7 @@
         <v>1.5</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1055" t="n">
         <v>3317</v>
@@ -31138,7 +31138,7 @@
         <v>1.5</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1061" t="n">
         <v>2361</v>
@@ -31167,7 +31167,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.25733208656311</v>
+        <v>1.25733196735382</v>
       </c>
       <c r="H1062" t="n">
         <v>7901</v>
@@ -31283,7 +31283,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.0662887096405</v>
+        <v>1.06628882884979</v>
       </c>
       <c r="H1066" t="n">
         <v>7051</v>
@@ -31341,7 +31341,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.0662887096405</v>
+        <v>1.06628882884979</v>
       </c>
       <c r="H1068" t="n">
         <v>3940</v>
@@ -31457,7 +31457,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.17291760444641</v>
+        <v>1.1729177236557</v>
       </c>
       <c r="H1072" t="n">
         <v>14581</v>
@@ -31544,7 +31544,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.14626026153564</v>
+        <v>1.14626038074493</v>
       </c>
       <c r="H1075" t="n">
         <v>4004</v>
@@ -31747,7 +31747,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.09294593334198</v>
+        <v>1.09294581413269</v>
       </c>
       <c r="H1082" t="n">
         <v>4621</v>
@@ -31834,7 +31834,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.09294593334198</v>
+        <v>1.09294581413269</v>
       </c>
       <c r="H1085" t="n">
         <v>1839</v>
@@ -32037,7 +32037,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.08406007289886</v>
+        <v>1.08406019210815</v>
       </c>
       <c r="H1092" t="n">
         <v>728</v>
@@ -32240,7 +32240,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.09294593334198</v>
+        <v>1.09294581413269</v>
       </c>
       <c r="H1099" t="n">
         <v>300</v>
@@ -32298,7 +32298,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.09294593334198</v>
+        <v>1.09294581413269</v>
       </c>
       <c r="H1101" t="n">
         <v>9120</v>
@@ -32414,7 +32414,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.09294593334198</v>
+        <v>1.09294581413269</v>
       </c>
       <c r="H1105" t="n">
         <v>2500</v>
@@ -32443,7 +32443,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.09294593334198</v>
+        <v>1.09294581413269</v>
       </c>
       <c r="H1106" t="n">
         <v>2001</v>
@@ -32472,7 +32472,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.07073152065277</v>
+        <v>1.07073163986206</v>
       </c>
       <c r="H1107" t="n">
         <v>2718</v>
@@ -32588,7 +32588,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1111" t="n">
         <v>1232</v>
@@ -32617,7 +32617,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1112" t="n">
         <v>0</v>
@@ -32704,7 +32704,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.05740308761597</v>
+        <v>1.05740296840668</v>
       </c>
       <c r="H1115" t="n">
         <v>3885</v>
@@ -32733,7 +32733,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1116" t="n">
         <v>9</v>
@@ -32762,7 +32762,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1117" t="n">
         <v>11065</v>
@@ -32791,7 +32791,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1118" t="n">
         <v>1500</v>
@@ -32820,7 +32820,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.07073152065277</v>
+        <v>1.07073163986206</v>
       </c>
       <c r="H1119" t="n">
         <v>22647</v>
@@ -32936,7 +32936,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1123" t="n">
         <v>24776</v>
@@ -33168,7 +33168,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.19513201713562</v>
+        <v>1.19513189792633</v>
       </c>
       <c r="H1131" t="n">
         <v>4283</v>
@@ -33226,7 +33226,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.19068896770477</v>
+        <v>1.19068908691406</v>
       </c>
       <c r="H1133" t="n">
         <v>1650</v>
@@ -33255,7 +33255,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.19068896770477</v>
+        <v>1.19068908691406</v>
       </c>
       <c r="H1134" t="n">
         <v>2402</v>
@@ -33429,7 +33429,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.17291760444641</v>
+        <v>1.1729177236557</v>
       </c>
       <c r="H1140" t="n">
         <v>100</v>
@@ -33603,7 +33603,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.19513201713562</v>
+        <v>1.19513189792633</v>
       </c>
       <c r="H1146" t="n">
         <v>13500</v>
@@ -33690,7 +33690,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H1149" t="n">
         <v>7987</v>
@@ -33922,7 +33922,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1157" t="n">
         <v>4748</v>
@@ -33980,7 +33980,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.25288915634155</v>
+        <v>1.25288927555084</v>
       </c>
       <c r="H1159" t="n">
         <v>3866</v>
@@ -34009,7 +34009,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1160" t="n">
         <v>1</v>
@@ -34038,7 +34038,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1161" t="n">
         <v>0</v>
@@ -34183,7 +34183,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.23956072330475</v>
+        <v>1.23956060409546</v>
       </c>
       <c r="H1166" t="n">
         <v>1607</v>
@@ -34386,7 +34386,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.25288915634155</v>
+        <v>1.25288927555084</v>
       </c>
       <c r="H1173" t="n">
         <v>5015</v>
@@ -34502,7 +34502,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1177" t="n">
         <v>475</v>
@@ -34647,7 +34647,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.23956072330475</v>
+        <v>1.23956060409546</v>
       </c>
       <c r="H1182" t="n">
         <v>250</v>
@@ -34676,7 +34676,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1183" t="n">
         <v>1274</v>
@@ -34734,7 +34734,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.24844634532928</v>
+        <v>1.24844646453857</v>
       </c>
       <c r="H1185" t="n">
         <v>3042</v>
@@ -34763,7 +34763,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.23956072330475</v>
+        <v>1.23956060409546</v>
       </c>
       <c r="H1186" t="n">
         <v>3500</v>
@@ -34850,7 +34850,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.23956072330475</v>
+        <v>1.23956060409546</v>
       </c>
       <c r="H1189" t="n">
         <v>37724</v>
@@ -34908,7 +34908,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.19513201713562</v>
+        <v>1.19513189792633</v>
       </c>
       <c r="H1191" t="n">
         <v>21793</v>
@@ -34966,7 +34966,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.19068896770477</v>
+        <v>1.19068908691406</v>
       </c>
       <c r="H1193" t="n">
         <v>1059</v>
@@ -35111,7 +35111,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.17291760444641</v>
+        <v>1.1729177236557</v>
       </c>
       <c r="H1198" t="n">
         <v>9301</v>
@@ -35633,7 +35633,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.0662887096405</v>
+        <v>1.06628882884979</v>
       </c>
       <c r="H1216" t="n">
         <v>6520</v>
@@ -35662,7 +35662,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.0662887096405</v>
+        <v>1.06628882884979</v>
       </c>
       <c r="H1217" t="n">
         <v>133</v>
@@ -35691,7 +35691,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.02630293369293</v>
+        <v>1.02630281448364</v>
       </c>
       <c r="H1218" t="n">
         <v>15161</v>
@@ -35720,7 +35720,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.04407441616058</v>
+        <v>1.04407429695129</v>
       </c>
       <c r="H1219" t="n">
         <v>18522</v>
@@ -35807,7 +35807,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.0307457447052</v>
+        <v>1.03074586391449</v>
       </c>
       <c r="H1222" t="n">
         <v>27247</v>
@@ -35894,7 +35894,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.964102685451508</v>
+        <v>0.964102745056152</v>
       </c>
       <c r="H1225" t="n">
         <v>5102</v>
@@ -35923,7 +35923,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.955217063426971</v>
+        <v>0.955217003822327</v>
       </c>
       <c r="H1226" t="n">
         <v>10655</v>
@@ -36039,7 +36039,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.946331322193146</v>
+        <v>0.946331262588501</v>
       </c>
       <c r="H1230" t="n">
         <v>14087</v>
@@ -36068,7 +36068,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.968545615673065</v>
+        <v>0.96854567527771</v>
       </c>
       <c r="H1231" t="n">
         <v>2410</v>
@@ -36155,7 +36155,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.04851710796356</v>
+        <v>1.04851722717285</v>
       </c>
       <c r="H1234" t="n">
         <v>36142</v>
@@ -36184,7 +36184,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.07073152065277</v>
+        <v>1.07073163986206</v>
       </c>
       <c r="H1235" t="n">
         <v>30691</v>
@@ -36242,7 +36242,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.0662887096405</v>
+        <v>1.06628882884979</v>
       </c>
       <c r="H1237" t="n">
         <v>11517</v>
@@ -36300,7 +36300,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.04851710796356</v>
+        <v>1.04851722717285</v>
       </c>
       <c r="H1239" t="n">
         <v>989</v>
@@ -36358,7 +36358,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.09294593334198</v>
+        <v>1.09294581413269</v>
       </c>
       <c r="H1241" t="n">
         <v>6231</v>
@@ -37576,7 +37576,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.14626026153564</v>
+        <v>1.14626038074493</v>
       </c>
       <c r="H1283" t="n">
         <v>2000</v>
@@ -37750,7 +37750,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.08406007289886</v>
+        <v>1.08406019210815</v>
       </c>
       <c r="H1289" t="n">
         <v>3000</v>
@@ -37779,7 +37779,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.07517457008362</v>
+        <v>1.07517445087433</v>
       </c>
       <c r="H1290" t="n">
         <v>4500</v>
@@ -37837,7 +37837,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.08406007289886</v>
+        <v>1.08406019210815</v>
       </c>
       <c r="H1292" t="n">
         <v>1924</v>
@@ -38011,7 +38011,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.17291760444641</v>
+        <v>1.1729177236557</v>
       </c>
       <c r="H1298" t="n">
         <v>21741</v>
@@ -38156,7 +38156,7 @@
         <v>1.5</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1303" t="n">
         <v>51935</v>
@@ -38243,7 +38243,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.38173246383667</v>
+        <v>1.38173234462738</v>
       </c>
       <c r="H1306" t="n">
         <v>8515</v>
@@ -38272,7 +38272,7 @@
         <v>1.5</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1307" t="n">
         <v>25570</v>
@@ -38388,7 +38388,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1311" t="n">
         <v>3731</v>
@@ -38417,7 +38417,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1312" t="n">
         <v>1150</v>
@@ -38504,7 +38504,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.25288915634155</v>
+        <v>1.25288927555084</v>
       </c>
       <c r="H1315" t="n">
         <v>6000</v>
@@ -38649,7 +38649,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.28398931026459</v>
+        <v>1.28398942947388</v>
       </c>
       <c r="H1320" t="n">
         <v>3651</v>
@@ -38707,7 +38707,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.34618949890137</v>
+        <v>1.34618937969208</v>
       </c>
       <c r="H1322" t="n">
         <v>19667</v>
@@ -38736,7 +38736,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.38173246383667</v>
+        <v>1.38173234462738</v>
       </c>
       <c r="H1323" t="n">
         <v>56426</v>
@@ -38794,7 +38794,7 @@
         <v>1.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1325" t="n">
         <v>21677</v>
@@ -38823,7 +38823,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H1326" t="n">
         <v>3364</v>
@@ -38852,7 +38852,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H1327" t="n">
         <v>4300</v>
@@ -38939,7 +38939,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H1330" t="n">
         <v>29594</v>
@@ -38997,7 +38997,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.3906182050705</v>
+        <v>1.39061832427979</v>
       </c>
       <c r="H1332" t="n">
         <v>3200</v>
@@ -39113,7 +39113,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.69273316860199</v>
+        <v>1.69273328781128</v>
       </c>
       <c r="H1336" t="n">
         <v>114924</v>
@@ -39142,7 +39142,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.67051899433136</v>
+        <v>1.67051887512207</v>
       </c>
       <c r="H1337" t="n">
         <v>44200</v>
@@ -39171,7 +39171,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1338" t="n">
         <v>49980</v>
@@ -39258,7 +39258,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.63497614860535</v>
+        <v>1.63497602939606</v>
       </c>
       <c r="H1341" t="n">
         <v>42761</v>
@@ -39287,7 +39287,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.652747631073</v>
+        <v>1.65274751186371</v>
       </c>
       <c r="H1342" t="n">
         <v>59990</v>
@@ -39345,7 +39345,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.66163313388824</v>
+        <v>1.66163325309753</v>
       </c>
       <c r="H1344" t="n">
         <v>2018</v>
@@ -39432,7 +39432,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1347" t="n">
         <v>15001</v>
@@ -39461,7 +39461,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.63941884040833</v>
+        <v>1.63941895961761</v>
       </c>
       <c r="H1348" t="n">
         <v>17077</v>
@@ -39519,7 +39519,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.56389009952545</v>
+        <v>1.56388998031616</v>
       </c>
       <c r="H1350" t="n">
         <v>11903</v>
@@ -39809,7 +39809,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.56389009952545</v>
+        <v>1.56388998031616</v>
       </c>
       <c r="H1360" t="n">
         <v>1498</v>
@@ -39838,7 +39838,7 @@
         <v>1.75</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.55500435829163</v>
+        <v>1.55500447750092</v>
       </c>
       <c r="H1361" t="n">
         <v>1866</v>
@@ -40186,7 +40186,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1373" t="n">
         <v>10407</v>
@@ -40476,7 +40476,7 @@
         <v>1.875</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.66607618331909</v>
+        <v>1.6660760641098</v>
       </c>
       <c r="H1383" t="n">
         <v>23028</v>
@@ -40505,7 +40505,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.67051899433136</v>
+        <v>1.67051887512207</v>
       </c>
       <c r="H1384" t="n">
         <v>11794</v>
@@ -40737,7 +40737,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1392" t="n">
         <v>16941</v>
@@ -40766,7 +40766,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1393" t="n">
         <v>10690</v>
@@ -40824,7 +40824,7 @@
         <v>1.875</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.66607618331909</v>
+        <v>1.6660760641098</v>
       </c>
       <c r="H1395" t="n">
         <v>8625</v>
@@ -40853,7 +40853,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1396" t="n">
         <v>11063</v>
@@ -40882,7 +40882,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1397" t="n">
         <v>4090</v>
@@ -41027,7 +41027,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1402" t="n">
         <v>17663</v>
@@ -41056,7 +41056,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.67051899433136</v>
+        <v>1.67051887512207</v>
       </c>
       <c r="H1403" t="n">
         <v>25601</v>
@@ -41085,7 +41085,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1404" t="n">
         <v>100</v>
@@ -41114,7 +41114,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.67051899433136</v>
+        <v>1.67051887512207</v>
       </c>
       <c r="H1405" t="n">
         <v>3250</v>
@@ -41143,7 +41143,7 @@
         <v>1.875</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.66607618331909</v>
+        <v>1.6660760641098</v>
       </c>
       <c r="H1406" t="n">
         <v>651</v>
@@ -41462,7 +41462,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1417" t="n">
         <v>65749</v>
@@ -41491,7 +41491,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.94597697257996</v>
+        <v>1.94597685337067</v>
       </c>
       <c r="H1418" t="n">
         <v>52870</v>
@@ -41839,7 +41839,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1430" t="n">
         <v>27338</v>
@@ -41984,7 +41984,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.89266264438629</v>
+        <v>1.892662525177</v>
       </c>
       <c r="H1435" t="n">
         <v>28893</v>
@@ -42071,7 +42071,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1438" t="n">
         <v>11816</v>
@@ -42100,7 +42100,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1439" t="n">
         <v>8215</v>
@@ -42129,7 +42129,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.98151993751526</v>
+        <v>1.98151981830597</v>
       </c>
       <c r="H1440" t="n">
         <v>105315</v>
@@ -42187,7 +42187,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.98151993751526</v>
+        <v>1.98151981830597</v>
       </c>
       <c r="H1442" t="n">
         <v>20712</v>
@@ -42390,7 +42390,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.98151993751526</v>
+        <v>1.98151981830597</v>
       </c>
       <c r="H1449" t="n">
         <v>25934</v>
@@ -42419,7 +42419,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.94597697257996</v>
+        <v>1.94597685337067</v>
       </c>
       <c r="H1450" t="n">
         <v>45609</v>
@@ -42535,7 +42535,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.13257741928101</v>
+        <v>2.13257765769958</v>
       </c>
       <c r="H1454" t="n">
         <v>115351</v>
@@ -42622,7 +42622,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.11480617523193</v>
+        <v>2.11480593681335</v>
       </c>
       <c r="H1457" t="n">
         <v>78075</v>
@@ -42680,7 +42680,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.13257741928101</v>
+        <v>2.13257765769958</v>
       </c>
       <c r="H1459" t="n">
         <v>48913</v>
@@ -42709,7 +42709,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.13257741928101</v>
+        <v>2.13257765769958</v>
       </c>
       <c r="H1460" t="n">
         <v>64369</v>
@@ -42738,7 +42738,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.14146304130554</v>
+        <v>2.14146327972412</v>
       </c>
       <c r="H1461" t="n">
         <v>56728</v>
@@ -42883,7 +42883,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.96374833583832</v>
+        <v>1.96374845504761</v>
       </c>
       <c r="H1466" t="n">
         <v>51656</v>
@@ -42912,7 +42912,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.96374833583832</v>
+        <v>1.96374845504761</v>
       </c>
       <c r="H1467" t="n">
         <v>62125</v>
@@ -43028,7 +43028,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.08814883232117</v>
+        <v>2.08814859390259</v>
       </c>
       <c r="H1471" t="n">
         <v>25693</v>
@@ -43057,7 +43057,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.0614914894104</v>
+        <v>2.06149172782898</v>
       </c>
       <c r="H1472" t="n">
         <v>9528</v>
@@ -43086,7 +43086,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.05260586738586</v>
+        <v>2.05260562896729</v>
       </c>
       <c r="H1473" t="n">
         <v>12166</v>
@@ -43115,7 +43115,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.05260586738586</v>
+        <v>2.05260562896729</v>
       </c>
       <c r="H1474" t="n">
         <v>20731</v>
@@ -43173,7 +43173,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.08814883232117</v>
+        <v>2.08814859390259</v>
       </c>
       <c r="H1476" t="n">
         <v>52586</v>
@@ -43202,7 +43202,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.08814883232117</v>
+        <v>2.08814859390259</v>
       </c>
       <c r="H1477" t="n">
         <v>16599</v>
@@ -43231,7 +43231,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.08814883232117</v>
+        <v>2.08814859390259</v>
       </c>
       <c r="H1478" t="n">
         <v>9063</v>
@@ -43260,7 +43260,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1479" t="n">
-        <v>2.09703421592712</v>
+        <v>2.0970344543457</v>
       </c>
       <c r="H1479" t="n">
         <v>54713</v>
@@ -43289,7 +43289,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.0614914894104</v>
+        <v>2.06149172782898</v>
       </c>
       <c r="H1480" t="n">
         <v>67552</v>
@@ -43840,7 +43840,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709135055542</v>
       </c>
       <c r="H1499" t="n">
         <v>19550</v>
@@ -43869,7 +43869,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.89266264438629</v>
+        <v>1.892662525177</v>
       </c>
       <c r="H1500" t="n">
         <v>21650</v>
@@ -43927,7 +43927,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1502" t="n">
         <v>15116</v>
@@ -44101,7 +44101,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.89266264438629</v>
+        <v>1.892662525177</v>
       </c>
       <c r="H1508" t="n">
         <v>17878</v>
@@ -44130,7 +44130,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.92820537090302</v>
+        <v>1.9282054901123</v>
       </c>
       <c r="H1509" t="n">
         <v>6792</v>
@@ -44159,7 +44159,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.92820537090302</v>
+        <v>1.9282054901123</v>
       </c>
       <c r="H1510" t="n">
         <v>19677</v>
@@ -44246,7 +44246,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.96374833583832</v>
+        <v>1.96374845504761</v>
       </c>
       <c r="H1513" t="n">
         <v>7975</v>
@@ -44275,7 +44275,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.98151993751526</v>
+        <v>1.98151981830597</v>
       </c>
       <c r="H1514" t="n">
         <v>2484</v>
@@ -44304,7 +44304,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.94597697257996</v>
+        <v>1.94597685337067</v>
       </c>
       <c r="H1515" t="n">
         <v>2415</v>
@@ -44362,7 +44362,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1517" t="n">
         <v>13564</v>
@@ -44681,7 +44681,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.92820537090302</v>
+        <v>1.9282054901123</v>
       </c>
       <c r="H1528" t="n">
         <v>15155</v>
@@ -44739,7 +44739,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.89266264438629</v>
+        <v>1.892662525177</v>
       </c>
       <c r="H1530" t="n">
         <v>5036</v>
@@ -44855,7 +44855,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.96374833583832</v>
+        <v>1.96374845504761</v>
       </c>
       <c r="H1534" t="n">
         <v>95563</v>
@@ -44884,7 +44884,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.05260586738586</v>
+        <v>2.05260562896729</v>
       </c>
       <c r="H1535" t="n">
         <v>152799</v>
@@ -45058,7 +45058,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.94597697257996</v>
+        <v>1.94597685337067</v>
       </c>
       <c r="H1541" t="n">
         <v>13212</v>
@@ -45087,7 +45087,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.89266264438629</v>
+        <v>1.892662525177</v>
       </c>
       <c r="H1542" t="n">
         <v>39721</v>
@@ -45667,7 +45667,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.772705078125</v>
+        <v>1.77270495891571</v>
       </c>
       <c r="H1562" t="n">
         <v>26489</v>
@@ -45725,7 +45725,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.74604773521423</v>
+        <v>1.74604785442352</v>
       </c>
       <c r="H1564" t="n">
         <v>8696</v>
@@ -45841,7 +45841,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.67496180534363</v>
+        <v>1.67496192455292</v>
       </c>
       <c r="H1568" t="n">
         <v>12751</v>
@@ -45957,7 +45957,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.54167568683624</v>
+        <v>1.54167580604553</v>
       </c>
       <c r="H1572" t="n">
         <v>15772</v>
@@ -46015,7 +46015,7 @@
         <v>1.875</v>
       </c>
       <c r="G1574" t="n">
-        <v>1.66607618331909</v>
+        <v>1.6660760641098</v>
       </c>
       <c r="H1574" t="n">
         <v>18947</v>
@@ -46044,7 +46044,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.63497614860535</v>
+        <v>1.63497602939606</v>
       </c>
       <c r="H1575" t="n">
         <v>4635</v>
@@ -46102,7 +46102,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1577" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1577" t="n">
         <v>40527</v>
@@ -46131,7 +46131,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.652747631073</v>
+        <v>1.65274751186371</v>
       </c>
       <c r="H1578" t="n">
         <v>68395</v>
@@ -46160,7 +46160,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1579" t="n">
-        <v>1.67051899433136</v>
+        <v>1.67051887512207</v>
       </c>
       <c r="H1579" t="n">
         <v>58957</v>
@@ -46218,7 +46218,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.60387587547302</v>
+        <v>1.60387575626373</v>
       </c>
       <c r="H1581" t="n">
         <v>49590</v>
@@ -46247,7 +46247,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.60387587547302</v>
+        <v>1.60387575626373</v>
       </c>
       <c r="H1582" t="n">
         <v>32522</v>
@@ -46305,7 +46305,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.67051899433136</v>
+        <v>1.67051887512207</v>
       </c>
       <c r="H1584" t="n">
         <v>805</v>
@@ -46392,7 +46392,7 @@
         <v>1.875</v>
       </c>
       <c r="G1587" t="n">
-        <v>1.66607618331909</v>
+        <v>1.6660760641098</v>
       </c>
       <c r="H1587" t="n">
         <v>115220</v>
@@ -46566,7 +46566,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.54611873626709</v>
+        <v>1.5461186170578</v>
       </c>
       <c r="H1593" t="n">
         <v>47601</v>
@@ -46653,7 +46653,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1596" t="n">
-        <v>1.54611873626709</v>
+        <v>1.5461186170578</v>
       </c>
       <c r="H1596" t="n">
         <v>23227</v>
@@ -46769,7 +46769,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.54167568683624</v>
+        <v>1.54167580604553</v>
       </c>
       <c r="H1600" t="n">
         <v>3700</v>
@@ -46827,7 +46827,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.54167568683624</v>
+        <v>1.54167580604553</v>
       </c>
       <c r="H1602" t="n">
         <v>24396</v>
@@ -46914,7 +46914,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.56389009952545</v>
+        <v>1.56388998031616</v>
       </c>
       <c r="H1605" t="n">
         <v>12425</v>
@@ -47088,7 +47088,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.98151993751526</v>
+        <v>1.98151981830597</v>
       </c>
       <c r="H1611" t="n">
         <v>172484</v>
@@ -47146,7 +47146,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1613" t="n">
-        <v>2.0614914894104</v>
+        <v>2.06149172782898</v>
       </c>
       <c r="H1613" t="n">
         <v>738098</v>
@@ -47349,7 +47349,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1620" t="n">
-        <v>1.772705078125</v>
+        <v>1.77270495891571</v>
       </c>
       <c r="H1620" t="n">
         <v>19815</v>
@@ -47552,7 +47552,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.0614914894104</v>
+        <v>2.06149172782898</v>
       </c>
       <c r="H1627" t="n">
         <v>237501</v>
@@ -47581,7 +47581,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1628" t="n">
-        <v>1.98151993751526</v>
+        <v>1.98151981830597</v>
       </c>
       <c r="H1628" t="n">
         <v>226003</v>
@@ -47610,7 +47610,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1629" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709135055542</v>
       </c>
       <c r="H1629" t="n">
         <v>48556</v>
@@ -47639,7 +47639,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>1.92820537090302</v>
+        <v>1.9282054901123</v>
       </c>
       <c r="H1630" t="n">
         <v>39551</v>
@@ -47668,7 +47668,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1631" t="n">
-        <v>1.98151993751526</v>
+        <v>1.98151981830597</v>
       </c>
       <c r="H1631" t="n">
         <v>88665</v>
@@ -47697,7 +47697,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1632" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709135055542</v>
       </c>
       <c r="H1632" t="n">
         <v>49844</v>
@@ -47755,7 +47755,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1634" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709135055542</v>
       </c>
       <c r="H1634" t="n">
         <v>11712</v>
@@ -47784,7 +47784,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1635" t="n">
-        <v>1.89266264438629</v>
+        <v>1.892662525177</v>
       </c>
       <c r="H1635" t="n">
         <v>18780</v>
@@ -47813,7 +47813,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1636" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1636" t="n">
         <v>6310</v>
@@ -47842,7 +47842,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1637" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1637" t="n">
         <v>42104</v>
@@ -47958,7 +47958,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1641" t="n">
-        <v>1.63497614860535</v>
+        <v>1.63497602939606</v>
       </c>
       <c r="H1641" t="n">
         <v>37668</v>
@@ -47987,7 +47987,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.66163313388824</v>
+        <v>1.66163325309753</v>
       </c>
       <c r="H1642" t="n">
         <v>12553</v>
@@ -48190,7 +48190,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.93709123134613</v>
+        <v>1.93709135055542</v>
       </c>
       <c r="H1649" t="n">
         <v>39528</v>
@@ -48277,7 +48277,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.91043412685394</v>
+        <v>1.91043400764465</v>
       </c>
       <c r="H1652" t="n">
         <v>10830</v>
@@ -48393,7 +48393,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1656" t="n">
-        <v>1.67051899433136</v>
+        <v>1.67051887512207</v>
       </c>
       <c r="H1656" t="n">
         <v>35951</v>
@@ -48596,7 +48596,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.69273316860199</v>
+        <v>1.69273328781128</v>
       </c>
       <c r="H1663" t="n">
         <v>11902</v>
@@ -48857,7 +48857,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1672" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1672" t="n">
         <v>2609</v>
@@ -49031,7 +49031,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1678" t="n">
-        <v>1.772705078125</v>
+        <v>1.77270495891571</v>
       </c>
       <c r="H1678" t="n">
         <v>4080</v>
@@ -49292,7 +49292,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1687" t="n">
-        <v>1.772705078125</v>
+        <v>1.77270495891571</v>
       </c>
       <c r="H1687" t="n">
         <v>2000</v>
@@ -49350,7 +49350,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.76381921768188</v>
+        <v>1.76381933689117</v>
       </c>
       <c r="H1689" t="n">
         <v>4500</v>
@@ -49553,7 +49553,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H1696" t="n">
         <v>9812</v>
@@ -49611,7 +49611,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.67496180534363</v>
+        <v>1.67496192455292</v>
       </c>
       <c r="H1698" t="n">
         <v>3501</v>
@@ -49640,7 +49640,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1699" t="n">
-        <v>1.63497614860535</v>
+        <v>1.63497602939606</v>
       </c>
       <c r="H1699" t="n">
         <v>4255</v>
@@ -49669,7 +49669,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.65719032287598</v>
+        <v>1.65719044208527</v>
       </c>
       <c r="H1700" t="n">
         <v>3701</v>
@@ -49698,7 +49698,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1701" t="n">
-        <v>1.66163313388824</v>
+        <v>1.66163325309753</v>
       </c>
       <c r="H1701" t="n">
         <v>936</v>
@@ -49901,7 +49901,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1708" t="n">
-        <v>1.67496180534363</v>
+        <v>1.67496192455292</v>
       </c>
       <c r="H1708" t="n">
         <v>5702</v>
@@ -49930,7 +49930,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1709" t="n">
-        <v>1.66163313388824</v>
+        <v>1.66163325309753</v>
       </c>
       <c r="H1709" t="n">
         <v>4151</v>
@@ -49959,7 +49959,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.63497614860535</v>
+        <v>1.63497602939606</v>
       </c>
       <c r="H1710" t="n">
         <v>4365</v>
@@ -50046,7 +50046,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.56389009952545</v>
+        <v>1.56388998031616</v>
       </c>
       <c r="H1713" t="n">
         <v>24121</v>
@@ -50104,7 +50104,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.53723287582397</v>
+        <v>1.53723299503326</v>
       </c>
       <c r="H1715" t="n">
         <v>1000</v>
@@ -50162,7 +50162,7 @@
         <v>1.5</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1717" t="n">
         <v>85300</v>
@@ -50858,7 +50858,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.24844634532928</v>
+        <v>1.24844646453857</v>
       </c>
       <c r="H1741" t="n">
         <v>6690</v>
@@ -50974,7 +50974,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.25288915634155</v>
+        <v>1.25288927555084</v>
       </c>
       <c r="H1745" t="n">
         <v>2451</v>
@@ -51003,7 +51003,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1746" t="n">
         <v>433</v>
@@ -51177,7 +51177,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1752" t="n">
-        <v>1.25288915634155</v>
+        <v>1.25288927555084</v>
       </c>
       <c r="H1752" t="n">
         <v>2600</v>
@@ -51322,7 +51322,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1757" t="n">
-        <v>1.24844634532928</v>
+        <v>1.24844646453857</v>
       </c>
       <c r="H1757" t="n">
         <v>6064</v>
@@ -51380,7 +51380,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1759" t="n">
         <v>15986</v>
@@ -51409,7 +51409,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1760" t="n">
-        <v>1.24844634532928</v>
+        <v>1.24844646453857</v>
       </c>
       <c r="H1760" t="n">
         <v>529</v>
@@ -51496,7 +51496,7 @@
         <v>1.5</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1763" t="n">
         <v>2750</v>
@@ -51554,7 +51554,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1765" t="n">
-        <v>1.3550751209259</v>
+        <v>1.35507524013519</v>
       </c>
       <c r="H1765" t="n">
         <v>3389</v>
@@ -51583,7 +51583,7 @@
         <v>1.5</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1766" t="n">
         <v>7934</v>
@@ -51815,7 +51815,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1774" t="n">
         <v>7396</v>
@@ -51931,7 +51931,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H1778" t="n">
         <v>10221</v>
@@ -51960,7 +51960,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1779" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H1779" t="n">
         <v>10700</v>
@@ -51989,7 +51989,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.34618949890137</v>
+        <v>1.34618937969208</v>
       </c>
       <c r="H1780" t="n">
         <v>13233</v>
@@ -52018,7 +52018,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1781" t="n">
-        <v>1.3906182050705</v>
+        <v>1.39061832427979</v>
       </c>
       <c r="H1781" t="n">
         <v>22831</v>
@@ -52047,7 +52047,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.42171835899353</v>
+        <v>1.42171823978424</v>
       </c>
       <c r="H1782" t="n">
         <v>11355</v>
@@ -52105,7 +52105,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1784" t="n">
-        <v>1.42171835899353</v>
+        <v>1.42171823978424</v>
       </c>
       <c r="H1784" t="n">
         <v>2575</v>
@@ -52192,7 +52192,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.38173246383667</v>
+        <v>1.38173234462738</v>
       </c>
       <c r="H1787" t="n">
         <v>15260</v>
@@ -52221,7 +52221,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.3906182050705</v>
+        <v>1.39061832427979</v>
       </c>
       <c r="H1788" t="n">
         <v>5200</v>
@@ -52279,7 +52279,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.38173246383667</v>
+        <v>1.38173234462738</v>
       </c>
       <c r="H1790" t="n">
         <v>12176</v>
@@ -52308,7 +52308,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1791" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950382709503</v>
       </c>
       <c r="H1791" t="n">
         <v>6627</v>
@@ -52337,7 +52337,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950382709503</v>
       </c>
       <c r="H1792" t="n">
         <v>7634</v>
@@ -52424,7 +52424,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H1795" t="n">
         <v>6400</v>
@@ -52540,7 +52540,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H1799" t="n">
         <v>1251</v>
@@ -52656,7 +52656,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1803" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H1803" t="n">
         <v>8805</v>
@@ -52888,7 +52888,7 @@
         <v>1.5</v>
       </c>
       <c r="G1811" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1811" t="n">
         <v>10698</v>
@@ -52917,7 +52917,7 @@
         <v>1.5</v>
       </c>
       <c r="G1812" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1812" t="n">
         <v>15981</v>
@@ -53062,7 +53062,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.28398931026459</v>
+        <v>1.28398942947388</v>
       </c>
       <c r="H1817" t="n">
         <v>61062</v>
@@ -53207,7 +53207,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1822" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1822" t="n">
         <v>11614</v>
@@ -53352,7 +53352,7 @@
         <v>1.5</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1827" t="n">
         <v>36584</v>
@@ -53381,7 +53381,7 @@
         <v>1.5</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1828" t="n">
         <v>30849</v>
@@ -53468,7 +53468,7 @@
         <v>1.5</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1831" t="n">
         <v>22500</v>
@@ -53700,7 +53700,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1839" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H1839" t="n">
         <v>11383</v>
@@ -53758,7 +53758,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.34618949890137</v>
+        <v>1.34618937969208</v>
       </c>
       <c r="H1841" t="n">
         <v>7926</v>
@@ -53816,7 +53816,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.34618949890137</v>
+        <v>1.34618937969208</v>
       </c>
       <c r="H1843" t="n">
         <v>13987</v>
@@ -54048,7 +54048,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1851" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1851" t="n">
         <v>12688</v>
@@ -54077,7 +54077,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.23956072330475</v>
+        <v>1.23956060409546</v>
       </c>
       <c r="H1852" t="n">
         <v>10296</v>
@@ -54106,7 +54106,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>1.25733208656311</v>
+        <v>1.25733196735382</v>
       </c>
       <c r="H1853" t="n">
         <v>15984</v>
@@ -54164,7 +54164,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.25733208656311</v>
+        <v>1.25733196735382</v>
       </c>
       <c r="H1855" t="n">
         <v>18900</v>
@@ -54193,7 +54193,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.24844634532928</v>
+        <v>1.24844646453857</v>
       </c>
       <c r="H1856" t="n">
         <v>12409</v>
@@ -54251,7 +54251,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1858" t="n">
         <v>8100</v>
@@ -54280,7 +54280,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1859" t="n">
         <v>6590</v>
@@ -54309,7 +54309,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1860" t="n">
         <v>5880</v>
@@ -54512,7 +54512,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.17291760444641</v>
+        <v>1.1729177236557</v>
       </c>
       <c r="H1867" t="n">
         <v>10594</v>
@@ -54570,7 +54570,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.19068896770477</v>
+        <v>1.19068908691406</v>
       </c>
       <c r="H1869" t="n">
         <v>12834</v>
@@ -54599,7 +54599,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.19513201713562</v>
+        <v>1.19513189792633</v>
       </c>
       <c r="H1870" t="n">
         <v>15745</v>
@@ -54686,7 +54686,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.19513201713562</v>
+        <v>1.19513189792633</v>
       </c>
       <c r="H1873" t="n">
         <v>8800</v>
@@ -54802,7 +54802,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1877" t="n">
         <v>2841</v>
@@ -54831,7 +54831,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1878" t="n">
         <v>453</v>
@@ -55092,7 +55092,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.23956072330475</v>
+        <v>1.23956060409546</v>
       </c>
       <c r="H1887" t="n">
         <v>11050</v>
@@ -55121,7 +55121,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1888" t="n">
         <v>1550</v>
@@ -55411,7 +55411,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.19068896770477</v>
+        <v>1.19068908691406</v>
       </c>
       <c r="H1898" t="n">
         <v>6797</v>
@@ -55498,7 +55498,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.23956072330475</v>
+        <v>1.23956060409546</v>
       </c>
       <c r="H1901" t="n">
         <v>7802</v>
@@ -55527,7 +55527,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.23956072330475</v>
+        <v>1.23956060409546</v>
       </c>
       <c r="H1902" t="n">
         <v>4305</v>
@@ -55556,7 +55556,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.23956072330475</v>
+        <v>1.23956060409546</v>
       </c>
       <c r="H1903" t="n">
         <v>2146</v>
@@ -55643,7 +55643,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.23956072330475</v>
+        <v>1.23956060409546</v>
       </c>
       <c r="H1906" t="n">
         <v>8952</v>
@@ -55672,7 +55672,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1907" t="n">
         <v>2450</v>
@@ -55701,7 +55701,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1908" t="n">
         <v>31243</v>
@@ -55759,7 +55759,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.23956072330475</v>
+        <v>1.23956060409546</v>
       </c>
       <c r="H1910" t="n">
         <v>4042</v>
@@ -55875,7 +55875,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.23956072330475</v>
+        <v>1.23956060409546</v>
       </c>
       <c r="H1914" t="n">
         <v>11822</v>
@@ -55933,7 +55933,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.23956072330475</v>
+        <v>1.23956060409546</v>
       </c>
       <c r="H1916" t="n">
         <v>17802</v>
@@ -55991,7 +55991,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1918" t="n">
         <v>29001</v>
@@ -56107,7 +56107,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.25288915634155</v>
+        <v>1.25288927555084</v>
       </c>
       <c r="H1922" t="n">
         <v>1538</v>
@@ -56165,7 +56165,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1924" t="n">
-        <v>1.25733208656311</v>
+        <v>1.25733196735382</v>
       </c>
       <c r="H1924" t="n">
         <v>59412</v>
@@ -56281,7 +56281,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.34618949890137</v>
+        <v>1.34618937969208</v>
       </c>
       <c r="H1928" t="n">
         <v>9399</v>
@@ -56310,7 +56310,7 @@
         <v>1.5</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1929" t="n">
         <v>8468</v>
@@ -56803,7 +56803,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1946" t="n">
-        <v>1.28398931026459</v>
+        <v>1.28398942947388</v>
       </c>
       <c r="H1946" t="n">
         <v>2870</v>
@@ -57093,7 +57093,7 @@
         <v>1.5</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1956" t="n">
         <v>2027</v>
@@ -57122,7 +57122,7 @@
         <v>1.5</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1957" t="n">
         <v>3864</v>
@@ -57151,7 +57151,7 @@
         <v>1.5</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1958" t="n">
         <v>2000</v>
@@ -57209,7 +57209,7 @@
         <v>1.5</v>
       </c>
       <c r="G1960" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1960" t="n">
         <v>3302</v>
@@ -57267,7 +57267,7 @@
         <v>1.5</v>
       </c>
       <c r="G1962" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H1962" t="n">
         <v>8101</v>
@@ -57876,7 +57876,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1983" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1983" t="n">
         <v>7623</v>
@@ -57905,7 +57905,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.26621770858765</v>
+        <v>1.26621782779694</v>
       </c>
       <c r="H1984" t="n">
         <v>2710</v>
@@ -57934,7 +57934,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.25733208656311</v>
+        <v>1.25733196735382</v>
       </c>
       <c r="H1985" t="n">
         <v>500</v>
@@ -58021,7 +58021,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1988" t="n">
         <v>3002</v>
@@ -58050,7 +58050,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.2351176738739</v>
+        <v>1.23511779308319</v>
       </c>
       <c r="H1989" t="n">
         <v>0</v>
@@ -58137,7 +58137,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.14626026153564</v>
+        <v>1.14626038074493</v>
       </c>
       <c r="H1992" t="n">
         <v>7793</v>
@@ -58195,7 +58195,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.19068896770477</v>
+        <v>1.19068908691406</v>
       </c>
       <c r="H1994" t="n">
         <v>12205</v>
@@ -58311,7 +58311,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1998" t="n">
-        <v>1.17291760444641</v>
+        <v>1.1729177236557</v>
       </c>
       <c r="H1998" t="n">
         <v>19450</v>
@@ -58340,7 +58340,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.14626026153564</v>
+        <v>1.14626038074493</v>
       </c>
       <c r="H1999" t="n">
         <v>8399</v>
@@ -58369,7 +58369,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.14626026153564</v>
+        <v>1.14626038074493</v>
       </c>
       <c r="H2000" t="n">
         <v>5713</v>
@@ -58398,7 +58398,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.19068896770477</v>
+        <v>1.19068908691406</v>
       </c>
       <c r="H2001" t="n">
         <v>4882</v>
@@ -58630,7 +58630,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G2009" t="n">
-        <v>1.14626026153564</v>
+        <v>1.14626038074493</v>
       </c>
       <c r="H2009" t="n">
         <v>13323</v>
@@ -58659,7 +58659,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G2010" t="n">
-        <v>1.17291760444641</v>
+        <v>1.1729177236557</v>
       </c>
       <c r="H2010" t="n">
         <v>5583</v>
@@ -58949,7 +58949,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G2020" t="n">
-        <v>1.37284660339355</v>
+        <v>1.37284672260284</v>
       </c>
       <c r="H2020" t="n">
         <v>18573</v>
@@ -59007,7 +59007,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.36396098136902</v>
+        <v>1.36396086215973</v>
       </c>
       <c r="H2022" t="n">
         <v>13110</v>
@@ -59442,7 +59442,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2037" t="n">
-        <v>1.652747631073</v>
+        <v>1.65274751186371</v>
       </c>
       <c r="H2037" t="n">
         <v>100406</v>
@@ -59500,7 +59500,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G2039" t="n">
-        <v>1.69273316860199</v>
+        <v>1.69273328781128</v>
       </c>
       <c r="H2039" t="n">
         <v>61842</v>
@@ -59529,7 +59529,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2040" t="n">
-        <v>1.652747631073</v>
+        <v>1.65274751186371</v>
       </c>
       <c r="H2040" t="n">
         <v>43595</v>
@@ -59558,7 +59558,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.68829047679901</v>
+        <v>1.68829035758972</v>
       </c>
       <c r="H2041" t="n">
         <v>7618</v>
@@ -59645,7 +59645,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2044" t="n">
-        <v>1.54167568683624</v>
+        <v>1.54167580604553</v>
       </c>
       <c r="H2044" t="n">
         <v>12449</v>
@@ -59674,7 +59674,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2045" t="n">
-        <v>1.54611873626709</v>
+        <v>1.5461186170578</v>
       </c>
       <c r="H2045" t="n">
         <v>17253</v>
@@ -59732,7 +59732,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2047" t="n">
-        <v>1.53723287582397</v>
+        <v>1.53723299503326</v>
       </c>
       <c r="H2047" t="n">
         <v>16065</v>
@@ -59790,7 +59790,7 @@
         <v>1.75</v>
       </c>
       <c r="G2049" t="n">
-        <v>1.55500435829163</v>
+        <v>1.55500447750092</v>
       </c>
       <c r="H2049" t="n">
         <v>9817</v>
@@ -59848,7 +59848,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2051" t="n">
-        <v>1.50169003009796</v>
+        <v>1.50168991088867</v>
       </c>
       <c r="H2051" t="n">
         <v>20007</v>
@@ -59935,7 +59935,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G2054" t="n">
-        <v>1.52834725379944</v>
+        <v>1.52834713459015</v>
       </c>
       <c r="H2054" t="n">
         <v>2596</v>
@@ -59964,7 +59964,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.46614694595337</v>
+        <v>1.46614682674408</v>
       </c>
       <c r="H2055" t="n">
         <v>14171</v>
@@ -60022,7 +60022,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2057" t="n">
-        <v>1.50169003009796</v>
+        <v>1.50168991088867</v>
       </c>
       <c r="H2057" t="n">
         <v>5812</v>
@@ -60225,7 +60225,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G2064" t="n">
-        <v>1.39950394630432</v>
+        <v>1.39950382709503</v>
       </c>
       <c r="H2064" t="n">
         <v>5469</v>
@@ -60399,7 +60399,7 @@
         <v>1.5</v>
       </c>
       <c r="G2070" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H2070" t="n">
         <v>1</v>
@@ -60428,7 +60428,7 @@
         <v>1.5</v>
       </c>
       <c r="G2071" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H2071" t="n">
         <v>1882</v>
@@ -60515,7 +60515,7 @@
         <v>1.5</v>
       </c>
       <c r="G2074" t="n">
-        <v>1.33286094665527</v>
+        <v>1.33286082744598</v>
       </c>
       <c r="H2074" t="n">
         <v>1502</v>
@@ -60689,7 +60689,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H2080" t="n">
         <v>5112</v>
@@ -60718,7 +60718,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G2081" t="n">
-        <v>1.33730375766754</v>
+        <v>1.33730387687683</v>
       </c>
       <c r="H2081" t="n">
         <v>5054</v>
@@ -60805,7 +60805,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G2084" t="n">
-        <v>1.3906182050705</v>
+        <v>1.39061832427979</v>
       </c>
       <c r="H2084" t="n">
         <v>23213</v>
@@ -60834,7 +60834,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G2085" t="n">
-        <v>1.42171835899353</v>
+        <v>1.42171823978424</v>
       </c>
       <c r="H2085" t="n">
         <v>12137</v>
@@ -60921,7 +60921,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G2088" t="n">
-        <v>1.42171835899353</v>
+        <v>1.42171823978424</v>
       </c>
       <c r="H2088" t="n">
         <v>2770</v>
@@ -60950,7 +60950,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.3906182050705</v>
+        <v>1.39061832427979</v>
       </c>
       <c r="H2089" t="n">
         <v>2766</v>
@@ -61066,7 +61066,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G2093" t="n">
-        <v>1.3906182050705</v>
+        <v>1.39061832427979</v>
       </c>
       <c r="H2093" t="n">
         <v>4034</v>
@@ -61095,7 +61095,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G2094" t="n">
-        <v>1.42171835899353</v>
+        <v>1.42171823978424</v>
       </c>
       <c r="H2094" t="n">
         <v>16512</v>
@@ -61240,7 +61240,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2099" t="n">
-        <v>1.63497614860535</v>
+        <v>1.63497602939606</v>
       </c>
       <c r="H2099" t="n">
         <v>51521</v>
@@ -61269,7 +61269,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2100" t="n">
-        <v>1.63941884040833</v>
+        <v>1.63941895961761</v>
       </c>
       <c r="H2100" t="n">
         <v>21883</v>
@@ -61298,7 +61298,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2101" t="n">
-        <v>1.63941884040833</v>
+        <v>1.63941895961761</v>
       </c>
       <c r="H2101" t="n">
         <v>1012</v>
@@ -61327,7 +61327,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G2102" t="n">
-        <v>1.60387587547302</v>
+        <v>1.60387575626373</v>
       </c>
       <c r="H2102" t="n">
         <v>12444</v>
@@ -61356,7 +61356,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.53723287582397</v>
+        <v>1.53723299503326</v>
       </c>
       <c r="H2103" t="n">
         <v>33473</v>
@@ -61414,7 +61414,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G2105" t="n">
-        <v>1.50169003009796</v>
+        <v>1.50168991088867</v>
       </c>
       <c r="H2105" t="n">
         <v>7001</v>
@@ -61472,7 +61472,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2107" t="n">
-        <v>1.56389009952545</v>
+        <v>1.56388998031616</v>
       </c>
       <c r="H2107" t="n">
         <v>5236</v>
@@ -61559,7 +61559,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.47947549819946</v>
+        <v>1.47947561740875</v>
       </c>
       <c r="H2110" t="n">
         <v>2480</v>
@@ -61617,7 +61617,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G2112" t="n">
-        <v>1.3906182050705</v>
+        <v>1.39061832427979</v>
       </c>
       <c r="H2112" t="n">
         <v>29998</v>
@@ -61675,7 +61675,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.42171835899353</v>
+        <v>1.42171823978424</v>
       </c>
       <c r="H2114" t="n">
         <v>302</v>
@@ -61820,7 +61820,7 @@
         <v>1.75</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.55500435829163</v>
+        <v>1.55500447750092</v>
       </c>
       <c r="H2119" t="n">
         <v>12375</v>
@@ -61878,7 +61878,7 @@
         <v>1.75</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.55500435829163</v>
+        <v>1.55500447750092</v>
       </c>
       <c r="H2121" t="n">
         <v>15385</v>
@@ -61907,7 +61907,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G2122" t="n">
-        <v>1.56389009952545</v>
+        <v>1.56388998031616</v>
       </c>
       <c r="H2122" t="n">
         <v>14550</v>
@@ -80125,6 +80125,35 @@
         <v>72773</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>60835</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLC.MI.xlsx
+++ b/data/PLC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.35138177871704</v>
       </c>
       <c r="G2" t="n">
-        <v>4.42682695388794</v>
+        <v>4.42682647705078</v>
       </c>
       <c r="H2" t="n">
         <v>748</v>
@@ -456,7 +456,7 @@
         <v>5.35138177871704</v>
       </c>
       <c r="G3" t="n">
-        <v>4.42682695388794</v>
+        <v>4.42682647705078</v>
       </c>
       <c r="H3" t="n">
         <v>253</v>
@@ -485,7 +485,7 @@
         <v>5.35138177871704</v>
       </c>
       <c r="G4" t="n">
-        <v>4.42682695388794</v>
+        <v>4.42682647705078</v>
       </c>
       <c r="H4" t="n">
         <v>349</v>
@@ -601,7 +601,7 @@
         <v>4.80663108825684</v>
       </c>
       <c r="G8" t="n">
-        <v>3.97619199752808</v>
+        <v>3.97619152069092</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -630,7 +630,7 @@
         <v>4.81019115447998</v>
       </c>
       <c r="G9" t="n">
-        <v>3.9791374206543</v>
+        <v>3.97913670539856</v>
       </c>
       <c r="H9" t="n">
         <v>912</v>
@@ -659,7 +659,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G10" t="n">
-        <v>3.68165922164917</v>
+        <v>3.68165874481201</v>
       </c>
       <c r="H10" t="n">
         <v>1371</v>
@@ -688,7 +688,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G11" t="n">
-        <v>3.68165922164917</v>
+        <v>3.68165874481201</v>
       </c>
       <c r="H11" t="n">
         <v>5201</v>
@@ -775,7 +775,7 @@
         <v>3.77409505844116</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12204647064209</v>
+        <v>3.12204670906067</v>
       </c>
       <c r="H14" t="n">
         <v>470</v>
@@ -804,7 +804,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H15" t="n">
         <v>2158</v>
@@ -978,7 +978,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G21" t="n">
-        <v>3.68165922164917</v>
+        <v>3.68165874481201</v>
       </c>
       <c r="H21" t="n">
         <v>978</v>
@@ -1007,7 +1007,7 @@
         <v>4.77102613449097</v>
       </c>
       <c r="G22" t="n">
-        <v>3.94673848152161</v>
+        <v>3.94673800468445</v>
       </c>
       <c r="H22" t="n">
         <v>3421</v>
@@ -1036,7 +1036,7 @@
         <v>4.53959512710571</v>
       </c>
       <c r="G23" t="n">
-        <v>3.75529170036316</v>
+        <v>3.75529146194458</v>
       </c>
       <c r="H23" t="n">
         <v>556</v>
@@ -1065,7 +1065,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G24" t="n">
-        <v>3.68165922164917</v>
+        <v>3.68165874481201</v>
       </c>
       <c r="H24" t="n">
         <v>56</v>
@@ -1123,7 +1123,7 @@
         <v>4.53959512710571</v>
       </c>
       <c r="G26" t="n">
-        <v>3.75529170036316</v>
+        <v>3.75529146194458</v>
       </c>
       <c r="H26" t="n">
         <v>224</v>
@@ -1181,7 +1181,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G28" t="n">
-        <v>3.68165922164917</v>
+        <v>3.68165874481201</v>
       </c>
       <c r="H28" t="n">
         <v>1864</v>
@@ -1210,7 +1210,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G29" t="n">
-        <v>3.68165922164917</v>
+        <v>3.68165874481201</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G30" t="n">
-        <v>3.69638562202454</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H30" t="n">
         <v>333</v>
@@ -1268,7 +1268,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G31" t="n">
-        <v>3.69638562202454</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H31" t="n">
         <v>33</v>
@@ -1297,7 +1297,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G32" t="n">
-        <v>3.69638562202454</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G33" t="n">
-        <v>3.69638562202454</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G34" t="n">
-        <v>3.69638562202454</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G35" t="n">
-        <v>3.69638562202454</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G36" t="n">
-        <v>3.69638562202454</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>4.46838617324829</v>
       </c>
       <c r="G37" t="n">
-        <v>3.69638562202454</v>
+        <v>3.69638514518738</v>
       </c>
       <c r="H37" t="n">
         <v>168</v>
@@ -1471,7 +1471,7 @@
         <v>3.99840402603149</v>
       </c>
       <c r="G38" t="n">
-        <v>3.30760192871094</v>
+        <v>3.30760169029236</v>
       </c>
       <c r="H38" t="n">
         <v>318</v>
@@ -1500,7 +1500,7 @@
         <v>4.03044891357422</v>
       </c>
       <c r="G39" t="n">
-        <v>3.33411002159119</v>
+        <v>3.33411026000977</v>
       </c>
       <c r="H39" t="n">
         <v>151</v>
@@ -1645,7 +1645,7 @@
         <v>4.03400897979736</v>
       </c>
       <c r="G44" t="n">
-        <v>3.33705544471741</v>
+        <v>3.33705520629883</v>
       </c>
       <c r="H44" t="n">
         <v>1197</v>
@@ -1674,7 +1674,7 @@
         <v>4.40785789489746</v>
       </c>
       <c r="G45" t="n">
-        <v>3.64631414413452</v>
+        <v>3.64631462097168</v>
       </c>
       <c r="H45" t="n">
         <v>280</v>
@@ -1703,7 +1703,7 @@
         <v>4.40785789489746</v>
       </c>
       <c r="G46" t="n">
-        <v>3.64631414413452</v>
+        <v>3.64631462097168</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G47" t="n">
-        <v>3.49315810203552</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H47" t="n">
         <v>290</v>
@@ -1761,7 +1761,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G48" t="n">
-        <v>3.49315810203552</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G49" t="n">
-        <v>3.49315810203552</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H49" t="n">
         <v>43</v>
@@ -1819,7 +1819,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G50" t="n">
-        <v>3.49315810203552</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>4.59300184249878</v>
       </c>
       <c r="G52" t="n">
-        <v>3.799471616745</v>
+        <v>3.79947113990784</v>
       </c>
       <c r="H52" t="n">
         <v>1124</v>
@@ -2022,7 +2022,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G57" t="n">
-        <v>3.68165922164917</v>
+        <v>3.68165874481201</v>
       </c>
       <c r="H57" t="n">
         <v>148</v>
@@ -2051,7 +2051,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G58" t="n">
-        <v>3.68165922164917</v>
+        <v>3.68165874481201</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>3.82750201225281</v>
       </c>
       <c r="G69" t="n">
-        <v>3.16622614860535</v>
+        <v>3.1662266254425</v>
       </c>
       <c r="H69" t="n">
         <v>357</v>
@@ -2544,7 +2544,7 @@
         <v>4.18176794052124</v>
       </c>
       <c r="G75" t="n">
-        <v>3.45928597450256</v>
+        <v>3.45928621292114</v>
       </c>
       <c r="H75" t="n">
         <v>1353</v>
@@ -2631,7 +2631,7 @@
         <v>3.94321703910828</v>
       </c>
       <c r="G78" t="n">
-        <v>3.26194930076599</v>
+        <v>3.26194953918457</v>
       </c>
       <c r="H78" t="n">
         <v>55</v>
@@ -2747,7 +2747,7 @@
         <v>4.29036283493042</v>
       </c>
       <c r="G82" t="n">
-        <v>3.54911923408508</v>
+        <v>3.5491189956665</v>
       </c>
       <c r="H82" t="n">
         <v>2234</v>
@@ -2979,7 +2979,7 @@
         <v>4.2102518081665</v>
       </c>
       <c r="G90" t="n">
-        <v>3.48284888267517</v>
+        <v>3.48284864425659</v>
       </c>
       <c r="H90" t="n">
         <v>1430</v>
@@ -3124,7 +3124,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G95" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H95" t="n">
         <v>1</v>
@@ -3153,7 +3153,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G96" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H96" t="n">
         <v>1123</v>
@@ -3298,7 +3298,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G101" t="n">
-        <v>2.85696721076965</v>
+        <v>2.85696744918823</v>
       </c>
       <c r="H101" t="n">
         <v>646</v>
@@ -3327,7 +3327,7 @@
         <v>3.90583205223083</v>
       </c>
       <c r="G102" t="n">
-        <v>3.23102331161499</v>
+        <v>3.23102355003357</v>
       </c>
       <c r="H102" t="n">
         <v>112</v>
@@ -3356,7 +3356,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G103" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H103" t="n">
         <v>356</v>
@@ -3385,7 +3385,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G104" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G105" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G106" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G107" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G108" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G109" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>4.01798677444458</v>
       </c>
       <c r="G110" t="n">
-        <v>3.32380104064941</v>
+        <v>3.32380127906799</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>3.5106201171875</v>
       </c>
       <c r="G111" t="n">
-        <v>2.90409207344055</v>
+        <v>2.90409231185913</v>
       </c>
       <c r="H111" t="n">
         <v>5</v>
@@ -3646,7 +3646,7 @@
         <v>3.64947891235352</v>
       </c>
       <c r="G113" t="n">
-        <v>3.01896047592163</v>
+        <v>3.01896023750305</v>
       </c>
       <c r="H113" t="n">
         <v>1270</v>
@@ -3878,7 +3878,7 @@
         <v>3.20442008972168</v>
       </c>
       <c r="G121" t="n">
-        <v>2.65079426765442</v>
+        <v>2.65079402923584</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>3.3005530834198</v>
       </c>
       <c r="G123" t="n">
-        <v>2.73031806945801</v>
+        <v>2.73031830787659</v>
       </c>
       <c r="H123" t="n">
         <v>190</v>
@@ -3965,7 +3965,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G124" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H124" t="n">
         <v>1581</v>
@@ -3994,7 +3994,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G125" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H125" t="n">
         <v>1216</v>
@@ -4023,7 +4023,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G126" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H126" t="n">
         <v>44</v>
@@ -4052,7 +4052,7 @@
         <v>2.95518708229065</v>
       </c>
       <c r="G127" t="n">
-        <v>2.44462084770203</v>
+        <v>2.44462060928345</v>
       </c>
       <c r="H127" t="n">
         <v>702</v>
@@ -4081,7 +4081,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G128" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H128" t="n">
         <v>113</v>
@@ -4110,7 +4110,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G129" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G130" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H130" t="n">
         <v>206</v>
@@ -4168,7 +4168,7 @@
         <v>2.88041806221008</v>
       </c>
       <c r="G131" t="n">
-        <v>2.38276958465576</v>
+        <v>2.38276982307434</v>
       </c>
       <c r="H131" t="n">
         <v>337</v>
@@ -4226,7 +4226,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G133" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H133" t="n">
         <v>596</v>
@@ -4255,7 +4255,7 @@
         <v>2.40331506729126</v>
       </c>
       <c r="G134" t="n">
-        <v>1.98809552192688</v>
+        <v>1.98809540271759</v>
       </c>
       <c r="H134" t="n">
         <v>22668</v>
@@ -4342,7 +4342,7 @@
         <v>2.04726791381836</v>
       </c>
       <c r="G137" t="n">
-        <v>1.6935623884201</v>
+        <v>1.69356250762939</v>
       </c>
       <c r="H137" t="n">
         <v>15377</v>
@@ -4371,7 +4371,7 @@
         <v>1.86924505233765</v>
       </c>
       <c r="G138" t="n">
-        <v>1.5462965965271</v>
+        <v>1.54629647731781</v>
       </c>
       <c r="H138" t="n">
         <v>19365</v>
@@ -4400,7 +4400,7 @@
         <v>2.13450002670288</v>
       </c>
       <c r="G139" t="n">
-        <v>1.76572346687317</v>
+        <v>1.76572358608246</v>
       </c>
       <c r="H139" t="n">
         <v>11343</v>
@@ -4429,7 +4429,7 @@
         <v>2.41043591499329</v>
       </c>
       <c r="G140" t="n">
-        <v>1.99398624897003</v>
+        <v>1.99398589134216</v>
       </c>
       <c r="H140" t="n">
         <v>25915</v>
@@ -4458,7 +4458,7 @@
         <v>2.25199508666992</v>
       </c>
       <c r="G141" t="n">
-        <v>1.86291921138763</v>
+        <v>1.86291897296906</v>
       </c>
       <c r="H141" t="n">
         <v>9636</v>
@@ -4487,7 +4487,7 @@
         <v>2.17010402679443</v>
       </c>
       <c r="G142" t="n">
-        <v>1.79517638683319</v>
+        <v>1.7951762676239</v>
       </c>
       <c r="H142" t="n">
         <v>2359</v>
@@ -4545,7 +4545,7 @@
         <v>2.26267695426941</v>
       </c>
       <c r="G144" t="n">
-        <v>1.8717554807663</v>
+        <v>1.87175559997559</v>
       </c>
       <c r="H144" t="n">
         <v>2313</v>
@@ -4603,7 +4603,7 @@
         <v>2.07753205299377</v>
       </c>
       <c r="G146" t="n">
-        <v>1.71859788894653</v>
+        <v>1.71859776973724</v>
       </c>
       <c r="H146" t="n">
         <v>6315</v>
@@ -4690,7 +4690,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G149" t="n">
-        <v>1.73774254322052</v>
+        <v>1.73774266242981</v>
       </c>
       <c r="H149" t="n">
         <v>918</v>
@@ -4719,7 +4719,7 @@
         <v>2.28582000732422</v>
       </c>
       <c r="G150" t="n">
-        <v>1.89090001583099</v>
+        <v>1.89090013504028</v>
       </c>
       <c r="H150" t="n">
         <v>14195</v>
@@ -4748,7 +4748,7 @@
         <v>2.28582000732422</v>
       </c>
       <c r="G151" t="n">
-        <v>1.89090001583099</v>
+        <v>1.89090013504028</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>2.28582000732422</v>
       </c>
       <c r="G152" t="n">
-        <v>1.89090001583099</v>
+        <v>1.89090013504028</v>
       </c>
       <c r="H152" t="n">
         <v>56</v>
@@ -4806,7 +4806,7 @@
         <v>1.97071802616119</v>
       </c>
       <c r="G153" t="n">
-        <v>1.63023817539215</v>
+        <v>1.63023805618286</v>
       </c>
       <c r="H153" t="n">
         <v>1399</v>
@@ -4893,7 +4893,7 @@
         <v>2.09711503982544</v>
       </c>
       <c r="G156" t="n">
-        <v>1.73479747772217</v>
+        <v>1.73479759693146</v>
       </c>
       <c r="H156" t="n">
         <v>280</v>
@@ -4951,7 +4951,7 @@
         <v>2.04370808601379</v>
       </c>
       <c r="G158" t="n">
-        <v>1.69061768054962</v>
+        <v>1.69061756134033</v>
       </c>
       <c r="H158" t="n">
         <v>1501</v>
@@ -5038,7 +5038,7 @@
         <v>2.02946591377258</v>
       </c>
       <c r="G161" t="n">
-        <v>1.67883610725403</v>
+        <v>1.67883622646332</v>
       </c>
       <c r="H161" t="n">
         <v>5715</v>
@@ -5067,7 +5067,7 @@
         <v>1.97961902618408</v>
       </c>
       <c r="G162" t="n">
-        <v>1.63760137557983</v>
+        <v>1.63760125637054</v>
       </c>
       <c r="H162" t="n">
         <v>645</v>
@@ -5125,7 +5125,7 @@
         <v>1.94935500621796</v>
       </c>
       <c r="G164" t="n">
-        <v>1.61256575584412</v>
+        <v>1.61256587505341</v>
       </c>
       <c r="H164" t="n">
         <v>829</v>
@@ -5212,7 +5212,7 @@
         <v>1.92265200614929</v>
       </c>
       <c r="G167" t="n">
-        <v>1.59047627449036</v>
+        <v>1.59047651290894</v>
       </c>
       <c r="H167" t="n">
         <v>926</v>
@@ -5241,7 +5241,7 @@
         <v>1.92265200614929</v>
       </c>
       <c r="G168" t="n">
-        <v>1.59047627449036</v>
+        <v>1.59047651290894</v>
       </c>
       <c r="H168" t="n">
         <v>561</v>
@@ -5270,7 +5270,7 @@
         <v>1.92265200614929</v>
       </c>
       <c r="G169" t="n">
-        <v>1.59047627449036</v>
+        <v>1.59047651290894</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>1.86924505233765</v>
       </c>
       <c r="G170" t="n">
-        <v>1.5462965965271</v>
+        <v>1.54629647731781</v>
       </c>
       <c r="H170" t="n">
         <v>690</v>
@@ -5328,7 +5328,7 @@
         <v>1.86924505233765</v>
       </c>
       <c r="G171" t="n">
-        <v>1.5462965965271</v>
+        <v>1.54629647731781</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1.83542001247406</v>
       </c>
       <c r="G172" t="n">
-        <v>1.51831543445587</v>
+        <v>1.51831531524658</v>
       </c>
       <c r="H172" t="n">
         <v>3960</v>
@@ -5386,7 +5386,7 @@
         <v>1.83542001247406</v>
       </c>
       <c r="G173" t="n">
-        <v>1.51831543445587</v>
+        <v>1.51831531524658</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>1.83542001247406</v>
       </c>
       <c r="G174" t="n">
-        <v>1.51831543445587</v>
+        <v>1.51831531524658</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.83363997936249</v>
       </c>
       <c r="G175" t="n">
-        <v>1.51684296131134</v>
+        <v>1.51684284210205</v>
       </c>
       <c r="H175" t="n">
         <v>1417</v>
@@ -5502,7 +5502,7 @@
         <v>2.17188501358032</v>
       </c>
       <c r="G177" t="n">
-        <v>1.79664957523346</v>
+        <v>1.79664969444275</v>
       </c>
       <c r="H177" t="n">
         <v>17162</v>
@@ -5676,7 +5676,7 @@
         <v>2.11847805976868</v>
       </c>
       <c r="G183" t="n">
-        <v>1.75246977806091</v>
+        <v>1.75246965885162</v>
       </c>
       <c r="H183" t="n">
         <v>951</v>
@@ -5763,7 +5763,7 @@
         <v>1.90485000610352</v>
       </c>
       <c r="G186" t="n">
-        <v>1.57574999332428</v>
+        <v>1.57575011253357</v>
       </c>
       <c r="H186" t="n">
         <v>3560</v>
@@ -5850,7 +5850,7 @@
         <v>1.90485000610352</v>
       </c>
       <c r="G189" t="n">
-        <v>1.57574999332428</v>
+        <v>1.57575011253357</v>
       </c>
       <c r="H189" t="n">
         <v>634</v>
@@ -5879,7 +5879,7 @@
         <v>1.99386096000671</v>
       </c>
       <c r="G190" t="n">
-        <v>1.64938247203827</v>
+        <v>1.64938259124756</v>
       </c>
       <c r="H190" t="n">
         <v>619</v>
@@ -5908,7 +5908,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G191" t="n">
-        <v>1.73774254322052</v>
+        <v>1.73774266242981</v>
       </c>
       <c r="H191" t="n">
         <v>4547</v>
@@ -5937,7 +5937,7 @@
         <v>2.29650092124939</v>
       </c>
       <c r="G192" t="n">
-        <v>1.8997358083725</v>
+        <v>1.89973556995392</v>
       </c>
       <c r="H192" t="n">
         <v>5945</v>
@@ -6053,7 +6053,7 @@
         <v>2.40331506729126</v>
       </c>
       <c r="G196" t="n">
-        <v>1.98809552192688</v>
+        <v>1.98809540271759</v>
       </c>
       <c r="H196" t="n">
         <v>7857</v>
@@ -6082,7 +6082,7 @@
         <v>2.31608390808105</v>
       </c>
       <c r="G197" t="n">
-        <v>1.91593539714813</v>
+        <v>1.91593551635742</v>
       </c>
       <c r="H197" t="n">
         <v>4776</v>
@@ -6111,7 +6111,7 @@
         <v>2.41577696800232</v>
       </c>
       <c r="G198" t="n">
-        <v>1.99840450286865</v>
+        <v>1.99840462207794</v>
       </c>
       <c r="H198" t="n">
         <v>1058</v>
@@ -6198,7 +6198,7 @@
         <v>2.35880899429321</v>
       </c>
       <c r="G201" t="n">
-        <v>1.95127880573273</v>
+        <v>1.95127904415131</v>
       </c>
       <c r="H201" t="n">
         <v>224</v>
@@ -6227,7 +6227,7 @@
         <v>2.13450002670288</v>
       </c>
       <c r="G202" t="n">
-        <v>1.76572346687317</v>
+        <v>1.76572358608246</v>
       </c>
       <c r="H202" t="n">
         <v>7171</v>
@@ -6256,7 +6256,7 @@
         <v>2.27869892120361</v>
       </c>
       <c r="G203" t="n">
-        <v>1.88500952720642</v>
+        <v>1.88500928878784</v>
       </c>
       <c r="H203" t="n">
         <v>9785</v>
@@ -6285,7 +6285,7 @@
         <v>2.15764307975769</v>
       </c>
       <c r="G204" t="n">
-        <v>1.78486824035645</v>
+        <v>1.78486812114716</v>
       </c>
       <c r="H204" t="n">
         <v>5715</v>
@@ -6372,7 +6372,7 @@
         <v>2.14340090751648</v>
       </c>
       <c r="G207" t="n">
-        <v>1.77308654785156</v>
+        <v>1.77308666706085</v>
       </c>
       <c r="H207" t="n">
         <v>2034</v>
@@ -6401,7 +6401,7 @@
         <v>2.16298294067383</v>
       </c>
       <c r="G208" t="n">
-        <v>1.78928554058075</v>
+        <v>1.78928542137146</v>
       </c>
       <c r="H208" t="n">
         <v>7479</v>
@@ -6604,7 +6604,7 @@
         <v>2.11669707298279</v>
       </c>
       <c r="G215" t="n">
-        <v>1.75099635124207</v>
+        <v>1.75099623203278</v>
       </c>
       <c r="H215" t="n">
         <v>561</v>
@@ -6662,7 +6662,7 @@
         <v>1.99920201301575</v>
       </c>
       <c r="G217" t="n">
-        <v>1.65380096435547</v>
+        <v>1.65380084514618</v>
       </c>
       <c r="H217" t="n">
         <v>467</v>
@@ -6749,7 +6749,7 @@
         <v>2.02946591377258</v>
       </c>
       <c r="G220" t="n">
-        <v>1.67883610725403</v>
+        <v>1.67883622646332</v>
       </c>
       <c r="H220" t="n">
         <v>898</v>
@@ -6778,7 +6778,7 @@
         <v>2.09711503982544</v>
       </c>
       <c r="G221" t="n">
-        <v>1.73479747772217</v>
+        <v>1.73479759693146</v>
       </c>
       <c r="H221" t="n">
         <v>56</v>
@@ -6894,7 +6894,7 @@
         <v>2.00098204612732</v>
       </c>
       <c r="G225" t="n">
-        <v>1.6552734375</v>
+        <v>1.65527331829071</v>
       </c>
       <c r="H225" t="n">
         <v>56</v>
@@ -6923,7 +6923,7 @@
         <v>2.00454306602478</v>
       </c>
       <c r="G226" t="n">
-        <v>1.65821921825409</v>
+        <v>1.6582190990448</v>
       </c>
       <c r="H226" t="n">
         <v>472</v>
@@ -7184,7 +7184,7 @@
         <v>1.97249805927277</v>
       </c>
       <c r="G235" t="n">
-        <v>1.63171064853668</v>
+        <v>1.63171052932739</v>
       </c>
       <c r="H235" t="n">
         <v>14</v>
@@ -7213,7 +7213,7 @@
         <v>2.04726791381836</v>
       </c>
       <c r="G236" t="n">
-        <v>1.6935623884201</v>
+        <v>1.69356250762939</v>
       </c>
       <c r="H236" t="n">
         <v>379</v>
@@ -7242,7 +7242,7 @@
         <v>2.04726791381836</v>
       </c>
       <c r="G237" t="n">
-        <v>1.6935623884201</v>
+        <v>1.69356250762939</v>
       </c>
       <c r="H237" t="n">
         <v>2813</v>
@@ -7329,7 +7329,7 @@
         <v>2.07041096687317</v>
       </c>
       <c r="G240" t="n">
-        <v>1.71270716190338</v>
+        <v>1.71270704269409</v>
       </c>
       <c r="H240" t="n">
         <v>281</v>
@@ -7358,7 +7358,7 @@
         <v>2.07041096687317</v>
       </c>
       <c r="G241" t="n">
-        <v>1.71270716190338</v>
+        <v>1.71270704269409</v>
       </c>
       <c r="H241" t="n">
         <v>112</v>
@@ -7387,7 +7387,7 @@
         <v>2.11847805976868</v>
       </c>
       <c r="G242" t="n">
-        <v>1.75246977806091</v>
+        <v>1.75246965885162</v>
       </c>
       <c r="H242" t="n">
         <v>2937</v>
@@ -7503,7 +7503,7 @@
         <v>2.10067510604858</v>
       </c>
       <c r="G246" t="n">
-        <v>1.73774254322052</v>
+        <v>1.73774266242981</v>
       </c>
       <c r="H246" t="n">
         <v>664</v>
@@ -7561,7 +7561,7 @@
         <v>2.0846529006958</v>
       </c>
       <c r="G248" t="n">
-        <v>1.72448837757111</v>
+        <v>1.7244884967804</v>
       </c>
       <c r="H248" t="n">
         <v>449</v>
@@ -7590,7 +7590,7 @@
         <v>2.04726791381836</v>
       </c>
       <c r="G249" t="n">
-        <v>1.6935623884201</v>
+        <v>1.69356250762939</v>
       </c>
       <c r="H249" t="n">
         <v>1</v>
@@ -7677,7 +7677,7 @@
         <v>2.04904794692993</v>
       </c>
       <c r="G252" t="n">
-        <v>1.69503486156464</v>
+        <v>1.69503498077393</v>
       </c>
       <c r="H252" t="n">
         <v>16761</v>
@@ -7706,7 +7706,7 @@
         <v>2.16654396057129</v>
       </c>
       <c r="G253" t="n">
-        <v>1.79223120212555</v>
+        <v>1.79223108291626</v>
       </c>
       <c r="H253" t="n">
         <v>9056</v>
@@ -7735,7 +7735,7 @@
         <v>2.45672202110291</v>
       </c>
       <c r="G254" t="n">
-        <v>2.03227519989014</v>
+        <v>2.03227543830872</v>
       </c>
       <c r="H254" t="n">
         <v>27479</v>
@@ -7793,7 +7793,7 @@
         <v>2.41221594810486</v>
       </c>
       <c r="G256" t="n">
-        <v>1.99545872211456</v>
+        <v>1.99545848369598</v>
       </c>
       <c r="H256" t="n">
         <v>7030</v>
@@ -7822,7 +7822,7 @@
         <v>2.34456706047058</v>
       </c>
       <c r="G257" t="n">
-        <v>1.939497590065</v>
+        <v>1.93949747085571</v>
       </c>
       <c r="H257" t="n">
         <v>4814</v>
@@ -7851,7 +7851,7 @@
         <v>2.74155902862549</v>
       </c>
       <c r="G258" t="n">
-        <v>2.26790142059326</v>
+        <v>2.26790118217468</v>
       </c>
       <c r="H258" t="n">
         <v>17046</v>
@@ -8025,7 +8025,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G264" t="n">
-        <v>3.68165922164917</v>
+        <v>3.68165874481201</v>
       </c>
       <c r="H264" t="n">
         <v>7281</v>
@@ -8054,7 +8054,7 @@
         <v>4.67133283615112</v>
       </c>
       <c r="G265" t="n">
-        <v>3.8642692565918</v>
+        <v>3.86426854133606</v>
       </c>
       <c r="H265" t="n">
         <v>108992</v>
@@ -8083,7 +8083,7 @@
         <v>4.35445117950439</v>
       </c>
       <c r="G266" t="n">
-        <v>3.60213494300842</v>
+        <v>3.60213470458984</v>
       </c>
       <c r="H266" t="n">
         <v>67774</v>
@@ -8112,7 +8112,7 @@
         <v>4.40073680877686</v>
       </c>
       <c r="G267" t="n">
-        <v>3.64042401313782</v>
+        <v>3.64042377471924</v>
       </c>
       <c r="H267" t="n">
         <v>57818</v>
@@ -8141,7 +8141,7 @@
         <v>4.45058393478394</v>
       </c>
       <c r="G268" t="n">
-        <v>3.68165922164917</v>
+        <v>3.68165874481201</v>
       </c>
       <c r="H268" t="n">
         <v>8984</v>
@@ -8170,7 +8170,7 @@
         <v>4.3793740272522</v>
       </c>
       <c r="G269" t="n">
-        <v>3.62275218963623</v>
+        <v>3.62275195121765</v>
       </c>
       <c r="H269" t="n">
         <v>7198</v>
@@ -8228,7 +8228,7 @@
         <v>4.05893182754517</v>
       </c>
       <c r="G271" t="n">
-        <v>3.35767221450806</v>
+        <v>3.35767245292664</v>
       </c>
       <c r="H271" t="n">
         <v>19224</v>
@@ -8257,7 +8257,7 @@
         <v>4.59300184249878</v>
       </c>
       <c r="G272" t="n">
-        <v>3.799471616745</v>
+        <v>3.79947113990784</v>
       </c>
       <c r="H272" t="n">
         <v>58292</v>
@@ -8315,7 +8315,7 @@
         <v>4.42210006713867</v>
       </c>
       <c r="G274" t="n">
-        <v>3.6580958366394</v>
+        <v>3.65809631347656</v>
       </c>
       <c r="H274" t="n">
         <v>7239</v>
@@ -8373,7 +8373,7 @@
         <v>4.43278121948242</v>
       </c>
       <c r="G276" t="n">
-        <v>3.66693186759949</v>
+        <v>3.66693210601807</v>
       </c>
       <c r="H276" t="n">
         <v>12359</v>
@@ -8402,7 +8402,7 @@
         <v>4.25653791427612</v>
       </c>
       <c r="G277" t="n">
-        <v>3.52113795280457</v>
+        <v>3.52113771438599</v>
       </c>
       <c r="H277" t="n">
         <v>9571</v>
@@ -8431,7 +8431,7 @@
         <v>4.25475788116455</v>
       </c>
       <c r="G278" t="n">
-        <v>3.51966571807861</v>
+        <v>3.51966547966003</v>
       </c>
       <c r="H278" t="n">
         <v>10019</v>
@@ -8460,7 +8460,7 @@
         <v>4.15506505966187</v>
       </c>
       <c r="G279" t="n">
-        <v>3.43719673156738</v>
+        <v>3.4371964931488</v>
       </c>
       <c r="H279" t="n">
         <v>3034</v>
@@ -8518,7 +8518,7 @@
         <v>4.22271394729614</v>
       </c>
       <c r="G281" t="n">
-        <v>3.49315810203552</v>
+        <v>3.49315786361694</v>
       </c>
       <c r="H281" t="n">
         <v>2699</v>
@@ -8576,7 +8576,7 @@
         <v>4.32596683502197</v>
       </c>
       <c r="G283" t="n">
-        <v>3.57857203483582</v>
+        <v>3.57857179641724</v>
       </c>
       <c r="H283" t="n">
         <v>27176</v>
@@ -8605,7 +8605,7 @@
         <v>4.32774782180786</v>
       </c>
       <c r="G284" t="n">
-        <v>3.58004522323608</v>
+        <v>3.58004474639893</v>
       </c>
       <c r="H284" t="n">
         <v>731</v>
@@ -8663,7 +8663,7 @@
         <v>4.07495403289795</v>
       </c>
       <c r="G286" t="n">
-        <v>3.37092614173889</v>
+        <v>3.37092661857605</v>
       </c>
       <c r="H286" t="n">
         <v>6601</v>
@@ -8692,7 +8692,7 @@
         <v>3.94677805900574</v>
       </c>
       <c r="G287" t="n">
-        <v>3.26489496231079</v>
+        <v>3.26489543914795</v>
       </c>
       <c r="H287" t="n">
         <v>2309</v>
@@ -8721,7 +8721,7 @@
         <v>3.92007398605347</v>
       </c>
       <c r="G288" t="n">
-        <v>3.24280476570129</v>
+        <v>3.24280500411987</v>
       </c>
       <c r="H288" t="n">
         <v>728</v>
@@ -8750,7 +8750,7 @@
         <v>3.92007398605347</v>
       </c>
       <c r="G289" t="n">
-        <v>3.24280476570129</v>
+        <v>3.24280500411987</v>
       </c>
       <c r="H289" t="n">
         <v>1247</v>
@@ -8837,7 +8837,7 @@
         <v>3.69932508468628</v>
       </c>
       <c r="G292" t="n">
-        <v>3.06019425392151</v>
+        <v>3.06019473075867</v>
       </c>
       <c r="H292" t="n">
         <v>4324</v>
@@ -8895,7 +8895,7 @@
         <v>3.85954594612122</v>
       </c>
       <c r="G294" t="n">
-        <v>3.1927342414856</v>
+        <v>3.19273400306702</v>
       </c>
       <c r="H294" t="n">
         <v>2137</v>
@@ -9098,7 +9098,7 @@
         <v>3.99306392669678</v>
       </c>
       <c r="G301" t="n">
-        <v>3.30318450927734</v>
+        <v>3.30318427085876</v>
       </c>
       <c r="H301" t="n">
         <v>4913</v>
@@ -9185,7 +9185,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G304" t="n">
-        <v>3.18831562995911</v>
+        <v>3.18831586837769</v>
       </c>
       <c r="H304" t="n">
         <v>1235</v>
@@ -9214,7 +9214,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G305" t="n">
-        <v>3.18831562995911</v>
+        <v>3.18831586837769</v>
       </c>
       <c r="H305" t="n">
         <v>1282</v>
@@ -9243,7 +9243,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G306" t="n">
-        <v>3.18831562995911</v>
+        <v>3.18831586837769</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>4.09275722503662</v>
       </c>
       <c r="G308" t="n">
-        <v>3.38565325737</v>
+        <v>3.38565349578857</v>
       </c>
       <c r="H308" t="n">
         <v>112</v>
@@ -9388,7 +9388,7 @@
         <v>3.85420489311218</v>
       </c>
       <c r="G311" t="n">
-        <v>3.18831562995911</v>
+        <v>3.18831586837769</v>
       </c>
       <c r="H311" t="n">
         <v>2222</v>
@@ -9475,7 +9475,7 @@
         <v>3.69576501846313</v>
       </c>
       <c r="G314" t="n">
-        <v>3.05724954605103</v>
+        <v>3.0572497844696</v>
       </c>
       <c r="H314" t="n">
         <v>1221</v>
@@ -9533,7 +9533,7 @@
         <v>3.66728091239929</v>
       </c>
       <c r="G316" t="n">
-        <v>3.033686876297</v>
+        <v>3.03368663787842</v>
       </c>
       <c r="H316" t="n">
         <v>1969</v>
@@ -9562,7 +9562,7 @@
         <v>3.66728091239929</v>
       </c>
       <c r="G317" t="n">
-        <v>3.033686876297</v>
+        <v>3.03368663787842</v>
       </c>
       <c r="H317" t="n">
         <v>2340</v>
@@ -9591,7 +9591,7 @@
         <v>3.65303897857666</v>
       </c>
       <c r="G318" t="n">
-        <v>3.02190542221069</v>
+        <v>3.02190518379211</v>
       </c>
       <c r="H318" t="n">
         <v>112</v>
@@ -9649,7 +9649,7 @@
         <v>3.53910398483276</v>
       </c>
       <c r="G320" t="n">
-        <v>2.92765498161316</v>
+        <v>2.92765474319458</v>
       </c>
       <c r="H320" t="n">
         <v>6607</v>
@@ -9678,7 +9678,7 @@
         <v>3.53376293182373</v>
       </c>
       <c r="G321" t="n">
-        <v>2.92323660850525</v>
+        <v>2.92323613166809</v>
       </c>
       <c r="H321" t="n">
         <v>3459</v>
@@ -9707,7 +9707,7 @@
         <v>3.56580805778503</v>
       </c>
       <c r="G322" t="n">
-        <v>2.94974493980408</v>
+        <v>2.94974517822266</v>
       </c>
       <c r="H322" t="n">
         <v>1994</v>
@@ -9794,7 +9794,7 @@
         <v>4.94904899597168</v>
       </c>
       <c r="G325" t="n">
-        <v>4.09400463104248</v>
+        <v>4.09400415420532</v>
       </c>
       <c r="H325" t="n">
         <v>60949</v>
@@ -9881,7 +9881,7 @@
         <v>4.41319894790649</v>
       </c>
       <c r="G328" t="n">
-        <v>3.65073251724243</v>
+        <v>3.65073275566101</v>
       </c>
       <c r="H328" t="n">
         <v>30835</v>
@@ -9939,7 +9939,7 @@
         <v>4.32596683502197</v>
       </c>
       <c r="G330" t="n">
-        <v>3.57857203483582</v>
+        <v>3.57857179641724</v>
       </c>
       <c r="H330" t="n">
         <v>34372</v>
@@ -9968,7 +9968,7 @@
         <v>3.92363500595093</v>
       </c>
       <c r="G331" t="n">
-        <v>3.24575066566467</v>
+        <v>3.24575042724609</v>
       </c>
       <c r="H331" t="n">
         <v>39316</v>
@@ -9997,7 +9997,7 @@
         <v>3.77409505844116</v>
       </c>
       <c r="G332" t="n">
-        <v>3.12204647064209</v>
+        <v>3.12204670906067</v>
       </c>
       <c r="H332" t="n">
         <v>5276</v>
@@ -10055,7 +10055,7 @@
         <v>3.98950290679932</v>
       </c>
       <c r="G334" t="n">
-        <v>3.30023860931396</v>
+        <v>3.30023837089539</v>
       </c>
       <c r="H334" t="n">
         <v>5942</v>
@@ -10113,7 +10113,7 @@
         <v>3.99662399291992</v>
       </c>
       <c r="G336" t="n">
-        <v>3.30612945556641</v>
+        <v>3.30612921714783</v>
       </c>
       <c r="H336" t="n">
         <v>4587</v>
@@ -10142,7 +10142,7 @@
         <v>4.0055251121521</v>
       </c>
       <c r="G337" t="n">
-        <v>3.3134925365448</v>
+        <v>3.31349229812622</v>
       </c>
       <c r="H337" t="n">
         <v>1616</v>
@@ -10229,7 +10229,7 @@
         <v>3.85598611831665</v>
       </c>
       <c r="G340" t="n">
-        <v>3.18978953361511</v>
+        <v>3.18978905677795</v>
       </c>
       <c r="H340" t="n">
         <v>3818</v>
@@ -10258,7 +10258,7 @@
         <v>3.8915901184082</v>
       </c>
       <c r="G341" t="n">
-        <v>3.21924209594727</v>
+        <v>3.21924185752869</v>
       </c>
       <c r="H341" t="n">
         <v>1665</v>
@@ -10287,7 +10287,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G342" t="n">
-        <v>3.16033554077148</v>
+        <v>3.16033577919006</v>
       </c>
       <c r="H342" t="n">
         <v>731</v>
@@ -10316,7 +10316,7 @@
         <v>3.92185401916504</v>
       </c>
       <c r="G343" t="n">
-        <v>3.24427723884583</v>
+        <v>3.2442774772644</v>
       </c>
       <c r="H343" t="n">
         <v>1372</v>
@@ -10374,7 +10374,7 @@
         <v>3.84530401229858</v>
       </c>
       <c r="G345" t="n">
-        <v>3.18095254898071</v>
+        <v>3.18095302581787</v>
       </c>
       <c r="H345" t="n">
         <v>842</v>
@@ -10403,7 +10403,7 @@
         <v>3.85954594612122</v>
       </c>
       <c r="G346" t="n">
-        <v>3.1927342414856</v>
+        <v>3.19273400306702</v>
       </c>
       <c r="H346" t="n">
         <v>320</v>
@@ -10461,7 +10461,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G348" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H348" t="n">
         <v>682</v>
@@ -10490,7 +10490,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G349" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H349" t="n">
         <v>2665</v>
@@ -10519,7 +10519,7 @@
         <v>3.8203809261322</v>
       </c>
       <c r="G350" t="n">
-        <v>3.16033554077148</v>
+        <v>3.16033577919006</v>
       </c>
       <c r="H350" t="n">
         <v>2507</v>
@@ -10548,7 +10548,7 @@
         <v>3.70822596549988</v>
       </c>
       <c r="G351" t="n">
-        <v>3.0675573348999</v>
+        <v>3.06755757331848</v>
       </c>
       <c r="H351" t="n">
         <v>1095</v>
@@ -10577,7 +10577,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G352" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H352" t="n">
         <v>2010</v>
@@ -10606,7 +10606,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G353" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G354" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H354" t="n">
         <v>3131</v>
@@ -10693,7 +10693,7 @@
         <v>3.82750201225281</v>
       </c>
       <c r="G356" t="n">
-        <v>3.16622614860535</v>
+        <v>3.1662266254425</v>
       </c>
       <c r="H356" t="n">
         <v>358</v>
@@ -10722,7 +10722,7 @@
         <v>3.80970001220703</v>
       </c>
       <c r="G357" t="n">
-        <v>3.15149998664856</v>
+        <v>3.15150022506714</v>
       </c>
       <c r="H357" t="n">
         <v>1714</v>
@@ -10896,7 +10896,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G363" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H363" t="n">
         <v>716</v>
@@ -10925,7 +10925,7 @@
         <v>3.82750201225281</v>
       </c>
       <c r="G364" t="n">
-        <v>3.16622614860535</v>
+        <v>3.1662266254425</v>
       </c>
       <c r="H364" t="n">
         <v>196</v>
@@ -11012,7 +11012,7 @@
         <v>3.69220399856567</v>
       </c>
       <c r="G367" t="n">
-        <v>3.05430364608765</v>
+        <v>3.05430388450623</v>
       </c>
       <c r="H367" t="n">
         <v>1012</v>
@@ -11041,7 +11041,7 @@
         <v>3.58004903793335</v>
       </c>
       <c r="G368" t="n">
-        <v>2.96152567863464</v>
+        <v>2.96152591705322</v>
       </c>
       <c r="H368" t="n">
         <v>2763</v>
@@ -11070,7 +11070,7 @@
         <v>3.59607195854187</v>
       </c>
       <c r="G369" t="n">
-        <v>2.97478079795837</v>
+        <v>2.97478055953979</v>
       </c>
       <c r="H369" t="n">
         <v>1067</v>
@@ -11099,7 +11099,7 @@
         <v>3.54800510406494</v>
       </c>
       <c r="G370" t="n">
-        <v>2.93501782417297</v>
+        <v>2.93501806259155</v>
       </c>
       <c r="H370" t="n">
         <v>3053</v>
@@ -11128,7 +11128,7 @@
         <v>3.53910398483276</v>
       </c>
       <c r="G371" t="n">
-        <v>2.92765498161316</v>
+        <v>2.92765474319458</v>
       </c>
       <c r="H371" t="n">
         <v>248</v>
@@ -11157,7 +11157,7 @@
         <v>3.8114800453186</v>
       </c>
       <c r="G372" t="n">
-        <v>3.15297245979309</v>
+        <v>3.15297269821167</v>
       </c>
       <c r="H372" t="n">
         <v>56763</v>
@@ -11186,7 +11186,7 @@
         <v>3.73849010467529</v>
       </c>
       <c r="G373" t="n">
-        <v>3.0925931930542</v>
+        <v>3.09259295463562</v>
       </c>
       <c r="H373" t="n">
         <v>6892</v>
@@ -11244,7 +11244,7 @@
         <v>3.64947891235352</v>
       </c>
       <c r="G375" t="n">
-        <v>3.01896047592163</v>
+        <v>3.01896023750305</v>
       </c>
       <c r="H375" t="n">
         <v>1474</v>
@@ -11273,7 +11273,7 @@
         <v>3.60675311088562</v>
       </c>
       <c r="G376" t="n">
-        <v>2.98361611366272</v>
+        <v>2.9836163520813</v>
       </c>
       <c r="H376" t="n">
         <v>874</v>
@@ -11331,7 +11331,7 @@
         <v>3.60675311088562</v>
       </c>
       <c r="G378" t="n">
-        <v>2.98361611366272</v>
+        <v>2.9836163520813</v>
       </c>
       <c r="H378" t="n">
         <v>22</v>
@@ -11447,7 +11447,7 @@
         <v>3.62989592552185</v>
       </c>
       <c r="G382" t="n">
-        <v>3.00276041030884</v>
+        <v>3.00276064872742</v>
       </c>
       <c r="H382" t="n">
         <v>112</v>
@@ -11476,7 +11476,7 @@
         <v>3.61565399169922</v>
       </c>
       <c r="G383" t="n">
-        <v>2.99097919464111</v>
+        <v>2.99097943305969</v>
       </c>
       <c r="H383" t="n">
         <v>775</v>
@@ -11534,7 +11534,7 @@
         <v>3.57114791870117</v>
       </c>
       <c r="G385" t="n">
-        <v>2.95416259765625</v>
+        <v>2.95416235923767</v>
       </c>
       <c r="H385" t="n">
         <v>1159</v>
@@ -11592,7 +11592,7 @@
         <v>3.43763089179993</v>
       </c>
       <c r="G387" t="n">
-        <v>2.84371304512024</v>
+        <v>2.84371328353882</v>
       </c>
       <c r="H387" t="n">
         <v>2655</v>
@@ -11621,7 +11621,7 @@
         <v>3.45187306404114</v>
       </c>
       <c r="G388" t="n">
-        <v>2.85549449920654</v>
+        <v>2.85549473762512</v>
       </c>
       <c r="H388" t="n">
         <v>1441</v>
@@ -11650,7 +11650,7 @@
         <v>3.47145509719849</v>
       </c>
       <c r="G389" t="n">
-        <v>2.87169361114502</v>
+        <v>2.8716938495636</v>
       </c>
       <c r="H389" t="n">
         <v>649</v>
@@ -11708,7 +11708,7 @@
         <v>3.48925805091858</v>
       </c>
       <c r="G391" t="n">
-        <v>2.8864209651947</v>
+        <v>2.88642072677612</v>
       </c>
       <c r="H391" t="n">
         <v>642</v>
@@ -11737,7 +11737,7 @@
         <v>3.52486205101013</v>
       </c>
       <c r="G392" t="n">
-        <v>2.91587352752686</v>
+        <v>2.91587328910828</v>
       </c>
       <c r="H392" t="n">
         <v>2488</v>
@@ -11766,7 +11766,7 @@
         <v>3.50884008407593</v>
       </c>
       <c r="G393" t="n">
-        <v>2.90261960029602</v>
+        <v>2.9026198387146</v>
       </c>
       <c r="H393" t="n">
         <v>12647</v>
@@ -11824,7 +11824,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G395" t="n">
-        <v>2.84224104881287</v>
+        <v>2.84224081039429</v>
       </c>
       <c r="H395" t="n">
         <v>954</v>
@@ -11853,7 +11853,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G396" t="n">
-        <v>2.84224104881287</v>
+        <v>2.84224081039429</v>
       </c>
       <c r="H396" t="n">
         <v>421</v>
@@ -11882,7 +11882,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G397" t="n">
-        <v>2.85696721076965</v>
+        <v>2.85696744918823</v>
       </c>
       <c r="H397" t="n">
         <v>617</v>
@@ -11911,7 +11911,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G398" t="n">
-        <v>2.85696721076965</v>
+        <v>2.85696744918823</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G399" t="n">
-        <v>2.85696721076965</v>
+        <v>2.85696744918823</v>
       </c>
       <c r="H399" t="n">
         <v>404</v>
@@ -11969,7 +11969,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G400" t="n">
-        <v>2.85696721076965</v>
+        <v>2.85696744918823</v>
       </c>
       <c r="H400" t="n">
         <v>314</v>
@@ -11998,7 +11998,7 @@
         <v>3.45365309715271</v>
       </c>
       <c r="G401" t="n">
-        <v>2.85696721076965</v>
+        <v>2.85696744918823</v>
       </c>
       <c r="H401" t="n">
         <v>226</v>
@@ -12056,7 +12056,7 @@
         <v>4.046471118927</v>
       </c>
       <c r="G403" t="n">
-        <v>3.34736466407776</v>
+        <v>3.34736442565918</v>
       </c>
       <c r="H403" t="n">
         <v>98461</v>
@@ -12143,7 +12143,7 @@
         <v>3.64947891235352</v>
       </c>
       <c r="G406" t="n">
-        <v>3.01896047592163</v>
+        <v>3.01896023750305</v>
       </c>
       <c r="H406" t="n">
         <v>28393</v>
@@ -12172,7 +12172,7 @@
         <v>3.64947891235352</v>
       </c>
       <c r="G407" t="n">
-        <v>3.01896047592163</v>
+        <v>3.01896023750305</v>
       </c>
       <c r="H407" t="n">
         <v>1648</v>
@@ -12259,7 +12259,7 @@
         <v>3.59785199165344</v>
       </c>
       <c r="G410" t="n">
-        <v>2.97625279426575</v>
+        <v>2.97625303268433</v>
       </c>
       <c r="H410" t="n">
         <v>2148</v>
@@ -12288,7 +12288,7 @@
         <v>3.59963202476501</v>
       </c>
       <c r="G411" t="n">
-        <v>2.97772550582886</v>
+        <v>2.97772574424744</v>
       </c>
       <c r="H411" t="n">
         <v>1</v>
@@ -12317,7 +12317,7 @@
         <v>3.59963202476501</v>
       </c>
       <c r="G412" t="n">
-        <v>2.97772550582886</v>
+        <v>2.97772574424744</v>
       </c>
       <c r="H412" t="n">
         <v>342</v>
@@ -12346,7 +12346,7 @@
         <v>3.56580805778503</v>
       </c>
       <c r="G413" t="n">
-        <v>2.94974493980408</v>
+        <v>2.94974517822266</v>
       </c>
       <c r="H413" t="n">
         <v>449</v>
@@ -12375,7 +12375,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G414" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H414" t="n">
         <v>393</v>
@@ -12404,7 +12404,7 @@
         <v>3.56224703788757</v>
       </c>
       <c r="G415" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H415" t="n">
         <v>140</v>
@@ -12433,7 +12433,7 @@
         <v>3.59607195854187</v>
       </c>
       <c r="G416" t="n">
-        <v>2.97478079795837</v>
+        <v>2.97478055953979</v>
       </c>
       <c r="H416" t="n">
         <v>168</v>
@@ -12520,7 +12520,7 @@
         <v>3.62989592552185</v>
       </c>
       <c r="G419" t="n">
-        <v>3.00276041030884</v>
+        <v>3.00276064872742</v>
       </c>
       <c r="H419" t="n">
         <v>481</v>
@@ -12549,7 +12549,7 @@
         <v>3.57826900482178</v>
       </c>
       <c r="G420" t="n">
-        <v>2.96005344390869</v>
+        <v>2.96005320549011</v>
       </c>
       <c r="H420" t="n">
         <v>11998</v>
@@ -12607,7 +12607,7 @@
         <v>3.61209392547607</v>
       </c>
       <c r="G422" t="n">
-        <v>2.98803400993347</v>
+        <v>2.98803424835205</v>
       </c>
       <c r="H422" t="n">
         <v>991</v>
@@ -12636,7 +12636,7 @@
         <v>3.61387395858765</v>
       </c>
       <c r="G423" t="n">
-        <v>2.98950672149658</v>
+        <v>2.98950695991516</v>
       </c>
       <c r="H423" t="n">
         <v>1460</v>
@@ -12665,7 +12665,7 @@
         <v>3.57292890548706</v>
       </c>
       <c r="G424" t="n">
-        <v>2.95563554763794</v>
+        <v>2.95563578605652</v>
       </c>
       <c r="H424" t="n">
         <v>3529</v>
@@ -12694,7 +12694,7 @@
         <v>3.51418089866638</v>
       </c>
       <c r="G425" t="n">
-        <v>2.90703773498535</v>
+        <v>2.90703749656677</v>
       </c>
       <c r="H425" t="n">
         <v>900</v>
@@ -12897,7 +12897,7 @@
         <v>3.47323489189148</v>
       </c>
       <c r="G432" t="n">
-        <v>2.87316608428955</v>
+        <v>2.87316584587097</v>
       </c>
       <c r="H432" t="n">
         <v>3521</v>
@@ -12926,7 +12926,7 @@
         <v>3.49281811714172</v>
       </c>
       <c r="G433" t="n">
-        <v>2.88936543464661</v>
+        <v>2.88936567306519</v>
       </c>
       <c r="H433" t="n">
         <v>2375</v>
@@ -12955,7 +12955,7 @@
         <v>3.43585109710693</v>
       </c>
       <c r="G434" t="n">
-        <v>2.84224104881287</v>
+        <v>2.84224081039429</v>
       </c>
       <c r="H434" t="n">
         <v>5513</v>
@@ -13013,7 +13013,7 @@
         <v>3.47145509719849</v>
       </c>
       <c r="G436" t="n">
-        <v>2.87169361114502</v>
+        <v>2.8716938495636</v>
       </c>
       <c r="H436" t="n">
         <v>1</v>
@@ -13042,7 +13042,7 @@
         <v>3.47145509719849</v>
       </c>
       <c r="G437" t="n">
-        <v>2.87169361114502</v>
+        <v>2.8716938495636</v>
       </c>
       <c r="H437" t="n">
         <v>1866</v>
@@ -13071,7 +13071,7 @@
         <v>3.52486205101013</v>
       </c>
       <c r="G438" t="n">
-        <v>2.91587352752686</v>
+        <v>2.91587328910828</v>
       </c>
       <c r="H438" t="n">
         <v>1685</v>
@@ -13100,7 +13100,7 @@
         <v>3.51418089866638</v>
       </c>
       <c r="G439" t="n">
-        <v>2.90703773498535</v>
+        <v>2.90703749656677</v>
       </c>
       <c r="H439" t="n">
         <v>1659</v>
@@ -13129,7 +13129,7 @@
         <v>3.51418089866638</v>
       </c>
       <c r="G440" t="n">
-        <v>2.90703773498535</v>
+        <v>2.90703749656677</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>3.41092705726624</v>
       </c>
       <c r="G441" t="n">
-        <v>2.82162308692932</v>
+        <v>2.82162284851074</v>
       </c>
       <c r="H441" t="n">
         <v>21711</v>
@@ -13187,7 +13187,7 @@
         <v>3.43407011032104</v>
       </c>
       <c r="G442" t="n">
-        <v>2.84076738357544</v>
+        <v>2.84076762199402</v>
       </c>
       <c r="H442" t="n">
         <v>1933</v>
@@ -13216,7 +13216,7 @@
         <v>3.43763089179993</v>
       </c>
       <c r="G443" t="n">
-        <v>2.84371304512024</v>
+        <v>2.84371328353882</v>
       </c>
       <c r="H443" t="n">
         <v>3393</v>
@@ -13245,7 +13245,7 @@
         <v>3.43763089179993</v>
       </c>
       <c r="G444" t="n">
-        <v>2.84371304512024</v>
+        <v>2.84371328353882</v>
       </c>
       <c r="H444" t="n">
         <v>56</v>
@@ -13564,7 +13564,7 @@
         <v>3.32903695106506</v>
       </c>
       <c r="G455" t="n">
-        <v>2.75388121604919</v>
+        <v>2.75388097763062</v>
       </c>
       <c r="H455" t="n">
         <v>6311</v>
@@ -13593,7 +13593,7 @@
         <v>3.27919006347656</v>
       </c>
       <c r="G456" t="n">
-        <v>2.71264576911926</v>
+        <v>2.71264600753784</v>
       </c>
       <c r="H456" t="n">
         <v>2696</v>
@@ -13883,7 +13883,7 @@
         <v>3.20798110961914</v>
       </c>
       <c r="G466" t="n">
-        <v>2.65373969078064</v>
+        <v>2.65373992919922</v>
       </c>
       <c r="H466" t="n">
         <v>3873</v>
@@ -13970,7 +13970,7 @@
         <v>3.20798110961914</v>
       </c>
       <c r="G469" t="n">
-        <v>2.65373969078064</v>
+        <v>2.65373992919922</v>
       </c>
       <c r="H469" t="n">
         <v>19</v>
@@ -13999,7 +13999,7 @@
         <v>3.18483805656433</v>
       </c>
       <c r="G470" t="n">
-        <v>2.63459539413452</v>
+        <v>2.63459515571594</v>
       </c>
       <c r="H470" t="n">
         <v>1182</v>
@@ -14057,7 +14057,7 @@
         <v>3.19373893737793</v>
       </c>
       <c r="G472" t="n">
-        <v>2.64195847511292</v>
+        <v>2.64195799827576</v>
       </c>
       <c r="H472" t="n">
         <v>2530</v>
@@ -14086,7 +14086,7 @@
         <v>3.29343199729919</v>
       </c>
       <c r="G473" t="n">
-        <v>2.72442722320557</v>
+        <v>2.72442746162415</v>
       </c>
       <c r="H473" t="n">
         <v>5172</v>
@@ -14115,7 +14115,7 @@
         <v>3.24002504348755</v>
       </c>
       <c r="G474" t="n">
-        <v>2.68024754524231</v>
+        <v>2.68024778366089</v>
       </c>
       <c r="H474" t="n">
         <v>2632</v>
@@ -14173,7 +14173,7 @@
         <v>3.20442008972168</v>
       </c>
       <c r="G476" t="n">
-        <v>2.65079426765442</v>
+        <v>2.65079402923584</v>
       </c>
       <c r="H476" t="n">
         <v>393</v>
@@ -14202,7 +14202,7 @@
         <v>3.18483805656433</v>
       </c>
       <c r="G477" t="n">
-        <v>2.63459539413452</v>
+        <v>2.63459515571594</v>
       </c>
       <c r="H477" t="n">
         <v>839</v>
@@ -14231,7 +14231,7 @@
         <v>3.20442008972168</v>
       </c>
       <c r="G478" t="n">
-        <v>2.65079426765442</v>
+        <v>2.65079402923584</v>
       </c>
       <c r="H478" t="n">
         <v>29</v>
@@ -14289,7 +14289,7 @@
         <v>3.074462890625</v>
       </c>
       <c r="G480" t="n">
-        <v>2.54328966140747</v>
+        <v>2.54328942298889</v>
       </c>
       <c r="H480" t="n">
         <v>577</v>
@@ -14318,7 +14318,7 @@
         <v>3.15101289749146</v>
       </c>
       <c r="G481" t="n">
-        <v>2.60661387443542</v>
+        <v>2.606614112854</v>
       </c>
       <c r="H481" t="n">
         <v>1291</v>
@@ -14347,7 +14347,7 @@
         <v>3.04419898986816</v>
       </c>
       <c r="G482" t="n">
-        <v>2.51825451850891</v>
+        <v>2.51825428009033</v>
       </c>
       <c r="H482" t="n">
         <v>589</v>
@@ -14376,7 +14376,7 @@
         <v>3.02105593681335</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49910950660706</v>
+        <v>2.49910974502563</v>
       </c>
       <c r="H483" t="n">
         <v>342</v>
@@ -14405,7 +14405,7 @@
         <v>3.02105593681335</v>
       </c>
       <c r="G484" t="n">
-        <v>2.49910950660706</v>
+        <v>2.49910974502563</v>
       </c>
       <c r="H484" t="n">
         <v>151</v>
@@ -14434,7 +14434,7 @@
         <v>2.90712094306946</v>
       </c>
       <c r="G485" t="n">
-        <v>2.40485906600952</v>
+        <v>2.4048593044281</v>
       </c>
       <c r="H485" t="n">
         <v>505</v>
@@ -14550,7 +14550,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G489" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H489" t="n">
         <v>1630</v>
@@ -14724,7 +14724,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G495" t="n">
-        <v>2.35920667648315</v>
+        <v>2.35920691490173</v>
       </c>
       <c r="H495" t="n">
         <v>466</v>
@@ -14753,7 +14753,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G496" t="n">
-        <v>2.35920667648315</v>
+        <v>2.35920691490173</v>
       </c>
       <c r="H496" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>2.85193395614624</v>
       </c>
       <c r="G497" t="n">
-        <v>2.35920667648315</v>
+        <v>2.35920691490173</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G498" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H498" t="n">
         <v>56</v>
@@ -14869,7 +14869,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G500" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H500" t="n">
         <v>449</v>
@@ -14898,7 +14898,7 @@
         <v>2.95518708229065</v>
       </c>
       <c r="G501" t="n">
-        <v>2.44462084770203</v>
+        <v>2.44462060928345</v>
       </c>
       <c r="H501" t="n">
         <v>1797</v>
@@ -14927,7 +14927,7 @@
         <v>2.98189091682434</v>
       </c>
       <c r="G502" t="n">
-        <v>2.4667112827301</v>
+        <v>2.46671104431152</v>
       </c>
       <c r="H502" t="n">
         <v>280</v>
@@ -14956,7 +14956,7 @@
         <v>2.98011088371277</v>
       </c>
       <c r="G503" t="n">
-        <v>2.46523880958557</v>
+        <v>2.46523857116699</v>
       </c>
       <c r="H503" t="n">
         <v>1171</v>
@@ -14985,7 +14985,7 @@
         <v>2.98011088371277</v>
       </c>
       <c r="G504" t="n">
-        <v>2.46523880958557</v>
+        <v>2.46523857116699</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>2.9195830821991</v>
       </c>
       <c r="G505" t="n">
-        <v>2.41516804695129</v>
+        <v>2.41516828536987</v>
       </c>
       <c r="H505" t="n">
         <v>674</v>
@@ -15130,7 +15130,7 @@
         <v>2.84837293624878</v>
       </c>
       <c r="G509" t="n">
-        <v>2.35626101493835</v>
+        <v>2.35626077651978</v>
       </c>
       <c r="H509" t="n">
         <v>5732</v>
@@ -15188,7 +15188,7 @@
         <v>3.25</v>
       </c>
       <c r="G511" t="n">
-        <v>2.68849897384644</v>
+        <v>2.68849921226501</v>
       </c>
       <c r="H511" t="n">
         <v>28967</v>
@@ -15275,7 +15275,7 @@
         <v>3.33750009536743</v>
       </c>
       <c r="G514" t="n">
-        <v>2.76088166236877</v>
+        <v>2.76088190078735</v>
       </c>
       <c r="H514" t="n">
         <v>17816</v>
@@ -15333,7 +15333,7 @@
         <v>3.25</v>
       </c>
       <c r="G516" t="n">
-        <v>2.68849897384644</v>
+        <v>2.68849921226501</v>
       </c>
       <c r="H516" t="n">
         <v>10298</v>
@@ -15391,7 +15391,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G518" t="n">
-        <v>2.64713764190674</v>
+        <v>2.64713740348816</v>
       </c>
       <c r="H518" t="n">
         <v>33959</v>
@@ -15449,7 +15449,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G520" t="n">
-        <v>2.46101069450378</v>
+        <v>2.46101093292236</v>
       </c>
       <c r="H520" t="n">
         <v>15414</v>
@@ -15507,7 +15507,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G522" t="n">
-        <v>2.31624531745911</v>
+        <v>2.31624555587769</v>
       </c>
       <c r="H522" t="n">
         <v>15526</v>
@@ -15623,7 +15623,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G526" t="n">
-        <v>2.04739546775818</v>
+        <v>2.0473952293396</v>
       </c>
       <c r="H526" t="n">
         <v>20378</v>
@@ -15739,7 +15739,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.96053636074066</v>
+        <v>1.96053647994995</v>
       </c>
       <c r="H530" t="n">
         <v>29220</v>
@@ -15768,7 +15768,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G531" t="n">
-        <v>1.86540472507477</v>
+        <v>1.86540484428406</v>
       </c>
       <c r="H531" t="n">
         <v>103365</v>
@@ -15826,7 +15826,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G533" t="n">
-        <v>1.84886014461517</v>
+        <v>1.84886002540588</v>
       </c>
       <c r="H533" t="n">
         <v>31186</v>
@@ -15855,7 +15855,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84058809280396</v>
+        <v>1.84058797359467</v>
       </c>
       <c r="H534" t="n">
         <v>86811</v>
@@ -15884,7 +15884,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G535" t="n">
-        <v>1.81577086448669</v>
+        <v>1.8157707452774</v>
       </c>
       <c r="H535" t="n">
         <v>32861</v>
@@ -15913,7 +15913,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G536" t="n">
-        <v>1.81990706920624</v>
+        <v>1.81990718841553</v>
       </c>
       <c r="H536" t="n">
         <v>22954</v>
@@ -16029,7 +16029,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>1.7206392288208</v>
+        <v>1.72063934803009</v>
       </c>
       <c r="H540" t="n">
         <v>15673</v>
@@ -16058,7 +16058,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G541" t="n">
-        <v>1.67927801609039</v>
+        <v>1.6792778968811</v>
       </c>
       <c r="H541" t="n">
         <v>22049</v>
@@ -16116,7 +16116,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G543" t="n">
-        <v>1.64618861675262</v>
+        <v>1.64618873596191</v>
       </c>
       <c r="H543" t="n">
         <v>14522</v>
@@ -16174,7 +16174,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G545" t="n">
-        <v>1.81577086448669</v>
+        <v>1.8157707452774</v>
       </c>
       <c r="H545" t="n">
         <v>124025</v>
@@ -16203,7 +16203,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G546" t="n">
-        <v>1.81990706920624</v>
+        <v>1.81990718841553</v>
       </c>
       <c r="H546" t="n">
         <v>72365</v>
@@ -16232,7 +16232,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G547" t="n">
-        <v>1.77440941333771</v>
+        <v>1.77440929412842</v>
       </c>
       <c r="H547" t="n">
         <v>15793</v>
@@ -16348,7 +16348,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G551" t="n">
-        <v>1.77440941333771</v>
+        <v>1.77440929412842</v>
       </c>
       <c r="H551" t="n">
         <v>14085</v>
@@ -16435,7 +16435,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G554" t="n">
-        <v>1.73304796218872</v>
+        <v>1.73304784297943</v>
       </c>
       <c r="H554" t="n">
         <v>14752</v>
@@ -16464,7 +16464,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G555" t="n">
-        <v>1.71650350093842</v>
+        <v>1.71650326251984</v>
       </c>
       <c r="H555" t="n">
         <v>11105</v>
@@ -16493,7 +16493,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>1.77440941333771</v>
+        <v>1.77440929412842</v>
       </c>
       <c r="H556" t="n">
         <v>3545</v>
@@ -16609,7 +16609,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G560" t="n">
-        <v>1.79509019851685</v>
+        <v>1.79509031772614</v>
       </c>
       <c r="H560" t="n">
         <v>2240</v>
@@ -16638,7 +16638,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G561" t="n">
-        <v>1.81990706920624</v>
+        <v>1.81990718841553</v>
       </c>
       <c r="H561" t="n">
         <v>17464</v>
@@ -16696,7 +16696,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G563" t="n">
-        <v>1.75372862815857</v>
+        <v>1.75372850894928</v>
       </c>
       <c r="H563" t="n">
         <v>4008</v>
@@ -16754,7 +16754,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G565" t="n">
-        <v>1.77440941333771</v>
+        <v>1.77440929412842</v>
       </c>
       <c r="H565" t="n">
         <v>4955</v>
@@ -16928,7 +16928,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G571" t="n">
-        <v>1.79509019851685</v>
+        <v>1.79509031772614</v>
       </c>
       <c r="H571" t="n">
         <v>4292</v>
@@ -16986,7 +16986,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G573" t="n">
-        <v>1.73304796218872</v>
+        <v>1.73304784297943</v>
       </c>
       <c r="H573" t="n">
         <v>2137</v>
@@ -17015,7 +17015,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G574" t="n">
-        <v>1.77440941333771</v>
+        <v>1.77440929412842</v>
       </c>
       <c r="H574" t="n">
         <v>3299</v>
@@ -17044,7 +17044,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>1.79922616481781</v>
+        <v>1.7992262840271</v>
       </c>
       <c r="H575" t="n">
         <v>4859</v>
@@ -17131,7 +17131,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G578" t="n">
-        <v>1.84886014461517</v>
+        <v>1.84886002540588</v>
       </c>
       <c r="H578" t="n">
         <v>35013</v>
@@ -17276,7 +17276,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>1.93158316612244</v>
+        <v>1.93158328533173</v>
       </c>
       <c r="H583" t="n">
         <v>72085</v>
@@ -17363,7 +17363,7 @@
         <v>2.73749995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.26454329490662</v>
+        <v>2.2645435333252</v>
       </c>
       <c r="H586" t="n">
         <v>241077</v>
@@ -17421,7 +17421,7 @@
         <v>2.5</v>
       </c>
       <c r="G588" t="n">
-        <v>2.06807637214661</v>
+        <v>2.06807661056519</v>
       </c>
       <c r="H588" t="n">
         <v>93249</v>
@@ -17450,7 +17450,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G589" t="n">
-        <v>2.34726643562317</v>
+        <v>2.34726667404175</v>
       </c>
       <c r="H589" t="n">
         <v>262760</v>
@@ -17479,7 +17479,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>2.34726643562317</v>
+        <v>2.34726667404175</v>
       </c>
       <c r="H590" t="n">
         <v>113565</v>
@@ -17508,7 +17508,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.31624531745911</v>
+        <v>2.31624555587769</v>
       </c>
       <c r="H591" t="n">
         <v>50643</v>
@@ -17537,7 +17537,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>2.31624531745911</v>
+        <v>2.31624555587769</v>
       </c>
       <c r="H592" t="n">
         <v>191122</v>
@@ -17653,7 +17653,7 @@
         <v>2.63750004768372</v>
       </c>
       <c r="G596" t="n">
-        <v>2.18182039260864</v>
+        <v>2.18182063102722</v>
       </c>
       <c r="H596" t="n">
         <v>87339</v>
@@ -17740,7 +17740,7 @@
         <v>2.63750004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>2.18182039260864</v>
+        <v>2.18182063102722</v>
       </c>
       <c r="H599" t="n">
         <v>23481</v>
@@ -17885,7 +17885,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G604" t="n">
-        <v>2.150799036026</v>
+        <v>2.15079927444458</v>
       </c>
       <c r="H604" t="n">
         <v>20536</v>
@@ -17943,7 +17943,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G606" t="n">
-        <v>2.10943746566772</v>
+        <v>2.1094377040863</v>
       </c>
       <c r="H606" t="n">
         <v>57475</v>
@@ -17972,7 +17972,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G607" t="n">
-        <v>2.03498673439026</v>
+        <v>2.03498721122742</v>
       </c>
       <c r="H607" t="n">
         <v>10511</v>
@@ -18059,7 +18059,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G610" t="n">
-        <v>2.03912305831909</v>
+        <v>2.03912281990051</v>
       </c>
       <c r="H610" t="n">
         <v>47299</v>
@@ -18117,7 +18117,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>1.92744696140289</v>
+        <v>1.9274468421936</v>
       </c>
       <c r="H612" t="n">
         <v>8870</v>
@@ -18175,7 +18175,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G614" t="n">
-        <v>1.86540472507477</v>
+        <v>1.86540484428406</v>
       </c>
       <c r="H614" t="n">
         <v>24381</v>
@@ -18204,7 +18204,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G615" t="n">
-        <v>1.84472393989563</v>
+        <v>1.84472405910492</v>
       </c>
       <c r="H615" t="n">
         <v>28679</v>
@@ -18349,7 +18349,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G620" t="n">
-        <v>1.98121738433838</v>
+        <v>1.98121726512909</v>
       </c>
       <c r="H620" t="n">
         <v>4625</v>
@@ -18378,7 +18378,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G621" t="n">
-        <v>1.94812786579132</v>
+        <v>1.94812762737274</v>
       </c>
       <c r="H621" t="n">
         <v>43607</v>
@@ -18407,7 +18407,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G622" t="n">
-        <v>1.86540472507477</v>
+        <v>1.86540484428406</v>
       </c>
       <c r="H622" t="n">
         <v>19869</v>
@@ -18436,7 +18436,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>1.93158316612244</v>
+        <v>1.93158328533173</v>
       </c>
       <c r="H623" t="n">
         <v>16422</v>
@@ -18523,7 +18523,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G626" t="n">
-        <v>1.92331111431122</v>
+        <v>1.92331099510193</v>
       </c>
       <c r="H626" t="n">
         <v>11025</v>
@@ -18552,7 +18552,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>1.88608527183533</v>
+        <v>1.8860856294632</v>
       </c>
       <c r="H627" t="n">
         <v>13640</v>
@@ -18639,7 +18639,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G630" t="n">
-        <v>1.89849412441254</v>
+        <v>1.89849400520325</v>
       </c>
       <c r="H630" t="n">
         <v>8296</v>
@@ -18697,7 +18697,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G632" t="n">
-        <v>1.89849412441254</v>
+        <v>1.89849400520325</v>
       </c>
       <c r="H632" t="n">
         <v>1989</v>
@@ -18871,7 +18871,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G638" t="n">
-        <v>1.84886014461517</v>
+        <v>1.84886002540588</v>
       </c>
       <c r="H638" t="n">
         <v>7040</v>
@@ -18958,7 +18958,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G641" t="n">
-        <v>1.78681790828705</v>
+        <v>1.78681802749634</v>
       </c>
       <c r="H641" t="n">
         <v>25425</v>
@@ -18987,7 +18987,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G642" t="n">
-        <v>1.81163501739502</v>
+        <v>1.81163477897644</v>
       </c>
       <c r="H642" t="n">
         <v>11225</v>
@@ -19016,7 +19016,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G643" t="n">
-        <v>1.79922616481781</v>
+        <v>1.7992262840271</v>
       </c>
       <c r="H643" t="n">
         <v>860</v>
@@ -19045,7 +19045,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G644" t="n">
-        <v>1.81163501739502</v>
+        <v>1.81163477897644</v>
       </c>
       <c r="H644" t="n">
         <v>10559</v>
@@ -19074,7 +19074,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G645" t="n">
-        <v>1.78681790828705</v>
+        <v>1.78681802749634</v>
       </c>
       <c r="H645" t="n">
         <v>5814</v>
@@ -19103,7 +19103,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>1.77440941333771</v>
+        <v>1.77440929412842</v>
       </c>
       <c r="H646" t="n">
         <v>13135</v>
@@ -19190,7 +19190,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.75372862815857</v>
+        <v>1.75372850894928</v>
       </c>
       <c r="H649" t="n">
         <v>426</v>
@@ -19306,7 +19306,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>1.79509019851685</v>
+        <v>1.79509031772614</v>
       </c>
       <c r="H653" t="n">
         <v>586</v>
@@ -19335,7 +19335,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>1.81990706920624</v>
+        <v>1.81990718841553</v>
       </c>
       <c r="H654" t="n">
         <v>16533</v>
@@ -19422,7 +19422,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G657" t="n">
-        <v>1.85134160518646</v>
+        <v>1.85134184360504</v>
       </c>
       <c r="H657" t="n">
         <v>9372</v>
@@ -19480,7 +19480,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G659" t="n">
-        <v>1.81990706920624</v>
+        <v>1.81990718841553</v>
       </c>
       <c r="H659" t="n">
         <v>3423</v>
@@ -19509,7 +19509,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G660" t="n">
-        <v>1.7983992099762</v>
+        <v>1.79839932918549</v>
       </c>
       <c r="H660" t="n">
         <v>3407</v>
@@ -19538,7 +19538,7 @@
         <v>2.17549991607666</v>
       </c>
       <c r="G661" t="n">
-        <v>1.79963982105255</v>
+        <v>1.79963994026184</v>
       </c>
       <c r="H661" t="n">
         <v>808</v>
@@ -19567,7 +19567,7 @@
         <v>2.20650005340576</v>
       </c>
       <c r="G662" t="n">
-        <v>1.82528412342072</v>
+        <v>1.82528424263</v>
       </c>
       <c r="H662" t="n">
         <v>405</v>
@@ -19596,7 +19596,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>1.79922616481781</v>
+        <v>1.7992262840271</v>
       </c>
       <c r="H663" t="n">
         <v>2053</v>
@@ -19683,7 +19683,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G666" t="n">
-        <v>1.83976066112518</v>
+        <v>1.83976078033447</v>
       </c>
       <c r="H666" t="n">
         <v>28805</v>
@@ -19857,7 +19857,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G672" t="n">
-        <v>1.75372862815857</v>
+        <v>1.75372850894928</v>
       </c>
       <c r="H672" t="n">
         <v>1260</v>
@@ -19886,7 +19886,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G673" t="n">
-        <v>1.76200091838837</v>
+        <v>1.76200115680695</v>
       </c>
       <c r="H673" t="n">
         <v>1302</v>
@@ -19915,7 +19915,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G674" t="n">
-        <v>1.75207424163818</v>
+        <v>1.75207412242889</v>
       </c>
       <c r="H674" t="n">
         <v>2280</v>
@@ -19973,7 +19973,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G676" t="n">
-        <v>1.68920481204987</v>
+        <v>1.68920469284058</v>
       </c>
       <c r="H676" t="n">
         <v>12451</v>
@@ -20031,7 +20031,7 @@
         <v>1.82879996299744</v>
       </c>
       <c r="G678" t="n">
-        <v>1.51283919811249</v>
+        <v>1.5128390789032</v>
       </c>
       <c r="H678" t="n">
         <v>26154</v>
@@ -20089,7 +20089,7 @@
         <v>1.79139995574951</v>
       </c>
       <c r="G680" t="n">
-        <v>1.48190057277679</v>
+        <v>1.48190069198608</v>
       </c>
       <c r="H680" t="n">
         <v>24993</v>
@@ -20147,7 +20147,7 @@
         <v>1.73259997367859</v>
       </c>
       <c r="G682" t="n">
-        <v>1.4332594871521</v>
+        <v>1.43325960636139</v>
       </c>
       <c r="H682" t="n">
         <v>5736</v>
@@ -20263,7 +20263,7 @@
         <v>1.72140002250671</v>
       </c>
       <c r="G686" t="n">
-        <v>1.4239946603775</v>
+        <v>1.42399454116821</v>
       </c>
       <c r="H686" t="n">
         <v>1520</v>
@@ -20321,7 +20321,7 @@
         <v>1.74440002441406</v>
       </c>
       <c r="G688" t="n">
-        <v>1.44302070140839</v>
+        <v>1.44302082061768</v>
       </c>
       <c r="H688" t="n">
         <v>2706</v>
@@ -20408,7 +20408,7 @@
         <v>1.73459994792938</v>
       </c>
       <c r="G691" t="n">
-        <v>1.43491399288177</v>
+        <v>1.43491387367249</v>
       </c>
       <c r="H691" t="n">
         <v>4507</v>
@@ -20437,7 +20437,7 @@
         <v>1.71580004692078</v>
       </c>
       <c r="G692" t="n">
-        <v>1.41936218738556</v>
+        <v>1.41936206817627</v>
       </c>
       <c r="H692" t="n">
         <v>2936</v>
@@ -20466,7 +20466,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G693" t="n">
-        <v>1.42283642292023</v>
+        <v>1.42283630371094</v>
       </c>
       <c r="H693" t="n">
         <v>484</v>
@@ -20495,7 +20495,7 @@
         <v>1.7305999994278</v>
       </c>
       <c r="G694" t="n">
-        <v>1.43160498142242</v>
+        <v>1.43160510063171</v>
       </c>
       <c r="H694" t="n">
         <v>5402</v>
@@ -20524,7 +20524,7 @@
         <v>1.73539996147156</v>
       </c>
       <c r="G695" t="n">
-        <v>1.43557572364807</v>
+        <v>1.43557584285736</v>
       </c>
       <c r="H695" t="n">
         <v>1802</v>
@@ -20553,7 +20553,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G696" t="n">
-        <v>1.42531824111938</v>
+        <v>1.4253181219101</v>
       </c>
       <c r="H696" t="n">
         <v>4908</v>
@@ -20582,7 +20582,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G697" t="n">
-        <v>1.42531824111938</v>
+        <v>1.4253181219101</v>
       </c>
       <c r="H697" t="n">
         <v>0</v>
@@ -20611,7 +20611,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G698" t="n">
-        <v>1.41952753067017</v>
+        <v>1.41952741146088</v>
       </c>
       <c r="H698" t="n">
         <v>9959</v>
@@ -20669,7 +20669,7 @@
         <v>1.74479997158051</v>
       </c>
       <c r="G700" t="n">
-        <v>1.44335186481476</v>
+        <v>1.44335198402405</v>
       </c>
       <c r="H700" t="n">
         <v>2020</v>
@@ -20727,7 +20727,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G702" t="n">
-        <v>1.43524491786957</v>
+        <v>1.43524503707886</v>
       </c>
       <c r="H702" t="n">
         <v>4220</v>
@@ -20843,7 +20843,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G706" t="n">
-        <v>1.41952753067017</v>
+        <v>1.41952741146088</v>
       </c>
       <c r="H706" t="n">
         <v>2390</v>
@@ -20872,7 +20872,7 @@
         <v>1.71539998054504</v>
       </c>
       <c r="G707" t="n">
-        <v>1.41903114318848</v>
+        <v>1.41903126239777</v>
       </c>
       <c r="H707" t="n">
         <v>1650</v>
@@ -20988,7 +20988,7 @@
         <v>1.66460001468658</v>
       </c>
       <c r="G711" t="n">
-        <v>1.37700796127319</v>
+        <v>1.37700772285461</v>
       </c>
       <c r="H711" t="n">
         <v>40</v>
@@ -21046,7 +21046,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G713" t="n">
-        <v>1.45592570304871</v>
+        <v>1.45592558383942</v>
       </c>
       <c r="H713" t="n">
         <v>6546</v>
@@ -21162,7 +21162,7 @@
         <v>1.73459994792938</v>
       </c>
       <c r="G717" t="n">
-        <v>1.43491399288177</v>
+        <v>1.43491387367249</v>
       </c>
       <c r="H717" t="n">
         <v>2000</v>
@@ -21220,7 +21220,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G719" t="n">
-        <v>1.43028140068054</v>
+        <v>1.43028163909912</v>
       </c>
       <c r="H719" t="n">
         <v>1706</v>
@@ -21249,7 +21249,7 @@
         <v>1.73539996147156</v>
       </c>
       <c r="G720" t="n">
-        <v>1.43557572364807</v>
+        <v>1.43557584285736</v>
       </c>
       <c r="H720" t="n">
         <v>21468</v>
@@ -21539,7 +21539,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G730" t="n">
-        <v>1.48653340339661</v>
+        <v>1.48653328418732</v>
       </c>
       <c r="H730" t="n">
         <v>642</v>
@@ -21568,7 +21568,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G731" t="n">
-        <v>1.48653340339661</v>
+        <v>1.48653328418732</v>
       </c>
       <c r="H731" t="n">
         <v>339</v>
@@ -21597,7 +21597,7 @@
         <v>1.83159995079041</v>
       </c>
       <c r="G732" t="n">
-        <v>1.51515543460846</v>
+        <v>1.51515531539917</v>
       </c>
       <c r="H732" t="n">
         <v>19406</v>
@@ -21742,7 +21742,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>1.48074245452881</v>
+        <v>1.4807425737381</v>
       </c>
       <c r="H737" t="n">
         <v>2570</v>
@@ -21829,7 +21829,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G740" t="n">
-        <v>1.46419811248779</v>
+        <v>1.46419787406921</v>
       </c>
       <c r="H740" t="n">
         <v>2269</v>
@@ -21858,7 +21858,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>1.48074245452881</v>
+        <v>1.4807425737381</v>
       </c>
       <c r="H741" t="n">
         <v>2079</v>
@@ -21887,7 +21887,7 @@
         <v>1.77240002155304</v>
       </c>
       <c r="G742" t="n">
-        <v>1.46618342399597</v>
+        <v>1.46618330478668</v>
       </c>
       <c r="H742" t="n">
         <v>214</v>
@@ -21916,7 +21916,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G743" t="n">
-        <v>1.48156988620758</v>
+        <v>1.48156976699829</v>
       </c>
       <c r="H743" t="n">
         <v>20</v>
@@ -22090,7 +22090,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G749" t="n">
-        <v>1.48156988620758</v>
+        <v>1.48156976699829</v>
       </c>
       <c r="H749" t="n">
         <v>1925</v>
@@ -22235,7 +22235,7 @@
         <v>1.78639996051788</v>
       </c>
       <c r="G754" t="n">
-        <v>1.47776448726654</v>
+        <v>1.47776460647583</v>
       </c>
       <c r="H754" t="n">
         <v>4001</v>
@@ -22264,7 +22264,7 @@
         <v>1.86979997158051</v>
       </c>
       <c r="G755" t="n">
-        <v>1.54675555229187</v>
+        <v>1.54675567150116</v>
       </c>
       <c r="H755" t="n">
         <v>6445</v>
@@ -22351,7 +22351,7 @@
         <v>1.92260003089905</v>
       </c>
       <c r="G758" t="n">
-        <v>1.66378653049469</v>
+        <v>1.66378664970398</v>
       </c>
       <c r="H758" t="n">
         <v>20</v>
@@ -22380,7 +22380,7 @@
         <v>1.93239998817444</v>
       </c>
       <c r="G759" t="n">
-        <v>1.67226731777191</v>
+        <v>1.67226719856262</v>
       </c>
       <c r="H759" t="n">
         <v>3791</v>
@@ -22438,7 +22438,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G761" t="n">
-        <v>1.61826741695404</v>
+        <v>1.61826729774475</v>
       </c>
       <c r="H761" t="n">
         <v>4580</v>
@@ -22496,7 +22496,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G763" t="n">
-        <v>1.67884433269501</v>
+        <v>1.67884421348572</v>
       </c>
       <c r="H763" t="n">
         <v>16054</v>
@@ -22554,7 +22554,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>1.69615185260773</v>
+        <v>1.69615197181702</v>
       </c>
       <c r="H765" t="n">
         <v>124</v>
@@ -22699,7 +22699,7 @@
         <v>1.94760000705719</v>
       </c>
       <c r="G770" t="n">
-        <v>1.68542122840881</v>
+        <v>1.68542098999023</v>
       </c>
       <c r="H770" t="n">
         <v>930</v>
@@ -22786,7 +22786,7 @@
         <v>1.89979994297028</v>
       </c>
       <c r="G773" t="n">
-        <v>1.64405572414398</v>
+        <v>1.64405560493469</v>
       </c>
       <c r="H773" t="n">
         <v>482</v>
@@ -22844,7 +22844,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G775" t="n">
-        <v>1.67884433269501</v>
+        <v>1.67884421348572</v>
       </c>
       <c r="H775" t="n">
         <v>3450</v>
@@ -22931,7 +22931,7 @@
         <v>1.95840001106262</v>
       </c>
       <c r="G778" t="n">
-        <v>1.69476723670959</v>
+        <v>1.69476711750031</v>
       </c>
       <c r="H778" t="n">
         <v>910</v>
@@ -22960,7 +22960,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>1.69615185260773</v>
+        <v>1.69615197181702</v>
       </c>
       <c r="H779" t="n">
         <v>2604</v>
@@ -22989,7 +22989,7 @@
         <v>1.93680000305176</v>
       </c>
       <c r="G780" t="n">
-        <v>1.67607498168945</v>
+        <v>1.67607486248016</v>
       </c>
       <c r="H780" t="n">
         <v>216</v>
@@ -23047,7 +23047,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G782" t="n">
-        <v>1.68126738071442</v>
+        <v>1.68126726150513</v>
       </c>
       <c r="H782" t="n">
         <v>2221</v>
@@ -23076,7 +23076,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G783" t="n">
-        <v>1.68126738071442</v>
+        <v>1.68126726150513</v>
       </c>
       <c r="H783" t="n">
         <v>0</v>
@@ -23105,7 +23105,7 @@
         <v>1.87839996814728</v>
       </c>
       <c r="G784" t="n">
-        <v>1.62553656101227</v>
+        <v>1.62553644180298</v>
       </c>
       <c r="H784" t="n">
         <v>2900</v>
@@ -23163,7 +23163,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G786" t="n">
-        <v>1.68749797344208</v>
+        <v>1.68749809265137</v>
       </c>
       <c r="H786" t="n">
         <v>4691</v>
@@ -23192,7 +23192,7 @@
         <v>1.90859997272491</v>
       </c>
       <c r="G787" t="n">
-        <v>1.65167105197906</v>
+        <v>1.65167117118835</v>
       </c>
       <c r="H787" t="n">
         <v>5503</v>
@@ -23221,7 +23221,7 @@
         <v>1.94280004501343</v>
       </c>
       <c r="G788" t="n">
-        <v>1.68126738071442</v>
+        <v>1.68126726150513</v>
       </c>
       <c r="H788" t="n">
         <v>2080</v>
@@ -23250,7 +23250,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G789" t="n">
-        <v>1.66759431362152</v>
+        <v>1.66759419441223</v>
       </c>
       <c r="H789" t="n">
         <v>1896</v>
@@ -23279,7 +23279,7 @@
         <v>1.89859998226166</v>
       </c>
       <c r="G790" t="n">
-        <v>1.64301717281342</v>
+        <v>1.64301729202271</v>
       </c>
       <c r="H790" t="n">
         <v>3830</v>
@@ -23308,7 +23308,7 @@
         <v>1.89979994297028</v>
       </c>
       <c r="G791" t="n">
-        <v>1.64405572414398</v>
+        <v>1.64405560493469</v>
       </c>
       <c r="H791" t="n">
         <v>83</v>
@@ -23337,7 +23337,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G792" t="n">
-        <v>1.67019033432007</v>
+        <v>1.67019021511078</v>
       </c>
       <c r="H792" t="n">
         <v>693</v>
@@ -23366,7 +23366,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G793" t="n">
-        <v>1.67019033432007</v>
+        <v>1.67019021511078</v>
       </c>
       <c r="H793" t="n">
         <v>0</v>
@@ -23424,7 +23424,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G795" t="n">
-        <v>1.65980577468872</v>
+        <v>1.65980565547943</v>
       </c>
       <c r="H795" t="n">
         <v>666</v>
@@ -23482,7 +23482,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G797" t="n">
-        <v>1.59836339950562</v>
+        <v>1.59836363792419</v>
       </c>
       <c r="H797" t="n">
         <v>6802</v>
@@ -23598,7 +23598,7 @@
         <v>1.89979994297028</v>
       </c>
       <c r="G801" t="n">
-        <v>1.64405572414398</v>
+        <v>1.64405560493469</v>
       </c>
       <c r="H801" t="n">
         <v>5259</v>
@@ -23627,7 +23627,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G802" t="n">
-        <v>1.62345969676971</v>
+        <v>1.62345957756042</v>
       </c>
       <c r="H802" t="n">
         <v>4654</v>
@@ -23656,7 +23656,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G803" t="n">
-        <v>1.63557493686676</v>
+        <v>1.63557505607605</v>
       </c>
       <c r="H803" t="n">
         <v>121</v>
@@ -23685,7 +23685,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G804" t="n">
-        <v>1.62086355686188</v>
+        <v>1.62086343765259</v>
       </c>
       <c r="H804" t="n">
         <v>1386</v>
@@ -23714,7 +23714,7 @@
         <v>1.8775999546051</v>
       </c>
       <c r="G805" t="n">
-        <v>1.62484419345856</v>
+        <v>1.62484407424927</v>
       </c>
       <c r="H805" t="n">
         <v>480</v>
@@ -23743,7 +23743,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G806" t="n">
-        <v>1.59230589866638</v>
+        <v>1.59230577945709</v>
       </c>
       <c r="H806" t="n">
         <v>3639</v>
@@ -23772,7 +23772,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G807" t="n">
-        <v>1.63557493686676</v>
+        <v>1.63557505607605</v>
       </c>
       <c r="H807" t="n">
         <v>5224</v>
@@ -23801,7 +23801,7 @@
         <v>1.83019995689392</v>
       </c>
       <c r="G808" t="n">
-        <v>1.58382499217987</v>
+        <v>1.58382511138916</v>
       </c>
       <c r="H808" t="n">
         <v>3098</v>
@@ -23830,7 +23830,7 @@
         <v>1.83019995689392</v>
       </c>
       <c r="G809" t="n">
-        <v>1.58382499217987</v>
+        <v>1.58382511138916</v>
       </c>
       <c r="H809" t="n">
         <v>144</v>
@@ -23917,7 +23917,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G812" t="n">
-        <v>1.60095953941345</v>
+        <v>1.60095965862274</v>
       </c>
       <c r="H812" t="n">
         <v>3785</v>
@@ -23946,7 +23946,7 @@
         <v>1.84940004348755</v>
       </c>
       <c r="G813" t="n">
-        <v>1.60044050216675</v>
+        <v>1.60044062137604</v>
       </c>
       <c r="H813" t="n">
         <v>662</v>
@@ -24004,7 +24004,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G815" t="n">
-        <v>1.54211354255676</v>
+        <v>1.54211342334747</v>
       </c>
       <c r="H815" t="n">
         <v>7327</v>
@@ -24120,7 +24120,7 @@
         <v>1.76960003376007</v>
       </c>
       <c r="G819" t="n">
-        <v>1.53138279914856</v>
+        <v>1.53138291835785</v>
       </c>
       <c r="H819" t="n">
         <v>2845</v>
@@ -24207,7 +24207,7 @@
         <v>1.75</v>
       </c>
       <c r="G822" t="n">
-        <v>1.51442122459412</v>
+        <v>1.51442134380341</v>
       </c>
       <c r="H822" t="n">
         <v>7919</v>
@@ -24294,7 +24294,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G825" t="n">
-        <v>1.50576758384705</v>
+        <v>1.50576746463776</v>
       </c>
       <c r="H825" t="n">
         <v>4969</v>
@@ -24352,7 +24352,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>1.47980582714081</v>
+        <v>1.4798059463501</v>
       </c>
       <c r="H827" t="n">
         <v>3742</v>
@@ -24381,7 +24381,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>1.47980582714081</v>
+        <v>1.4798059463501</v>
       </c>
       <c r="H828" t="n">
         <v>3769</v>
@@ -24497,7 +24497,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G832" t="n">
-        <v>1.49711358547211</v>
+        <v>1.4971137046814</v>
       </c>
       <c r="H832" t="n">
         <v>2164</v>
@@ -24526,7 +24526,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G833" t="n">
-        <v>1.44951736927032</v>
+        <v>1.4495176076889</v>
       </c>
       <c r="H833" t="n">
         <v>2154</v>
@@ -24613,7 +24613,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G836" t="n">
-        <v>1.47547912597656</v>
+        <v>1.47547900676727</v>
       </c>
       <c r="H836" t="n">
         <v>5150</v>
@@ -24642,7 +24642,7 @@
         <v>1.75</v>
       </c>
       <c r="G837" t="n">
-        <v>1.51442122459412</v>
+        <v>1.51442134380341</v>
       </c>
       <c r="H837" t="n">
         <v>7450</v>
@@ -24700,7 +24700,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G839" t="n">
-        <v>1.54903650283813</v>
+        <v>1.54903662204742</v>
       </c>
       <c r="H839" t="n">
         <v>12013</v>
@@ -24729,7 +24729,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G840" t="n">
-        <v>1.47980582714081</v>
+        <v>1.4798059463501</v>
       </c>
       <c r="H840" t="n">
         <v>19618</v>
@@ -24787,7 +24787,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G842" t="n">
-        <v>1.44519066810608</v>
+        <v>1.4451904296875</v>
       </c>
       <c r="H842" t="n">
         <v>11178</v>
@@ -24816,7 +24816,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G843" t="n">
-        <v>1.44519066810608</v>
+        <v>1.4451904296875</v>
       </c>
       <c r="H843" t="n">
         <v>3119</v>
@@ -24903,7 +24903,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G846" t="n">
-        <v>1.46682512760162</v>
+        <v>1.46682524681091</v>
       </c>
       <c r="H846" t="n">
         <v>1032</v>
@@ -24932,7 +24932,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G847" t="n">
-        <v>1.47980582714081</v>
+        <v>1.4798059463501</v>
       </c>
       <c r="H847" t="n">
         <v>2642</v>
@@ -24961,7 +24961,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G848" t="n">
-        <v>1.47980582714081</v>
+        <v>1.4798059463501</v>
       </c>
       <c r="H848" t="n">
         <v>4589</v>
@@ -25048,7 +25048,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G851" t="n">
-        <v>1.44951736927032</v>
+        <v>1.4495176076889</v>
       </c>
       <c r="H851" t="n">
         <v>3089</v>
@@ -25077,7 +25077,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G852" t="n">
-        <v>1.44951736927032</v>
+        <v>1.4495176076889</v>
       </c>
       <c r="H852" t="n">
         <v>11501</v>
@@ -25106,7 +25106,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G853" t="n">
-        <v>1.44519066810608</v>
+        <v>1.4451904296875</v>
       </c>
       <c r="H853" t="n">
         <v>1626</v>
@@ -25135,7 +25135,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G854" t="n">
-        <v>1.43653666973114</v>
+        <v>1.43653678894043</v>
       </c>
       <c r="H854" t="n">
         <v>137</v>
@@ -25193,7 +25193,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G856" t="n">
-        <v>1.34134459495544</v>
+        <v>1.34134447574615</v>
       </c>
       <c r="H856" t="n">
         <v>9092</v>
@@ -25251,7 +25251,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G858" t="n">
-        <v>1.44951736927032</v>
+        <v>1.4495176076889</v>
       </c>
       <c r="H858" t="n">
         <v>1469</v>
@@ -25280,7 +25280,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G859" t="n">
-        <v>1.43653666973114</v>
+        <v>1.43653678894043</v>
       </c>
       <c r="H859" t="n">
         <v>201</v>
@@ -25367,7 +25367,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G862" t="n">
-        <v>1.43653666973114</v>
+        <v>1.43653678894043</v>
       </c>
       <c r="H862" t="n">
         <v>9847</v>
@@ -25454,7 +25454,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G865" t="n">
-        <v>1.41922891139984</v>
+        <v>1.41922914981842</v>
       </c>
       <c r="H865" t="n">
         <v>7928</v>
@@ -25483,7 +25483,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G866" t="n">
-        <v>1.41922891139984</v>
+        <v>1.41922914981842</v>
       </c>
       <c r="H866" t="n">
         <v>1621</v>
@@ -25512,7 +25512,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G867" t="n">
-        <v>1.43653666973114</v>
+        <v>1.43653678894043</v>
       </c>
       <c r="H867" t="n">
         <v>4184</v>
@@ -25686,7 +25686,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G873" t="n">
-        <v>1.41922891139984</v>
+        <v>1.41922914981842</v>
       </c>
       <c r="H873" t="n">
         <v>3139</v>
@@ -25715,7 +25715,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G874" t="n">
-        <v>1.41490209102631</v>
+        <v>1.4149022102356</v>
       </c>
       <c r="H874" t="n">
         <v>614</v>
@@ -25773,7 +25773,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>1.33269059658051</v>
+        <v>1.33269083499908</v>
       </c>
       <c r="H876" t="n">
         <v>951</v>
@@ -25802,7 +25802,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G877" t="n">
-        <v>1.3846138715744</v>
+        <v>1.38461375236511</v>
       </c>
       <c r="H877" t="n">
         <v>3726</v>
@@ -25831,7 +25831,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G878" t="n">
-        <v>1.38028693199158</v>
+        <v>1.38028681278229</v>
       </c>
       <c r="H878" t="n">
         <v>7486</v>
@@ -25860,7 +25860,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G879" t="n">
-        <v>1.38028693199158</v>
+        <v>1.38028681278229</v>
       </c>
       <c r="H879" t="n">
         <v>2002</v>
@@ -25947,7 +25947,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G882" t="n">
-        <v>1.36297917366028</v>
+        <v>1.36297905445099</v>
       </c>
       <c r="H882" t="n">
         <v>2128</v>
@@ -25976,7 +25976,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G883" t="n">
-        <v>1.3846138715744</v>
+        <v>1.38461375236511</v>
       </c>
       <c r="H883" t="n">
         <v>4134</v>
@@ -26005,7 +26005,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G884" t="n">
-        <v>1.3846138715744</v>
+        <v>1.38461375236511</v>
       </c>
       <c r="H884" t="n">
         <v>1525</v>
@@ -26063,7 +26063,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G886" t="n">
-        <v>1.3846138715744</v>
+        <v>1.38461375236511</v>
       </c>
       <c r="H886" t="n">
         <v>1608</v>
@@ -26092,7 +26092,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G887" t="n">
-        <v>1.37163317203522</v>
+        <v>1.37163305282593</v>
       </c>
       <c r="H887" t="n">
         <v>8464</v>
@@ -26150,7 +26150,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G889" t="n">
-        <v>1.34999847412109</v>
+        <v>1.3499983549118</v>
       </c>
       <c r="H889" t="n">
         <v>10750</v>
@@ -26208,7 +26208,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>1.33269059658051</v>
+        <v>1.33269083499908</v>
       </c>
       <c r="H891" t="n">
         <v>4712</v>
@@ -26237,7 +26237,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G892" t="n">
-        <v>1.31105625629425</v>
+        <v>1.31105601787567</v>
       </c>
       <c r="H892" t="n">
         <v>200</v>
@@ -80154,6 +80154,35 @@
         <v>60835</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>66607</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>
